--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-08-21 第 115000081 期；威力彩 2026-08-20 第 115000067 期</t>
+          <t>大樂透 2026-08-21 第 115000081 期；威力彩 2026-08-24 第 115000068 期</t>
         </is>
       </c>
     </row>
@@ -112,7 +112,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -121,7 +121,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -143,7 +143,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9, 11, 14, 29, 35, 38</t>
+          <t>9, 14, 29, 31, 35, 38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3508,7 +3508,7 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>1.0</v>
+        <v>0.976</v>
       </c>
       <c r="D4">
         <v>23.8</v>
@@ -3523,7 +3523,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>均衡分散</t>
+          <t>冷號觀察</t>
         </is>
       </c>
       <c r="B5">
@@ -3533,10 +3533,10 @@
         <v>0.952</v>
       </c>
       <c r="D5">
-        <v>21.4</v>
+        <v>28.6</v>
       </c>
       <c r="E5">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -3545,20 +3545,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>冷號觀察</t>
+          <t>均衡分散</t>
         </is>
       </c>
       <c r="B6">
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.952</v>
+        <v>0.929</v>
       </c>
       <c r="D6">
-        <v>28.6</v>
+        <v>21.4</v>
       </c>
       <c r="E6">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -3648,25 +3648,25 @@
         <v>29</v>
       </c>
       <c r="C2">
-        <v>73.4</v>
+        <v>73.61</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E2">
         <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>100.0</v>
+        <v>92.86</v>
       </c>
       <c r="H2">
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>0.0</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="3">
@@ -3674,28 +3674,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C3">
-        <v>73.16</v>
+        <v>70.32</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>92.86</v>
+        <v>78.57</v>
       </c>
       <c r="H3">
-        <v>100.0</v>
+        <v>83.33</v>
       </c>
       <c r="I3">
-        <v>0.0</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="4">
@@ -3703,28 +3703,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C4">
-        <v>69.91</v>
+        <v>69.44</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>78.57</v>
+        <v>92.86</v>
       </c>
       <c r="H4">
         <v>83.33</v>
       </c>
       <c r="I4">
-        <v>9.38</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="5">
@@ -3732,28 +3732,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C5">
-        <v>68.5</v>
+        <v>65.38</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>78.57</v>
+        <v>71.43</v>
       </c>
       <c r="H5">
-        <v>83.33</v>
+        <v>50.0</v>
       </c>
       <c r="I5">
-        <v>0.0</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="6">
@@ -3761,10 +3761,10 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C6">
-        <v>66.44</v>
+        <v>65.01</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -3773,7 +3773,7 @@
         <v>4</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G6">
         <v>71.43</v>
@@ -3782,7 +3782,7 @@
         <v>66.67</v>
       </c>
       <c r="I6">
-        <v>15.62</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="7">
@@ -3790,28 +3790,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>65.09</v>
+        <v>64.55</v>
       </c>
       <c r="D7">
         <v>10</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G7">
         <v>71.43</v>
       </c>
       <c r="H7">
-        <v>50.0</v>
+        <v>66.67</v>
       </c>
       <c r="I7">
-        <v>34.38</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="8">
@@ -3819,28 +3819,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C8">
-        <v>64.56</v>
+        <v>63.61</v>
       </c>
       <c r="D8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E8">
         <v>4</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>71.43</v>
+        <v>57.14</v>
       </c>
       <c r="H8">
         <v>66.67</v>
       </c>
       <c r="I8">
-        <v>3.12</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="9">
@@ -3848,10 +3848,10 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C9">
-        <v>63.68</v>
+        <v>62.66</v>
       </c>
       <c r="D9">
         <v>10</v>
@@ -3860,7 +3860,7 @@
         <v>3</v>
       </c>
       <c r="F9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G9">
         <v>71.43</v>
@@ -3869,7 +3869,7 @@
         <v>50.0</v>
       </c>
       <c r="I9">
-        <v>25.0</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="10">
@@ -3877,10 +3877,10 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>62.25</v>
+        <v>61.71</v>
       </c>
       <c r="D10">
         <v>8</v>
@@ -3889,7 +3889,7 @@
         <v>3</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G10">
         <v>57.14</v>
@@ -3898,7 +3898,7 @@
         <v>50.0</v>
       </c>
       <c r="I10">
-        <v>18.75</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="11">
@@ -3906,10 +3906,10 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>62.25</v>
+        <v>60.81</v>
       </c>
       <c r="D11">
         <v>8</v>
@@ -3918,7 +3918,7 @@
         <v>3</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G11">
         <v>57.14</v>
@@ -3927,7 +3927,7 @@
         <v>50.0</v>
       </c>
       <c r="I11">
-        <v>18.75</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="12">
@@ -3935,28 +3935,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C12">
-        <v>61.32</v>
+        <v>59.85</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G12">
-        <v>57.14</v>
+        <v>71.43</v>
       </c>
       <c r="H12">
-        <v>50.0</v>
+        <v>33.33</v>
       </c>
       <c r="I12">
-        <v>12.5</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="13">
@@ -3964,10 +3964,10 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C13">
-        <v>60.38</v>
+        <v>59.44</v>
       </c>
       <c r="D13">
         <v>8</v>
@@ -3976,7 +3976,7 @@
         <v>3</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13">
         <v>57.14</v>
@@ -3985,7 +3985,7 @@
         <v>50.0</v>
       </c>
       <c r="I13">
-        <v>6.25</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="14">
@@ -3996,7 +3996,7 @@
         <v>34</v>
       </c>
       <c r="C14">
-        <v>58.35</v>
+        <v>58.73</v>
       </c>
       <c r="D14">
         <v>11</v>
@@ -4005,7 +4005,7 @@
         <v>2</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G14">
         <v>78.57</v>
@@ -4014,7 +4014,7 @@
         <v>33.33</v>
       </c>
       <c r="I14">
-        <v>15.62</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="15">
@@ -4025,7 +4025,7 @@
         <v>15</v>
       </c>
       <c r="C15">
-        <v>58.1</v>
+        <v>58.49</v>
       </c>
       <c r="D15">
         <v>10</v>
@@ -4034,7 +4034,7 @@
         <v>2</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15">
         <v>71.43</v>
@@ -4043,7 +4043,7 @@
         <v>33.33</v>
       </c>
       <c r="I15">
-        <v>15.62</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="16">
@@ -4054,7 +4054,7 @@
         <v>17</v>
       </c>
       <c r="C16">
-        <v>58.09</v>
+        <v>58.46</v>
       </c>
       <c r="D16">
         <v>8</v>
@@ -4063,7 +4063,7 @@
         <v>2</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16">
         <v>57.14</v>
@@ -4072,7 +4072,7 @@
         <v>33.33</v>
       </c>
       <c r="I16">
-        <v>18.75</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="17">
@@ -4080,28 +4080,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C17">
-        <v>57.2</v>
+        <v>58.46</v>
       </c>
       <c r="D17">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G17">
-        <v>100.0</v>
+        <v>57.14</v>
       </c>
       <c r="H17">
         <v>33.33</v>
       </c>
       <c r="I17">
-        <v>3.12</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="18">
@@ -4109,28 +4109,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C18">
-        <v>57.17</v>
+        <v>57.64</v>
       </c>
       <c r="D18">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18">
-        <v>71.43</v>
+        <v>100.0</v>
       </c>
       <c r="H18">
         <v>33.33</v>
       </c>
       <c r="I18">
-        <v>9.38</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="19">
@@ -4138,13 +4138,13 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C19">
-        <v>57.15</v>
+        <v>57.58</v>
       </c>
       <c r="D19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -4153,13 +4153,13 @@
         <v>4</v>
       </c>
       <c r="G19">
-        <v>57.14</v>
+        <v>71.43</v>
       </c>
       <c r="H19">
         <v>33.33</v>
       </c>
       <c r="I19">
-        <v>12.5</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="20">
@@ -4167,28 +4167,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C20">
-        <v>56.93</v>
+        <v>57.55</v>
       </c>
       <c r="D20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G20">
-        <v>64.29</v>
+        <v>57.14</v>
       </c>
       <c r="H20">
         <v>33.33</v>
       </c>
       <c r="I20">
-        <v>9.38</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="21">
@@ -4196,10 +4196,10 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C21">
-        <v>56.21</v>
+        <v>57.09</v>
       </c>
       <c r="D21">
         <v>8</v>
@@ -4208,7 +4208,7 @@
         <v>2</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G21">
         <v>57.14</v>
@@ -4217,7 +4217,7 @@
         <v>33.33</v>
       </c>
       <c r="I21">
-        <v>6.25</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="22">
@@ -4225,28 +4225,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C22">
-        <v>54.65</v>
+        <v>56.49</v>
       </c>
       <c r="D22">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>78.57</v>
+        <v>92.86</v>
       </c>
       <c r="H22">
-        <v>16.67</v>
+        <v>33.33</v>
       </c>
       <c r="I22">
-        <v>18.75</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="23">
@@ -4254,28 +4254,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C23">
-        <v>54.26</v>
+        <v>55.93</v>
       </c>
       <c r="D23">
         <v>6</v>
       </c>
       <c r="E23">
+        <v>4</v>
+      </c>
+      <c r="F23">
         <v>0</v>
-      </c>
-      <c r="F23">
-        <v>32</v>
       </c>
       <c r="G23">
         <v>42.86</v>
       </c>
       <c r="H23">
+        <v>66.67</v>
+      </c>
+      <c r="I23">
         <v>0.0</v>
-      </c>
-      <c r="I23">
-        <v>100.0</v>
       </c>
     </row>
     <row r="24">
@@ -4283,28 +4283,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C24">
-        <v>52.7</v>
+        <v>55.27</v>
       </c>
       <c r="D24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>42.86</v>
+        <v>57.14</v>
       </c>
       <c r="H24">
-        <v>50.0</v>
+        <v>33.33</v>
       </c>
       <c r="I24">
-        <v>6.25</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="25">
@@ -4312,28 +4312,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C25">
-        <v>52.33</v>
+        <v>55.02</v>
       </c>
       <c r="D25">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G25">
-        <v>92.86</v>
+        <v>78.57</v>
       </c>
       <c r="H25">
         <v>16.67</v>
       </c>
       <c r="I25">
-        <v>0.0</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="26">
@@ -4341,28 +4341,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="C26">
-        <v>51.76</v>
+        <v>54.26</v>
       </c>
       <c r="D26">
         <v>6</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G26">
         <v>42.86</v>
       </c>
       <c r="H26">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
       <c r="I26">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="27">
@@ -4370,28 +4370,28 @@
         <v>26</v>
       </c>
       <c r="B27">
+        <v>10</v>
+      </c>
+      <c r="C27">
+        <v>53.12</v>
+      </c>
+      <c r="D27">
         <v>6</v>
       </c>
-      <c r="C27">
-        <v>51.69</v>
-      </c>
-      <c r="D27">
-        <v>7</v>
-      </c>
       <c r="E27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F27">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G27">
+        <v>42.86</v>
+      </c>
+      <c r="H27">
         <v>50.0</v>
       </c>
-      <c r="H27">
-        <v>16.67</v>
-      </c>
       <c r="I27">
-        <v>28.12</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="28">
@@ -4399,28 +4399,28 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C28">
-        <v>49.12</v>
+        <v>51.76</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E28">
         <v>3</v>
       </c>
       <c r="F28">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>35.71</v>
+        <v>42.86</v>
       </c>
       <c r="H28">
         <v>50.0</v>
       </c>
       <c r="I28">
-        <v>9.38</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="29">
@@ -4431,7 +4431,7 @@
         <v>32</v>
       </c>
       <c r="C29">
-        <v>48.58</v>
+        <v>48.88</v>
       </c>
       <c r="D29">
         <v>6</v>
@@ -4440,7 +4440,7 @@
         <v>1</v>
       </c>
       <c r="F29">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G29">
         <v>42.86</v>
@@ -4449,7 +4449,7 @@
         <v>16.67</v>
       </c>
       <c r="I29">
-        <v>34.38</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="30">
@@ -4460,7 +4460,7 @@
         <v>1</v>
       </c>
       <c r="C30">
-        <v>47.59</v>
+        <v>48.05</v>
       </c>
       <c r="D30">
         <v>6</v>
@@ -4469,7 +4469,7 @@
         <v>2</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30">
         <v>42.86</v>
@@ -4478,7 +4478,7 @@
         <v>33.33</v>
       </c>
       <c r="I30">
-        <v>0.0</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="31">
@@ -4486,28 +4486,28 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C31">
-        <v>45.42</v>
+        <v>48.05</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E31">
         <v>2</v>
       </c>
       <c r="F31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G31">
-        <v>35.71</v>
+        <v>42.86</v>
       </c>
       <c r="H31">
         <v>33.33</v>
       </c>
       <c r="I31">
-        <v>12.5</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="32">
@@ -4518,7 +4518,7 @@
         <v>30</v>
       </c>
       <c r="C32">
-        <v>40.91</v>
+        <v>41.32</v>
       </c>
       <c r="D32">
         <v>4</v>
@@ -4527,7 +4527,7 @@
         <v>2</v>
       </c>
       <c r="F32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G32">
         <v>28.57</v>
@@ -4536,7 +4536,7 @@
         <v>33.33</v>
       </c>
       <c r="I32">
-        <v>9.38</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="33">
@@ -4547,7 +4547,7 @@
         <v>5</v>
       </c>
       <c r="C33">
-        <v>39.85</v>
+        <v>40.29</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -4556,7 +4556,7 @@
         <v>1</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33">
         <v>35.71</v>
@@ -4565,7 +4565,7 @@
         <v>16.67</v>
       </c>
       <c r="I33">
-        <v>3.12</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="34">
@@ -4576,7 +4576,7 @@
         <v>18</v>
       </c>
       <c r="C34">
-        <v>39.85</v>
+        <v>40.29</v>
       </c>
       <c r="D34">
         <v>5</v>
@@ -4585,7 +4585,7 @@
         <v>1</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34">
         <v>35.71</v>
@@ -4594,7 +4594,7 @@
         <v>16.67</v>
       </c>
       <c r="I34">
-        <v>3.12</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="35">
@@ -4605,7 +4605,7 @@
         <v>12</v>
       </c>
       <c r="C35">
-        <v>39.68</v>
+        <v>40.01</v>
       </c>
       <c r="D35">
         <v>3</v>
@@ -4614,7 +4614,7 @@
         <v>2</v>
       </c>
       <c r="F35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G35">
         <v>21.43</v>
@@ -4623,7 +4623,7 @@
         <v>33.33</v>
       </c>
       <c r="I35">
-        <v>28.12</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="36">
@@ -4634,7 +4634,7 @@
         <v>16</v>
       </c>
       <c r="C36">
-        <v>38.2</v>
+        <v>38.44</v>
       </c>
       <c r="D36">
         <v>4</v>
@@ -4643,7 +4643,7 @@
         <v>0</v>
       </c>
       <c r="F36">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G36">
         <v>28.57</v>
@@ -4652,7 +4652,7 @@
         <v>0.0</v>
       </c>
       <c r="I36">
-        <v>46.88</v>
+        <v>48.48</v>
       </c>
     </row>
     <row r="37">
@@ -4663,7 +4663,7 @@
         <v>3</v>
       </c>
       <c r="C37">
-        <v>36.28</v>
+        <v>36.7</v>
       </c>
       <c r="D37">
         <v>4</v>
@@ -4672,7 +4672,7 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G37">
         <v>28.57</v>
@@ -4681,7 +4681,7 @@
         <v>16.67</v>
       </c>
       <c r="I37">
-        <v>6.25</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="38">
@@ -4692,7 +4692,7 @@
         <v>20</v>
       </c>
       <c r="C38">
-        <v>33.17</v>
+        <v>33.57</v>
       </c>
       <c r="D38">
         <v>3</v>
@@ -4701,7 +4701,7 @@
         <v>1</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G38">
         <v>21.43</v>
@@ -4710,7 +4710,7 @@
         <v>16.67</v>
       </c>
       <c r="I38">
-        <v>12.5</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="39">
@@ -4721,7 +4721,7 @@
         <v>37</v>
       </c>
       <c r="C39">
-        <v>32.88</v>
+        <v>33.16</v>
       </c>
       <c r="D39">
         <v>2</v>
@@ -4730,7 +4730,7 @@
         <v>1</v>
       </c>
       <c r="F39">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G39">
         <v>14.29</v>
@@ -4739,7 +4739,7 @@
         <v>16.67</v>
       </c>
       <c r="I39">
-        <v>37.5</v>
+        <v>39.39</v>
       </c>
     </row>
   </sheetData>
@@ -4798,216 +4798,216 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>9</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3">
         <v>11</v>
       </c>
-      <c r="E3">
-        <v>18</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
       <c r="G3">
+        <v>29</v>
+      </c>
+      <c r="H3">
         <v>35</v>
       </c>
-      <c r="H3">
-        <v>38</v>
-      </c>
       <c r="I3">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H4">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G5">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H5">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F6">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H6">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>7</v>
+      </c>
+      <c r="E7">
+        <v>8</v>
+      </c>
+      <c r="F7">
+        <v>20</v>
+      </c>
+      <c r="G7">
+        <v>26</v>
+      </c>
+      <c r="H7">
+        <v>33</v>
+      </c>
+      <c r="I7">
         <v>4</v>
-      </c>
-      <c r="D7">
-        <v>15</v>
-      </c>
-      <c r="E7">
-        <v>22</v>
-      </c>
-      <c r="F7">
-        <v>26</v>
-      </c>
-      <c r="G7">
-        <v>34</v>
-      </c>
-      <c r="H7">
-        <v>36</v>
-      </c>
-      <c r="I7">
-        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C8">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F8">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G8">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H8">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I8">
         <v>7</v>
@@ -5015,30 +5015,30 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <v>14</v>
+      </c>
+      <c r="E9">
+        <v>17</v>
+      </c>
+      <c r="F9">
         <v>19</v>
       </c>
-      <c r="D9">
-        <v>22</v>
-      </c>
-      <c r="E9">
-        <v>28</v>
-      </c>
-      <c r="F9">
-        <v>31</v>
-      </c>
       <c r="G9">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H9">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I9">
         <v>7</v>
@@ -5046,30 +5046,30 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C10">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D10">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E10">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F10">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G10">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H10">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I10">
         <v>7</v>
@@ -5077,24 +5077,24 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D11">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E11">
         <v>13</v>
       </c>
       <c r="F11">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G11">
         <v>29</v>
@@ -5103,97 +5103,97 @@
         <v>31</v>
       </c>
       <c r="I11">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C12">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D12">
+        <v>12</v>
+      </c>
+      <c r="E12">
+        <v>13</v>
+      </c>
+      <c r="F12">
         <v>23</v>
       </c>
-      <c r="E12">
-        <v>25</v>
-      </c>
-      <c r="F12">
+      <c r="G12">
         <v>29</v>
       </c>
-      <c r="G12">
-        <v>34</v>
-      </c>
       <c r="H12">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I12">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C13">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E13">
+        <v>25</v>
+      </c>
+      <c r="F13">
         <v>29</v>
       </c>
-      <c r="F13">
-        <v>32</v>
-      </c>
       <c r="G13">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H13">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G14">
         <v>35</v>
       </c>
       <c r="H14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I14">
         <v>6</v>
@@ -5201,402 +5201,402 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D15">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E15">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F15">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G15">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H15">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F16">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G16">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H16">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I16">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D17">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E17">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F17">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G17">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H17">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I17">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C18">
+        <v>5</v>
+      </c>
+      <c r="D18">
         <v>6</v>
       </c>
-      <c r="D18">
-        <v>10</v>
-      </c>
       <c r="E18">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F18">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G18">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H18">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C19">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D19">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E19">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F19">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G19">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H19">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I19">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D20">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E20">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F20">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G20">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H20">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I20">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>8</v>
+      </c>
+      <c r="E21">
+        <v>9</v>
+      </c>
+      <c r="F21">
+        <v>15</v>
+      </c>
+      <c r="G21">
+        <v>18</v>
+      </c>
+      <c r="H21">
+        <v>23</v>
+      </c>
+      <c r="I21">
         <v>4</v>
-      </c>
-      <c r="D21">
-        <v>17</v>
-      </c>
-      <c r="E21">
-        <v>19</v>
-      </c>
-      <c r="F21">
-        <v>25</v>
-      </c>
-      <c r="G21">
-        <v>28</v>
-      </c>
-      <c r="H21">
-        <v>29</v>
-      </c>
-      <c r="I21">
-        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C22">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D22">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E22">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F22">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G22">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H22">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I22">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D23">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E23">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F23">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G23">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H23">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I23">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C24">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D24">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E24">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F24">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G24">
         <v>28</v>
       </c>
       <c r="H24">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I24">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C25">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D25">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E25">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F25">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G25">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H25">
         <v>35</v>
       </c>
       <c r="I25">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E26">
+        <v>9</v>
+      </c>
+      <c r="F26">
+        <v>15</v>
+      </c>
+      <c r="G26">
         <v>24</v>
       </c>
-      <c r="F26">
-        <v>31</v>
-      </c>
-      <c r="G26">
-        <v>34</v>
-      </c>
       <c r="H26">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I26">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C27">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E27">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F27">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G27">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H27">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I27">
         <v>3</v>
@@ -5604,554 +5604,554 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C28">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D28">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E28">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F28">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G28">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H28">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C29">
         <v>6</v>
       </c>
       <c r="D29">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E29">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F29">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G29">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H29">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I29">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C30">
         <v>6</v>
       </c>
       <c r="D30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E30">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F30">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G30">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H30">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I30">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C31">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D31">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E31">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F31">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G31">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H31">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I31">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D32">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E32">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F32">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G32">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H32">
         <v>38</v>
       </c>
       <c r="I32">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C33">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D33">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E33">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F33">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G33">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H33">
         <v>38</v>
       </c>
       <c r="I33">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D34">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E34">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F34">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G34">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H34">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I34">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C35">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D35">
+        <v>4</v>
+      </c>
+      <c r="E35">
+        <v>13</v>
+      </c>
+      <c r="F35">
+        <v>19</v>
+      </c>
+      <c r="G35">
+        <v>27</v>
+      </c>
+      <c r="H35">
+        <v>30</v>
+      </c>
+      <c r="I35">
         <v>8</v>
-      </c>
-      <c r="E35">
-        <v>27</v>
-      </c>
-      <c r="F35">
-        <v>33</v>
-      </c>
-      <c r="G35">
-        <v>35</v>
-      </c>
-      <c r="H35">
-        <v>38</v>
-      </c>
-      <c r="I35">
-        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C36">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D36">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E36">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F36">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G36">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H36">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I36">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D37">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E37">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F37">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G37">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H37">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I37">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D38">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E38">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F38">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G38">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H38">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I38">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000030</v>
+        <v>115000031</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D39">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E39">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F39">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G39">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H39">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="I39">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000029</v>
+        <v>115000030</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E40">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F40">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G40">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H40">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I40">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000028</v>
+        <v>115000029</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D41">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E41">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F41">
         <v>27</v>
       </c>
       <c r="G41">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H41">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I41">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000027</v>
+        <v>115000028</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C42">
         <v>5</v>
       </c>
       <c r="D42">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E42">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F42">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G42">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H42">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I42">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000026</v>
+        <v>115000027</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C43">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D43">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E43">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F43">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G43">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H43">
         <v>34</v>
       </c>
       <c r="I43">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000025</v>
+        <v>115000026</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C44">
+        <v>2</v>
+      </c>
+      <c r="D44">
         <v>13</v>
       </c>
-      <c r="D44">
-        <v>14</v>
-      </c>
       <c r="E44">
+        <v>21</v>
+      </c>
+      <c r="F44">
         <v>22</v>
       </c>
-      <c r="F44">
-        <v>28</v>
-      </c>
       <c r="G44">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H44">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I44">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000024</v>
+        <v>115000025</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D45">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E45">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F45">
         <v>28</v>
       </c>
       <c r="G45">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H45">
         <v>38</v>
@@ -6162,58 +6162,58 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000023</v>
+        <v>115000024</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46">
         <v>9</v>
       </c>
-      <c r="D46">
-        <v>13</v>
-      </c>
       <c r="E46">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F46">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G46">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H46">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I46">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000022</v>
+        <v>115000023</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C47">
+        <v>9</v>
+      </c>
+      <c r="D47">
+        <v>13</v>
+      </c>
+      <c r="E47">
         <v>14</v>
       </c>
-      <c r="D47">
-        <v>26</v>
-      </c>
-      <c r="E47">
-        <v>28</v>
-      </c>
       <c r="F47">
+        <v>18</v>
+      </c>
+      <c r="G47">
         <v>31</v>
-      </c>
-      <c r="G47">
-        <v>32</v>
       </c>
       <c r="H47">
         <v>34</v>
@@ -6224,61 +6224,61 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000021</v>
+        <v>115000022</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C48">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D48">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E48">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F48">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G48">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H48">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I48">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000020</v>
+        <v>115000021</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D49">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E49">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F49">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G49">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H49">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I49">
         <v>8</v>
@@ -6286,15 +6286,15 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000019</v>
+        <v>115000020</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="C50">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D50">
         <v>11</v>
@@ -6303,47 +6303,47 @@
         <v>14</v>
       </c>
       <c r="F50">
+        <v>17</v>
+      </c>
+      <c r="G50">
+        <v>29</v>
+      </c>
+      <c r="H50">
         <v>32</v>
       </c>
-      <c r="G50">
-        <v>36</v>
-      </c>
-      <c r="H50">
-        <v>38</v>
-      </c>
       <c r="I50">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000018</v>
+        <v>115000019</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="C51">
         <v>7</v>
       </c>
       <c r="D51">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E51">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F51">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G51">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H51">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="I51">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-08-21 第 115000081 期；威力彩 2026-08-24 第 115000068 期</t>
+          <t>大樂透 2026-08-25 第 115000082 期；威力彩 2026-08-24 第 115000068 期</t>
         </is>
       </c>
     </row>
@@ -47,7 +47,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -56,7 +56,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -96,7 +96,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.215 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.285 碼/期</t>
         </is>
       </c>
     </row>
@@ -214,10 +214,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>0.905</v>
+        <v>0.952</v>
       </c>
       <c r="D2">
-        <v>26.2</v>
+        <v>28.6</v>
       </c>
       <c r="E2">
         <v>0.0</v>
@@ -236,10 +236,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>0.881</v>
+        <v>0.929</v>
       </c>
       <c r="D3">
-        <v>23.8</v>
+        <v>26.2</v>
       </c>
       <c r="E3">
         <v>0.0</v>
@@ -258,10 +258,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>0.762</v>
+        <v>0.738</v>
       </c>
       <c r="D4">
-        <v>21.4</v>
+        <v>19.0</v>
       </c>
       <c r="E4">
         <v>2.4</v>
@@ -280,10 +280,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>0.762</v>
+        <v>0.738</v>
       </c>
       <c r="D5">
-        <v>19.0</v>
+        <v>16.7</v>
       </c>
       <c r="E5">
         <v>2.4</v>
@@ -302,7 +302,7 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.69</v>
+        <v>0.667</v>
       </c>
       <c r="D6">
         <v>11.9</v>
@@ -324,7 +324,7 @@
         <v>42</v>
       </c>
       <c r="C7">
-        <v>0.595</v>
+        <v>0.619</v>
       </c>
       <c r="D7">
         <v>9.5</v>
@@ -398,7 +398,7 @@
         <v>15</v>
       </c>
       <c r="C2">
-        <v>72.69</v>
+        <v>71.73</v>
       </c>
       <c r="D2">
         <v>7</v>
@@ -407,16 +407,16 @@
         <v>5</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="H2">
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>15.62</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="3">
@@ -424,13 +424,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C3">
-        <v>70.4</v>
+        <v>70.0</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -439,7 +439,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>66.67</v>
+        <v>100.0</v>
       </c>
       <c r="H3">
         <v>100.0</v>
@@ -453,28 +453,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>67.22</v>
+        <v>69.32</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="H4">
-        <v>80.0</v>
+        <v>100.0</v>
       </c>
       <c r="I4">
-        <v>12.5</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="5">
@@ -482,28 +482,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C5">
-        <v>66.54</v>
+        <v>68.58</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5">
+        <v>76.92</v>
+      </c>
+      <c r="H5">
         <v>100.0</v>
       </c>
-      <c r="H5">
-        <v>80.0</v>
-      </c>
       <c r="I5">
-        <v>6.25</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
@@ -511,28 +511,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C6">
-        <v>66.02</v>
+        <v>64.91</v>
       </c>
       <c r="D6">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>4</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>91.67</v>
+        <v>46.15</v>
       </c>
       <c r="H6">
         <v>80.0</v>
       </c>
       <c r="I6">
-        <v>3.12</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="7">
@@ -540,13 +540,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C7">
-        <v>65.64</v>
+        <v>64.34</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -555,13 +555,13 @@
         <v>2</v>
       </c>
       <c r="G7">
-        <v>50.0</v>
+        <v>84.62</v>
       </c>
       <c r="H7">
         <v>80.0</v>
       </c>
       <c r="I7">
-        <v>6.25</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="8">
@@ -569,13 +569,13 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C8">
-        <v>65.5</v>
+        <v>64.0</v>
       </c>
       <c r="D8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E8">
         <v>4</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>83.33</v>
+        <v>53.85</v>
       </c>
       <c r="H8">
         <v>80.0</v>
@@ -598,28 +598,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C9">
-        <v>61.29</v>
+        <v>63.55</v>
       </c>
       <c r="D9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>58.33</v>
+        <v>46.15</v>
       </c>
       <c r="H9">
-        <v>60.0</v>
+        <v>80.0</v>
       </c>
       <c r="I9">
-        <v>6.25</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="10">
@@ -627,28 +627,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C10">
-        <v>61.07</v>
+        <v>61.28</v>
       </c>
       <c r="D10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G10">
-        <v>100.0</v>
+        <v>53.85</v>
       </c>
       <c r="H10">
         <v>60.0</v>
       </c>
       <c r="I10">
-        <v>3.12</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="11">
@@ -659,7 +659,7 @@
         <v>18</v>
       </c>
       <c r="C11">
-        <v>60.97</v>
+        <v>59.91</v>
       </c>
       <c r="D11">
         <v>7</v>
@@ -668,16 +668,16 @@
         <v>2</v>
       </c>
       <c r="F11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G11">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="H11">
         <v>40.0</v>
       </c>
       <c r="I11">
-        <v>37.5</v>
+        <v>39.39</v>
       </c>
     </row>
     <row r="12">
@@ -688,7 +688,7 @@
         <v>14</v>
       </c>
       <c r="C12">
-        <v>60.4</v>
+        <v>59.32</v>
       </c>
       <c r="D12">
         <v>8</v>
@@ -697,16 +697,16 @@
         <v>3</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="H12">
         <v>60.0</v>
       </c>
       <c r="I12">
-        <v>0.0</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="13">
@@ -714,28 +714,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C13">
-        <v>60.4</v>
+        <v>59.2</v>
       </c>
       <c r="D13">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13">
-        <v>66.67</v>
+        <v>92.31</v>
       </c>
       <c r="H13">
         <v>60.0</v>
       </c>
       <c r="I13">
-        <v>0.0</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="14">
@@ -743,13 +743,13 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C14">
-        <v>58.26</v>
+        <v>56.73</v>
       </c>
       <c r="D14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -758,13 +758,13 @@
         <v>6</v>
       </c>
       <c r="G14">
-        <v>75.0</v>
+        <v>53.85</v>
       </c>
       <c r="H14">
         <v>40.0</v>
       </c>
       <c r="I14">
-        <v>18.75</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="15">
@@ -775,7 +775,7 @@
         <v>4</v>
       </c>
       <c r="C15">
-        <v>57.79</v>
+        <v>56.45</v>
       </c>
       <c r="D15">
         <v>9</v>
@@ -784,16 +784,16 @@
         <v>2</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15">
-        <v>75.0</v>
+        <v>69.23</v>
       </c>
       <c r="H15">
         <v>40.0</v>
       </c>
       <c r="I15">
-        <v>15.62</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="16">
@@ -801,28 +801,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C16">
-        <v>57.69</v>
+        <v>54.91</v>
       </c>
       <c r="D16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16">
         <v>2</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G16">
-        <v>58.33</v>
+        <v>46.15</v>
       </c>
       <c r="H16">
         <v>40.0</v>
       </c>
       <c r="I16">
-        <v>15.62</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="17">
@@ -830,28 +830,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="C17">
-        <v>56.86</v>
+        <v>54.77</v>
       </c>
       <c r="D17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G17">
-        <v>75.0</v>
+        <v>61.54</v>
       </c>
       <c r="H17">
         <v>40.0</v>
       </c>
       <c r="I17">
-        <v>9.38</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="18">
@@ -859,28 +859,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="C18">
-        <v>56.16</v>
+        <v>54.46</v>
       </c>
       <c r="D18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G18">
-        <v>41.67</v>
+        <v>53.85</v>
       </c>
       <c r="H18">
-        <v>60.0</v>
+        <v>20.0</v>
       </c>
       <c r="I18">
-        <v>9.38</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="19">
@@ -888,28 +888,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>55.87</v>
+        <v>54.45</v>
       </c>
       <c r="D19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19">
-        <v>66.67</v>
+        <v>46.15</v>
       </c>
       <c r="H19">
         <v>40.0</v>
       </c>
       <c r="I19">
-        <v>3.12</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="20">
@@ -917,28 +917,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C20">
-        <v>55.64</v>
+        <v>54.45</v>
       </c>
       <c r="D20">
         <v>6</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G20">
-        <v>50.0</v>
+        <v>46.15</v>
       </c>
       <c r="H20">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="I20">
-        <v>6.25</v>
+        <v>72.73</v>
       </c>
     </row>
     <row r="21">
@@ -946,28 +946,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C21">
-        <v>55.51</v>
+        <v>54.32</v>
       </c>
       <c r="D21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21">
         <v>1</v>
       </c>
-      <c r="F21">
-        <v>11</v>
-      </c>
       <c r="G21">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="H21">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I21">
-        <v>34.38</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="22">
@@ -975,28 +975,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="C22">
-        <v>55.48</v>
+        <v>54.0</v>
       </c>
       <c r="D22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G22">
-        <v>50.0</v>
+        <v>53.85</v>
       </c>
       <c r="H22">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I22">
-        <v>71.88</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="23">
@@ -1004,28 +1004,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C23">
-        <v>55.4</v>
+        <v>52.64</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G23">
-        <v>66.67</v>
+        <v>53.85</v>
       </c>
       <c r="H23">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="I23">
-        <v>0.0</v>
+        <v>57.58</v>
       </c>
     </row>
     <row r="24">
@@ -1033,28 +1033,28 @@
         <v>23</v>
       </c>
       <c r="B24">
+        <v>11</v>
+      </c>
+      <c r="C24">
+        <v>51.9</v>
+      </c>
+      <c r="D24">
+        <v>9</v>
+      </c>
+      <c r="E24">
         <v>1</v>
       </c>
-      <c r="C24">
-        <v>55.17</v>
-      </c>
-      <c r="D24">
-        <v>6</v>
-      </c>
-      <c r="E24">
-        <v>2</v>
-      </c>
       <c r="F24">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G24">
-        <v>50.0</v>
+        <v>69.23</v>
       </c>
       <c r="H24">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I24">
-        <v>3.12</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="25">
@@ -1062,28 +1062,28 @@
         <v>24</v>
       </c>
       <c r="B25">
+        <v>20</v>
+      </c>
+      <c r="C25">
+        <v>51.73</v>
+      </c>
+      <c r="D25">
         <v>6</v>
-      </c>
-      <c r="C25">
-        <v>55.04</v>
-      </c>
-      <c r="D25">
-        <v>7</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G25">
-        <v>58.33</v>
+        <v>46.15</v>
       </c>
       <c r="H25">
         <v>20.0</v>
       </c>
       <c r="I25">
-        <v>31.25</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="26">
@@ -1091,28 +1091,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C26">
-        <v>54.86</v>
+        <v>51.52</v>
       </c>
       <c r="D26">
+        <v>5</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+      <c r="F26">
         <v>6</v>
       </c>
-      <c r="E26">
-        <v>1</v>
-      </c>
-      <c r="F26">
-        <v>11</v>
-      </c>
       <c r="G26">
-        <v>50.0</v>
+        <v>38.46</v>
       </c>
       <c r="H26">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I26">
-        <v>34.38</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="27">
@@ -1120,28 +1120,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C27">
-        <v>54.75</v>
+        <v>51.06</v>
       </c>
       <c r="D27">
         <v>5</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G27">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="H27">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="I27">
-        <v>0.0</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="28">
@@ -1149,28 +1149,28 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C28">
-        <v>54.54</v>
+        <v>50.85</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F28">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="G28">
-        <v>50.0</v>
+        <v>30.77</v>
       </c>
       <c r="H28">
-        <v>0.0</v>
+        <v>60.0</v>
       </c>
       <c r="I28">
-        <v>65.62</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="29">
@@ -1178,28 +1178,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C29">
-        <v>53.79</v>
+        <v>50.54</v>
       </c>
       <c r="D29">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G29">
-        <v>58.33</v>
+        <v>69.23</v>
       </c>
       <c r="H29">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I29">
-        <v>56.25</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="30">
@@ -1207,28 +1207,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C30">
-        <v>52.51</v>
+        <v>50.15</v>
       </c>
       <c r="D30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G30">
-        <v>50.0</v>
+        <v>38.46</v>
       </c>
       <c r="H30">
         <v>20.0</v>
       </c>
       <c r="I30">
-        <v>18.75</v>
+        <v>42.42</v>
       </c>
     </row>
     <row r="31">
@@ -1236,28 +1236,28 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C31">
-        <v>52.09</v>
+        <v>49.32</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G31">
-        <v>41.67</v>
+        <v>61.54</v>
       </c>
       <c r="H31">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I31">
-        <v>15.62</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="32">
@@ -1265,28 +1265,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="C32">
-        <v>51.63</v>
+        <v>49.24</v>
       </c>
       <c r="D32">
         <v>5</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G32">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="H32">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I32">
-        <v>12.5</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="33">
@@ -1294,28 +1294,28 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C33">
-        <v>51.31</v>
+        <v>49.0</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
       <c r="F33">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>41.67</v>
+        <v>53.85</v>
       </c>
       <c r="H33">
         <v>20.0</v>
       </c>
       <c r="I33">
-        <v>43.75</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="34">
@@ -1323,28 +1323,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C34">
-        <v>50.84</v>
+        <v>48.79</v>
       </c>
       <c r="D34">
         <v>5</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G34">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="H34">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I34">
-        <v>40.62</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="35">
@@ -1352,28 +1352,28 @@
         <v>34</v>
       </c>
       <c r="B35">
+        <v>28</v>
+      </c>
+      <c r="C35">
+        <v>47.42</v>
+      </c>
+      <c r="D35">
         <v>5</v>
       </c>
-      <c r="C35">
-        <v>50.64</v>
-      </c>
-      <c r="D35">
-        <v>6</v>
-      </c>
       <c r="E35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="G35">
-        <v>50.0</v>
+        <v>38.46</v>
       </c>
       <c r="H35">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I35">
-        <v>6.25</v>
+        <v>57.58</v>
       </c>
     </row>
     <row r="36">
@@ -1381,28 +1381,28 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C36">
-        <v>50.22</v>
+        <v>47.21</v>
       </c>
       <c r="D36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E36">
         <v>2</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G36">
-        <v>41.67</v>
+        <v>30.77</v>
       </c>
       <c r="H36">
         <v>40.0</v>
       </c>
       <c r="I36">
-        <v>3.12</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="37">
@@ -1410,28 +1410,28 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C37">
-        <v>48.19</v>
+        <v>46.76</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E37">
         <v>0</v>
       </c>
       <c r="F37">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G37">
-        <v>41.67</v>
+        <v>30.77</v>
       </c>
       <c r="H37">
         <v>0.0</v>
       </c>
       <c r="I37">
-        <v>56.25</v>
+        <v>84.85</v>
       </c>
     </row>
     <row r="38">
@@ -1439,28 +1439,28 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C38">
-        <v>47.61</v>
+        <v>45.61</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G38">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="H38">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="I38">
-        <v>18.75</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="39">
@@ -1468,28 +1468,28 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C39">
-        <v>47.46</v>
+        <v>45.15</v>
       </c>
       <c r="D39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="G39">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="H39">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I39">
-        <v>84.38</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="40">
@@ -1497,28 +1497,28 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C40">
-        <v>44.85</v>
+        <v>44.94</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F40">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="G40">
-        <v>25.0</v>
+        <v>30.77</v>
       </c>
       <c r="H40">
-        <v>0.0</v>
+        <v>40.0</v>
       </c>
       <c r="I40">
-        <v>100.0</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="41">
@@ -1526,28 +1526,28 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C41">
-        <v>44.49</v>
+        <v>44.27</v>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="G41">
-        <v>33.33</v>
+        <v>23.08</v>
       </c>
       <c r="H41">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I41">
-        <v>31.25</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="42">
@@ -1555,28 +1555,28 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C42">
-        <v>43.6</v>
+        <v>44.03</v>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G42">
-        <v>25.0</v>
+        <v>30.77</v>
       </c>
       <c r="H42">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I42">
-        <v>25.0</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="43">
@@ -1584,28 +1584,28 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C43">
-        <v>43.08</v>
+        <v>43.36</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G43">
-        <v>33.33</v>
+        <v>23.08</v>
       </c>
       <c r="H43">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I43">
-        <v>21.88</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="44">
@@ -1616,7 +1616,7 @@
         <v>38</v>
       </c>
       <c r="C44">
-        <v>42.51</v>
+        <v>42.0</v>
       </c>
       <c r="D44">
         <v>3</v>
@@ -1625,16 +1625,16 @@
         <v>0</v>
       </c>
       <c r="F44">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G44">
-        <v>25.0</v>
+        <v>23.08</v>
       </c>
       <c r="H44">
         <v>0.0</v>
       </c>
       <c r="I44">
-        <v>84.38</v>
+        <v>84.85</v>
       </c>
     </row>
     <row r="45">
@@ -1645,7 +1645,7 @@
         <v>9</v>
       </c>
       <c r="C45">
-        <v>42.14</v>
+        <v>41.76</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -1654,16 +1654,16 @@
         <v>1</v>
       </c>
       <c r="F45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G45">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="H45">
         <v>20.0</v>
       </c>
       <c r="I45">
-        <v>15.62</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="46">
@@ -1674,7 +1674,7 @@
         <v>21</v>
       </c>
       <c r="C46">
-        <v>41.67</v>
+        <v>41.3</v>
       </c>
       <c r="D46">
         <v>4</v>
@@ -1683,16 +1683,16 @@
         <v>1</v>
       </c>
       <c r="F46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G46">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="H46">
         <v>20.0</v>
       </c>
       <c r="I46">
-        <v>12.5</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="47">
@@ -1703,7 +1703,7 @@
         <v>41</v>
       </c>
       <c r="C47">
-        <v>41.67</v>
+        <v>41.3</v>
       </c>
       <c r="D47">
         <v>4</v>
@@ -1712,16 +1712,16 @@
         <v>1</v>
       </c>
       <c r="F47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G47">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="H47">
         <v>20.0</v>
       </c>
       <c r="I47">
-        <v>12.5</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="48">
@@ -1732,7 +1732,7 @@
         <v>42</v>
       </c>
       <c r="C48">
-        <v>40.94</v>
+        <v>40.64</v>
       </c>
       <c r="D48">
         <v>3</v>
@@ -1741,16 +1741,16 @@
         <v>1</v>
       </c>
       <c r="F48">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G48">
-        <v>25.0</v>
+        <v>23.08</v>
       </c>
       <c r="H48">
         <v>20.0</v>
       </c>
       <c r="I48">
-        <v>40.62</v>
+        <v>42.42</v>
       </c>
     </row>
     <row r="49">
@@ -1761,7 +1761,7 @@
         <v>30</v>
       </c>
       <c r="C49">
-        <v>37.19</v>
+        <v>37.0</v>
       </c>
       <c r="D49">
         <v>3</v>
@@ -1770,16 +1770,16 @@
         <v>1</v>
       </c>
       <c r="F49">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G49">
-        <v>25.0</v>
+        <v>23.08</v>
       </c>
       <c r="H49">
         <v>20.0</v>
       </c>
       <c r="I49">
-        <v>15.62</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="50">
@@ -1790,7 +1790,7 @@
         <v>31</v>
       </c>
       <c r="C50">
-        <v>31.2</v>
+        <v>31.12</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -1799,16 +1799,16 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G50">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="H50">
         <v>0.0</v>
       </c>
       <c r="I50">
-        <v>75.0</v>
+        <v>75.76</v>
       </c>
     </row>
   </sheetData>
@@ -1867,421 +1867,421 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H2">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I2">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D3">
         <v>14</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H3">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E4">
         <v>25</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H4">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I4">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>12</v>
       </c>
       <c r="E5">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H5">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D6">
         <v>12</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H6">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I6">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G7">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H7">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I7">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C8">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D8">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F8">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H8">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F9">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G9">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H9">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I9">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D10">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E10">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F10">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G10">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H10">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I10">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E11">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F11">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G11">
         <v>35</v>
       </c>
       <c r="H11">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I11">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E12">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F12">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G12">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H12">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I12">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C13">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E13">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F13">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G13">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H13">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I13">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E14">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F14">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G14">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H14">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I14">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C15">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D15">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E15">
         <v>15</v>
@@ -2290,345 +2290,345 @@
         <v>18</v>
       </c>
       <c r="G15">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H15">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I15">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C16">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D16">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E16">
+        <v>15</v>
+      </c>
+      <c r="F16">
+        <v>18</v>
+      </c>
+      <c r="G16">
         <v>19</v>
       </c>
-      <c r="F16">
-        <v>23</v>
-      </c>
-      <c r="G16">
-        <v>39</v>
-      </c>
       <c r="H16">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I16">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D17">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E17">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F17">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G17">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H17">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I17">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C18">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D18">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E18">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F18">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G18">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H18">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C19">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D19">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E19">
+        <v>23</v>
+      </c>
+      <c r="F19">
+        <v>24</v>
+      </c>
+      <c r="G19">
         <v>29</v>
       </c>
-      <c r="F19">
-        <v>33</v>
-      </c>
-      <c r="G19">
-        <v>34</v>
-      </c>
       <c r="H19">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I19">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C20">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D20">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E20">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F20">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G20">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H20">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I20">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E21">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F21">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G21">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H21">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I21">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E22">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F22">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G22">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H22">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I22">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C23">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E23">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F23">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G23">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H23">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I23">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D24">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E24">
         <v>25</v>
       </c>
       <c r="F24">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G24">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H24">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I24">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C25">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D25">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E25">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F25">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G25">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H25">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I25">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C26">
+        <v>8</v>
+      </c>
+      <c r="D26">
+        <v>9</v>
+      </c>
+      <c r="E26">
+        <v>16</v>
+      </c>
+      <c r="F26">
         <v>20</v>
-      </c>
-      <c r="D26">
-        <v>26</v>
-      </c>
-      <c r="E26">
-        <v>29</v>
-      </c>
-      <c r="F26">
-        <v>31</v>
       </c>
       <c r="G26">
         <v>37</v>
@@ -2637,782 +2637,782 @@
         <v>49</v>
       </c>
       <c r="I26">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C27">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D27">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E27">
         <v>29</v>
       </c>
       <c r="F27">
+        <v>31</v>
+      </c>
+      <c r="G27">
         <v>37</v>
       </c>
-      <c r="G27">
-        <v>47</v>
-      </c>
       <c r="H27">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I27">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C28">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D28">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E28">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F28">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G28">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="H28">
         <v>48</v>
       </c>
       <c r="I28">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C29">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D29">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E29">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F29">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G29">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H29">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I29">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C30">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D30">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E30">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F30">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G30">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H30">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C31">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D31">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E31">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F31">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G31">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H31">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I31">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D32">
+        <v>12</v>
+      </c>
+      <c r="E32">
         <v>18</v>
       </c>
-      <c r="E32">
-        <v>25</v>
-      </c>
       <c r="F32">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G32">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H32">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I32">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C33">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D33">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E33">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F33">
         <v>28</v>
       </c>
       <c r="G33">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H33">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I33">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D34">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E34">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F34">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G34">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H34">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I34">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D35">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E35">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F35">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G35">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H35">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I35">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C36">
+        <v>6</v>
+      </c>
+      <c r="D36">
+        <v>10</v>
+      </c>
+      <c r="E36">
+        <v>14</v>
+      </c>
+      <c r="F36">
+        <v>25</v>
+      </c>
+      <c r="G36">
+        <v>26</v>
+      </c>
+      <c r="H36">
+        <v>32</v>
+      </c>
+      <c r="I36">
         <v>7</v>
-      </c>
-      <c r="D36">
-        <v>14</v>
-      </c>
-      <c r="E36">
-        <v>16</v>
-      </c>
-      <c r="F36">
-        <v>37</v>
-      </c>
-      <c r="G36">
-        <v>39</v>
-      </c>
-      <c r="H36">
-        <v>47</v>
-      </c>
-      <c r="I36">
-        <v>34</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D37">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E37">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F37">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G37">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H37">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I37">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E38">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F38">
+        <v>19</v>
+      </c>
+      <c r="G38">
+        <v>20</v>
+      </c>
+      <c r="H38">
+        <v>40</v>
+      </c>
+      <c r="I38">
         <v>22</v>
-      </c>
-      <c r="G38">
-        <v>40</v>
-      </c>
-      <c r="H38">
-        <v>45</v>
-      </c>
-      <c r="I38">
-        <v>18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C39">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E39">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F39">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G39">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H39">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I39">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C40">
         <v>4</v>
       </c>
       <c r="D40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E40">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F40">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G40">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H40">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I40">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E41">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F41">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G41">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H41">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I41">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D42">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E42">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F42">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G42">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H42">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I42">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C43">
         <v>5</v>
       </c>
       <c r="D43">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E43">
+        <v>13</v>
+      </c>
+      <c r="F43">
         <v>25</v>
       </c>
-      <c r="F43">
-        <v>40</v>
-      </c>
       <c r="G43">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H43">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I43">
-        <v>39</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D44">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E44">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F44">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G44">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H44">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I44">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C45">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D45">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E45">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F45">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G45">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H45">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I45">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C46">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D46">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E46">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F46">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G46">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H46">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I46">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D47">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E47">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F47">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G47">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H47">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I47">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C48">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D48">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E48">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F48">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G48">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H48">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I48">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C49">
         <v>5</v>
       </c>
       <c r="D49">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E49">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F49">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G49">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H49">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I49">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C50">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D50">
         <v>11</v>
       </c>
       <c r="E50">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F50">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="G50">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="H50">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="I50">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="C51">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D51">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E51">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F51">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="G51">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="H51">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="I51">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-08-25 第 115000082 期；威力彩 2026-08-24 第 115000068 期</t>
+          <t>大樂透 2026-08-25 第 115000082 期；威力彩 2026-08-27 第 115000069 期</t>
         </is>
       </c>
     </row>
@@ -112,7 +112,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -121,7 +121,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -143,7 +143,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9, 14, 29, 31, 35, 38</t>
+          <t>9, 24, 29, 31, 35, 38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -152,7 +152,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>0.976</v>
+        <v>1.0</v>
       </c>
       <c r="D4">
         <v>23.8</v>
@@ -3523,7 +3523,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>冷號觀察</t>
+          <t>均衡分散</t>
         </is>
       </c>
       <c r="B5">
@@ -3533,10 +3533,10 @@
         <v>0.952</v>
       </c>
       <c r="D5">
-        <v>28.6</v>
+        <v>21.4</v>
       </c>
       <c r="E5">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -3545,20 +3545,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>均衡分散</t>
+          <t>冷號觀察</t>
         </is>
       </c>
       <c r="B6">
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.929</v>
+        <v>0.952</v>
       </c>
       <c r="D6">
-        <v>21.4</v>
+        <v>28.6</v>
       </c>
       <c r="E6">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -3648,7 +3648,7 @@
         <v>29</v>
       </c>
       <c r="C2">
-        <v>73.61</v>
+        <v>74.04</v>
       </c>
       <c r="D2">
         <v>13</v>
@@ -3657,7 +3657,7 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>92.86</v>
@@ -3666,7 +3666,7 @@
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>3.03</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="3">
@@ -3674,28 +3674,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C3">
-        <v>70.32</v>
+        <v>69.87</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E3">
         <v>5</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>78.57</v>
+        <v>92.86</v>
       </c>
       <c r="H3">
         <v>83.33</v>
       </c>
       <c r="I3">
-        <v>12.12</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="4">
@@ -3703,28 +3703,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>69.44</v>
+        <v>68.26</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>92.86</v>
+        <v>71.43</v>
       </c>
       <c r="H4">
         <v>83.33</v>
       </c>
       <c r="I4">
-        <v>3.03</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="5">
@@ -3732,28 +3732,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C5">
-        <v>65.38</v>
+        <v>66.55</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>71.43</v>
+        <v>78.57</v>
       </c>
       <c r="H5">
-        <v>50.0</v>
+        <v>66.67</v>
       </c>
       <c r="I5">
-        <v>36.36</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="6">
@@ -3764,7 +3764,7 @@
         <v>19</v>
       </c>
       <c r="C6">
-        <v>65.01</v>
+        <v>65.42</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -3773,7 +3773,7 @@
         <v>4</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6">
         <v>71.43</v>
@@ -3782,7 +3782,7 @@
         <v>66.67</v>
       </c>
       <c r="I6">
-        <v>6.06</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="7">
@@ -3790,13 +3790,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C7">
-        <v>64.55</v>
+        <v>64.05</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -3805,13 +3805,13 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>71.43</v>
+        <v>57.14</v>
       </c>
       <c r="H7">
         <v>66.67</v>
       </c>
       <c r="I7">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="8">
@@ -3819,7 +3819,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C8">
         <v>63.61</v>
@@ -3851,7 +3851,7 @@
         <v>22</v>
       </c>
       <c r="C9">
-        <v>62.66</v>
+        <v>63.02</v>
       </c>
       <c r="D9">
         <v>10</v>
@@ -3860,7 +3860,7 @@
         <v>3</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G9">
         <v>71.43</v>
@@ -3869,7 +3869,7 @@
         <v>50.0</v>
       </c>
       <c r="I9">
-        <v>18.18</v>
+        <v>20.59</v>
       </c>
     </row>
     <row r="10">
@@ -3880,7 +3880,7 @@
         <v>8</v>
       </c>
       <c r="C10">
-        <v>61.71</v>
+        <v>62.09</v>
       </c>
       <c r="D10">
         <v>8</v>
@@ -3889,7 +3889,7 @@
         <v>3</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G10">
         <v>57.14</v>
@@ -3898,7 +3898,7 @@
         <v>50.0</v>
       </c>
       <c r="I10">
-        <v>15.15</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="11">
@@ -3906,28 +3906,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C11">
-        <v>60.81</v>
+        <v>60.9</v>
       </c>
       <c r="D11">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>57.14</v>
+        <v>100.0</v>
       </c>
       <c r="H11">
         <v>50.0</v>
       </c>
       <c r="I11">
-        <v>9.09</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="12">
@@ -3938,7 +3938,7 @@
         <v>13</v>
       </c>
       <c r="C12">
-        <v>59.85</v>
+        <v>60.17</v>
       </c>
       <c r="D12">
         <v>10</v>
@@ -3947,7 +3947,7 @@
         <v>2</v>
       </c>
       <c r="F12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>71.43</v>
@@ -3956,7 +3956,7 @@
         <v>33.33</v>
       </c>
       <c r="I12">
-        <v>27.27</v>
+        <v>29.41</v>
       </c>
     </row>
     <row r="13">
@@ -3964,13 +3964,13 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C13">
-        <v>59.44</v>
+        <v>60.17</v>
       </c>
       <c r="D13">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>57.14</v>
+        <v>78.57</v>
       </c>
       <c r="H13">
         <v>50.0</v>
@@ -3993,28 +3993,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C14">
-        <v>58.73</v>
+        <v>60.09</v>
       </c>
       <c r="D14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>78.57</v>
+        <v>42.86</v>
       </c>
       <c r="H14">
-        <v>33.33</v>
+        <v>83.33</v>
       </c>
       <c r="I14">
-        <v>18.18</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="15">
@@ -4022,28 +4022,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C15">
-        <v>58.49</v>
+        <v>59.09</v>
       </c>
       <c r="D15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15">
         <v>2</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G15">
-        <v>71.43</v>
+        <v>78.57</v>
       </c>
       <c r="H15">
         <v>33.33</v>
       </c>
       <c r="I15">
-        <v>18.18</v>
+        <v>20.59</v>
       </c>
     </row>
     <row r="16">
@@ -4054,7 +4054,7 @@
         <v>17</v>
       </c>
       <c r="C16">
-        <v>58.46</v>
+        <v>58.8</v>
       </c>
       <c r="D16">
         <v>8</v>
@@ -4063,7 +4063,7 @@
         <v>2</v>
       </c>
       <c r="F16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G16">
         <v>57.14</v>
@@ -4072,7 +4072,7 @@
         <v>33.33</v>
       </c>
       <c r="I16">
-        <v>21.21</v>
+        <v>23.53</v>
       </c>
     </row>
     <row r="17">
@@ -4083,7 +4083,7 @@
         <v>21</v>
       </c>
       <c r="C17">
-        <v>58.46</v>
+        <v>58.8</v>
       </c>
       <c r="D17">
         <v>8</v>
@@ -4092,7 +4092,7 @@
         <v>2</v>
       </c>
       <c r="F17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G17">
         <v>57.14</v>
@@ -4101,7 +4101,7 @@
         <v>33.33</v>
       </c>
       <c r="I17">
-        <v>21.21</v>
+        <v>23.53</v>
       </c>
     </row>
     <row r="18">
@@ -4109,28 +4109,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C18">
-        <v>57.64</v>
+        <v>57.97</v>
       </c>
       <c r="D18">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G18">
-        <v>100.0</v>
+        <v>71.43</v>
       </c>
       <c r="H18">
         <v>33.33</v>
       </c>
       <c r="I18">
-        <v>6.06</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="19">
@@ -4138,28 +4138,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C19">
-        <v>57.58</v>
+        <v>57.92</v>
       </c>
       <c r="D19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G19">
-        <v>71.43</v>
+        <v>57.14</v>
       </c>
       <c r="H19">
         <v>33.33</v>
       </c>
       <c r="I19">
-        <v>12.12</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="20">
@@ -4167,28 +4167,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C20">
-        <v>57.55</v>
+        <v>57.81</v>
       </c>
       <c r="D20">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G20">
-        <v>57.14</v>
+        <v>92.86</v>
       </c>
       <c r="H20">
         <v>33.33</v>
       </c>
       <c r="I20">
-        <v>15.15</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="21">
@@ -4199,7 +4199,7 @@
         <v>25</v>
       </c>
       <c r="C21">
-        <v>57.09</v>
+        <v>57.48</v>
       </c>
       <c r="D21">
         <v>8</v>
@@ -4208,7 +4208,7 @@
         <v>2</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G21">
         <v>57.14</v>
@@ -4217,7 +4217,7 @@
         <v>33.33</v>
       </c>
       <c r="I21">
-        <v>12.12</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="22">
@@ -4225,28 +4225,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C22">
-        <v>56.49</v>
+        <v>57.04</v>
       </c>
       <c r="D22">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E22">
         <v>2</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G22">
-        <v>92.86</v>
+        <v>57.14</v>
       </c>
       <c r="H22">
         <v>33.33</v>
       </c>
       <c r="I22">
-        <v>0.0</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="23">
@@ -4254,25 +4254,25 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="C23">
-        <v>55.93</v>
+        <v>55.8</v>
       </c>
       <c r="D23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
       <c r="G23">
-        <v>42.86</v>
+        <v>50.0</v>
       </c>
       <c r="H23">
-        <v>66.67</v>
+        <v>50.0</v>
       </c>
       <c r="I23">
         <v>0.0</v>
@@ -4286,7 +4286,7 @@
         <v>6</v>
       </c>
       <c r="C24">
-        <v>55.27</v>
+        <v>55.72</v>
       </c>
       <c r="D24">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24">
         <v>57.14</v>
@@ -4304,7 +4304,7 @@
         <v>33.33</v>
       </c>
       <c r="I24">
-        <v>0.0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="25">
@@ -4315,25 +4315,25 @@
         <v>14</v>
       </c>
       <c r="C25">
-        <v>55.02</v>
+        <v>55.13</v>
       </c>
       <c r="D25">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G25">
-        <v>78.57</v>
+        <v>71.43</v>
       </c>
       <c r="H25">
         <v>16.67</v>
       </c>
       <c r="I25">
-        <v>21.21</v>
+        <v>23.53</v>
       </c>
     </row>
     <row r="26">
@@ -4341,28 +4341,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C26">
-        <v>54.26</v>
+        <v>54.69</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="G26">
-        <v>42.86</v>
+        <v>71.43</v>
       </c>
       <c r="H26">
-        <v>0.0</v>
+        <v>16.67</v>
       </c>
       <c r="I26">
-        <v>100.0</v>
+        <v>20.59</v>
       </c>
     </row>
     <row r="27">
@@ -4370,28 +4370,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C27">
-        <v>53.12</v>
+        <v>54.26</v>
       </c>
       <c r="D27">
         <v>6</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="G27">
         <v>42.86</v>
       </c>
       <c r="H27">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
       <c r="I27">
-        <v>9.09</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="28">
@@ -4399,10 +4399,10 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C28">
-        <v>51.76</v>
+        <v>53.52</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -4411,7 +4411,7 @@
         <v>3</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G28">
         <v>42.86</v>
@@ -4420,7 +4420,7 @@
         <v>50.0</v>
       </c>
       <c r="I28">
-        <v>0.0</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="29">
@@ -4428,28 +4428,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C29">
-        <v>48.88</v>
+        <v>52.2</v>
       </c>
       <c r="D29">
         <v>6</v>
       </c>
       <c r="E29">
+        <v>3</v>
+      </c>
+      <c r="F29">
         <v>1</v>
-      </c>
-      <c r="F29">
-        <v>12</v>
       </c>
       <c r="G29">
         <v>42.86</v>
       </c>
       <c r="H29">
-        <v>16.67</v>
+        <v>50.0</v>
       </c>
       <c r="I29">
-        <v>36.36</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="30">
@@ -4460,7 +4460,7 @@
         <v>1</v>
       </c>
       <c r="C30">
-        <v>48.05</v>
+        <v>48.47</v>
       </c>
       <c r="D30">
         <v>6</v>
@@ -4469,7 +4469,7 @@
         <v>2</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30">
         <v>42.86</v>
@@ -4478,7 +4478,7 @@
         <v>33.33</v>
       </c>
       <c r="I30">
-        <v>3.03</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="31">
@@ -4486,28 +4486,28 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="C31">
-        <v>48.05</v>
+        <v>45.12</v>
       </c>
       <c r="D31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G31">
-        <v>42.86</v>
+        <v>35.71</v>
       </c>
       <c r="H31">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="I31">
-        <v>3.03</v>
+        <v>38.24</v>
       </c>
     </row>
     <row r="32">
@@ -4515,28 +4515,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C32">
-        <v>41.32</v>
+        <v>40.7</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G32">
-        <v>28.57</v>
+        <v>35.71</v>
       </c>
       <c r="H32">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="I32">
-        <v>12.12</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="33">
@@ -4544,10 +4544,10 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C33">
-        <v>40.29</v>
+        <v>40.7</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -4556,7 +4556,7 @@
         <v>1</v>
       </c>
       <c r="F33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G33">
         <v>35.71</v>
@@ -4565,7 +4565,7 @@
         <v>16.67</v>
       </c>
       <c r="I33">
-        <v>6.06</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="34">
@@ -4573,28 +4573,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C34">
-        <v>40.29</v>
+        <v>38.67</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G34">
-        <v>35.71</v>
+        <v>28.57</v>
       </c>
       <c r="H34">
-        <v>16.67</v>
+        <v>0.0</v>
       </c>
       <c r="I34">
-        <v>6.06</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="35">
@@ -4602,28 +4602,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C35">
-        <v>40.01</v>
+        <v>37.55</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G35">
-        <v>21.43</v>
+        <v>28.57</v>
       </c>
       <c r="H35">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="I35">
-        <v>30.3</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="36">
@@ -4631,28 +4631,28 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C36">
-        <v>38.44</v>
+        <v>37.1</v>
       </c>
       <c r="D36">
         <v>4</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G36">
         <v>28.57</v>
       </c>
       <c r="H36">
-        <v>0.0</v>
+        <v>16.67</v>
       </c>
       <c r="I36">
-        <v>48.48</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="37">
@@ -4660,28 +4660,28 @@
         <v>36</v>
       </c>
       <c r="B37">
+        <v>12</v>
+      </c>
+      <c r="C37">
+        <v>36.15</v>
+      </c>
+      <c r="D37">
         <v>3</v>
-      </c>
-      <c r="C37">
-        <v>36.7</v>
-      </c>
-      <c r="D37">
-        <v>4</v>
       </c>
       <c r="E37">
         <v>1</v>
       </c>
       <c r="F37">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G37">
-        <v>28.57</v>
+        <v>21.43</v>
       </c>
       <c r="H37">
         <v>16.67</v>
       </c>
       <c r="I37">
-        <v>9.09</v>
+        <v>32.35</v>
       </c>
     </row>
     <row r="38">
@@ -4692,7 +4692,7 @@
         <v>20</v>
       </c>
       <c r="C38">
-        <v>33.57</v>
+        <v>33.94</v>
       </c>
       <c r="D38">
         <v>3</v>
@@ -4701,7 +4701,7 @@
         <v>1</v>
       </c>
       <c r="F38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G38">
         <v>21.43</v>
@@ -4710,7 +4710,7 @@
         <v>16.67</v>
       </c>
       <c r="I38">
-        <v>15.15</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="39">
@@ -4721,7 +4721,7 @@
         <v>37</v>
       </c>
       <c r="C39">
-        <v>33.16</v>
+        <v>33.43</v>
       </c>
       <c r="D39">
         <v>2</v>
@@ -4730,7 +4730,7 @@
         <v>1</v>
       </c>
       <c r="F39">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G39">
         <v>14.29</v>
@@ -4739,7 +4739,7 @@
         <v>16.67</v>
       </c>
       <c r="I39">
-        <v>39.39</v>
+        <v>41.18</v>
       </c>
     </row>
   </sheetData>
@@ -4798,15 +4798,15 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>7</v>
@@ -4815,230 +4815,230 @@
         <v>9</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H2">
         <v>36</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E3">
         <v>9</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>9</v>
+      </c>
+      <c r="F4">
         <v>11</v>
       </c>
-      <c r="E4">
-        <v>18</v>
-      </c>
-      <c r="F4">
-        <v>19</v>
-      </c>
       <c r="G4">
+        <v>29</v>
+      </c>
+      <c r="H4">
         <v>35</v>
       </c>
-      <c r="H4">
-        <v>38</v>
-      </c>
       <c r="I4">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H5">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C6">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H6">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H7">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8">
+        <v>8</v>
+      </c>
+      <c r="F8">
+        <v>20</v>
+      </c>
+      <c r="G8">
+        <v>26</v>
+      </c>
+      <c r="H8">
+        <v>33</v>
+      </c>
+      <c r="I8">
         <v>4</v>
-      </c>
-      <c r="D8">
-        <v>15</v>
-      </c>
-      <c r="E8">
-        <v>22</v>
-      </c>
-      <c r="F8">
-        <v>26</v>
-      </c>
-      <c r="G8">
-        <v>34</v>
-      </c>
-      <c r="H8">
-        <v>36</v>
-      </c>
-      <c r="I8">
-        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E9">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F9">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G9">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H9">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I9">
         <v>7</v>
@@ -5046,30 +5046,30 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C10">
+        <v>8</v>
+      </c>
+      <c r="D10">
+        <v>14</v>
+      </c>
+      <c r="E10">
+        <v>17</v>
+      </c>
+      <c r="F10">
         <v>19</v>
       </c>
-      <c r="D10">
-        <v>22</v>
-      </c>
-      <c r="E10">
-        <v>28</v>
-      </c>
-      <c r="F10">
-        <v>31</v>
-      </c>
       <c r="G10">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H10">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I10">
         <v>7</v>
@@ -5077,30 +5077,30 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C11">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E11">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F11">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G11">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H11">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I11">
         <v>7</v>
@@ -5108,24 +5108,24 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D12">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E12">
         <v>13</v>
       </c>
       <c r="F12">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G12">
         <v>29</v>
@@ -5134,97 +5134,97 @@
         <v>31</v>
       </c>
       <c r="I12">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C13">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D13">
+        <v>12</v>
+      </c>
+      <c r="E13">
+        <v>13</v>
+      </c>
+      <c r="F13">
         <v>23</v>
       </c>
-      <c r="E13">
-        <v>25</v>
-      </c>
-      <c r="F13">
+      <c r="G13">
         <v>29</v>
       </c>
-      <c r="G13">
-        <v>34</v>
-      </c>
       <c r="H13">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I13">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C14">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E14">
+        <v>25</v>
+      </c>
+      <c r="F14">
         <v>29</v>
       </c>
-      <c r="F14">
-        <v>32</v>
-      </c>
       <c r="G14">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I14">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E15">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F15">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G15">
         <v>35</v>
       </c>
       <c r="H15">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I15">
         <v>6</v>
@@ -5232,402 +5232,402 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D16">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E16">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F16">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G16">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H16">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F17">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G17">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H17">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I17">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D18">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E18">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F18">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G18">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H18">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I18">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C19">
+        <v>5</v>
+      </c>
+      <c r="D19">
         <v>6</v>
       </c>
-      <c r="D19">
-        <v>10</v>
-      </c>
       <c r="E19">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F19">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G19">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H19">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C20">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D20">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E20">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F20">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G20">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H20">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I20">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D21">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E21">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F21">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G21">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H21">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I21">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <v>8</v>
+      </c>
+      <c r="E22">
+        <v>9</v>
+      </c>
+      <c r="F22">
+        <v>15</v>
+      </c>
+      <c r="G22">
+        <v>18</v>
+      </c>
+      <c r="H22">
+        <v>23</v>
+      </c>
+      <c r="I22">
         <v>4</v>
-      </c>
-      <c r="D22">
-        <v>17</v>
-      </c>
-      <c r="E22">
-        <v>19</v>
-      </c>
-      <c r="F22">
-        <v>25</v>
-      </c>
-      <c r="G22">
-        <v>28</v>
-      </c>
-      <c r="H22">
-        <v>29</v>
-      </c>
-      <c r="I22">
-        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D23">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E23">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F23">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G23">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H23">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I23">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D24">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E24">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F24">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G24">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H24">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I24">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C25">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D25">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E25">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F25">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G25">
         <v>28</v>
       </c>
       <c r="H25">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I25">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C26">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D26">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E26">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F26">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G26">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H26">
         <v>35</v>
       </c>
       <c r="I26">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E27">
+        <v>9</v>
+      </c>
+      <c r="F27">
+        <v>15</v>
+      </c>
+      <c r="G27">
         <v>24</v>
       </c>
-      <c r="F27">
-        <v>31</v>
-      </c>
-      <c r="G27">
-        <v>34</v>
-      </c>
       <c r="H27">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I27">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C28">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D28">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E28">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F28">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G28">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H28">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I28">
         <v>3</v>
@@ -5635,554 +5635,554 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C29">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D29">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E29">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F29">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G29">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H29">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I29">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C30">
         <v>6</v>
       </c>
       <c r="D30">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E30">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F30">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G30">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H30">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I30">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C31">
         <v>6</v>
       </c>
       <c r="D31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E31">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F31">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G31">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H31">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I31">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C32">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D32">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E32">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F32">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G32">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H32">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I32">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C33">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D33">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E33">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F33">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G33">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H33">
         <v>38</v>
       </c>
       <c r="I33">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C34">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D34">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E34">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F34">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G34">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H34">
         <v>38</v>
       </c>
       <c r="I34">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E35">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F35">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G35">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H35">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I35">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C36">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D36">
+        <v>4</v>
+      </c>
+      <c r="E36">
+        <v>13</v>
+      </c>
+      <c r="F36">
+        <v>19</v>
+      </c>
+      <c r="G36">
+        <v>27</v>
+      </c>
+      <c r="H36">
+        <v>30</v>
+      </c>
+      <c r="I36">
         <v>8</v>
-      </c>
-      <c r="E36">
-        <v>27</v>
-      </c>
-      <c r="F36">
-        <v>33</v>
-      </c>
-      <c r="G36">
-        <v>35</v>
-      </c>
-      <c r="H36">
-        <v>38</v>
-      </c>
-      <c r="I36">
-        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D37">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E37">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F37">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G37">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H37">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I37">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D38">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E38">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F38">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G38">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H38">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I38">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C39">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D39">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E39">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F39">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G39">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H39">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I39">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000030</v>
+        <v>115000031</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D40">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E40">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F40">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G40">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H40">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="I40">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000029</v>
+        <v>115000030</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E41">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F41">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G41">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H41">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I41">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000028</v>
+        <v>115000029</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E42">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F42">
         <v>27</v>
       </c>
       <c r="G42">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H42">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I42">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000027</v>
+        <v>115000028</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C43">
         <v>5</v>
       </c>
       <c r="D43">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E43">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F43">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G43">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H43">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I43">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000026</v>
+        <v>115000027</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D44">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E44">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F44">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G44">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H44">
         <v>34</v>
       </c>
       <c r="I44">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000025</v>
+        <v>115000026</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C45">
+        <v>2</v>
+      </c>
+      <c r="D45">
         <v>13</v>
       </c>
-      <c r="D45">
-        <v>14</v>
-      </c>
       <c r="E45">
+        <v>21</v>
+      </c>
+      <c r="F45">
         <v>22</v>
       </c>
-      <c r="F45">
-        <v>28</v>
-      </c>
       <c r="G45">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H45">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I45">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000024</v>
+        <v>115000025</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D46">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E46">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F46">
         <v>28</v>
       </c>
       <c r="G46">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H46">
         <v>38</v>
@@ -6193,58 +6193,58 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000023</v>
+        <v>115000024</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
         <v>9</v>
       </c>
-      <c r="D47">
-        <v>13</v>
-      </c>
       <c r="E47">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F47">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G47">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H47">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I47">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000022</v>
+        <v>115000023</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C48">
+        <v>9</v>
+      </c>
+      <c r="D48">
+        <v>13</v>
+      </c>
+      <c r="E48">
         <v>14</v>
       </c>
-      <c r="D48">
-        <v>26</v>
-      </c>
-      <c r="E48">
-        <v>28</v>
-      </c>
       <c r="F48">
+        <v>18</v>
+      </c>
+      <c r="G48">
         <v>31</v>
-      </c>
-      <c r="G48">
-        <v>32</v>
       </c>
       <c r="H48">
         <v>34</v>
@@ -6255,61 +6255,61 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000021</v>
+        <v>115000022</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C49">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D49">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E49">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F49">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G49">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H49">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I49">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000020</v>
+        <v>115000021</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D50">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E50">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F50">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G50">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H50">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I50">
         <v>8</v>
@@ -6317,15 +6317,15 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000019</v>
+        <v>115000020</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="C51">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D51">
         <v>11</v>
@@ -6334,16 +6334,16 @@
         <v>14</v>
       </c>
       <c r="F51">
+        <v>17</v>
+      </c>
+      <c r="G51">
+        <v>29</v>
+      </c>
+      <c r="H51">
         <v>32</v>
       </c>
-      <c r="G51">
-        <v>36</v>
-      </c>
-      <c r="H51">
-        <v>38</v>
-      </c>
       <c r="I51">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-08-25 第 115000082 期；威力彩 2026-08-27 第 115000069 期</t>
+          <t>大樂透 2026-08-28 第 115000083 期；威力彩 2026-08-27 第 115000069 期</t>
         </is>
       </c>
     </row>
@@ -47,7 +47,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -56,7 +56,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -78,7 +78,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4, 11, 12, 25, 26, 29</t>
+          <t>4, 12, 16, 25, 26, 29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -96,7 +96,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.285 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.262 碼/期</t>
         </is>
       </c>
     </row>
@@ -214,10 +214,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>0.952</v>
+        <v>0.929</v>
       </c>
       <c r="D2">
-        <v>28.6</v>
+        <v>26.2</v>
       </c>
       <c r="E2">
         <v>0.0</v>
@@ -236,10 +236,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>0.929</v>
+        <v>0.905</v>
       </c>
       <c r="D3">
-        <v>26.2</v>
+        <v>23.8</v>
       </c>
       <c r="E3">
         <v>0.0</v>
@@ -251,7 +251,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>均衡分散</t>
+          <t>近期趨勢</t>
         </is>
       </c>
       <c r="B4">
@@ -261,7 +261,7 @@
         <v>0.738</v>
       </c>
       <c r="D4">
-        <v>19.0</v>
+        <v>16.7</v>
       </c>
       <c r="E4">
         <v>2.4</v>
@@ -273,14 +273,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>近期趨勢</t>
+          <t>均衡分散</t>
         </is>
       </c>
       <c r="B5">
         <v>42</v>
       </c>
       <c r="C5">
-        <v>0.738</v>
+        <v>0.714</v>
       </c>
       <c r="D5">
         <v>16.7</v>
@@ -395,28 +395,28 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C2">
-        <v>71.73</v>
+        <v>70.55</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>53.85</v>
+        <v>91.67</v>
       </c>
       <c r="H2">
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>18.18</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="3">
@@ -427,25 +427,25 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>70.0</v>
+        <v>66.87</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3">
         <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
         <v>100.0</v>
       </c>
       <c r="H3">
-        <v>100.0</v>
+        <v>83.33</v>
       </c>
       <c r="I3">
-        <v>0.0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="4">
@@ -453,28 +453,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C4">
-        <v>69.32</v>
+        <v>65.1</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G4">
-        <v>61.54</v>
+        <v>58.33</v>
       </c>
       <c r="H4">
-        <v>100.0</v>
+        <v>66.67</v>
       </c>
       <c r="I4">
-        <v>3.03</v>
+        <v>20.59</v>
       </c>
     </row>
     <row r="5">
@@ -482,28 +482,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5">
-        <v>68.58</v>
+        <v>63.49</v>
       </c>
       <c r="D5">
         <v>10</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>76.92</v>
+        <v>83.33</v>
       </c>
       <c r="H5">
-        <v>100.0</v>
+        <v>66.67</v>
       </c>
       <c r="I5">
-        <v>0.0</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="6">
@@ -514,7 +514,7 @@
         <v>34</v>
       </c>
       <c r="C6">
-        <v>64.91</v>
+        <v>63.13</v>
       </c>
       <c r="D6">
         <v>6</v>
@@ -523,16 +523,16 @@
         <v>4</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>46.15</v>
+        <v>50.0</v>
       </c>
       <c r="H6">
-        <v>80.0</v>
+        <v>66.67</v>
       </c>
       <c r="I6">
-        <v>9.09</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="7">
@@ -540,13 +540,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>64.34</v>
+        <v>62.95</v>
       </c>
       <c r="D7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -555,13 +555,13 @@
         <v>2</v>
       </c>
       <c r="G7">
-        <v>84.62</v>
+        <v>66.67</v>
       </c>
       <c r="H7">
-        <v>80.0</v>
+        <v>66.67</v>
       </c>
       <c r="I7">
-        <v>6.06</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="8">
@@ -572,7 +572,7 @@
         <v>35</v>
       </c>
       <c r="C8">
-        <v>64.0</v>
+        <v>62.46</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -581,16 +581,16 @@
         <v>4</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>53.85</v>
+        <v>58.33</v>
       </c>
       <c r="H8">
-        <v>80.0</v>
+        <v>66.67</v>
       </c>
       <c r="I8">
-        <v>0.0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="9">
@@ -601,7 +601,7 @@
         <v>24</v>
       </c>
       <c r="C9">
-        <v>63.55</v>
+        <v>61.81</v>
       </c>
       <c r="D9">
         <v>6</v>
@@ -610,16 +610,16 @@
         <v>4</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>46.15</v>
+        <v>50.0</v>
       </c>
       <c r="H9">
-        <v>80.0</v>
+        <v>66.67</v>
       </c>
       <c r="I9">
-        <v>0.0</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="10">
@@ -627,28 +627,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C10">
-        <v>61.28</v>
+        <v>59.42</v>
       </c>
       <c r="D10">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>53.85</v>
+        <v>100.0</v>
       </c>
       <c r="H10">
-        <v>60.0</v>
+        <v>50.0</v>
       </c>
       <c r="I10">
-        <v>15.15</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="11">
@@ -656,28 +656,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C11">
-        <v>59.91</v>
+        <v>58.73</v>
       </c>
       <c r="D11">
         <v>7</v>
       </c>
       <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11">
         <v>2</v>
       </c>
-      <c r="F11">
-        <v>13</v>
-      </c>
       <c r="G11">
-        <v>53.85</v>
+        <v>58.33</v>
       </c>
       <c r="H11">
-        <v>40.0</v>
+        <v>50.0</v>
       </c>
       <c r="I11">
-        <v>39.39</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="12">
@@ -685,10 +685,10 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C12">
-        <v>59.32</v>
+        <v>57.9</v>
       </c>
       <c r="D12">
         <v>8</v>
@@ -697,16 +697,16 @@
         <v>3</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>61.54</v>
+        <v>66.67</v>
       </c>
       <c r="H12">
-        <v>60.0</v>
+        <v>50.0</v>
       </c>
       <c r="I12">
-        <v>3.03</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="13">
@@ -714,28 +714,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C13">
-        <v>59.2</v>
+        <v>57.9</v>
       </c>
       <c r="D13">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>92.31</v>
+        <v>66.67</v>
       </c>
       <c r="H13">
-        <v>60.0</v>
+        <v>50.0</v>
       </c>
       <c r="I13">
-        <v>6.06</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="14">
@@ -743,28 +743,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="C14">
-        <v>56.73</v>
+        <v>56.87</v>
       </c>
       <c r="D14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E14">
         <v>2</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G14">
-        <v>53.85</v>
+        <v>75.0</v>
       </c>
       <c r="H14">
-        <v>40.0</v>
+        <v>33.33</v>
       </c>
       <c r="I14">
-        <v>18.18</v>
+        <v>20.59</v>
       </c>
     </row>
     <row r="15">
@@ -772,13 +772,13 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C15">
-        <v>56.45</v>
+        <v>56.33</v>
       </c>
       <c r="D15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -787,13 +787,13 @@
         <v>6</v>
       </c>
       <c r="G15">
-        <v>69.23</v>
+        <v>58.33</v>
       </c>
       <c r="H15">
-        <v>40.0</v>
+        <v>33.33</v>
       </c>
       <c r="I15">
-        <v>18.18</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="16">
@@ -801,28 +801,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C16">
-        <v>54.91</v>
+        <v>55.73</v>
       </c>
       <c r="D16">
         <v>6</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="G16">
-        <v>46.15</v>
+        <v>50.0</v>
       </c>
       <c r="H16">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="I16">
-        <v>9.09</v>
+        <v>73.53</v>
       </c>
     </row>
     <row r="17">
@@ -830,28 +830,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="C17">
-        <v>54.77</v>
+        <v>55.69</v>
       </c>
       <c r="D17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G17">
-        <v>61.54</v>
+        <v>58.33</v>
       </c>
       <c r="H17">
-        <v>40.0</v>
+        <v>16.67</v>
       </c>
       <c r="I17">
-        <v>6.06</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="18">
@@ -862,7 +862,7 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>54.46</v>
+        <v>55.25</v>
       </c>
       <c r="D18">
         <v>7</v>
@@ -871,16 +871,16 @@
         <v>1</v>
       </c>
       <c r="F18">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G18">
-        <v>53.85</v>
+        <v>58.33</v>
       </c>
       <c r="H18">
-        <v>20.0</v>
+        <v>16.67</v>
       </c>
       <c r="I18">
-        <v>36.36</v>
+        <v>38.24</v>
       </c>
     </row>
     <row r="19">
@@ -888,28 +888,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="C19">
-        <v>54.45</v>
+        <v>55.06</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19">
-        <v>46.15</v>
+        <v>66.67</v>
       </c>
       <c r="H19">
-        <v>40.0</v>
+        <v>33.33</v>
       </c>
       <c r="I19">
-        <v>6.06</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="20">
@@ -917,28 +917,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="C20">
-        <v>54.45</v>
+        <v>54.81</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G20">
-        <v>46.15</v>
+        <v>58.33</v>
       </c>
       <c r="H20">
-        <v>0.0</v>
+        <v>16.67</v>
       </c>
       <c r="I20">
-        <v>72.73</v>
+        <v>35.29</v>
       </c>
     </row>
     <row r="21">
@@ -946,28 +946,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C21">
-        <v>54.32</v>
+        <v>54.8</v>
       </c>
       <c r="D21">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E21">
         <v>2</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G21">
-        <v>61.54</v>
+        <v>50.0</v>
       </c>
       <c r="H21">
-        <v>40.0</v>
+        <v>33.33</v>
       </c>
       <c r="I21">
-        <v>3.03</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="22">
@@ -975,28 +975,28 @@
         <v>21</v>
       </c>
       <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>54.36</v>
+      </c>
+      <c r="D22">
         <v>6</v>
       </c>
-      <c r="C22">
-        <v>54.0</v>
-      </c>
-      <c r="D22">
-        <v>7</v>
-      </c>
       <c r="E22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G22">
-        <v>53.85</v>
+        <v>50.0</v>
       </c>
       <c r="H22">
-        <v>20.0</v>
+        <v>33.33</v>
       </c>
       <c r="I22">
-        <v>33.33</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="23">
@@ -1007,7 +1007,7 @@
         <v>48</v>
       </c>
       <c r="C23">
-        <v>52.64</v>
+        <v>54.17</v>
       </c>
       <c r="D23">
         <v>7</v>
@@ -1016,16 +1016,16 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G23">
-        <v>53.85</v>
+        <v>58.33</v>
       </c>
       <c r="H23">
         <v>0.0</v>
       </c>
       <c r="I23">
-        <v>57.58</v>
+        <v>58.82</v>
       </c>
     </row>
     <row r="24">
@@ -1033,28 +1033,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C24">
-        <v>51.9</v>
+        <v>53.68</v>
       </c>
       <c r="D24">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>69.23</v>
+        <v>58.33</v>
       </c>
       <c r="H24">
-        <v>20.0</v>
+        <v>33.33</v>
       </c>
       <c r="I24">
-        <v>21.21</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="25">
@@ -1062,28 +1062,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C25">
-        <v>51.73</v>
+        <v>53.1</v>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G25">
-        <v>46.15</v>
+        <v>66.67</v>
       </c>
       <c r="H25">
-        <v>20.0</v>
+        <v>16.67</v>
       </c>
       <c r="I25">
-        <v>21.21</v>
+        <v>23.53</v>
       </c>
     </row>
     <row r="26">
@@ -1091,28 +1091,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C26">
-        <v>51.52</v>
+        <v>52.25</v>
       </c>
       <c r="D26">
         <v>5</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>38.46</v>
+        <v>41.67</v>
       </c>
       <c r="H26">
-        <v>40.0</v>
+        <v>50.0</v>
       </c>
       <c r="I26">
-        <v>18.18</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
@@ -1120,28 +1120,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C27">
-        <v>51.06</v>
+        <v>51.82</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F27">
         <v>5</v>
       </c>
       <c r="G27">
-        <v>38.46</v>
+        <v>75.0</v>
       </c>
       <c r="H27">
-        <v>40.0</v>
+        <v>16.67</v>
       </c>
       <c r="I27">
-        <v>15.15</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="28">
@@ -1149,28 +1149,28 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C28">
-        <v>50.85</v>
+        <v>51.17</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F28">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G28">
-        <v>30.77</v>
+        <v>41.67</v>
       </c>
       <c r="H28">
-        <v>60.0</v>
+        <v>33.33</v>
       </c>
       <c r="I28">
-        <v>12.12</v>
+        <v>20.59</v>
       </c>
     </row>
     <row r="29">
@@ -1178,28 +1178,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C29">
-        <v>50.54</v>
+        <v>50.73</v>
       </c>
       <c r="D29">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G29">
-        <v>69.23</v>
+        <v>41.67</v>
       </c>
       <c r="H29">
-        <v>20.0</v>
+        <v>33.33</v>
       </c>
       <c r="I29">
-        <v>12.12</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="30">
@@ -1207,28 +1207,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="C30">
-        <v>50.15</v>
+        <v>50.45</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G30">
-        <v>38.46</v>
+        <v>66.67</v>
       </c>
       <c r="H30">
-        <v>20.0</v>
+        <v>16.67</v>
       </c>
       <c r="I30">
-        <v>42.42</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="31">
@@ -1236,13 +1236,13 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C31">
-        <v>49.32</v>
+        <v>49.96</v>
       </c>
       <c r="D31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -1251,13 +1251,13 @@
         <v>1</v>
       </c>
       <c r="G31">
-        <v>61.54</v>
+        <v>58.33</v>
       </c>
       <c r="H31">
-        <v>20.0</v>
+        <v>16.67</v>
       </c>
       <c r="I31">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="32">
@@ -1268,7 +1268,7 @@
         <v>45</v>
       </c>
       <c r="C32">
-        <v>49.24</v>
+        <v>49.65</v>
       </c>
       <c r="D32">
         <v>5</v>
@@ -1277,16 +1277,16 @@
         <v>1</v>
       </c>
       <c r="F32">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G32">
-        <v>38.46</v>
+        <v>41.67</v>
       </c>
       <c r="H32">
-        <v>20.0</v>
+        <v>16.67</v>
       </c>
       <c r="I32">
-        <v>36.36</v>
+        <v>38.24</v>
       </c>
     </row>
     <row r="33">
@@ -1294,28 +1294,28 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C33">
-        <v>49.0</v>
+        <v>49.51</v>
       </c>
       <c r="D33">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G33">
-        <v>53.85</v>
+        <v>33.33</v>
       </c>
       <c r="H33">
-        <v>20.0</v>
+        <v>50.0</v>
       </c>
       <c r="I33">
-        <v>0.0</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="34">
@@ -1323,28 +1323,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C34">
-        <v>48.79</v>
+        <v>48.57</v>
       </c>
       <c r="D34">
         <v>5</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G34">
-        <v>38.46</v>
+        <v>41.67</v>
       </c>
       <c r="H34">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="I34">
-        <v>0.0</v>
+        <v>58.82</v>
       </c>
     </row>
     <row r="35">
@@ -1352,28 +1352,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C35">
-        <v>47.42</v>
+        <v>48.52</v>
       </c>
       <c r="D35">
         <v>5</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F35">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="G35">
-        <v>38.46</v>
+        <v>41.67</v>
       </c>
       <c r="H35">
-        <v>0.0</v>
+        <v>33.33</v>
       </c>
       <c r="I35">
-        <v>57.58</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="36">
@@ -1381,28 +1381,28 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="C36">
-        <v>47.21</v>
+        <v>47.59</v>
       </c>
       <c r="D36">
         <v>4</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="G36">
-        <v>30.77</v>
+        <v>33.33</v>
       </c>
       <c r="H36">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="I36">
-        <v>21.21</v>
+        <v>85.29</v>
       </c>
     </row>
     <row r="37">
@@ -1410,28 +1410,28 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="C37">
-        <v>46.76</v>
+        <v>46.81</v>
       </c>
       <c r="D37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E37">
         <v>0</v>
       </c>
       <c r="F37">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G37">
-        <v>30.77</v>
+        <v>41.67</v>
       </c>
       <c r="H37">
         <v>0.0</v>
       </c>
       <c r="I37">
-        <v>84.85</v>
+        <v>47.06</v>
       </c>
     </row>
     <row r="38">
@@ -1439,10 +1439,10 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C38">
-        <v>45.61</v>
+        <v>46.37</v>
       </c>
       <c r="D38">
         <v>5</v>
@@ -1454,13 +1454,13 @@
         <v>15</v>
       </c>
       <c r="G38">
-        <v>38.46</v>
+        <v>41.67</v>
       </c>
       <c r="H38">
         <v>0.0</v>
       </c>
       <c r="I38">
-        <v>45.45</v>
+        <v>44.12</v>
       </c>
     </row>
     <row r="39">
@@ -1471,7 +1471,7 @@
         <v>5</v>
       </c>
       <c r="C39">
-        <v>45.15</v>
+        <v>45.68</v>
       </c>
       <c r="D39">
         <v>5</v>
@@ -1480,16 +1480,16 @@
         <v>1</v>
       </c>
       <c r="F39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G39">
-        <v>38.46</v>
+        <v>41.67</v>
       </c>
       <c r="H39">
-        <v>20.0</v>
+        <v>16.67</v>
       </c>
       <c r="I39">
-        <v>9.09</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="40">
@@ -1497,28 +1497,28 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C40">
-        <v>44.94</v>
+        <v>44.85</v>
       </c>
       <c r="D40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="G40">
-        <v>30.77</v>
+        <v>25.0</v>
       </c>
       <c r="H40">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="I40">
-        <v>6.06</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="41">
@@ -1526,28 +1526,28 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C41">
-        <v>44.27</v>
+        <v>44.45</v>
       </c>
       <c r="D41">
+        <v>4</v>
+      </c>
+      <c r="E41">
+        <v>2</v>
+      </c>
+      <c r="F41">
         <v>3</v>
       </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-      <c r="F41">
-        <v>33</v>
-      </c>
       <c r="G41">
-        <v>23.08</v>
+        <v>33.33</v>
       </c>
       <c r="H41">
-        <v>0.0</v>
+        <v>33.33</v>
       </c>
       <c r="I41">
-        <v>100.0</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="42">
@@ -1558,7 +1558,7 @@
         <v>17</v>
       </c>
       <c r="C42">
-        <v>44.03</v>
+        <v>44.26</v>
       </c>
       <c r="D42">
         <v>4</v>
@@ -1567,16 +1567,16 @@
         <v>1</v>
       </c>
       <c r="F42">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G42">
-        <v>30.77</v>
+        <v>33.33</v>
       </c>
       <c r="H42">
-        <v>20.0</v>
+        <v>16.67</v>
       </c>
       <c r="I42">
-        <v>33.33</v>
+        <v>35.29</v>
       </c>
     </row>
     <row r="43">
@@ -1584,28 +1584,28 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C43">
-        <v>43.36</v>
+        <v>43.13</v>
       </c>
       <c r="D43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E43">
         <v>2</v>
       </c>
       <c r="F43">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G43">
-        <v>23.08</v>
+        <v>33.33</v>
       </c>
       <c r="H43">
-        <v>40.0</v>
+        <v>33.33</v>
       </c>
       <c r="I43">
-        <v>27.27</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="44">
@@ -1616,7 +1616,7 @@
         <v>38</v>
       </c>
       <c r="C44">
-        <v>42.0</v>
+        <v>42.64</v>
       </c>
       <c r="D44">
         <v>3</v>
@@ -1625,16 +1625,16 @@
         <v>0</v>
       </c>
       <c r="F44">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G44">
-        <v>23.08</v>
+        <v>25.0</v>
       </c>
       <c r="H44">
         <v>0.0</v>
       </c>
       <c r="I44">
-        <v>84.85</v>
+        <v>85.29</v>
       </c>
     </row>
     <row r="45">
@@ -1642,28 +1642,28 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C45">
-        <v>41.76</v>
+        <v>42.59</v>
       </c>
       <c r="D45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G45">
-        <v>30.77</v>
+        <v>25.0</v>
       </c>
       <c r="H45">
-        <v>20.0</v>
+        <v>33.33</v>
       </c>
       <c r="I45">
-        <v>18.18</v>
+        <v>29.41</v>
       </c>
     </row>
     <row r="46">
@@ -1674,7 +1674,7 @@
         <v>21</v>
       </c>
       <c r="C46">
-        <v>41.3</v>
+        <v>41.61</v>
       </c>
       <c r="D46">
         <v>4</v>
@@ -1683,16 +1683,16 @@
         <v>1</v>
       </c>
       <c r="F46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G46">
-        <v>30.77</v>
+        <v>33.33</v>
       </c>
       <c r="H46">
-        <v>20.0</v>
+        <v>16.67</v>
       </c>
       <c r="I46">
-        <v>15.15</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="47">
@@ -1703,7 +1703,7 @@
         <v>41</v>
       </c>
       <c r="C47">
-        <v>41.3</v>
+        <v>41.61</v>
       </c>
       <c r="D47">
         <v>4</v>
@@ -1712,16 +1712,16 @@
         <v>1</v>
       </c>
       <c r="F47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G47">
-        <v>30.77</v>
+        <v>33.33</v>
       </c>
       <c r="H47">
-        <v>20.0</v>
+        <v>16.67</v>
       </c>
       <c r="I47">
-        <v>15.15</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="48">
@@ -1729,10 +1729,10 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C48">
-        <v>40.64</v>
+        <v>37.11</v>
       </c>
       <c r="D48">
         <v>3</v>
@@ -1741,16 +1741,16 @@
         <v>1</v>
       </c>
       <c r="F48">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G48">
-        <v>23.08</v>
+        <v>25.0</v>
       </c>
       <c r="H48">
-        <v>20.0</v>
+        <v>16.67</v>
       </c>
       <c r="I48">
-        <v>42.42</v>
+        <v>20.59</v>
       </c>
     </row>
     <row r="49">
@@ -1758,28 +1758,28 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C49">
-        <v>37.0</v>
+        <v>36.47</v>
       </c>
       <c r="D49">
         <v>3</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G49">
-        <v>23.08</v>
+        <v>25.0</v>
       </c>
       <c r="H49">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I49">
-        <v>18.18</v>
+        <v>44.12</v>
       </c>
     </row>
     <row r="50">
@@ -1790,7 +1790,7 @@
         <v>31</v>
       </c>
       <c r="C50">
-        <v>31.12</v>
+        <v>31.42</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -1799,16 +1799,16 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G50">
-        <v>7.69</v>
+        <v>8.33</v>
       </c>
       <c r="H50">
         <v>0.0</v>
       </c>
       <c r="I50">
-        <v>75.76</v>
+        <v>76.47</v>
       </c>
     </row>
   </sheetData>
@@ -1867,452 +1867,452 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E2">
+        <v>23</v>
+      </c>
+      <c r="F2">
         <v>26</v>
       </c>
-      <c r="F2">
-        <v>32</v>
-      </c>
       <c r="G2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I3">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D4">
         <v>14</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H4">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E5">
         <v>25</v>
       </c>
       <c r="F5">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G5">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H5">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I5">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>12</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G6">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H6">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D7">
         <v>12</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F7">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H7">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I7">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E8">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F8">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G8">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H8">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I8">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C9">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D9">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E9">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F9">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G9">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H9">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C10">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F10">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H10">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I10">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D11">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E11">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F11">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G11">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H11">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I11">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E12">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F12">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G12">
         <v>35</v>
       </c>
       <c r="H12">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I12">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E13">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F13">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G13">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H13">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I13">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C14">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E14">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F14">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G14">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H14">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I14">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D15">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E15">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F15">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G15">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H15">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I15">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C16">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D16">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -2321,345 +2321,345 @@
         <v>18</v>
       </c>
       <c r="G16">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H16">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I16">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C17">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D17">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E17">
+        <v>15</v>
+      </c>
+      <c r="F17">
+        <v>18</v>
+      </c>
+      <c r="G17">
         <v>19</v>
       </c>
-      <c r="F17">
-        <v>23</v>
-      </c>
-      <c r="G17">
-        <v>39</v>
-      </c>
       <c r="H17">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I17">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C18">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D18">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E18">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F18">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G18">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H18">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I18">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C19">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D19">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E19">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F19">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G19">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H19">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C20">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D20">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E20">
+        <v>23</v>
+      </c>
+      <c r="F20">
+        <v>24</v>
+      </c>
+      <c r="G20">
         <v>29</v>
       </c>
-      <c r="F20">
-        <v>33</v>
-      </c>
-      <c r="G20">
-        <v>34</v>
-      </c>
       <c r="H20">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I20">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D21">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E21">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F21">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G21">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H21">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I21">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E22">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F22">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G22">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H22">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I22">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E23">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F23">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G23">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H23">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I23">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C24">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E24">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F24">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G24">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H24">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I24">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C25">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D25">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E25">
         <v>25</v>
       </c>
       <c r="F25">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G25">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H25">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I25">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C26">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D26">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E26">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F26">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G26">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H26">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I26">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C27">
+        <v>8</v>
+      </c>
+      <c r="D27">
+        <v>9</v>
+      </c>
+      <c r="E27">
+        <v>16</v>
+      </c>
+      <c r="F27">
         <v>20</v>
-      </c>
-      <c r="D27">
-        <v>26</v>
-      </c>
-      <c r="E27">
-        <v>29</v>
-      </c>
-      <c r="F27">
-        <v>31</v>
       </c>
       <c r="G27">
         <v>37</v>
@@ -2668,751 +2668,751 @@
         <v>49</v>
       </c>
       <c r="I27">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C28">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D28">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E28">
         <v>29</v>
       </c>
       <c r="F28">
+        <v>31</v>
+      </c>
+      <c r="G28">
         <v>37</v>
       </c>
-      <c r="G28">
-        <v>47</v>
-      </c>
       <c r="H28">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I28">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C29">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D29">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E29">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F29">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G29">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="H29">
         <v>48</v>
       </c>
       <c r="I29">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C30">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D30">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E30">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F30">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G30">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H30">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I30">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C31">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D31">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E31">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F31">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G31">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H31">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I31">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D32">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E32">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F32">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G32">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H32">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I32">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D33">
+        <v>12</v>
+      </c>
+      <c r="E33">
         <v>18</v>
       </c>
-      <c r="E33">
-        <v>25</v>
-      </c>
       <c r="F33">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G33">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H33">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I33">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C34">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D34">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E34">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F34">
         <v>28</v>
       </c>
       <c r="G34">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H34">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I34">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C35">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D35">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E35">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F35">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G35">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H35">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I35">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D36">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E36">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F36">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G36">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H36">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I36">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C37">
+        <v>6</v>
+      </c>
+      <c r="D37">
+        <v>10</v>
+      </c>
+      <c r="E37">
+        <v>14</v>
+      </c>
+      <c r="F37">
+        <v>25</v>
+      </c>
+      <c r="G37">
+        <v>26</v>
+      </c>
+      <c r="H37">
+        <v>32</v>
+      </c>
+      <c r="I37">
         <v>7</v>
-      </c>
-      <c r="D37">
-        <v>14</v>
-      </c>
-      <c r="E37">
-        <v>16</v>
-      </c>
-      <c r="F37">
-        <v>37</v>
-      </c>
-      <c r="G37">
-        <v>39</v>
-      </c>
-      <c r="H37">
-        <v>47</v>
-      </c>
-      <c r="I37">
-        <v>34</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D38">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E38">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F38">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G38">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H38">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I38">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C39">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E39">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F39">
+        <v>19</v>
+      </c>
+      <c r="G39">
+        <v>20</v>
+      </c>
+      <c r="H39">
+        <v>40</v>
+      </c>
+      <c r="I39">
         <v>22</v>
-      </c>
-      <c r="G39">
-        <v>40</v>
-      </c>
-      <c r="H39">
-        <v>45</v>
-      </c>
-      <c r="I39">
-        <v>18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C40">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D40">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E40">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F40">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G40">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H40">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I40">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C41">
         <v>4</v>
       </c>
       <c r="D41">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E41">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F41">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G41">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H41">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I41">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E42">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F42">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G42">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H42">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I42">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C43">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D43">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E43">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F43">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G43">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H43">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I43">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C44">
         <v>5</v>
       </c>
       <c r="D44">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E44">
+        <v>13</v>
+      </c>
+      <c r="F44">
         <v>25</v>
       </c>
-      <c r="F44">
-        <v>40</v>
-      </c>
       <c r="G44">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H44">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I44">
-        <v>39</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D45">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E45">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F45">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G45">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H45">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I45">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C46">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D46">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E46">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F46">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G46">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H46">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I46">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C47">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D47">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E47">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F47">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G47">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H47">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I47">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C48">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D48">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E48">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F48">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G48">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H48">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I48">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C49">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D49">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E49">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F49">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G49">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H49">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I49">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C50">
         <v>5</v>
       </c>
       <c r="D50">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E50">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F50">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G50">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H50">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I50">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C51">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D51">
         <v>11</v>
       </c>
       <c r="E51">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F51">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="G51">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="H51">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="I51">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-08-28 第 115000083 期；威力彩 2026-08-27 第 115000069 期</t>
+          <t>大樂透 2026-08-28 第 115000083 期；威力彩 2026-08-31 第 115000070 期</t>
         </is>
       </c>
     </row>
@@ -112,7 +112,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -121,7 +121,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -143,7 +143,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9, 24, 29, 31, 35, 38</t>
+          <t>9, 19, 24, 29, 35, 38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3464,7 +3464,7 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>1.048</v>
+        <v>1.024</v>
       </c>
       <c r="D2">
         <v>31.0</v>
@@ -3486,7 +3486,7 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>1.048</v>
+        <v>1.024</v>
       </c>
       <c r="D3">
         <v>31.0</v>
@@ -3523,17 +3523,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>均衡分散</t>
+          <t>冷號觀察</t>
         </is>
       </c>
       <c r="B5">
         <v>42</v>
       </c>
       <c r="C5">
-        <v>0.952</v>
+        <v>1.0</v>
       </c>
       <c r="D5">
-        <v>21.4</v>
+        <v>31.0</v>
       </c>
       <c r="E5">
         <v>4.8</v>
@@ -3545,7 +3545,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>冷號觀察</t>
+          <t>均衡分散</t>
         </is>
       </c>
       <c r="B6">
@@ -3555,10 +3555,10 @@
         <v>0.952</v>
       </c>
       <c r="D6">
-        <v>28.6</v>
+        <v>21.4</v>
       </c>
       <c r="E6">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -3574,10 +3574,10 @@
         <v>42</v>
       </c>
       <c r="C7">
-        <v>0.667</v>
+        <v>0.643</v>
       </c>
       <c r="D7">
-        <v>11.9</v>
+        <v>9.5</v>
       </c>
       <c r="E7">
         <v>0.0</v>
@@ -3648,25 +3648,25 @@
         <v>29</v>
       </c>
       <c r="C2">
-        <v>74.04</v>
+        <v>74.2</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>92.86</v>
+        <v>85.71</v>
       </c>
       <c r="H2">
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>5.88</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="3">
@@ -3674,28 +3674,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C3">
-        <v>69.87</v>
+        <v>72.67</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E3">
         <v>5</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>92.86</v>
+        <v>78.57</v>
       </c>
       <c r="H3">
-        <v>83.33</v>
+        <v>100.0</v>
       </c>
       <c r="I3">
-        <v>5.88</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="4">
@@ -3706,25 +3706,25 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>68.26</v>
+        <v>72.62</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>71.43</v>
+        <v>64.29</v>
       </c>
       <c r="H4">
-        <v>83.33</v>
+        <v>100.0</v>
       </c>
       <c r="I4">
-        <v>0.0</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="5">
@@ -3735,7 +3735,7 @@
         <v>31</v>
       </c>
       <c r="C5">
-        <v>66.55</v>
+        <v>70.24</v>
       </c>
       <c r="D5">
         <v>11</v>
@@ -3744,16 +3744,16 @@
         <v>4</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G5">
         <v>78.57</v>
       </c>
       <c r="H5">
-        <v>66.67</v>
+        <v>80.0</v>
       </c>
       <c r="I5">
-        <v>14.71</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="6">
@@ -3761,13 +3761,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C6">
-        <v>65.42</v>
+        <v>69.44</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -3776,13 +3776,13 @@
         <v>3</v>
       </c>
       <c r="G6">
-        <v>71.43</v>
+        <v>92.86</v>
       </c>
       <c r="H6">
-        <v>66.67</v>
+        <v>80.0</v>
       </c>
       <c r="I6">
-        <v>8.82</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="7">
@@ -3793,7 +3793,7 @@
         <v>23</v>
       </c>
       <c r="C7">
-        <v>64.05</v>
+        <v>67.8</v>
       </c>
       <c r="D7">
         <v>8</v>
@@ -3802,16 +3802,16 @@
         <v>4</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7">
         <v>57.14</v>
       </c>
       <c r="H7">
-        <v>66.67</v>
+        <v>80.0</v>
       </c>
       <c r="I7">
-        <v>2.94</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="8">
@@ -3822,7 +3822,7 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>63.61</v>
+        <v>67.37</v>
       </c>
       <c r="D8">
         <v>8</v>
@@ -3831,16 +3831,16 @@
         <v>4</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8">
         <v>57.14</v>
       </c>
       <c r="H8">
-        <v>66.67</v>
+        <v>80.0</v>
       </c>
       <c r="I8">
-        <v>0.0</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="9">
@@ -3848,28 +3848,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>63.02</v>
+        <v>67.19</v>
       </c>
       <c r="D9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>71.43</v>
+        <v>64.29</v>
       </c>
       <c r="H9">
-        <v>50.0</v>
+        <v>80.0</v>
       </c>
       <c r="I9">
-        <v>20.59</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="10">
@@ -3877,28 +3877,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="C10">
-        <v>62.09</v>
+        <v>64.69</v>
       </c>
       <c r="D10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>57.14</v>
+        <v>42.86</v>
       </c>
       <c r="H10">
-        <v>50.0</v>
+        <v>100.0</v>
       </c>
       <c r="I10">
-        <v>17.65</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="11">
@@ -3909,7 +3909,7 @@
         <v>9</v>
       </c>
       <c r="C11">
-        <v>60.9</v>
+        <v>63.83</v>
       </c>
       <c r="D11">
         <v>14</v>
@@ -3918,16 +3918,16 @@
         <v>3</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11">
         <v>100.0</v>
       </c>
       <c r="H11">
-        <v>50.0</v>
+        <v>60.0</v>
       </c>
       <c r="I11">
-        <v>0.0</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="12">
@@ -3935,28 +3935,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C12">
-        <v>60.17</v>
+        <v>62.19</v>
       </c>
       <c r="D12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>71.43</v>
+        <v>64.29</v>
       </c>
       <c r="H12">
-        <v>33.33</v>
+        <v>60.0</v>
       </c>
       <c r="I12">
-        <v>29.41</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="13">
@@ -3964,28 +3964,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C13">
-        <v>60.17</v>
+        <v>62.14</v>
       </c>
       <c r="D13">
+        <v>10</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13">
         <v>11</v>
       </c>
-      <c r="E13">
-        <v>3</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
       <c r="G13">
-        <v>78.57</v>
+        <v>71.43</v>
       </c>
       <c r="H13">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="I13">
-        <v>0.0</v>
+        <v>31.43</v>
       </c>
     </row>
     <row r="14">
@@ -3993,28 +3993,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C14">
-        <v>60.09</v>
+        <v>61.1</v>
       </c>
       <c r="D14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G14">
-        <v>42.86</v>
+        <v>78.57</v>
       </c>
       <c r="H14">
-        <v>83.33</v>
+        <v>40.0</v>
       </c>
       <c r="I14">
-        <v>0.0</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="15">
@@ -4022,28 +4022,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C15">
-        <v>59.09</v>
+        <v>60.86</v>
       </c>
       <c r="D15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E15">
         <v>2</v>
       </c>
       <c r="F15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G15">
-        <v>78.57</v>
+        <v>71.43</v>
       </c>
       <c r="H15">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I15">
-        <v>20.59</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="16">
@@ -4051,10 +4051,10 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C16">
-        <v>58.8</v>
+        <v>60.8</v>
       </c>
       <c r="D16">
         <v>8</v>
@@ -4063,16 +4063,16 @@
         <v>2</v>
       </c>
       <c r="F16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G16">
         <v>57.14</v>
       </c>
       <c r="H16">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I16">
-        <v>23.53</v>
+        <v>25.71</v>
       </c>
     </row>
     <row r="17">
@@ -4080,28 +4080,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C17">
-        <v>58.8</v>
+        <v>60.0</v>
       </c>
       <c r="D17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
       <c r="F17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G17">
-        <v>57.14</v>
+        <v>71.43</v>
       </c>
       <c r="H17">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I17">
-        <v>23.53</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="18">
@@ -4109,28 +4109,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C18">
-        <v>57.97</v>
+        <v>59.94</v>
       </c>
       <c r="D18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G18">
-        <v>71.43</v>
+        <v>57.14</v>
       </c>
       <c r="H18">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I18">
-        <v>14.71</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="19">
@@ -4138,28 +4138,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C19">
-        <v>57.92</v>
+        <v>59.87</v>
       </c>
       <c r="D19">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G19">
-        <v>57.14</v>
+        <v>92.86</v>
       </c>
       <c r="H19">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I19">
-        <v>17.65</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="20">
@@ -4167,28 +4167,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C20">
-        <v>57.81</v>
+        <v>59.51</v>
       </c>
       <c r="D20">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G20">
-        <v>92.86</v>
+        <v>57.14</v>
       </c>
       <c r="H20">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I20">
-        <v>8.82</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="21">
@@ -4196,28 +4196,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C21">
-        <v>57.48</v>
+        <v>58.73</v>
       </c>
       <c r="D21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>57.14</v>
+        <v>50.0</v>
       </c>
       <c r="H21">
-        <v>33.33</v>
+        <v>60.0</v>
       </c>
       <c r="I21">
-        <v>14.71</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="22">
@@ -4225,28 +4225,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C22">
-        <v>57.04</v>
+        <v>58.1</v>
       </c>
       <c r="D22">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E22">
         <v>2</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G22">
-        <v>57.14</v>
+        <v>78.57</v>
       </c>
       <c r="H22">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I22">
-        <v>11.76</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="23">
@@ -4254,28 +4254,28 @@
         <v>22</v>
       </c>
       <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>57.8</v>
+      </c>
+      <c r="D23">
+        <v>8</v>
+      </c>
+      <c r="E23">
         <v>2</v>
       </c>
-      <c r="C23">
-        <v>55.8</v>
-      </c>
-      <c r="D23">
-        <v>7</v>
-      </c>
-      <c r="E23">
-        <v>3</v>
-      </c>
       <c r="F23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>50.0</v>
+        <v>57.14</v>
       </c>
       <c r="H23">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="I23">
-        <v>0.0</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="24">
@@ -4283,28 +4283,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C24">
-        <v>55.72</v>
+        <v>57.16</v>
       </c>
       <c r="D24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E24">
         <v>2</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G24">
-        <v>57.14</v>
+        <v>50.0</v>
       </c>
       <c r="H24">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I24">
-        <v>2.94</v>
+        <v>25.71</v>
       </c>
     </row>
     <row r="25">
@@ -4315,25 +4315,25 @@
         <v>14</v>
       </c>
       <c r="C25">
-        <v>55.13</v>
+        <v>56.04</v>
       </c>
       <c r="D25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G25">
-        <v>71.43</v>
+        <v>64.29</v>
       </c>
       <c r="H25">
-        <v>16.67</v>
+        <v>20.0</v>
       </c>
       <c r="I25">
-        <v>23.53</v>
+        <v>25.71</v>
       </c>
     </row>
     <row r="26">
@@ -4344,7 +4344,7 @@
         <v>15</v>
       </c>
       <c r="C26">
-        <v>54.69</v>
+        <v>55.86</v>
       </c>
       <c r="D26">
         <v>10</v>
@@ -4353,16 +4353,16 @@
         <v>1</v>
       </c>
       <c r="F26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G26">
         <v>71.43</v>
       </c>
       <c r="H26">
-        <v>16.67</v>
+        <v>20.0</v>
       </c>
       <c r="I26">
-        <v>20.59</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="27">
@@ -4370,28 +4370,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C27">
-        <v>54.26</v>
+        <v>55.11</v>
       </c>
       <c r="D27">
         <v>6</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F27">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="G27">
         <v>42.86</v>
       </c>
       <c r="H27">
-        <v>0.0</v>
+        <v>60.0</v>
       </c>
       <c r="I27">
-        <v>100.0</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="28">
@@ -4399,28 +4399,28 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C28">
-        <v>53.52</v>
+        <v>54.26</v>
       </c>
       <c r="D28">
         <v>6</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="G28">
         <v>42.86</v>
       </c>
       <c r="H28">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
       <c r="I28">
-        <v>11.76</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="29">
@@ -4428,28 +4428,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C29">
-        <v>52.2</v>
+        <v>51.4</v>
       </c>
       <c r="D29">
         <v>6</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G29">
         <v>42.86</v>
       </c>
       <c r="H29">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="I29">
-        <v>2.94</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="30">
@@ -4460,25 +4460,25 @@
         <v>1</v>
       </c>
       <c r="C30">
-        <v>48.47</v>
+        <v>46.5</v>
       </c>
       <c r="D30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30">
         <v>2</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30">
-        <v>42.86</v>
+        <v>35.71</v>
       </c>
       <c r="H30">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I30">
-        <v>5.88</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="31">
@@ -4489,25 +4489,25 @@
         <v>32</v>
       </c>
       <c r="C31">
-        <v>45.12</v>
+        <v>45.21</v>
       </c>
       <c r="D31">
         <v>5</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G31">
         <v>35.71</v>
       </c>
       <c r="H31">
-        <v>16.67</v>
+        <v>40.0</v>
       </c>
       <c r="I31">
-        <v>38.24</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="32">
@@ -4518,7 +4518,7 @@
         <v>5</v>
       </c>
       <c r="C32">
-        <v>40.7</v>
+        <v>41.93</v>
       </c>
       <c r="D32">
         <v>5</v>
@@ -4527,16 +4527,16 @@
         <v>1</v>
       </c>
       <c r="F32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G32">
         <v>35.71</v>
       </c>
       <c r="H32">
-        <v>16.67</v>
+        <v>20.0</v>
       </c>
       <c r="I32">
-        <v>8.82</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="33">
@@ -4547,7 +4547,7 @@
         <v>18</v>
       </c>
       <c r="C33">
-        <v>40.7</v>
+        <v>41.93</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -4556,16 +4556,16 @@
         <v>1</v>
       </c>
       <c r="F33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G33">
         <v>35.71</v>
       </c>
       <c r="H33">
-        <v>16.67</v>
+        <v>20.0</v>
       </c>
       <c r="I33">
-        <v>8.82</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="34">
@@ -4573,28 +4573,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C34">
-        <v>38.67</v>
+        <v>41.17</v>
       </c>
       <c r="D34">
         <v>4</v>
       </c>
       <c r="E34">
+        <v>2</v>
+      </c>
+      <c r="F34">
         <v>0</v>
-      </c>
-      <c r="F34">
-        <v>17</v>
       </c>
       <c r="G34">
         <v>28.57</v>
       </c>
       <c r="H34">
+        <v>40.0</v>
+      </c>
+      <c r="I34">
         <v>0.0</v>
-      </c>
-      <c r="I34">
-        <v>50.0</v>
       </c>
     </row>
     <row r="35">
@@ -4602,28 +4602,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C35">
-        <v>37.55</v>
+        <v>38.89</v>
       </c>
       <c r="D35">
         <v>4</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G35">
         <v>28.57</v>
       </c>
       <c r="H35">
-        <v>16.67</v>
+        <v>0.0</v>
       </c>
       <c r="I35">
-        <v>14.71</v>
+        <v>51.43</v>
       </c>
     </row>
     <row r="36">
@@ -4631,10 +4631,10 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C36">
-        <v>37.1</v>
+        <v>38.74</v>
       </c>
       <c r="D36">
         <v>4</v>
@@ -4643,16 +4643,16 @@
         <v>1</v>
       </c>
       <c r="F36">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G36">
         <v>28.57</v>
       </c>
       <c r="H36">
-        <v>16.67</v>
+        <v>20.0</v>
       </c>
       <c r="I36">
-        <v>11.76</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="37">
@@ -4660,28 +4660,28 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C37">
-        <v>36.15</v>
+        <v>38.31</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37">
         <v>1</v>
       </c>
       <c r="F37">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G37">
-        <v>21.43</v>
+        <v>28.57</v>
       </c>
       <c r="H37">
-        <v>16.67</v>
+        <v>20.0</v>
       </c>
       <c r="I37">
-        <v>32.35</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="38">
@@ -4692,7 +4692,7 @@
         <v>20</v>
       </c>
       <c r="C38">
-        <v>33.94</v>
+        <v>35.13</v>
       </c>
       <c r="D38">
         <v>3</v>
@@ -4701,16 +4701,16 @@
         <v>1</v>
       </c>
       <c r="F38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G38">
         <v>21.43</v>
       </c>
       <c r="H38">
-        <v>16.67</v>
+        <v>20.0</v>
       </c>
       <c r="I38">
-        <v>17.65</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="39">
@@ -4721,25 +4721,25 @@
         <v>37</v>
       </c>
       <c r="C39">
-        <v>33.43</v>
+        <v>32.13</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
       <c r="F39">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>14.29</v>
+        <v>21.43</v>
       </c>
       <c r="H39">
-        <v>16.67</v>
+        <v>20.0</v>
       </c>
       <c r="I39">
-        <v>41.18</v>
+        <v>0.0</v>
       </c>
     </row>
   </sheetData>
@@ -4798,46 +4798,46 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>8</v>
+      </c>
+      <c r="E2">
+        <v>12</v>
+      </c>
+      <c r="F2">
+        <v>19</v>
+      </c>
+      <c r="G2">
+        <v>32</v>
+      </c>
+      <c r="H2">
+        <v>37</v>
+      </c>
+      <c r="I2">
         <v>2</v>
-      </c>
-      <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>9</v>
-      </c>
-      <c r="F2">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>24</v>
-      </c>
-      <c r="H2">
-        <v>36</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>7</v>
@@ -4846,230 +4846,230 @@
         <v>9</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H3">
         <v>36</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>9</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>9</v>
+      </c>
+      <c r="F5">
         <v>11</v>
       </c>
-      <c r="E5">
-        <v>18</v>
-      </c>
-      <c r="F5">
-        <v>19</v>
-      </c>
       <c r="G5">
+        <v>29</v>
+      </c>
+      <c r="H5">
         <v>35</v>
       </c>
-      <c r="H5">
-        <v>38</v>
-      </c>
       <c r="I5">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H6">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C7">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H7">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G8">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H8">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>7</v>
+      </c>
+      <c r="E9">
+        <v>8</v>
+      </c>
+      <c r="F9">
+        <v>20</v>
+      </c>
+      <c r="G9">
+        <v>26</v>
+      </c>
+      <c r="H9">
+        <v>33</v>
+      </c>
+      <c r="I9">
         <v>4</v>
-      </c>
-      <c r="D9">
-        <v>15</v>
-      </c>
-      <c r="E9">
-        <v>22</v>
-      </c>
-      <c r="F9">
-        <v>26</v>
-      </c>
-      <c r="G9">
-        <v>34</v>
-      </c>
-      <c r="H9">
-        <v>36</v>
-      </c>
-      <c r="I9">
-        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F10">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G10">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H10">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I10">
         <v>7</v>
@@ -5077,30 +5077,30 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C11">
+        <v>8</v>
+      </c>
+      <c r="D11">
+        <v>14</v>
+      </c>
+      <c r="E11">
+        <v>17</v>
+      </c>
+      <c r="F11">
         <v>19</v>
       </c>
-      <c r="D11">
-        <v>22</v>
-      </c>
-      <c r="E11">
-        <v>28</v>
-      </c>
-      <c r="F11">
-        <v>31</v>
-      </c>
       <c r="G11">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H11">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I11">
         <v>7</v>
@@ -5108,30 +5108,30 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C12">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D12">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E12">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F12">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G12">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H12">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I12">
         <v>7</v>
@@ -5139,24 +5139,24 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D13">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E13">
         <v>13</v>
       </c>
       <c r="F13">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G13">
         <v>29</v>
@@ -5165,97 +5165,97 @@
         <v>31</v>
       </c>
       <c r="I13">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C14">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D14">
+        <v>12</v>
+      </c>
+      <c r="E14">
+        <v>13</v>
+      </c>
+      <c r="F14">
         <v>23</v>
       </c>
-      <c r="E14">
-        <v>25</v>
-      </c>
-      <c r="F14">
+      <c r="G14">
         <v>29</v>
       </c>
-      <c r="G14">
-        <v>34</v>
-      </c>
       <c r="H14">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I14">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C15">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D15">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E15">
+        <v>25</v>
+      </c>
+      <c r="F15">
         <v>29</v>
       </c>
-      <c r="F15">
-        <v>32</v>
-      </c>
       <c r="G15">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H15">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I15">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E16">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F16">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G16">
         <v>35</v>
       </c>
       <c r="H16">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I16">
         <v>6</v>
@@ -5263,402 +5263,402 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D17">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E17">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F17">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G17">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H17">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F18">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G18">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H18">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I18">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E19">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F19">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G19">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H19">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I19">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C20">
+        <v>5</v>
+      </c>
+      <c r="D20">
         <v>6</v>
       </c>
-      <c r="D20">
-        <v>10</v>
-      </c>
       <c r="E20">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F20">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G20">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H20">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C21">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D21">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E21">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F21">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G21">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H21">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I21">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D22">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E22">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F22">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G22">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H22">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I22">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23">
+        <v>8</v>
+      </c>
+      <c r="E23">
+        <v>9</v>
+      </c>
+      <c r="F23">
+        <v>15</v>
+      </c>
+      <c r="G23">
+        <v>18</v>
+      </c>
+      <c r="H23">
+        <v>23</v>
+      </c>
+      <c r="I23">
         <v>4</v>
-      </c>
-      <c r="D23">
-        <v>17</v>
-      </c>
-      <c r="E23">
-        <v>19</v>
-      </c>
-      <c r="F23">
-        <v>25</v>
-      </c>
-      <c r="G23">
-        <v>28</v>
-      </c>
-      <c r="H23">
-        <v>29</v>
-      </c>
-      <c r="I23">
-        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C24">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D24">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E24">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G24">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H24">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I24">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D25">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E25">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F25">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G25">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H25">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I25">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C26">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D26">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E26">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F26">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G26">
         <v>28</v>
       </c>
       <c r="H26">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I26">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C27">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D27">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E27">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F27">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G27">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H27">
         <v>35</v>
       </c>
       <c r="I27">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E28">
+        <v>9</v>
+      </c>
+      <c r="F28">
+        <v>15</v>
+      </c>
+      <c r="G28">
         <v>24</v>
       </c>
-      <c r="F28">
-        <v>31</v>
-      </c>
-      <c r="G28">
-        <v>34</v>
-      </c>
       <c r="H28">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I28">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C29">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D29">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E29">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F29">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G29">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H29">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I29">
         <v>3</v>
@@ -5666,554 +5666,554 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C30">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D30">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E30">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F30">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G30">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H30">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C31">
         <v>6</v>
       </c>
       <c r="D31">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E31">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F31">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G31">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H31">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I31">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C32">
         <v>6</v>
       </c>
       <c r="D32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E32">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F32">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G32">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H32">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I32">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C33">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D33">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E33">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F33">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G33">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H33">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I33">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C34">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D34">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E34">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F34">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G34">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H34">
         <v>38</v>
       </c>
       <c r="I34">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C35">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D35">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E35">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F35">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G35">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H35">
         <v>38</v>
       </c>
       <c r="I35">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E36">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F36">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G36">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H36">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I36">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C37">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D37">
+        <v>4</v>
+      </c>
+      <c r="E37">
+        <v>13</v>
+      </c>
+      <c r="F37">
+        <v>19</v>
+      </c>
+      <c r="G37">
+        <v>27</v>
+      </c>
+      <c r="H37">
+        <v>30</v>
+      </c>
+      <c r="I37">
         <v>8</v>
-      </c>
-      <c r="E37">
-        <v>27</v>
-      </c>
-      <c r="F37">
-        <v>33</v>
-      </c>
-      <c r="G37">
-        <v>35</v>
-      </c>
-      <c r="H37">
-        <v>38</v>
-      </c>
-      <c r="I37">
-        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D38">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E38">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F38">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G38">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H38">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I38">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C39">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D39">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E39">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F39">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G39">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H39">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I39">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C40">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D40">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E40">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F40">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G40">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H40">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I40">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000030</v>
+        <v>115000031</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D41">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E41">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F41">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G41">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H41">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="I41">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000029</v>
+        <v>115000030</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E42">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F42">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G42">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H42">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I42">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000028</v>
+        <v>115000029</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E43">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F43">
         <v>27</v>
       </c>
       <c r="G43">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H43">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I43">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000027</v>
+        <v>115000028</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C44">
         <v>5</v>
       </c>
       <c r="D44">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E44">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F44">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G44">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H44">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I44">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000026</v>
+        <v>115000027</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C45">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D45">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E45">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F45">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G45">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H45">
         <v>34</v>
       </c>
       <c r="I45">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000025</v>
+        <v>115000026</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C46">
+        <v>2</v>
+      </c>
+      <c r="D46">
         <v>13</v>
       </c>
-      <c r="D46">
-        <v>14</v>
-      </c>
       <c r="E46">
+        <v>21</v>
+      </c>
+      <c r="F46">
         <v>22</v>
       </c>
-      <c r="F46">
-        <v>28</v>
-      </c>
       <c r="G46">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H46">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I46">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000024</v>
+        <v>115000025</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D47">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E47">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F47">
         <v>28</v>
       </c>
       <c r="G47">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H47">
         <v>38</v>
@@ -6224,58 +6224,58 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000023</v>
+        <v>115000024</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48">
         <v>9</v>
       </c>
-      <c r="D48">
-        <v>13</v>
-      </c>
       <c r="E48">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F48">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G48">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H48">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I48">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000022</v>
+        <v>115000023</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C49">
+        <v>9</v>
+      </c>
+      <c r="D49">
+        <v>13</v>
+      </c>
+      <c r="E49">
         <v>14</v>
       </c>
-      <c r="D49">
-        <v>26</v>
-      </c>
-      <c r="E49">
-        <v>28</v>
-      </c>
       <c r="F49">
+        <v>18</v>
+      </c>
+      <c r="G49">
         <v>31</v>
-      </c>
-      <c r="G49">
-        <v>32</v>
       </c>
       <c r="H49">
         <v>34</v>
@@ -6286,61 +6286,61 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000021</v>
+        <v>115000022</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C50">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D50">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E50">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F50">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G50">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H50">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I50">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000020</v>
+        <v>115000021</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D51">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E51">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F51">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G51">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H51">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I51">
         <v>8</v>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-08-28 第 115000083 期；威力彩 2026-08-31 第 115000070 期</t>
+          <t>大樂透 2026-09-01 第 115000084 期；威力彩 2026-08-31 第 115000070 期</t>
         </is>
       </c>
     </row>
@@ -47,7 +47,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>115000083</v>
+        <v>115000084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -56,7 +56,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -96,7 +96,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.262 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.357 碼/期</t>
         </is>
       </c>
     </row>
@@ -214,16 +214,16 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>0.929</v>
+        <v>1.0</v>
       </c>
       <c r="D2">
-        <v>26.2</v>
+        <v>28.6</v>
       </c>
       <c r="E2">
-        <v>0.0</v>
+        <v>2.4</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -236,16 +236,16 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>0.905</v>
+        <v>0.976</v>
       </c>
       <c r="D3">
-        <v>23.8</v>
+        <v>26.2</v>
       </c>
       <c r="E3">
-        <v>0.0</v>
+        <v>2.4</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -258,7 +258,7 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>0.738</v>
+        <v>0.762</v>
       </c>
       <c r="D4">
         <v>16.7</v>
@@ -280,7 +280,7 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>0.714</v>
+        <v>0.738</v>
       </c>
       <c r="D5">
         <v>16.7</v>
@@ -302,10 +302,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.667</v>
+        <v>0.643</v>
       </c>
       <c r="D6">
-        <v>11.9</v>
+        <v>9.5</v>
       </c>
       <c r="E6">
         <v>0.0</v>
@@ -398,19 +398,19 @@
         <v>26</v>
       </c>
       <c r="C2">
-        <v>70.55</v>
+        <v>70.6</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>91.67</v>
+        <v>100.0</v>
       </c>
       <c r="H2">
         <v>100.0</v>
@@ -427,7 +427,7 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>66.87</v>
+        <v>64.31</v>
       </c>
       <c r="D3">
         <v>12</v>
@@ -436,16 +436,16 @@
         <v>5</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
         <v>100.0</v>
       </c>
       <c r="H3">
-        <v>83.33</v>
+        <v>71.43</v>
       </c>
       <c r="I3">
-        <v>2.94</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="4">
@@ -453,28 +453,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C4">
-        <v>65.1</v>
+        <v>61.5</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E4">
         <v>4</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G4">
-        <v>58.33</v>
+        <v>83.33</v>
       </c>
       <c r="H4">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="I4">
-        <v>20.59</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="5">
@@ -482,28 +482,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C5">
-        <v>63.49</v>
+        <v>61.13</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>83.33</v>
+        <v>50.0</v>
       </c>
       <c r="H5">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="I5">
-        <v>8.82</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="6">
@@ -511,28 +511,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>63.13</v>
+        <v>60.97</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E6">
         <v>4</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>50.0</v>
+        <v>66.67</v>
       </c>
       <c r="H6">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="I6">
-        <v>11.76</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="7">
@@ -540,13 +540,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C7">
-        <v>62.95</v>
+        <v>60.49</v>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -555,13 +555,13 @@
         <v>2</v>
       </c>
       <c r="G7">
-        <v>66.67</v>
+        <v>58.33</v>
       </c>
       <c r="H7">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="I7">
-        <v>5.88</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="8">
@@ -569,28 +569,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C8">
-        <v>62.46</v>
+        <v>59.84</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8">
         <v>4</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>58.33</v>
+        <v>50.0</v>
       </c>
       <c r="H8">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="I8">
-        <v>2.94</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="9">
@@ -598,28 +598,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C9">
-        <v>61.81</v>
+        <v>59.49</v>
       </c>
       <c r="D9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G9">
-        <v>50.0</v>
+        <v>58.33</v>
       </c>
       <c r="H9">
-        <v>66.67</v>
+        <v>42.86</v>
       </c>
       <c r="I9">
-        <v>2.94</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="10">
@@ -627,13 +627,13 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C10">
-        <v>59.42</v>
+        <v>57.35</v>
       </c>
       <c r="D10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -642,13 +642,13 @@
         <v>3</v>
       </c>
       <c r="G10">
-        <v>100.0</v>
+        <v>58.33</v>
       </c>
       <c r="H10">
-        <v>50.0</v>
+        <v>42.86</v>
       </c>
       <c r="I10">
-        <v>8.82</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="11">
@@ -656,28 +656,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C11">
-        <v>58.73</v>
+        <v>56.55</v>
       </c>
       <c r="D11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>58.33</v>
+        <v>66.67</v>
       </c>
       <c r="H11">
-        <v>50.0</v>
+        <v>42.86</v>
       </c>
       <c r="I11">
-        <v>5.88</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="12">
@@ -685,10 +685,10 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C12">
-        <v>57.9</v>
+        <v>56.55</v>
       </c>
       <c r="D12">
         <v>8</v>
@@ -697,16 +697,16 @@
         <v>3</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12">
         <v>66.67</v>
       </c>
       <c r="H12">
-        <v>50.0</v>
+        <v>42.86</v>
       </c>
       <c r="I12">
-        <v>0.0</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="13">
@@ -714,13 +714,13 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C13">
-        <v>57.9</v>
+        <v>56.31</v>
       </c>
       <c r="D13">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -729,10 +729,10 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>66.67</v>
+        <v>100.0</v>
       </c>
       <c r="H13">
-        <v>50.0</v>
+        <v>42.86</v>
       </c>
       <c r="I13">
         <v>0.0</v>
@@ -743,28 +743,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C14">
-        <v>56.87</v>
+        <v>56.12</v>
       </c>
       <c r="D14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>75.0</v>
+        <v>66.67</v>
       </c>
       <c r="H14">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="I14">
-        <v>20.59</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="15">
@@ -772,28 +772,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C15">
-        <v>56.33</v>
+        <v>54.49</v>
       </c>
       <c r="D15">
         <v>7</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G15">
         <v>58.33</v>
       </c>
       <c r="H15">
-        <v>33.33</v>
+        <v>14.29</v>
       </c>
       <c r="I15">
-        <v>17.65</v>
+        <v>37.14</v>
       </c>
     </row>
     <row r="16">
@@ -801,28 +801,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C16">
-        <v>55.73</v>
+        <v>54.21</v>
       </c>
       <c r="D16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G16">
-        <v>50.0</v>
+        <v>58.33</v>
       </c>
       <c r="H16">
-        <v>0.0</v>
+        <v>28.57</v>
       </c>
       <c r="I16">
-        <v>73.53</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="17">
@@ -830,28 +830,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C17">
-        <v>55.69</v>
+        <v>53.99</v>
       </c>
       <c r="D17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G17">
-        <v>58.33</v>
+        <v>50.0</v>
       </c>
       <c r="H17">
-        <v>16.67</v>
+        <v>28.57</v>
       </c>
       <c r="I17">
-        <v>41.18</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="18">
@@ -859,28 +859,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>55.25</v>
+        <v>53.56</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G18">
-        <v>58.33</v>
+        <v>50.0</v>
       </c>
       <c r="H18">
-        <v>16.67</v>
+        <v>28.57</v>
       </c>
       <c r="I18">
-        <v>38.24</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="19">
@@ -888,28 +888,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="C19">
-        <v>55.06</v>
+        <v>52.92</v>
       </c>
       <c r="D19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G19">
-        <v>66.67</v>
+        <v>58.33</v>
       </c>
       <c r="H19">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="I19">
-        <v>8.82</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="20">
@@ -917,10 +917,10 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C20">
-        <v>54.81</v>
+        <v>52.78</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -929,16 +929,16 @@
         <v>1</v>
       </c>
       <c r="F20">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G20">
         <v>58.33</v>
       </c>
       <c r="H20">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="I20">
-        <v>35.29</v>
+        <v>25.71</v>
       </c>
     </row>
     <row r="21">
@@ -946,28 +946,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C21">
-        <v>54.8</v>
+        <v>52.64</v>
       </c>
       <c r="D21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E21">
         <v>2</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>50.0</v>
+        <v>83.33</v>
       </c>
       <c r="H21">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="I21">
-        <v>11.76</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="22">
@@ -975,28 +975,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C22">
-        <v>54.36</v>
+        <v>52.54</v>
       </c>
       <c r="D22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E22">
         <v>2</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>50.0</v>
+        <v>66.67</v>
       </c>
       <c r="H22">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="I22">
-        <v>8.82</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="23">
@@ -1004,28 +1004,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="C23">
-        <v>54.17</v>
+        <v>52.45</v>
       </c>
       <c r="D23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G23">
-        <v>58.33</v>
+        <v>75.0</v>
       </c>
       <c r="H23">
-        <v>0.0</v>
+        <v>14.29</v>
       </c>
       <c r="I23">
-        <v>58.82</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="24">
@@ -1033,28 +1033,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C24">
-        <v>53.68</v>
+        <v>51.78</v>
       </c>
       <c r="D24">
         <v>7</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G24">
         <v>58.33</v>
       </c>
       <c r="H24">
-        <v>33.33</v>
+        <v>0.0</v>
       </c>
       <c r="I24">
-        <v>0.0</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="25">
@@ -1062,28 +1062,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="C25">
-        <v>53.1</v>
+        <v>50.89</v>
       </c>
       <c r="D25">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="G25">
-        <v>66.67</v>
+        <v>41.67</v>
       </c>
       <c r="H25">
-        <v>16.67</v>
+        <v>0.0</v>
       </c>
       <c r="I25">
-        <v>23.53</v>
+        <v>74.29</v>
       </c>
     </row>
     <row r="26">
@@ -1094,7 +1094,7 @@
         <v>44</v>
       </c>
       <c r="C26">
-        <v>52.25</v>
+        <v>50.89</v>
       </c>
       <c r="D26">
         <v>5</v>
@@ -1103,16 +1103,16 @@
         <v>3</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26">
         <v>41.67</v>
       </c>
       <c r="H26">
-        <v>50.0</v>
+        <v>42.86</v>
       </c>
       <c r="I26">
-        <v>0.0</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="27">
@@ -1120,28 +1120,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="C27">
-        <v>51.82</v>
+        <v>50.21</v>
       </c>
       <c r="D27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G27">
-        <v>75.0</v>
+        <v>58.33</v>
       </c>
       <c r="H27">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="I27">
-        <v>14.71</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="28">
@@ -1149,10 +1149,10 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="C28">
-        <v>51.17</v>
+        <v>49.89</v>
       </c>
       <c r="D28">
         <v>5</v>
@@ -1167,10 +1167,10 @@
         <v>41.67</v>
       </c>
       <c r="H28">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="I28">
-        <v>20.59</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="29">
@@ -1178,28 +1178,28 @@
         <v>28</v>
       </c>
       <c r="B29">
+        <v>40</v>
+      </c>
+      <c r="C29">
+        <v>49.78</v>
+      </c>
+      <c r="D29">
+        <v>7</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
         <v>2</v>
       </c>
-      <c r="C29">
-        <v>50.73</v>
-      </c>
-      <c r="D29">
-        <v>5</v>
-      </c>
-      <c r="E29">
-        <v>2</v>
-      </c>
-      <c r="F29">
-        <v>6</v>
-      </c>
       <c r="G29">
-        <v>41.67</v>
+        <v>58.33</v>
       </c>
       <c r="H29">
-        <v>33.33</v>
+        <v>14.29</v>
       </c>
       <c r="I29">
-        <v>17.65</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="30">
@@ -1207,28 +1207,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C30">
-        <v>50.45</v>
+        <v>49.32</v>
       </c>
       <c r="D30">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G30">
-        <v>66.67</v>
+        <v>41.67</v>
       </c>
       <c r="H30">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="I30">
-        <v>5.88</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="31">
@@ -1236,28 +1236,28 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C31">
-        <v>49.96</v>
+        <v>48.97</v>
       </c>
       <c r="D31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31">
-        <v>58.33</v>
+        <v>66.67</v>
       </c>
       <c r="H31">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="I31">
-        <v>2.94</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="32">
@@ -1265,28 +1265,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C32">
-        <v>49.65</v>
+        <v>48.75</v>
       </c>
       <c r="D32">
         <v>5</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G32">
         <v>41.67</v>
       </c>
       <c r="H32">
-        <v>16.67</v>
+        <v>0.0</v>
       </c>
       <c r="I32">
-        <v>38.24</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="33">
@@ -1297,7 +1297,7 @@
         <v>46</v>
       </c>
       <c r="C33">
-        <v>49.51</v>
+        <v>48.09</v>
       </c>
       <c r="D33">
         <v>4</v>
@@ -1306,16 +1306,16 @@
         <v>3</v>
       </c>
       <c r="F33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G33">
         <v>33.33</v>
       </c>
       <c r="H33">
-        <v>50.0</v>
+        <v>42.86</v>
       </c>
       <c r="I33">
-        <v>14.71</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="34">
@@ -1323,28 +1323,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C34">
-        <v>48.57</v>
+        <v>47.75</v>
       </c>
       <c r="D34">
         <v>5</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F34">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G34">
         <v>41.67</v>
       </c>
       <c r="H34">
-        <v>0.0</v>
+        <v>28.57</v>
       </c>
       <c r="I34">
-        <v>58.82</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="35">
@@ -1352,28 +1352,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C35">
-        <v>48.52</v>
+        <v>47.66</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G35">
-        <v>41.67</v>
+        <v>33.33</v>
       </c>
       <c r="H35">
-        <v>33.33</v>
+        <v>0.0</v>
       </c>
       <c r="I35">
-        <v>2.94</v>
+        <v>85.71</v>
       </c>
     </row>
     <row r="36">
@@ -1381,28 +1381,28 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="C36">
-        <v>47.59</v>
+        <v>47.04</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E36">
         <v>0</v>
       </c>
       <c r="F36">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G36">
-        <v>33.33</v>
+        <v>41.67</v>
       </c>
       <c r="H36">
         <v>0.0</v>
       </c>
       <c r="I36">
-        <v>85.29</v>
+        <v>48.57</v>
       </c>
     </row>
     <row r="37">
@@ -1410,28 +1410,28 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C37">
-        <v>46.81</v>
+        <v>46.75</v>
       </c>
       <c r="D37">
         <v>5</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G37">
         <v>41.67</v>
       </c>
       <c r="H37">
-        <v>0.0</v>
+        <v>14.29</v>
       </c>
       <c r="I37">
-        <v>47.06</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="38">
@@ -1442,7 +1442,7 @@
         <v>13</v>
       </c>
       <c r="C38">
-        <v>46.37</v>
+        <v>46.61</v>
       </c>
       <c r="D38">
         <v>5</v>
@@ -1451,7 +1451,7 @@
         <v>0</v>
       </c>
       <c r="F38">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G38">
         <v>41.67</v>
@@ -1460,7 +1460,7 @@
         <v>0.0</v>
       </c>
       <c r="I38">
-        <v>44.12</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="39">
@@ -1468,28 +1468,28 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C39">
-        <v>45.68</v>
+        <v>44.85</v>
       </c>
       <c r="D39">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="G39">
-        <v>41.67</v>
+        <v>25.0</v>
       </c>
       <c r="H39">
-        <v>16.67</v>
+        <v>0.0</v>
       </c>
       <c r="I39">
-        <v>11.76</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="40">
@@ -1497,28 +1497,28 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C40">
-        <v>44.85</v>
+        <v>43.94</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="G40">
-        <v>25.0</v>
+        <v>33.33</v>
       </c>
       <c r="H40">
-        <v>0.0</v>
+        <v>14.29</v>
       </c>
       <c r="I40">
-        <v>100.0</v>
+        <v>37.14</v>
       </c>
     </row>
     <row r="41">
@@ -1529,7 +1529,7 @@
         <v>27</v>
       </c>
       <c r="C41">
-        <v>44.45</v>
+        <v>43.66</v>
       </c>
       <c r="D41">
         <v>4</v>
@@ -1538,16 +1538,16 @@
         <v>2</v>
       </c>
       <c r="F41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G41">
         <v>33.33</v>
       </c>
       <c r="H41">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="I41">
-        <v>8.82</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="42">
@@ -1555,28 +1555,28 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C42">
-        <v>44.26</v>
+        <v>42.71</v>
       </c>
       <c r="D42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="G42">
-        <v>33.33</v>
+        <v>25.0</v>
       </c>
       <c r="H42">
-        <v>16.67</v>
+        <v>0.0</v>
       </c>
       <c r="I42">
-        <v>35.29</v>
+        <v>85.71</v>
       </c>
     </row>
     <row r="43">
@@ -1587,7 +1587,7 @@
         <v>9</v>
       </c>
       <c r="C43">
-        <v>43.13</v>
+        <v>42.37</v>
       </c>
       <c r="D43">
         <v>4</v>
@@ -1596,16 +1596,16 @@
         <v>2</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43">
         <v>33.33</v>
       </c>
       <c r="H43">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="I43">
-        <v>0.0</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="44">
@@ -1613,28 +1613,28 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C44">
-        <v>42.64</v>
+        <v>41.37</v>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="G44">
-        <v>25.0</v>
+        <v>33.33</v>
       </c>
       <c r="H44">
-        <v>0.0</v>
+        <v>14.29</v>
       </c>
       <c r="I44">
-        <v>85.29</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="45">
@@ -1642,28 +1642,28 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="C45">
-        <v>42.59</v>
+        <v>41.37</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G45">
-        <v>25.0</v>
+        <v>33.33</v>
       </c>
       <c r="H45">
-        <v>33.33</v>
+        <v>14.29</v>
       </c>
       <c r="I45">
-        <v>29.41</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="46">
@@ -1671,10 +1671,10 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C46">
-        <v>41.61</v>
+        <v>40.52</v>
       </c>
       <c r="D46">
         <v>4</v>
@@ -1683,16 +1683,16 @@
         <v>1</v>
       </c>
       <c r="F46">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G46">
         <v>33.33</v>
       </c>
       <c r="H46">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="I46">
-        <v>17.65</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="47">
@@ -1700,28 +1700,28 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="C47">
-        <v>41.61</v>
+        <v>38.14</v>
       </c>
       <c r="D47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E47">
         <v>1</v>
       </c>
       <c r="F47">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G47">
-        <v>33.33</v>
+        <v>25.0</v>
       </c>
       <c r="H47">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="I47">
-        <v>17.65</v>
+        <v>31.43</v>
       </c>
     </row>
     <row r="48">
@@ -1732,7 +1732,7 @@
         <v>30</v>
       </c>
       <c r="C48">
-        <v>37.11</v>
+        <v>36.85</v>
       </c>
       <c r="D48">
         <v>3</v>
@@ -1741,16 +1741,16 @@
         <v>1</v>
       </c>
       <c r="F48">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G48">
         <v>25.0</v>
       </c>
       <c r="H48">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="I48">
-        <v>20.59</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="49">
@@ -1761,7 +1761,7 @@
         <v>42</v>
       </c>
       <c r="C49">
-        <v>36.47</v>
+        <v>36.71</v>
       </c>
       <c r="D49">
         <v>3</v>
@@ -1770,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="F49">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G49">
         <v>25.0</v>
@@ -1779,7 +1779,7 @@
         <v>0.0</v>
       </c>
       <c r="I49">
-        <v>44.12</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="50">
@@ -1790,7 +1790,7 @@
         <v>31</v>
       </c>
       <c r="C50">
-        <v>31.42</v>
+        <v>31.52</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G50">
         <v>8.33</v>
@@ -1808,7 +1808,7 @@
         <v>0.0</v>
       </c>
       <c r="I50">
-        <v>76.47</v>
+        <v>77.14</v>
       </c>
     </row>
   </sheetData>
@@ -1867,483 +1867,483 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000083</v>
+        <v>115000084</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>26</v>
       </c>
       <c r="G2">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H2">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E3">
+        <v>23</v>
+      </c>
+      <c r="F3">
         <v>26</v>
       </c>
-      <c r="F3">
-        <v>32</v>
-      </c>
       <c r="G3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H4">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I4">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <v>14</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F5">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H5">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E6">
         <v>25</v>
       </c>
       <c r="F6">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H6">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I6">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>12</v>
       </c>
       <c r="E7">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F7">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G7">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H7">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D8">
         <v>12</v>
       </c>
       <c r="E8">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F8">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G8">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H8">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I8">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E9">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F9">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G9">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H9">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I9">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C10">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D10">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E10">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F10">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G10">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H10">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I10">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C11">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D11">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F11">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G11">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H11">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I11">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D12">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E12">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F12">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G12">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H12">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I12">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E13">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F13">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G13">
         <v>35</v>
       </c>
       <c r="H13">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I13">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F14">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G14">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H14">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I14">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C15">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E15">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F15">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G15">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H15">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I15">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E16">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F16">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G16">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H16">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I16">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C17">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D17">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E17">
         <v>15</v>
@@ -2352,345 +2352,345 @@
         <v>18</v>
       </c>
       <c r="G17">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H17">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I17">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C18">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D18">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E18">
+        <v>15</v>
+      </c>
+      <c r="F18">
+        <v>18</v>
+      </c>
+      <c r="G18">
         <v>19</v>
       </c>
-      <c r="F18">
-        <v>23</v>
-      </c>
-      <c r="G18">
-        <v>39</v>
-      </c>
       <c r="H18">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I18">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C19">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D19">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E19">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F19">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G19">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H19">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I19">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C20">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D20">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E20">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F20">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G20">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H20">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C21">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D21">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E21">
+        <v>23</v>
+      </c>
+      <c r="F21">
+        <v>24</v>
+      </c>
+      <c r="G21">
         <v>29</v>
       </c>
-      <c r="F21">
-        <v>33</v>
-      </c>
-      <c r="G21">
-        <v>34</v>
-      </c>
       <c r="H21">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I21">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D22">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E22">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F22">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G22">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H22">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I22">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E23">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F23">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G23">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H23">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I23">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E24">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F24">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G24">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H24">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I24">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C25">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E25">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F25">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G25">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H25">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I25">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C26">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D26">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E26">
         <v>25</v>
       </c>
       <c r="F26">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G26">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H26">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I26">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C27">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D27">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E27">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F27">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G27">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H27">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I27">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C28">
+        <v>8</v>
+      </c>
+      <c r="D28">
+        <v>9</v>
+      </c>
+      <c r="E28">
+        <v>16</v>
+      </c>
+      <c r="F28">
         <v>20</v>
-      </c>
-      <c r="D28">
-        <v>26</v>
-      </c>
-      <c r="E28">
-        <v>29</v>
-      </c>
-      <c r="F28">
-        <v>31</v>
       </c>
       <c r="G28">
         <v>37</v>
@@ -2699,720 +2699,720 @@
         <v>49</v>
       </c>
       <c r="I28">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D29">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E29">
         <v>29</v>
       </c>
       <c r="F29">
+        <v>31</v>
+      </c>
+      <c r="G29">
         <v>37</v>
       </c>
-      <c r="G29">
-        <v>47</v>
-      </c>
       <c r="H29">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I29">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C30">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D30">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E30">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F30">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G30">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="H30">
         <v>48</v>
       </c>
       <c r="I30">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C31">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D31">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E31">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F31">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G31">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H31">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I31">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C32">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D32">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E32">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F32">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G32">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H32">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I32">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C33">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D33">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E33">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F33">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G33">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H33">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I33">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D34">
+        <v>12</v>
+      </c>
+      <c r="E34">
         <v>18</v>
       </c>
-      <c r="E34">
-        <v>25</v>
-      </c>
       <c r="F34">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G34">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H34">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I34">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C35">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D35">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E35">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F35">
         <v>28</v>
       </c>
       <c r="G35">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H35">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I35">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D36">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E36">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F36">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G36">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H36">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I36">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D37">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E37">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F37">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G37">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H37">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I37">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C38">
+        <v>6</v>
+      </c>
+      <c r="D38">
+        <v>10</v>
+      </c>
+      <c r="E38">
+        <v>14</v>
+      </c>
+      <c r="F38">
+        <v>25</v>
+      </c>
+      <c r="G38">
+        <v>26</v>
+      </c>
+      <c r="H38">
+        <v>32</v>
+      </c>
+      <c r="I38">
         <v>7</v>
-      </c>
-      <c r="D38">
-        <v>14</v>
-      </c>
-      <c r="E38">
-        <v>16</v>
-      </c>
-      <c r="F38">
-        <v>37</v>
-      </c>
-      <c r="G38">
-        <v>39</v>
-      </c>
-      <c r="H38">
-        <v>47</v>
-      </c>
-      <c r="I38">
-        <v>34</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D39">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E39">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F39">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G39">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H39">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I39">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C40">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D40">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E40">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F40">
+        <v>19</v>
+      </c>
+      <c r="G40">
+        <v>20</v>
+      </c>
+      <c r="H40">
+        <v>40</v>
+      </c>
+      <c r="I40">
         <v>22</v>
-      </c>
-      <c r="G40">
-        <v>40</v>
-      </c>
-      <c r="H40">
-        <v>45</v>
-      </c>
-      <c r="I40">
-        <v>18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D41">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E41">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F41">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G41">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H41">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I41">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C42">
         <v>4</v>
       </c>
       <c r="D42">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E42">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F42">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G42">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H42">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I42">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E43">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F43">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G43">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H43">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I43">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C44">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D44">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E44">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F44">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G44">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H44">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I44">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C45">
         <v>5</v>
       </c>
       <c r="D45">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E45">
+        <v>13</v>
+      </c>
+      <c r="F45">
         <v>25</v>
       </c>
-      <c r="F45">
-        <v>40</v>
-      </c>
       <c r="G45">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H45">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I45">
-        <v>39</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D46">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E46">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F46">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G46">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H46">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I46">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C47">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D47">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E47">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F47">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G47">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H47">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I47">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C48">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D48">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E48">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F48">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G48">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H48">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I48">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C49">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D49">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E49">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F49">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G49">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H49">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I49">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C50">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D50">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E50">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F50">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G50">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H50">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I50">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C51">
         <v>5</v>
       </c>
       <c r="D51">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E51">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F51">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G51">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H51">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I51">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-09-01 第 115000084 期；威力彩 2026-08-31 第 115000070 期</t>
+          <t>大樂透 2026-09-01 第 115000084 期；威力彩 2026-09-03 第 115000071 期</t>
         </is>
       </c>
     </row>
@@ -112,7 +112,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -121,7 +121,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3464,10 +3464,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>1.024</v>
+        <v>1.0</v>
       </c>
       <c r="D2">
-        <v>31.0</v>
+        <v>28.6</v>
       </c>
       <c r="E2">
         <v>4.8</v>
@@ -3479,14 +3479,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>冷熱混合</t>
+          <t>冷號觀察</t>
         </is>
       </c>
       <c r="B3">
         <v>42</v>
       </c>
       <c r="C3">
-        <v>1.024</v>
+        <v>1.0</v>
       </c>
       <c r="D3">
         <v>31.0</v>
@@ -3501,7 +3501,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>近期趨勢</t>
+          <t>冷熱混合</t>
         </is>
       </c>
       <c r="B4">
@@ -3511,10 +3511,10 @@
         <v>1.0</v>
       </c>
       <c r="D4">
-        <v>23.8</v>
+        <v>28.6</v>
       </c>
       <c r="E4">
-        <v>7.1</v>
+        <v>4.8</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -3523,17 +3523,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>冷號觀察</t>
+          <t>近期趨勢</t>
         </is>
       </c>
       <c r="B5">
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1.0</v>
+        <v>0.952</v>
       </c>
       <c r="D5">
-        <v>31.0</v>
+        <v>21.4</v>
       </c>
       <c r="E5">
         <v>4.8</v>
@@ -3552,10 +3552,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.952</v>
+        <v>0.929</v>
       </c>
       <c r="D6">
-        <v>21.4</v>
+        <v>19.0</v>
       </c>
       <c r="E6">
         <v>4.8</v>
@@ -3574,7 +3574,7 @@
         <v>42</v>
       </c>
       <c r="C7">
-        <v>0.643</v>
+        <v>0.619</v>
       </c>
       <c r="D7">
         <v>9.5</v>
@@ -3645,28 +3645,28 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C2">
-        <v>74.2</v>
+        <v>74.89</v>
       </c>
       <c r="D2">
         <v>12</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>85.71</v>
+        <v>92.31</v>
       </c>
       <c r="H2">
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>8.57</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="3">
@@ -3674,13 +3674,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>72.67</v>
+        <v>69.5</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -3689,10 +3689,10 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>78.57</v>
+        <v>69.23</v>
       </c>
       <c r="H3">
-        <v>100.0</v>
+        <v>83.33</v>
       </c>
       <c r="I3">
         <v>0.0</v>
@@ -3703,28 +3703,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C4">
-        <v>72.62</v>
+        <v>68.66</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G4">
-        <v>64.29</v>
+        <v>76.92</v>
       </c>
       <c r="H4">
-        <v>100.0</v>
+        <v>66.67</v>
       </c>
       <c r="I4">
-        <v>2.86</v>
+        <v>19.44</v>
       </c>
     </row>
     <row r="5">
@@ -3732,28 +3732,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C5">
-        <v>70.24</v>
+        <v>68.23</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>78.57</v>
+        <v>92.31</v>
       </c>
       <c r="H5">
-        <v>80.0</v>
+        <v>66.67</v>
       </c>
       <c r="I5">
-        <v>17.14</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="6">
@@ -3761,13 +3761,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C6">
-        <v>69.44</v>
+        <v>66.18</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -3776,13 +3776,13 @@
         <v>3</v>
       </c>
       <c r="G6">
-        <v>92.86</v>
+        <v>61.54</v>
       </c>
       <c r="H6">
-        <v>80.0</v>
+        <v>66.67</v>
       </c>
       <c r="I6">
-        <v>8.57</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="7">
@@ -3790,13 +3790,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>67.8</v>
+        <v>66.17</v>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -3805,13 +3805,13 @@
         <v>2</v>
       </c>
       <c r="G7">
-        <v>57.14</v>
+        <v>69.23</v>
       </c>
       <c r="H7">
-        <v>80.0</v>
+        <v>66.67</v>
       </c>
       <c r="I7">
-        <v>5.71</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="8">
@@ -3819,13 +3819,13 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>67.37</v>
+        <v>65.75</v>
       </c>
       <c r="D8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8">
         <v>4</v>
@@ -3834,13 +3834,13 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>57.14</v>
+        <v>69.23</v>
       </c>
       <c r="H8">
-        <v>80.0</v>
+        <v>66.67</v>
       </c>
       <c r="I8">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="9">
@@ -3848,28 +3848,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C9">
-        <v>67.19</v>
+        <v>64.47</v>
       </c>
       <c r="D9">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9">
         <v>4</v>
       </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
       <c r="G9">
-        <v>64.29</v>
+        <v>100.0</v>
       </c>
       <c r="H9">
-        <v>80.0</v>
+        <v>50.0</v>
       </c>
       <c r="I9">
-        <v>0.0</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="10">
@@ -3877,28 +3877,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C10">
-        <v>64.69</v>
+        <v>63.63</v>
       </c>
       <c r="D10">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10">
-        <v>42.86</v>
+        <v>100.0</v>
       </c>
       <c r="H10">
-        <v>100.0</v>
+        <v>50.0</v>
       </c>
       <c r="I10">
-        <v>2.86</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="11">
@@ -3906,28 +3906,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C11">
-        <v>63.83</v>
+        <v>62.41</v>
       </c>
       <c r="D11">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G11">
-        <v>100.0</v>
+        <v>76.92</v>
       </c>
       <c r="H11">
-        <v>60.0</v>
+        <v>33.33</v>
       </c>
       <c r="I11">
-        <v>2.86</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="12">
@@ -3935,28 +3935,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="C12">
-        <v>62.19</v>
+        <v>61.91</v>
       </c>
       <c r="D12">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G12">
-        <v>64.29</v>
+        <v>46.15</v>
       </c>
       <c r="H12">
-        <v>60.0</v>
+        <v>83.33</v>
       </c>
       <c r="I12">
-        <v>0.0</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="13">
@@ -3964,28 +3964,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C13">
-        <v>62.14</v>
+        <v>61.57</v>
       </c>
       <c r="D13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13">
         <v>2</v>
       </c>
       <c r="F13">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G13">
-        <v>71.43</v>
+        <v>84.62</v>
       </c>
       <c r="H13">
-        <v>40.0</v>
+        <v>33.33</v>
       </c>
       <c r="I13">
-        <v>31.43</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="14">
@@ -3993,28 +3993,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="C14">
-        <v>61.1</v>
+        <v>61.18</v>
       </c>
       <c r="D14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G14">
-        <v>78.57</v>
+        <v>61.54</v>
       </c>
       <c r="H14">
-        <v>40.0</v>
+        <v>50.0</v>
       </c>
       <c r="I14">
-        <v>22.86</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="15">
@@ -4022,28 +4022,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C15">
-        <v>60.86</v>
+        <v>61.17</v>
       </c>
       <c r="D15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>71.43</v>
+        <v>69.23</v>
       </c>
       <c r="H15">
-        <v>40.0</v>
+        <v>50.0</v>
       </c>
       <c r="I15">
-        <v>22.86</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="16">
@@ -4051,28 +4051,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C16">
-        <v>60.8</v>
+        <v>61.17</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>57.14</v>
+        <v>69.23</v>
       </c>
       <c r="H16">
-        <v>40.0</v>
+        <v>50.0</v>
       </c>
       <c r="I16">
-        <v>25.71</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="17">
@@ -4080,10 +4080,10 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C17">
-        <v>60.0</v>
+        <v>61.16</v>
       </c>
       <c r="D17">
         <v>10</v>
@@ -4092,16 +4092,16 @@
         <v>2</v>
       </c>
       <c r="F17">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G17">
-        <v>71.43</v>
+        <v>76.92</v>
       </c>
       <c r="H17">
-        <v>40.0</v>
+        <v>33.33</v>
       </c>
       <c r="I17">
-        <v>17.14</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="18">
@@ -4109,10 +4109,10 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C18">
-        <v>59.94</v>
+        <v>60.76</v>
       </c>
       <c r="D18">
         <v>8</v>
@@ -4121,16 +4121,16 @@
         <v>2</v>
       </c>
       <c r="F18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G18">
-        <v>57.14</v>
+        <v>61.54</v>
       </c>
       <c r="H18">
-        <v>40.0</v>
+        <v>33.33</v>
       </c>
       <c r="I18">
-        <v>20.0</v>
+        <v>27.78</v>
       </c>
     </row>
     <row r="19">
@@ -4138,28 +4138,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C19">
-        <v>59.87</v>
+        <v>60.32</v>
       </c>
       <c r="D19">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G19">
-        <v>92.86</v>
+        <v>76.92</v>
       </c>
       <c r="H19">
-        <v>40.0</v>
+        <v>33.33</v>
       </c>
       <c r="I19">
-        <v>11.43</v>
+        <v>19.44</v>
       </c>
     </row>
     <row r="20">
@@ -4167,28 +4167,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C20">
-        <v>59.51</v>
+        <v>57.79</v>
       </c>
       <c r="D20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E20">
+        <v>3</v>
+      </c>
+      <c r="F20">
         <v>2</v>
       </c>
-      <c r="F20">
-        <v>6</v>
-      </c>
       <c r="G20">
-        <v>57.14</v>
+        <v>53.85</v>
       </c>
       <c r="H20">
-        <v>40.0</v>
+        <v>50.0</v>
       </c>
       <c r="I20">
-        <v>17.14</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="21">
@@ -4196,28 +4196,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C21">
-        <v>58.73</v>
+        <v>57.0</v>
       </c>
       <c r="D21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G21">
-        <v>50.0</v>
+        <v>69.23</v>
       </c>
       <c r="H21">
-        <v>60.0</v>
+        <v>16.67</v>
       </c>
       <c r="I21">
-        <v>2.86</v>
+        <v>27.78</v>
       </c>
     </row>
     <row r="22">
@@ -4225,28 +4225,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C22">
-        <v>58.1</v>
+        <v>56.95</v>
       </c>
       <c r="D22">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E22">
         <v>2</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G22">
-        <v>78.57</v>
+        <v>53.85</v>
       </c>
       <c r="H22">
-        <v>40.0</v>
+        <v>33.33</v>
       </c>
       <c r="I22">
-        <v>2.86</v>
+        <v>27.78</v>
       </c>
     </row>
     <row r="23">
@@ -4254,28 +4254,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C23">
-        <v>57.8</v>
+        <v>56.59</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G23">
-        <v>57.14</v>
+        <v>69.23</v>
       </c>
       <c r="H23">
-        <v>40.0</v>
+        <v>16.67</v>
       </c>
       <c r="I23">
-        <v>5.71</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="24">
@@ -4283,28 +4283,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C24">
-        <v>57.16</v>
+        <v>56.55</v>
       </c>
       <c r="D24">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G24">
-        <v>50.0</v>
+        <v>100.0</v>
       </c>
       <c r="H24">
-        <v>40.0</v>
+        <v>16.67</v>
       </c>
       <c r="I24">
-        <v>25.71</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="25">
@@ -4312,28 +4312,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C25">
-        <v>56.04</v>
+        <v>55.7</v>
       </c>
       <c r="D25">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G25">
-        <v>64.29</v>
+        <v>53.85</v>
       </c>
       <c r="H25">
-        <v>20.0</v>
+        <v>33.33</v>
       </c>
       <c r="I25">
-        <v>25.71</v>
+        <v>19.44</v>
       </c>
     </row>
     <row r="26">
@@ -4341,28 +4341,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C26">
-        <v>55.86</v>
+        <v>54.49</v>
       </c>
       <c r="D26">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G26">
-        <v>71.43</v>
+        <v>84.62</v>
       </c>
       <c r="H26">
-        <v>20.0</v>
+        <v>16.67</v>
       </c>
       <c r="I26">
-        <v>22.86</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="27">
@@ -4373,7 +4373,7 @@
         <v>26</v>
       </c>
       <c r="C27">
-        <v>55.11</v>
+        <v>53.99</v>
       </c>
       <c r="D27">
         <v>6</v>
@@ -4382,16 +4382,16 @@
         <v>3</v>
       </c>
       <c r="F27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27">
-        <v>42.86</v>
+        <v>46.15</v>
       </c>
       <c r="H27">
-        <v>60.0</v>
+        <v>50.0</v>
       </c>
       <c r="I27">
-        <v>5.71</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="28">
@@ -4399,28 +4399,28 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C28">
-        <v>54.26</v>
+        <v>52.74</v>
       </c>
       <c r="D28">
         <v>6</v>
       </c>
       <c r="E28">
+        <v>3</v>
+      </c>
+      <c r="F28">
         <v>0</v>
       </c>
-      <c r="F28">
-        <v>35</v>
-      </c>
       <c r="G28">
-        <v>42.86</v>
+        <v>46.15</v>
       </c>
       <c r="H28">
+        <v>50.0</v>
+      </c>
+      <c r="I28">
         <v>0.0</v>
-      </c>
-      <c r="I28">
-        <v>100.0</v>
       </c>
     </row>
     <row r="29">
@@ -4431,7 +4431,7 @@
         <v>10</v>
       </c>
       <c r="C29">
-        <v>51.4</v>
+        <v>51.08</v>
       </c>
       <c r="D29">
         <v>6</v>
@@ -4440,16 +4440,16 @@
         <v>2</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G29">
-        <v>42.86</v>
+        <v>46.15</v>
       </c>
       <c r="H29">
-        <v>40.0</v>
+        <v>33.33</v>
       </c>
       <c r="I29">
-        <v>14.29</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="30">
@@ -4457,28 +4457,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C30">
-        <v>46.5</v>
+        <v>51.04</v>
       </c>
       <c r="D30">
         <v>5</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="G30">
-        <v>35.71</v>
+        <v>38.46</v>
       </c>
       <c r="H30">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="I30">
-        <v>8.57</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="31">
@@ -4486,10 +4486,10 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C31">
-        <v>45.21</v>
+        <v>44.37</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -4501,10 +4501,10 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>35.71</v>
+        <v>38.46</v>
       </c>
       <c r="H31">
-        <v>40.0</v>
+        <v>33.33</v>
       </c>
       <c r="I31">
         <v>0.0</v>
@@ -4518,7 +4518,7 @@
         <v>5</v>
       </c>
       <c r="C32">
-        <v>41.93</v>
+        <v>42.29</v>
       </c>
       <c r="D32">
         <v>5</v>
@@ -4527,16 +4527,16 @@
         <v>1</v>
       </c>
       <c r="F32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G32">
-        <v>35.71</v>
+        <v>38.46</v>
       </c>
       <c r="H32">
-        <v>20.0</v>
+        <v>16.67</v>
       </c>
       <c r="I32">
-        <v>11.43</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="33">
@@ -4547,7 +4547,7 @@
         <v>18</v>
       </c>
       <c r="C33">
-        <v>41.93</v>
+        <v>42.29</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -4556,16 +4556,16 @@
         <v>1</v>
       </c>
       <c r="F33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G33">
-        <v>35.71</v>
+        <v>38.46</v>
       </c>
       <c r="H33">
-        <v>20.0</v>
+        <v>16.67</v>
       </c>
       <c r="I33">
-        <v>11.43</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="34">
@@ -4573,28 +4573,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C34">
-        <v>41.17</v>
+        <v>40.62</v>
       </c>
       <c r="D34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34">
-        <v>28.57</v>
+        <v>38.46</v>
       </c>
       <c r="H34">
-        <v>40.0</v>
+        <v>16.67</v>
       </c>
       <c r="I34">
-        <v>0.0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="35">
@@ -4602,28 +4602,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C35">
-        <v>38.89</v>
+        <v>40.58</v>
       </c>
       <c r="D35">
         <v>4</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F35">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G35">
-        <v>28.57</v>
+        <v>30.77</v>
       </c>
       <c r="H35">
-        <v>0.0</v>
+        <v>33.33</v>
       </c>
       <c r="I35">
-        <v>51.43</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="36">
@@ -4631,28 +4631,28 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C36">
-        <v>38.74</v>
+        <v>39.75</v>
       </c>
       <c r="D36">
         <v>4</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G36">
-        <v>28.57</v>
+        <v>30.77</v>
       </c>
       <c r="H36">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I36">
-        <v>17.14</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="37">
@@ -4663,7 +4663,7 @@
         <v>3</v>
       </c>
       <c r="C37">
-        <v>38.31</v>
+        <v>38.5</v>
       </c>
       <c r="D37">
         <v>4</v>
@@ -4672,16 +4672,16 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G37">
-        <v>28.57</v>
+        <v>30.77</v>
       </c>
       <c r="H37">
-        <v>20.0</v>
+        <v>16.67</v>
       </c>
       <c r="I37">
-        <v>14.29</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="38">
@@ -4692,7 +4692,7 @@
         <v>20</v>
       </c>
       <c r="C38">
-        <v>35.13</v>
+        <v>35.12</v>
       </c>
       <c r="D38">
         <v>3</v>
@@ -4701,16 +4701,16 @@
         <v>1</v>
       </c>
       <c r="F38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G38">
-        <v>21.43</v>
+        <v>23.08</v>
       </c>
       <c r="H38">
-        <v>20.0</v>
+        <v>16.67</v>
       </c>
       <c r="I38">
-        <v>20.0</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="39">
@@ -4721,7 +4721,7 @@
         <v>37</v>
       </c>
       <c r="C39">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="D39">
         <v>3</v>
@@ -4730,16 +4730,16 @@
         <v>1</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39">
-        <v>21.43</v>
+        <v>23.08</v>
       </c>
       <c r="H39">
-        <v>20.0</v>
+        <v>16.67</v>
       </c>
       <c r="I39">
-        <v>0.0</v>
+        <v>2.78</v>
       </c>
     </row>
   </sheetData>
@@ -4798,77 +4798,77 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F2">
         <v>19</v>
       </c>
       <c r="G2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H2">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>12</v>
+      </c>
+      <c r="F3">
+        <v>19</v>
+      </c>
+      <c r="G3">
+        <v>32</v>
+      </c>
+      <c r="H3">
+        <v>37</v>
+      </c>
+      <c r="I3">
         <v>2</v>
-      </c>
-      <c r="D3">
-        <v>7</v>
-      </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>24</v>
-      </c>
-      <c r="H3">
-        <v>36</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D4">
         <v>7</v>
@@ -4877,230 +4877,230 @@
         <v>9</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H4">
         <v>36</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E5">
         <v>9</v>
       </c>
       <c r="F5">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
         <v>11</v>
       </c>
-      <c r="E6">
-        <v>18</v>
-      </c>
-      <c r="F6">
-        <v>19</v>
-      </c>
       <c r="G6">
+        <v>29</v>
+      </c>
+      <c r="H6">
         <v>35</v>
       </c>
-      <c r="H6">
-        <v>38</v>
-      </c>
       <c r="I6">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G7">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H7">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C8">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E8">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G8">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H8">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I8">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D9">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E9">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F9">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G9">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H9">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>7</v>
+      </c>
+      <c r="E10">
+        <v>8</v>
+      </c>
+      <c r="F10">
+        <v>20</v>
+      </c>
+      <c r="G10">
+        <v>26</v>
+      </c>
+      <c r="H10">
+        <v>33</v>
+      </c>
+      <c r="I10">
         <v>4</v>
-      </c>
-      <c r="D10">
-        <v>15</v>
-      </c>
-      <c r="E10">
-        <v>22</v>
-      </c>
-      <c r="F10">
-        <v>26</v>
-      </c>
-      <c r="G10">
-        <v>34</v>
-      </c>
-      <c r="H10">
-        <v>36</v>
-      </c>
-      <c r="I10">
-        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C11">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D11">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E11">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F11">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G11">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H11">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I11">
         <v>7</v>
@@ -5108,30 +5108,30 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C12">
+        <v>8</v>
+      </c>
+      <c r="D12">
+        <v>14</v>
+      </c>
+      <c r="E12">
+        <v>17</v>
+      </c>
+      <c r="F12">
         <v>19</v>
       </c>
-      <c r="D12">
-        <v>22</v>
-      </c>
-      <c r="E12">
-        <v>28</v>
-      </c>
-      <c r="F12">
-        <v>31</v>
-      </c>
       <c r="G12">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H12">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I12">
         <v>7</v>
@@ -5139,30 +5139,30 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C13">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D13">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E13">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F13">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G13">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H13">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I13">
         <v>7</v>
@@ -5170,24 +5170,24 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E14">
         <v>13</v>
       </c>
       <c r="F14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G14">
         <v>29</v>
@@ -5196,97 +5196,97 @@
         <v>31</v>
       </c>
       <c r="I14">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C15">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D15">
+        <v>12</v>
+      </c>
+      <c r="E15">
+        <v>13</v>
+      </c>
+      <c r="F15">
         <v>23</v>
       </c>
-      <c r="E15">
-        <v>25</v>
-      </c>
-      <c r="F15">
+      <c r="G15">
         <v>29</v>
       </c>
-      <c r="G15">
-        <v>34</v>
-      </c>
       <c r="H15">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I15">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C16">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D16">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E16">
+        <v>25</v>
+      </c>
+      <c r="F16">
         <v>29</v>
       </c>
-      <c r="F16">
-        <v>32</v>
-      </c>
       <c r="G16">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H16">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I16">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E17">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F17">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G17">
         <v>35</v>
       </c>
       <c r="H17">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I17">
         <v>6</v>
@@ -5294,402 +5294,402 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C18">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D18">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E18">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F18">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G18">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H18">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D19">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F19">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G19">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H19">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I19">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E20">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F20">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G20">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H20">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I20">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C21">
+        <v>5</v>
+      </c>
+      <c r="D21">
         <v>6</v>
       </c>
-      <c r="D21">
-        <v>10</v>
-      </c>
       <c r="E21">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F21">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G21">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H21">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C22">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D22">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E22">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F22">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G22">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H22">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I22">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E23">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F23">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G23">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H23">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I23">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>8</v>
+      </c>
+      <c r="E24">
+        <v>9</v>
+      </c>
+      <c r="F24">
+        <v>15</v>
+      </c>
+      <c r="G24">
+        <v>18</v>
+      </c>
+      <c r="H24">
+        <v>23</v>
+      </c>
+      <c r="I24">
         <v>4</v>
-      </c>
-      <c r="D24">
-        <v>17</v>
-      </c>
-      <c r="E24">
-        <v>19</v>
-      </c>
-      <c r="F24">
-        <v>25</v>
-      </c>
-      <c r="G24">
-        <v>28</v>
-      </c>
-      <c r="H24">
-        <v>29</v>
-      </c>
-      <c r="I24">
-        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C25">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D25">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E25">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F25">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G25">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H25">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I25">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D26">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E26">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F26">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G26">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H26">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I26">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C27">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D27">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E27">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F27">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G27">
         <v>28</v>
       </c>
       <c r="H27">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I27">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C28">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D28">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E28">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F28">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G28">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H28">
         <v>35</v>
       </c>
       <c r="I28">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E29">
+        <v>9</v>
+      </c>
+      <c r="F29">
+        <v>15</v>
+      </c>
+      <c r="G29">
         <v>24</v>
       </c>
-      <c r="F29">
-        <v>31</v>
-      </c>
-      <c r="G29">
-        <v>34</v>
-      </c>
       <c r="H29">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I29">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C30">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D30">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E30">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F30">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G30">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H30">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I30">
         <v>3</v>
@@ -5697,554 +5697,554 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C31">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D31">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E31">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F31">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G31">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H31">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I31">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C32">
         <v>6</v>
       </c>
       <c r="D32">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E32">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F32">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G32">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H32">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I32">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C33">
         <v>6</v>
       </c>
       <c r="D33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E33">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F33">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G33">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H33">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I33">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C34">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D34">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E34">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F34">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G34">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H34">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I34">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C35">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D35">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E35">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F35">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G35">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H35">
         <v>38</v>
       </c>
       <c r="I35">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C36">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D36">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E36">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F36">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G36">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H36">
         <v>38</v>
       </c>
       <c r="I36">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D37">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E37">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F37">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G37">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H37">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I37">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C38">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D38">
+        <v>4</v>
+      </c>
+      <c r="E38">
+        <v>13</v>
+      </c>
+      <c r="F38">
+        <v>19</v>
+      </c>
+      <c r="G38">
+        <v>27</v>
+      </c>
+      <c r="H38">
+        <v>30</v>
+      </c>
+      <c r="I38">
         <v>8</v>
-      </c>
-      <c r="E38">
-        <v>27</v>
-      </c>
-      <c r="F38">
-        <v>33</v>
-      </c>
-      <c r="G38">
-        <v>35</v>
-      </c>
-      <c r="H38">
-        <v>38</v>
-      </c>
-      <c r="I38">
-        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D39">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E39">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F39">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G39">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H39">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I39">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C40">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D40">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E40">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F40">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G40">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H40">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I40">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D41">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E41">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F41">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G41">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H41">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I41">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000030</v>
+        <v>115000031</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D42">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E42">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F42">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G42">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H42">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="I42">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000029</v>
+        <v>115000030</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D43">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E43">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F43">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G43">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H43">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I43">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000028</v>
+        <v>115000029</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E44">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F44">
         <v>27</v>
       </c>
       <c r="G44">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H44">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I44">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000027</v>
+        <v>115000028</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C45">
         <v>5</v>
       </c>
       <c r="D45">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E45">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F45">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G45">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H45">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I45">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000026</v>
+        <v>115000027</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C46">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D46">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E46">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F46">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G46">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H46">
         <v>34</v>
       </c>
       <c r="I46">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000025</v>
+        <v>115000026</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C47">
+        <v>2</v>
+      </c>
+      <c r="D47">
         <v>13</v>
       </c>
-      <c r="D47">
-        <v>14</v>
-      </c>
       <c r="E47">
+        <v>21</v>
+      </c>
+      <c r="F47">
         <v>22</v>
       </c>
-      <c r="F47">
-        <v>28</v>
-      </c>
       <c r="G47">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H47">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I47">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000024</v>
+        <v>115000025</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D48">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E48">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F48">
         <v>28</v>
       </c>
       <c r="G48">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H48">
         <v>38</v>
@@ -6255,58 +6255,58 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000023</v>
+        <v>115000024</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49">
         <v>9</v>
       </c>
-      <c r="D49">
-        <v>13</v>
-      </c>
       <c r="E49">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F49">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G49">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H49">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I49">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000022</v>
+        <v>115000023</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C50">
+        <v>9</v>
+      </c>
+      <c r="D50">
+        <v>13</v>
+      </c>
+      <c r="E50">
         <v>14</v>
       </c>
-      <c r="D50">
-        <v>26</v>
-      </c>
-      <c r="E50">
-        <v>28</v>
-      </c>
       <c r="F50">
+        <v>18</v>
+      </c>
+      <c r="G50">
         <v>31</v>
-      </c>
-      <c r="G50">
-        <v>32</v>
       </c>
       <c r="H50">
         <v>34</v>
@@ -6317,33 +6317,33 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000021</v>
+        <v>115000022</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C51">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D51">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E51">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F51">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G51">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H51">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I51">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-09-01 第 115000084 期；威力彩 2026-09-03 第 115000071 期</t>
+          <t>大樂透 2026-09-04 第 115000085 期；威力彩 2026-09-03 第 115000071 期</t>
         </is>
       </c>
     </row>
@@ -47,7 +47,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>115000084</v>
+        <v>115000085</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -56,7 +56,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -96,7 +96,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.357 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.381 碼/期</t>
         </is>
       </c>
     </row>
@@ -302,7 +302,7 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.643</v>
+        <v>0.619</v>
       </c>
       <c r="D6">
         <v>9.5</v>
@@ -398,7 +398,7 @@
         <v>26</v>
       </c>
       <c r="C2">
-        <v>70.6</v>
+        <v>71.02</v>
       </c>
       <c r="D2">
         <v>12</v>
@@ -407,7 +407,7 @@
         <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>100.0</v>
@@ -416,7 +416,7 @@
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>0.0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="3">
@@ -427,25 +427,25 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>64.31</v>
+        <v>64.66</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3">
         <v>5</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>100.0</v>
+        <v>91.67</v>
       </c>
       <c r="H3">
         <v>71.43</v>
       </c>
       <c r="I3">
-        <v>5.71</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="4">
@@ -453,13 +453,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>61.5</v>
+        <v>61.35</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -468,13 +468,13 @@
         <v>4</v>
       </c>
       <c r="G4">
-        <v>83.33</v>
+        <v>66.67</v>
       </c>
       <c r="H4">
         <v>57.14</v>
       </c>
       <c r="I4">
-        <v>11.43</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="5">
@@ -482,28 +482,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C5">
-        <v>61.13</v>
+        <v>60.88</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>50.0</v>
+        <v>58.33</v>
       </c>
       <c r="H5">
         <v>57.14</v>
       </c>
       <c r="I5">
-        <v>14.29</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C6">
-        <v>60.97</v>
+        <v>60.23</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -526,13 +526,13 @@
         <v>3</v>
       </c>
       <c r="G6">
-        <v>66.67</v>
+        <v>50.0</v>
       </c>
       <c r="H6">
         <v>57.14</v>
       </c>
       <c r="I6">
-        <v>8.57</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="7">
@@ -540,28 +540,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C7">
-        <v>60.49</v>
+        <v>59.81</v>
       </c>
       <c r="D7">
         <v>7</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G7">
         <v>58.33</v>
       </c>
       <c r="H7">
-        <v>57.14</v>
+        <v>42.86</v>
       </c>
       <c r="I7">
-        <v>5.71</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="8">
@@ -569,28 +569,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8">
-        <v>59.84</v>
+        <v>58.3</v>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G8">
-        <v>50.0</v>
+        <v>83.33</v>
       </c>
       <c r="H8">
-        <v>57.14</v>
+        <v>42.86</v>
       </c>
       <c r="I8">
-        <v>5.71</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="9">
@@ -598,28 +598,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C9">
-        <v>59.49</v>
+        <v>57.92</v>
       </c>
       <c r="D9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G9">
-        <v>58.33</v>
+        <v>50.0</v>
       </c>
       <c r="H9">
         <v>42.86</v>
       </c>
       <c r="I9">
-        <v>22.86</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         <v>14</v>
       </c>
       <c r="C10">
-        <v>57.35</v>
+        <v>57.73</v>
       </c>
       <c r="D10">
         <v>7</v>
@@ -639,7 +639,7 @@
         <v>3</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10">
         <v>58.33</v>
@@ -648,7 +648,7 @@
         <v>42.86</v>
       </c>
       <c r="I10">
-        <v>8.57</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="11">
@@ -659,7 +659,7 @@
         <v>23</v>
       </c>
       <c r="C11">
-        <v>56.55</v>
+        <v>56.95</v>
       </c>
       <c r="D11">
         <v>8</v>
@@ -668,7 +668,7 @@
         <v>3</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11">
         <v>66.67</v>
@@ -677,7 +677,7 @@
         <v>42.86</v>
       </c>
       <c r="I11">
-        <v>2.86</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="12">
@@ -685,13 +685,13 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C12">
-        <v>56.55</v>
+        <v>56.73</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -700,13 +700,13 @@
         <v>1</v>
       </c>
       <c r="G12">
-        <v>66.67</v>
+        <v>100.0</v>
       </c>
       <c r="H12">
         <v>42.86</v>
       </c>
       <c r="I12">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="13">
@@ -714,28 +714,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C13">
-        <v>56.31</v>
+        <v>56.53</v>
       </c>
       <c r="D13">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>100.0</v>
+        <v>66.67</v>
       </c>
       <c r="H13">
         <v>42.86</v>
       </c>
       <c r="I13">
-        <v>0.0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="14">
@@ -743,28 +743,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>56.12</v>
+        <v>54.75</v>
       </c>
       <c r="D14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G14">
-        <v>66.67</v>
+        <v>58.33</v>
       </c>
       <c r="H14">
-        <v>42.86</v>
+        <v>14.29</v>
       </c>
       <c r="I14">
-        <v>0.0</v>
+        <v>38.89</v>
       </c>
     </row>
     <row r="15">
@@ -772,28 +772,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="C15">
-        <v>54.49</v>
+        <v>54.58</v>
       </c>
       <c r="D15">
         <v>7</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G15">
         <v>58.33</v>
       </c>
       <c r="H15">
-        <v>14.29</v>
+        <v>28.57</v>
       </c>
       <c r="I15">
-        <v>37.14</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="16">
@@ -801,28 +801,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C16">
-        <v>54.21</v>
+        <v>54.34</v>
       </c>
       <c r="D16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16">
         <v>2</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G16">
-        <v>58.33</v>
+        <v>50.0</v>
       </c>
       <c r="H16">
         <v>28.57</v>
       </c>
       <c r="I16">
-        <v>11.43</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="17">
@@ -830,10 +830,10 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>53.99</v>
+        <v>53.93</v>
       </c>
       <c r="D17">
         <v>6</v>
@@ -851,7 +851,7 @@
         <v>28.57</v>
       </c>
       <c r="I17">
-        <v>14.29</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="18">
@@ -859,28 +859,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="C18">
-        <v>53.56</v>
+        <v>53.38</v>
       </c>
       <c r="D18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G18">
-        <v>50.0</v>
+        <v>66.67</v>
       </c>
       <c r="H18">
         <v>28.57</v>
       </c>
       <c r="I18">
-        <v>11.43</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="19">
@@ -891,7 +891,7 @@
         <v>20</v>
       </c>
       <c r="C19">
-        <v>52.92</v>
+        <v>53.33</v>
       </c>
       <c r="D19">
         <v>7</v>
@@ -900,7 +900,7 @@
         <v>2</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19">
         <v>58.33</v>
@@ -909,7 +909,7 @@
         <v>28.57</v>
       </c>
       <c r="I19">
-        <v>2.86</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="20">
@@ -920,7 +920,7 @@
         <v>11</v>
       </c>
       <c r="C20">
-        <v>52.78</v>
+        <v>53.09</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -929,7 +929,7 @@
         <v>1</v>
       </c>
       <c r="F20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>58.33</v>
@@ -938,7 +938,7 @@
         <v>14.29</v>
       </c>
       <c r="I20">
-        <v>25.71</v>
+        <v>27.78</v>
       </c>
     </row>
     <row r="21">
@@ -949,7 +949,7 @@
         <v>16</v>
       </c>
       <c r="C21">
-        <v>52.64</v>
+        <v>53.06</v>
       </c>
       <c r="D21">
         <v>10</v>
@@ -958,7 +958,7 @@
         <v>2</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21">
         <v>83.33</v>
@@ -967,7 +967,7 @@
         <v>28.57</v>
       </c>
       <c r="I21">
-        <v>0.0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="22">
@@ -975,28 +975,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C22">
-        <v>52.54</v>
+        <v>52.77</v>
       </c>
       <c r="D22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G22">
-        <v>66.67</v>
+        <v>75.0</v>
       </c>
       <c r="H22">
-        <v>28.57</v>
+        <v>14.29</v>
       </c>
       <c r="I22">
-        <v>0.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="23">
@@ -1004,28 +1004,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="C23">
-        <v>52.45</v>
+        <v>51.3</v>
       </c>
       <c r="D23">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>75.0</v>
+        <v>41.67</v>
       </c>
       <c r="H23">
-        <v>14.29</v>
+        <v>42.86</v>
       </c>
       <c r="I23">
-        <v>22.86</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="24">
@@ -1033,28 +1033,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C24">
-        <v>51.78</v>
+        <v>50.47</v>
       </c>
       <c r="D24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E24">
+        <v>3</v>
+      </c>
+      <c r="F24">
         <v>0</v>
       </c>
-      <c r="F24">
-        <v>15</v>
-      </c>
       <c r="G24">
-        <v>58.33</v>
+        <v>41.67</v>
       </c>
       <c r="H24">
+        <v>42.86</v>
+      </c>
+      <c r="I24">
         <v>0.0</v>
-      </c>
-      <c r="I24">
-        <v>42.86</v>
       </c>
     </row>
     <row r="25">
@@ -1062,28 +1062,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="C25">
-        <v>50.89</v>
+        <v>50.23</v>
       </c>
       <c r="D25">
         <v>5</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="G25">
         <v>41.67</v>
       </c>
       <c r="H25">
-        <v>0.0</v>
+        <v>28.57</v>
       </c>
       <c r="I25">
-        <v>74.29</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="26">
@@ -1091,28 +1091,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C26">
-        <v>50.89</v>
+        <v>50.17</v>
       </c>
       <c r="D26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
         <v>3</v>
       </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
       <c r="G26">
-        <v>41.67</v>
+        <v>58.33</v>
       </c>
       <c r="H26">
-        <v>42.86</v>
+        <v>14.29</v>
       </c>
       <c r="I26">
-        <v>2.86</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="27">
@@ -1123,25 +1123,25 @@
         <v>47</v>
       </c>
       <c r="C27">
-        <v>50.21</v>
+        <v>49.94</v>
       </c>
       <c r="D27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27">
-        <v>58.33</v>
+        <v>50.0</v>
       </c>
       <c r="H27">
         <v>14.29</v>
       </c>
       <c r="I27">
-        <v>8.57</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="28">
@@ -1149,28 +1149,28 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C28">
-        <v>49.89</v>
+        <v>49.39</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G28">
-        <v>41.67</v>
+        <v>66.67</v>
       </c>
       <c r="H28">
-        <v>28.57</v>
+        <v>14.29</v>
       </c>
       <c r="I28">
-        <v>20.0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="29">
@@ -1178,10 +1178,10 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C29">
-        <v>49.78</v>
+        <v>49.34</v>
       </c>
       <c r="D29">
         <v>7</v>
@@ -1190,7 +1190,7 @@
         <v>1</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29">
         <v>58.33</v>
@@ -1199,7 +1199,7 @@
         <v>14.29</v>
       </c>
       <c r="I29">
-        <v>5.71</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="30">
@@ -1207,28 +1207,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="C30">
-        <v>49.32</v>
+        <v>48.97</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>41.67</v>
+        <v>66.67</v>
       </c>
       <c r="H30">
         <v>14.29</v>
       </c>
       <c r="I30">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="31">
@@ -1236,28 +1236,28 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C31">
-        <v>48.97</v>
+        <v>48.92</v>
       </c>
       <c r="D31">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G31">
-        <v>66.67</v>
+        <v>41.67</v>
       </c>
       <c r="H31">
-        <v>14.29</v>
+        <v>0.0</v>
       </c>
       <c r="I31">
-        <v>0.0</v>
+        <v>61.11</v>
       </c>
     </row>
     <row r="32">
@@ -1265,28 +1265,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C32">
-        <v>48.75</v>
+        <v>48.27</v>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32">
         <v>0</v>
       </c>
-      <c r="F32">
-        <v>21</v>
-      </c>
       <c r="G32">
-        <v>41.67</v>
+        <v>50.0</v>
       </c>
       <c r="H32">
+        <v>14.29</v>
+      </c>
+      <c r="I32">
         <v>0.0</v>
-      </c>
-      <c r="I32">
-        <v>60.0</v>
       </c>
     </row>
     <row r="33">
@@ -1294,28 +1294,28 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C33">
-        <v>48.09</v>
+        <v>48.14</v>
       </c>
       <c r="D33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E33">
+        <v>2</v>
+      </c>
+      <c r="F33">
         <v>3</v>
       </c>
-      <c r="F33">
-        <v>6</v>
-      </c>
       <c r="G33">
-        <v>33.33</v>
+        <v>41.67</v>
       </c>
       <c r="H33">
-        <v>42.86</v>
+        <v>28.57</v>
       </c>
       <c r="I33">
-        <v>17.14</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="34">
@@ -1323,28 +1323,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C34">
-        <v>47.75</v>
+        <v>47.72</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="G34">
-        <v>41.67</v>
+        <v>33.33</v>
       </c>
       <c r="H34">
-        <v>28.57</v>
+        <v>0.0</v>
       </c>
       <c r="I34">
-        <v>5.71</v>
+        <v>86.11</v>
       </c>
     </row>
     <row r="35">
@@ -1352,28 +1352,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="C35">
-        <v>47.66</v>
+        <v>47.25</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E35">
         <v>0</v>
       </c>
       <c r="F35">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G35">
-        <v>33.33</v>
+        <v>41.67</v>
       </c>
       <c r="H35">
         <v>0.0</v>
       </c>
       <c r="I35">
-        <v>85.71</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="36">
@@ -1381,28 +1381,28 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C36">
-        <v>47.04</v>
+        <v>47.07</v>
       </c>
       <c r="D36">
         <v>5</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G36">
         <v>41.67</v>
       </c>
       <c r="H36">
-        <v>0.0</v>
+        <v>14.29</v>
       </c>
       <c r="I36">
-        <v>48.57</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="37">
@@ -1410,28 +1410,28 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="C37">
-        <v>46.75</v>
+        <v>46.89</v>
       </c>
       <c r="D37">
         <v>5</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G37">
         <v>41.67</v>
       </c>
       <c r="H37">
-        <v>14.29</v>
+        <v>28.57</v>
       </c>
       <c r="I37">
-        <v>22.86</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="38">
@@ -1439,10 +1439,10 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C38">
-        <v>46.61</v>
+        <v>46.0</v>
       </c>
       <c r="D38">
         <v>5</v>
@@ -1451,7 +1451,7 @@
         <v>0</v>
       </c>
       <c r="F38">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G38">
         <v>41.67</v>
@@ -1460,7 +1460,7 @@
         <v>0.0</v>
       </c>
       <c r="I38">
-        <v>45.71</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="39">
@@ -1468,28 +1468,28 @@
         <v>38</v>
       </c>
       <c r="B39">
+        <v>46</v>
+      </c>
+      <c r="C39">
+        <v>44.86</v>
+      </c>
+      <c r="D39">
+        <v>4</v>
+      </c>
+      <c r="E39">
+        <v>2</v>
+      </c>
+      <c r="F39">
         <v>7</v>
       </c>
-      <c r="C39">
-        <v>44.85</v>
-      </c>
-      <c r="D39">
-        <v>3</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-      <c r="F39">
-        <v>35</v>
-      </c>
       <c r="G39">
-        <v>25.0</v>
+        <v>33.33</v>
       </c>
       <c r="H39">
-        <v>0.0</v>
+        <v>28.57</v>
       </c>
       <c r="I39">
-        <v>100.0</v>
+        <v>19.44</v>
       </c>
     </row>
     <row r="40">
@@ -1497,28 +1497,28 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C40">
-        <v>43.94</v>
+        <v>44.85</v>
       </c>
       <c r="D40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="G40">
-        <v>33.33</v>
+        <v>25.0</v>
       </c>
       <c r="H40">
-        <v>14.29</v>
+        <v>0.0</v>
       </c>
       <c r="I40">
-        <v>37.14</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="41">
@@ -1526,28 +1526,28 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C41">
-        <v>43.66</v>
+        <v>43.32</v>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F41">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>33.33</v>
+        <v>41.67</v>
       </c>
       <c r="H41">
-        <v>28.57</v>
+        <v>14.29</v>
       </c>
       <c r="I41">
-        <v>11.43</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="42">
@@ -1555,28 +1555,28 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C42">
-        <v>42.71</v>
+        <v>42.78</v>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F42">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G42">
-        <v>25.0</v>
+        <v>33.33</v>
       </c>
       <c r="H42">
-        <v>0.0</v>
+        <v>28.57</v>
       </c>
       <c r="I42">
-        <v>85.71</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="43">
@@ -1584,10 +1584,10 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C43">
-        <v>42.37</v>
+        <v>41.94</v>
       </c>
       <c r="D43">
         <v>4</v>
@@ -1596,7 +1596,7 @@
         <v>2</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43">
         <v>33.33</v>
@@ -1605,7 +1605,7 @@
         <v>28.57</v>
       </c>
       <c r="I43">
-        <v>2.86</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="44">
@@ -1616,7 +1616,7 @@
         <v>21</v>
       </c>
       <c r="C44">
-        <v>41.37</v>
+        <v>41.7</v>
       </c>
       <c r="D44">
         <v>4</v>
@@ -1625,7 +1625,7 @@
         <v>1</v>
       </c>
       <c r="F44">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G44">
         <v>33.33</v>
@@ -1634,7 +1634,7 @@
         <v>14.29</v>
       </c>
       <c r="I44">
-        <v>20.0</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="45">
@@ -1645,7 +1645,7 @@
         <v>41</v>
       </c>
       <c r="C45">
-        <v>41.37</v>
+        <v>41.7</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -1654,7 +1654,7 @@
         <v>1</v>
       </c>
       <c r="F45">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G45">
         <v>33.33</v>
@@ -1663,7 +1663,7 @@
         <v>14.29</v>
       </c>
       <c r="I45">
-        <v>20.0</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="46">
@@ -1671,28 +1671,28 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="C46">
-        <v>40.52</v>
+        <v>37.82</v>
       </c>
       <c r="D46">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G46">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="H46">
-        <v>14.29</v>
+        <v>0.0</v>
       </c>
       <c r="I46">
-        <v>14.29</v>
+        <v>86.11</v>
       </c>
     </row>
     <row r="47">
@@ -1700,10 +1700,10 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C47">
-        <v>38.14</v>
+        <v>37.17</v>
       </c>
       <c r="D47">
         <v>3</v>
@@ -1712,7 +1712,7 @@
         <v>1</v>
       </c>
       <c r="F47">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G47">
         <v>25.0</v>
@@ -1721,7 +1721,7 @@
         <v>14.29</v>
       </c>
       <c r="I47">
-        <v>31.43</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="48">
@@ -1729,28 +1729,28 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C48">
-        <v>36.85</v>
+        <v>36.93</v>
       </c>
       <c r="D48">
         <v>3</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G48">
         <v>25.0</v>
       </c>
       <c r="H48">
-        <v>14.29</v>
+        <v>0.0</v>
       </c>
       <c r="I48">
-        <v>22.86</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="49">
@@ -1758,28 +1758,28 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="C49">
-        <v>36.71</v>
+        <v>35.92</v>
       </c>
       <c r="D49">
         <v>3</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G49">
         <v>25.0</v>
       </c>
       <c r="H49">
-        <v>0.0</v>
+        <v>14.29</v>
       </c>
       <c r="I49">
-        <v>45.71</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="50">
@@ -1790,7 +1790,7 @@
         <v>31</v>
       </c>
       <c r="C50">
-        <v>31.52</v>
+        <v>31.62</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G50">
         <v>8.33</v>
@@ -1808,7 +1808,7 @@
         <v>0.0</v>
       </c>
       <c r="I50">
-        <v>77.14</v>
+        <v>77.78</v>
       </c>
     </row>
   </sheetData>
@@ -1867,514 +1867,514 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000084</v>
+        <v>115000085</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E2">
+        <v>17</v>
+      </c>
+      <c r="F2">
+        <v>18</v>
+      </c>
+      <c r="G2">
+        <v>27</v>
+      </c>
+      <c r="H2">
+        <v>37</v>
+      </c>
+      <c r="I2">
         <v>19</v>
-      </c>
-      <c r="F2">
-        <v>26</v>
-      </c>
-      <c r="G2">
-        <v>29</v>
-      </c>
-      <c r="H2">
-        <v>48</v>
-      </c>
-      <c r="I2">
-        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000083</v>
+        <v>115000084</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>26</v>
       </c>
       <c r="G3">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H3">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C4">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E4">
+        <v>23</v>
+      </c>
+      <c r="F4">
         <v>26</v>
       </c>
-      <c r="F4">
-        <v>32</v>
-      </c>
       <c r="G4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H4">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C5">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H5">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I5">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D6">
         <v>14</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H6">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E7">
         <v>25</v>
       </c>
       <c r="F7">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G7">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H7">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I7">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <v>12</v>
       </c>
       <c r="E8">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G8">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H8">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D9">
         <v>12</v>
       </c>
       <c r="E9">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F9">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G9">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H9">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I9">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E10">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F10">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G10">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H10">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I10">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C11">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D11">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E11">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F11">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H11">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I11">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C12">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F12">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H12">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I12">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D13">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E13">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F13">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G13">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H13">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I13">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E14">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F14">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G14">
         <v>35</v>
       </c>
       <c r="H14">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I14">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F15">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G15">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H15">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I15">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C16">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E16">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F16">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G16">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H16">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I16">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C17">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D17">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E17">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F17">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G17">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H17">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I17">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C18">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D18">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E18">
         <v>15</v>
@@ -2383,345 +2383,345 @@
         <v>18</v>
       </c>
       <c r="G18">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H18">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I18">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C19">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D19">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E19">
+        <v>15</v>
+      </c>
+      <c r="F19">
+        <v>18</v>
+      </c>
+      <c r="G19">
         <v>19</v>
       </c>
-      <c r="F19">
-        <v>23</v>
-      </c>
-      <c r="G19">
-        <v>39</v>
-      </c>
       <c r="H19">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I19">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C20">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D20">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E20">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F20">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G20">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H20">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I20">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C21">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D21">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E21">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F21">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G21">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H21">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C22">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D22">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E22">
+        <v>23</v>
+      </c>
+      <c r="F22">
+        <v>24</v>
+      </c>
+      <c r="G22">
         <v>29</v>
       </c>
-      <c r="F22">
-        <v>33</v>
-      </c>
-      <c r="G22">
-        <v>34</v>
-      </c>
       <c r="H22">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I22">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D23">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E23">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F23">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G23">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H23">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I23">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E24">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F24">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G24">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H24">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I24">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E25">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F25">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G25">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H25">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I25">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C26">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E26">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F26">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G26">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H26">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I26">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C27">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D27">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E27">
         <v>25</v>
       </c>
       <c r="F27">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G27">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H27">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I27">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C28">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D28">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E28">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F28">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G28">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H28">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I28">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C29">
+        <v>8</v>
+      </c>
+      <c r="D29">
+        <v>9</v>
+      </c>
+      <c r="E29">
+        <v>16</v>
+      </c>
+      <c r="F29">
         <v>20</v>
-      </c>
-      <c r="D29">
-        <v>26</v>
-      </c>
-      <c r="E29">
-        <v>29</v>
-      </c>
-      <c r="F29">
-        <v>31</v>
       </c>
       <c r="G29">
         <v>37</v>
@@ -2730,689 +2730,689 @@
         <v>49</v>
       </c>
       <c r="I29">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C30">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D30">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E30">
         <v>29</v>
       </c>
       <c r="F30">
+        <v>31</v>
+      </c>
+      <c r="G30">
         <v>37</v>
       </c>
-      <c r="G30">
-        <v>47</v>
-      </c>
       <c r="H30">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I30">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C31">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D31">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E31">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F31">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G31">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="H31">
         <v>48</v>
       </c>
       <c r="I31">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C32">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D32">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E32">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F32">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G32">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H32">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I32">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C33">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D33">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E33">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F33">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G33">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H33">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I33">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C34">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D34">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E34">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F34">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G34">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H34">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I34">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D35">
+        <v>12</v>
+      </c>
+      <c r="E35">
         <v>18</v>
       </c>
-      <c r="E35">
-        <v>25</v>
-      </c>
       <c r="F35">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G35">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H35">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I35">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D36">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E36">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F36">
         <v>28</v>
       </c>
       <c r="G36">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H36">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I36">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D37">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E37">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F37">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G37">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H37">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I37">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D38">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E38">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F38">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G38">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H38">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I38">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C39">
+        <v>6</v>
+      </c>
+      <c r="D39">
+        <v>10</v>
+      </c>
+      <c r="E39">
+        <v>14</v>
+      </c>
+      <c r="F39">
+        <v>25</v>
+      </c>
+      <c r="G39">
+        <v>26</v>
+      </c>
+      <c r="H39">
+        <v>32</v>
+      </c>
+      <c r="I39">
         <v>7</v>
-      </c>
-      <c r="D39">
-        <v>14</v>
-      </c>
-      <c r="E39">
-        <v>16</v>
-      </c>
-      <c r="F39">
-        <v>37</v>
-      </c>
-      <c r="G39">
-        <v>39</v>
-      </c>
-      <c r="H39">
-        <v>47</v>
-      </c>
-      <c r="I39">
-        <v>34</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D40">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E40">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F40">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G40">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H40">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I40">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D41">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E41">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F41">
+        <v>19</v>
+      </c>
+      <c r="G41">
+        <v>20</v>
+      </c>
+      <c r="H41">
+        <v>40</v>
+      </c>
+      <c r="I41">
         <v>22</v>
-      </c>
-      <c r="G41">
-        <v>40</v>
-      </c>
-      <c r="H41">
-        <v>45</v>
-      </c>
-      <c r="I41">
-        <v>18</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C42">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D42">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E42">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F42">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G42">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H42">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I42">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C43">
         <v>4</v>
       </c>
       <c r="D43">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E43">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F43">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G43">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H43">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I43">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E44">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F44">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G44">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H44">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I44">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C45">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D45">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E45">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F45">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G45">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H45">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I45">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C46">
         <v>5</v>
       </c>
       <c r="D46">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E46">
+        <v>13</v>
+      </c>
+      <c r="F46">
         <v>25</v>
       </c>
-      <c r="F46">
-        <v>40</v>
-      </c>
       <c r="G46">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H46">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I46">
-        <v>39</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D47">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E47">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F47">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G47">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H47">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I47">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C48">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D48">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E48">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F48">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G48">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H48">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I48">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C49">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D49">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E49">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F49">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G49">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H49">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I49">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C50">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D50">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E50">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F50">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G50">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H50">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I50">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D51">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E51">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F51">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G51">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H51">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I51">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-09-04 第 115000085 期；威力彩 2026-09-03 第 115000071 期</t>
+          <t>大樂透 2026-09-04 第 115000085 期；威力彩 2026-09-07 第 115000072 期</t>
         </is>
       </c>
     </row>
@@ -112,7 +112,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -121,7 +121,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -143,7 +143,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9, 19, 24, 29, 35, 38</t>
+          <t>9, 19, 22, 29, 35, 38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -152,7 +152,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -161,7 +161,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.381 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.357 碼/期</t>
         </is>
       </c>
     </row>
@@ -3464,10 +3464,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>1.0</v>
+        <v>1.024</v>
       </c>
       <c r="D2">
-        <v>28.6</v>
+        <v>31.0</v>
       </c>
       <c r="E2">
         <v>4.8</v>
@@ -3479,14 +3479,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>冷號觀察</t>
+          <t>冷熱混合</t>
         </is>
       </c>
       <c r="B3">
         <v>42</v>
       </c>
       <c r="C3">
-        <v>1.0</v>
+        <v>1.024</v>
       </c>
       <c r="D3">
         <v>31.0</v>
@@ -3501,7 +3501,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>冷熱混合</t>
+          <t>近期趨勢</t>
         </is>
       </c>
       <c r="B4">
@@ -3511,7 +3511,7 @@
         <v>1.0</v>
       </c>
       <c r="D4">
-        <v>28.6</v>
+        <v>23.8</v>
       </c>
       <c r="E4">
         <v>4.8</v>
@@ -3523,14 +3523,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>近期趨勢</t>
+          <t>均衡分散</t>
         </is>
       </c>
       <c r="B5">
         <v>42</v>
       </c>
       <c r="C5">
-        <v>0.952</v>
+        <v>0.976</v>
       </c>
       <c r="D5">
         <v>21.4</v>
@@ -3545,20 +3545,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>均衡分散</t>
+          <t>冷號觀察</t>
         </is>
       </c>
       <c r="B6">
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.929</v>
+        <v>0.976</v>
       </c>
       <c r="D6">
-        <v>19.0</v>
+        <v>31.0</v>
       </c>
       <c r="E6">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -3574,10 +3574,10 @@
         <v>42</v>
       </c>
       <c r="C7">
-        <v>0.619</v>
+        <v>0.667</v>
       </c>
       <c r="D7">
-        <v>9.5</v>
+        <v>11.9</v>
       </c>
       <c r="E7">
         <v>0.0</v>
@@ -3648,7 +3648,7 @@
         <v>19</v>
       </c>
       <c r="C2">
-        <v>74.89</v>
+        <v>73.32</v>
       </c>
       <c r="D2">
         <v>12</v>
@@ -3657,16 +3657,16 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>92.31</v>
+        <v>85.71</v>
       </c>
       <c r="H2">
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>0.0</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="3">
@@ -3677,22 +3677,22 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>69.5</v>
+        <v>72.43</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>69.23</v>
+        <v>71.43</v>
       </c>
       <c r="H3">
-        <v>83.33</v>
+        <v>100.0</v>
       </c>
       <c r="I3">
         <v>0.0</v>
@@ -3706,25 +3706,25 @@
         <v>31</v>
       </c>
       <c r="C4">
-        <v>68.66</v>
+        <v>67.1</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4">
         <v>4</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G4">
-        <v>76.92</v>
+        <v>64.29</v>
       </c>
       <c r="H4">
         <v>66.67</v>
       </c>
       <c r="I4">
-        <v>19.44</v>
+        <v>21.62</v>
       </c>
     </row>
     <row r="5">
@@ -3732,28 +3732,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>68.23</v>
+        <v>65.07</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>92.31</v>
+        <v>64.29</v>
       </c>
       <c r="H5">
         <v>66.67</v>
       </c>
       <c r="I5">
-        <v>11.11</v>
+        <v>8.11</v>
       </c>
     </row>
     <row r="6">
@@ -3761,28 +3761,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C6">
-        <v>66.18</v>
+        <v>65.07</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E6">
         <v>4</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>61.54</v>
+        <v>100.0</v>
       </c>
       <c r="H6">
         <v>66.67</v>
       </c>
       <c r="I6">
-        <v>8.33</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7">
@@ -3790,28 +3790,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C7">
-        <v>66.17</v>
+        <v>64.83</v>
       </c>
       <c r="D7">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E7">
         <v>4</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>69.23</v>
+        <v>92.86</v>
       </c>
       <c r="H7">
         <v>66.67</v>
       </c>
       <c r="I7">
-        <v>5.56</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8">
@@ -3822,7 +3822,7 @@
         <v>8</v>
       </c>
       <c r="C8">
-        <v>65.75</v>
+        <v>64.67</v>
       </c>
       <c r="D8">
         <v>9</v>
@@ -3831,16 +3831,16 @@
         <v>4</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>69.23</v>
+        <v>64.29</v>
       </c>
       <c r="H8">
         <v>66.67</v>
       </c>
       <c r="I8">
-        <v>2.78</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="9">
@@ -3848,10 +3848,10 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="C9">
-        <v>64.47</v>
+        <v>61.87</v>
       </c>
       <c r="D9">
         <v>13</v>
@@ -3860,16 +3860,16 @@
         <v>3</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9">
-        <v>100.0</v>
+        <v>92.86</v>
       </c>
       <c r="H9">
         <v>50.0</v>
       </c>
       <c r="I9">
-        <v>11.11</v>
+        <v>8.11</v>
       </c>
     </row>
     <row r="10">
@@ -3877,28 +3877,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C10">
-        <v>63.63</v>
+        <v>61.06</v>
       </c>
       <c r="D10">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>100.0</v>
+        <v>57.14</v>
       </c>
       <c r="H10">
         <v>50.0</v>
       </c>
       <c r="I10">
-        <v>5.56</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="11">
@@ -3909,7 +3909,7 @@
         <v>13</v>
       </c>
       <c r="C11">
-        <v>62.41</v>
+        <v>61.03</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -3918,16 +3918,16 @@
         <v>2</v>
       </c>
       <c r="F11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G11">
-        <v>76.92</v>
+        <v>71.43</v>
       </c>
       <c r="H11">
         <v>33.33</v>
       </c>
       <c r="I11">
-        <v>33.33</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="12">
@@ -3935,28 +3935,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="C12">
-        <v>61.91</v>
+        <v>60.25</v>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F12">
         <v>2</v>
       </c>
       <c r="G12">
-        <v>46.15</v>
+        <v>57.14</v>
       </c>
       <c r="H12">
-        <v>83.33</v>
+        <v>50.0</v>
       </c>
       <c r="I12">
-        <v>5.56</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="13">
@@ -3964,28 +3964,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C13">
-        <v>61.57</v>
+        <v>60.17</v>
       </c>
       <c r="D13">
         <v>11</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>84.62</v>
+        <v>78.57</v>
       </c>
       <c r="H13">
-        <v>33.33</v>
+        <v>50.0</v>
       </c>
       <c r="I13">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="14">
@@ -3993,13 +3993,13 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>61.18</v>
+        <v>60.09</v>
       </c>
       <c r="D14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -4008,13 +4008,13 @@
         <v>1</v>
       </c>
       <c r="G14">
-        <v>61.54</v>
+        <v>64.29</v>
       </c>
       <c r="H14">
         <v>50.0</v>
       </c>
       <c r="I14">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="15">
@@ -4022,10 +4022,10 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C15">
-        <v>61.17</v>
+        <v>60.09</v>
       </c>
       <c r="D15">
         <v>9</v>
@@ -4034,16 +4034,16 @@
         <v>3</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15">
-        <v>69.23</v>
+        <v>64.29</v>
       </c>
       <c r="H15">
         <v>50.0</v>
       </c>
       <c r="I15">
-        <v>0.0</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="16">
@@ -4051,28 +4051,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C16">
-        <v>61.17</v>
+        <v>59.73</v>
       </c>
       <c r="D16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G16">
-        <v>69.23</v>
+        <v>57.14</v>
       </c>
       <c r="H16">
-        <v>50.0</v>
+        <v>33.33</v>
       </c>
       <c r="I16">
-        <v>0.0</v>
+        <v>29.73</v>
       </c>
     </row>
     <row r="17">
@@ -4080,28 +4080,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C17">
-        <v>61.16</v>
+        <v>58.76</v>
       </c>
       <c r="D17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
       <c r="F17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G17">
-        <v>76.92</v>
+        <v>64.29</v>
       </c>
       <c r="H17">
         <v>33.33</v>
       </c>
       <c r="I17">
-        <v>25.0</v>
+        <v>21.62</v>
       </c>
     </row>
     <row r="18">
@@ -4109,28 +4109,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C18">
-        <v>60.76</v>
+        <v>57.14</v>
       </c>
       <c r="D18">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F18">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G18">
-        <v>61.54</v>
+        <v>42.86</v>
       </c>
       <c r="H18">
-        <v>33.33</v>
+        <v>66.67</v>
       </c>
       <c r="I18">
-        <v>27.78</v>
+        <v>8.11</v>
       </c>
     </row>
     <row r="19">
@@ -4138,28 +4138,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>60.32</v>
+        <v>57.02</v>
       </c>
       <c r="D19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G19">
-        <v>76.92</v>
+        <v>50.0</v>
       </c>
       <c r="H19">
-        <v>33.33</v>
+        <v>50.0</v>
       </c>
       <c r="I19">
-        <v>19.44</v>
+        <v>8.11</v>
       </c>
     </row>
     <row r="20">
@@ -4167,28 +4167,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="C20">
-        <v>57.79</v>
+        <v>55.65</v>
       </c>
       <c r="D20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G20">
-        <v>53.85</v>
+        <v>71.43</v>
       </c>
       <c r="H20">
-        <v>50.0</v>
+        <v>16.67</v>
       </c>
       <c r="I20">
-        <v>5.56</v>
+        <v>27.03</v>
       </c>
     </row>
     <row r="21">
@@ -4199,25 +4199,25 @@
         <v>14</v>
       </c>
       <c r="C21">
-        <v>57.0</v>
+        <v>55.52</v>
       </c>
       <c r="D21">
         <v>9</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>69.23</v>
+        <v>64.29</v>
       </c>
       <c r="H21">
-        <v>16.67</v>
+        <v>33.33</v>
       </c>
       <c r="I21">
-        <v>27.78</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="22">
@@ -4225,28 +4225,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C22">
-        <v>56.95</v>
+        <v>55.41</v>
       </c>
       <c r="D22">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22">
         <v>10</v>
       </c>
       <c r="G22">
-        <v>53.85</v>
+        <v>64.29</v>
       </c>
       <c r="H22">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="I22">
-        <v>27.78</v>
+        <v>27.03</v>
       </c>
     </row>
     <row r="23">
@@ -4254,28 +4254,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C23">
-        <v>56.59</v>
+        <v>55.27</v>
       </c>
       <c r="D23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>69.23</v>
+        <v>57.14</v>
       </c>
       <c r="H23">
-        <v>16.67</v>
+        <v>33.33</v>
       </c>
       <c r="I23">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="24">
@@ -4286,7 +4286,7 @@
         <v>38</v>
       </c>
       <c r="C24">
-        <v>56.55</v>
+        <v>54.76</v>
       </c>
       <c r="D24">
         <v>13</v>
@@ -4295,16 +4295,16 @@
         <v>1</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G24">
-        <v>100.0</v>
+        <v>92.86</v>
       </c>
       <c r="H24">
         <v>16.67</v>
       </c>
       <c r="I24">
-        <v>13.89</v>
+        <v>16.22</v>
       </c>
     </row>
     <row r="25">
@@ -4312,28 +4312,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C25">
-        <v>55.7</v>
+        <v>53.05</v>
       </c>
       <c r="D25">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G25">
-        <v>53.85</v>
+        <v>78.57</v>
       </c>
       <c r="H25">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="I25">
-        <v>19.44</v>
+        <v>8.11</v>
       </c>
     </row>
     <row r="26">
@@ -4341,28 +4341,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>54.49</v>
+        <v>52.16</v>
       </c>
       <c r="D26">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E26">
+        <v>3</v>
+      </c>
+      <c r="F26">
         <v>1</v>
       </c>
-      <c r="F26">
-        <v>2</v>
-      </c>
       <c r="G26">
-        <v>84.62</v>
+        <v>42.86</v>
       </c>
       <c r="H26">
-        <v>16.67</v>
+        <v>50.0</v>
       </c>
       <c r="I26">
-        <v>5.56</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="27">
@@ -4370,28 +4370,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C27">
-        <v>53.99</v>
+        <v>50.71</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G27">
-        <v>46.15</v>
+        <v>50.0</v>
       </c>
       <c r="H27">
-        <v>50.0</v>
+        <v>16.67</v>
       </c>
       <c r="I27">
-        <v>8.33</v>
+        <v>21.62</v>
       </c>
     </row>
     <row r="28">
@@ -4399,28 +4399,28 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C28">
-        <v>52.74</v>
+        <v>50.43</v>
       </c>
       <c r="D28">
         <v>6</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G28">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="H28">
-        <v>50.0</v>
+        <v>33.33</v>
       </c>
       <c r="I28">
-        <v>0.0</v>
+        <v>18.92</v>
       </c>
     </row>
     <row r="29">
@@ -4428,28 +4428,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C29">
-        <v>51.08</v>
+        <v>50.21</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F29">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G29">
-        <v>46.15</v>
+        <v>35.71</v>
       </c>
       <c r="H29">
-        <v>33.33</v>
+        <v>0.0</v>
       </c>
       <c r="I29">
-        <v>16.67</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="30">
@@ -4457,28 +4457,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C30">
-        <v>51.04</v>
+        <v>49.33</v>
       </c>
       <c r="D30">
         <v>5</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F30">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="G30">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="H30">
-        <v>0.0</v>
+        <v>50.0</v>
       </c>
       <c r="I30">
-        <v>100.0</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="31">
@@ -4489,7 +4489,7 @@
         <v>30</v>
       </c>
       <c r="C31">
-        <v>44.37</v>
+        <v>43.95</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -4498,16 +4498,16 @@
         <v>2</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="H31">
         <v>33.33</v>
       </c>
       <c r="I31">
-        <v>0.0</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="32">
@@ -4518,7 +4518,7 @@
         <v>5</v>
       </c>
       <c r="C32">
-        <v>42.29</v>
+        <v>41.81</v>
       </c>
       <c r="D32">
         <v>5</v>
@@ -4527,16 +4527,16 @@
         <v>1</v>
       </c>
       <c r="F32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G32">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="H32">
         <v>16.67</v>
       </c>
       <c r="I32">
-        <v>13.89</v>
+        <v>16.22</v>
       </c>
     </row>
     <row r="33">
@@ -4547,7 +4547,7 @@
         <v>18</v>
       </c>
       <c r="C33">
-        <v>42.29</v>
+        <v>41.81</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -4556,16 +4556,16 @@
         <v>1</v>
       </c>
       <c r="F33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G33">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="H33">
         <v>16.67</v>
       </c>
       <c r="I33">
-        <v>13.89</v>
+        <v>16.22</v>
       </c>
     </row>
     <row r="34">
@@ -4573,28 +4573,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C34">
-        <v>40.62</v>
+        <v>40.31</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34">
-        <v>38.46</v>
+        <v>28.57</v>
       </c>
       <c r="H34">
-        <v>16.67</v>
+        <v>33.33</v>
       </c>
       <c r="I34">
-        <v>2.78</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="35">
@@ -4602,28 +4602,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C35">
-        <v>40.58</v>
+        <v>39.28</v>
       </c>
       <c r="D35">
         <v>4</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G35">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="H35">
-        <v>33.33</v>
+        <v>0.0</v>
       </c>
       <c r="I35">
-        <v>2.78</v>
+        <v>54.05</v>
       </c>
     </row>
     <row r="36">
@@ -4631,28 +4631,28 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C36">
-        <v>39.75</v>
+        <v>38.18</v>
       </c>
       <c r="D36">
         <v>4</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G36">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="H36">
-        <v>0.0</v>
+        <v>16.67</v>
       </c>
       <c r="I36">
-        <v>52.78</v>
+        <v>18.92</v>
       </c>
     </row>
     <row r="37">
@@ -4660,10 +4660,10 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C37">
-        <v>38.5</v>
+        <v>36.15</v>
       </c>
       <c r="D37">
         <v>4</v>
@@ -4672,16 +4672,16 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G37">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="H37">
         <v>16.67</v>
       </c>
       <c r="I37">
-        <v>16.67</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="38">
@@ -4692,7 +4692,7 @@
         <v>20</v>
       </c>
       <c r="C38">
-        <v>35.12</v>
+        <v>34.94</v>
       </c>
       <c r="D38">
         <v>3</v>
@@ -4701,16 +4701,16 @@
         <v>1</v>
       </c>
       <c r="F38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G38">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="H38">
         <v>16.67</v>
       </c>
       <c r="I38">
-        <v>22.22</v>
+        <v>24.32</v>
       </c>
     </row>
     <row r="39">
@@ -4721,7 +4721,7 @@
         <v>37</v>
       </c>
       <c r="C39">
-        <v>32.21</v>
+        <v>32.11</v>
       </c>
       <c r="D39">
         <v>3</v>
@@ -4730,16 +4730,16 @@
         <v>1</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="H39">
         <v>16.67</v>
       </c>
       <c r="I39">
-        <v>2.78</v>
+        <v>5.41</v>
       </c>
     </row>
   </sheetData>
@@ -4798,108 +4798,108 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F3">
         <v>19</v>
       </c>
       <c r="G3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H3">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>8</v>
+      </c>
+      <c r="E4">
+        <v>12</v>
+      </c>
+      <c r="F4">
+        <v>19</v>
+      </c>
+      <c r="G4">
+        <v>32</v>
+      </c>
+      <c r="H4">
+        <v>37</v>
+      </c>
+      <c r="I4">
         <v>2</v>
-      </c>
-      <c r="D4">
-        <v>7</v>
-      </c>
-      <c r="E4">
-        <v>9</v>
-      </c>
-      <c r="F4">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>24</v>
-      </c>
-      <c r="H4">
-        <v>36</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D5">
         <v>7</v>
@@ -4908,230 +4908,230 @@
         <v>9</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H5">
         <v>36</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E6">
         <v>9</v>
       </c>
       <c r="F6">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>9</v>
+      </c>
+      <c r="F7">
         <v>11</v>
       </c>
-      <c r="E7">
-        <v>18</v>
-      </c>
-      <c r="F7">
-        <v>19</v>
-      </c>
       <c r="G7">
+        <v>29</v>
+      </c>
+      <c r="H7">
         <v>35</v>
       </c>
-      <c r="H7">
-        <v>38</v>
-      </c>
       <c r="I7">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G8">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H8">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="I8">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C9">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E9">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G9">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H9">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D10">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E10">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F10">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G10">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H10">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I10">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>7</v>
+      </c>
+      <c r="E11">
+        <v>8</v>
+      </c>
+      <c r="F11">
+        <v>20</v>
+      </c>
+      <c r="G11">
+        <v>26</v>
+      </c>
+      <c r="H11">
+        <v>33</v>
+      </c>
+      <c r="I11">
         <v>4</v>
-      </c>
-      <c r="D11">
-        <v>15</v>
-      </c>
-      <c r="E11">
-        <v>22</v>
-      </c>
-      <c r="F11">
-        <v>26</v>
-      </c>
-      <c r="G11">
-        <v>34</v>
-      </c>
-      <c r="H11">
-        <v>36</v>
-      </c>
-      <c r="I11">
-        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C12">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D12">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E12">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F12">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G12">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H12">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I12">
         <v>7</v>
@@ -5139,30 +5139,30 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C13">
+        <v>8</v>
+      </c>
+      <c r="D13">
+        <v>14</v>
+      </c>
+      <c r="E13">
+        <v>17</v>
+      </c>
+      <c r="F13">
         <v>19</v>
       </c>
-      <c r="D13">
-        <v>22</v>
-      </c>
-      <c r="E13">
-        <v>28</v>
-      </c>
-      <c r="F13">
-        <v>31</v>
-      </c>
       <c r="G13">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H13">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I13">
         <v>7</v>
@@ -5170,30 +5170,30 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C14">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D14">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E14">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F14">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I14">
         <v>7</v>
@@ -5201,24 +5201,24 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E15">
         <v>13</v>
       </c>
       <c r="F15">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G15">
         <v>29</v>
@@ -5227,97 +5227,97 @@
         <v>31</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C16">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D16">
+        <v>12</v>
+      </c>
+      <c r="E16">
+        <v>13</v>
+      </c>
+      <c r="F16">
         <v>23</v>
       </c>
-      <c r="E16">
-        <v>25</v>
-      </c>
-      <c r="F16">
+      <c r="G16">
         <v>29</v>
       </c>
-      <c r="G16">
-        <v>34</v>
-      </c>
       <c r="H16">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I16">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C17">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D17">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E17">
+        <v>25</v>
+      </c>
+      <c r="F17">
         <v>29</v>
       </c>
-      <c r="F17">
-        <v>32</v>
-      </c>
       <c r="G17">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H17">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I17">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C18">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E18">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F18">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G18">
         <v>35</v>
       </c>
       <c r="H18">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I18">
         <v>6</v>
@@ -5325,402 +5325,402 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C19">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D19">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E19">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F19">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G19">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H19">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D20">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E20">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F20">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G20">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H20">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I20">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E21">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F21">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G21">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H21">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C22">
+        <v>5</v>
+      </c>
+      <c r="D22">
         <v>6</v>
       </c>
-      <c r="D22">
-        <v>10</v>
-      </c>
       <c r="E22">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F22">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G22">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H22">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C23">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D23">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E23">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F23">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G23">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H23">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I23">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D24">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E24">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F24">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G24">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I24">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
+        <v>8</v>
+      </c>
+      <c r="E25">
+        <v>9</v>
+      </c>
+      <c r="F25">
+        <v>15</v>
+      </c>
+      <c r="G25">
+        <v>18</v>
+      </c>
+      <c r="H25">
+        <v>23</v>
+      </c>
+      <c r="I25">
         <v>4</v>
-      </c>
-      <c r="D25">
-        <v>17</v>
-      </c>
-      <c r="E25">
-        <v>19</v>
-      </c>
-      <c r="F25">
-        <v>25</v>
-      </c>
-      <c r="G25">
-        <v>28</v>
-      </c>
-      <c r="H25">
-        <v>29</v>
-      </c>
-      <c r="I25">
-        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C26">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D26">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E26">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F26">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G26">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H26">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I26">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D27">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E27">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F27">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G27">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H27">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I27">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C28">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D28">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E28">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F28">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G28">
         <v>28</v>
       </c>
       <c r="H28">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I28">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D29">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E29">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F29">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G29">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H29">
         <v>35</v>
       </c>
       <c r="I29">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E30">
+        <v>9</v>
+      </c>
+      <c r="F30">
+        <v>15</v>
+      </c>
+      <c r="G30">
         <v>24</v>
       </c>
-      <c r="F30">
-        <v>31</v>
-      </c>
-      <c r="G30">
-        <v>34</v>
-      </c>
       <c r="H30">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I30">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C31">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D31">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E31">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F31">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G31">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I31">
         <v>3</v>
@@ -5728,554 +5728,554 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D32">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E32">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F32">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G32">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H32">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I32">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C33">
         <v>6</v>
       </c>
       <c r="D33">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E33">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F33">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G33">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H33">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I33">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C34">
         <v>6</v>
       </c>
       <c r="D34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E34">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F34">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G34">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H34">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I34">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C35">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D35">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E35">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F35">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G35">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H35">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I35">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C36">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D36">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E36">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F36">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G36">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H36">
         <v>38</v>
       </c>
       <c r="I36">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C37">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D37">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E37">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F37">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G37">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H37">
         <v>38</v>
       </c>
       <c r="I37">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E38">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F38">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G38">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H38">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I38">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C39">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D39">
+        <v>4</v>
+      </c>
+      <c r="E39">
+        <v>13</v>
+      </c>
+      <c r="F39">
+        <v>19</v>
+      </c>
+      <c r="G39">
+        <v>27</v>
+      </c>
+      <c r="H39">
+        <v>30</v>
+      </c>
+      <c r="I39">
         <v>8</v>
-      </c>
-      <c r="E39">
-        <v>27</v>
-      </c>
-      <c r="F39">
-        <v>33</v>
-      </c>
-      <c r="G39">
-        <v>35</v>
-      </c>
-      <c r="H39">
-        <v>38</v>
-      </c>
-      <c r="I39">
-        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C40">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D40">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E40">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F40">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G40">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H40">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I40">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D41">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E41">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F41">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G41">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H41">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I41">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C42">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D42">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E42">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F42">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G42">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H42">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I42">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000030</v>
+        <v>115000031</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D43">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E43">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F43">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G43">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H43">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="I43">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000029</v>
+        <v>115000030</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D44">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E44">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F44">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G44">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H44">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I44">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000028</v>
+        <v>115000029</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D45">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E45">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F45">
         <v>27</v>
       </c>
       <c r="G45">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H45">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I45">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000027</v>
+        <v>115000028</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C46">
         <v>5</v>
       </c>
       <c r="D46">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E46">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F46">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G46">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H46">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I46">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000026</v>
+        <v>115000027</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D47">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E47">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F47">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G47">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H47">
         <v>34</v>
       </c>
       <c r="I47">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000025</v>
+        <v>115000026</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C48">
+        <v>2</v>
+      </c>
+      <c r="D48">
         <v>13</v>
       </c>
-      <c r="D48">
-        <v>14</v>
-      </c>
       <c r="E48">
+        <v>21</v>
+      </c>
+      <c r="F48">
         <v>22</v>
       </c>
-      <c r="F48">
-        <v>28</v>
-      </c>
       <c r="G48">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H48">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I48">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000024</v>
+        <v>115000025</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D49">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E49">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F49">
         <v>28</v>
       </c>
       <c r="G49">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H49">
         <v>38</v>
@@ -6286,58 +6286,58 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000023</v>
+        <v>115000024</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50">
         <v>9</v>
       </c>
-      <c r="D50">
-        <v>13</v>
-      </c>
       <c r="E50">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F50">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G50">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H50">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I50">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000022</v>
+        <v>115000023</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C51">
+        <v>9</v>
+      </c>
+      <c r="D51">
+        <v>13</v>
+      </c>
+      <c r="E51">
         <v>14</v>
       </c>
-      <c r="D51">
-        <v>26</v>
-      </c>
-      <c r="E51">
-        <v>28</v>
-      </c>
       <c r="F51">
+        <v>18</v>
+      </c>
+      <c r="G51">
         <v>31</v>
-      </c>
-      <c r="G51">
-        <v>32</v>
       </c>
       <c r="H51">
         <v>34</v>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-09-04 第 115000085 期；威力彩 2026-09-07 第 115000072 期</t>
+          <t>大樂透 2026-09-08 第 115000086 期；威力彩 2026-09-07 第 115000072 期</t>
         </is>
       </c>
     </row>
@@ -47,7 +47,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>115000085</v>
+        <v>115000086</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -56,7 +56,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -96,7 +96,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.381 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.333 碼/期</t>
         </is>
       </c>
     </row>
@@ -214,7 +214,7 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>1.0</v>
+        <v>0.976</v>
       </c>
       <c r="D2">
         <v>28.6</v>
@@ -236,7 +236,7 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>0.976</v>
+        <v>0.952</v>
       </c>
       <c r="D3">
         <v>26.2</v>
@@ -258,10 +258,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>0.762</v>
+        <v>0.81</v>
       </c>
       <c r="D4">
-        <v>16.7</v>
+        <v>19.0</v>
       </c>
       <c r="E4">
         <v>2.4</v>
@@ -280,10 +280,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>0.738</v>
+        <v>0.786</v>
       </c>
       <c r="D5">
-        <v>16.7</v>
+        <v>19.0</v>
       </c>
       <c r="E5">
         <v>2.4</v>
@@ -302,7 +302,7 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.619</v>
+        <v>0.643</v>
       </c>
       <c r="D6">
         <v>9.5</v>
@@ -398,16 +398,16 @@
         <v>26</v>
       </c>
       <c r="C2">
-        <v>71.02</v>
+        <v>71.41</v>
       </c>
       <c r="D2">
         <v>12</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>100.0</v>
@@ -416,7 +416,7 @@
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>2.78</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="3">
@@ -424,28 +424,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C3">
-        <v>64.66</v>
+        <v>66.23</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E3">
         <v>5</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>91.67</v>
+        <v>66.67</v>
       </c>
       <c r="H3">
-        <v>71.43</v>
+        <v>83.33</v>
       </c>
       <c r="I3">
-        <v>8.33</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="4">
@@ -456,7 +456,7 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>61.35</v>
+        <v>64.09</v>
       </c>
       <c r="D4">
         <v>8</v>
@@ -465,16 +465,16 @@
         <v>4</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4">
         <v>66.67</v>
       </c>
       <c r="H4">
-        <v>57.14</v>
+        <v>66.67</v>
       </c>
       <c r="I4">
-        <v>11.11</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="5">
@@ -482,28 +482,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>60.88</v>
+        <v>63.84</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>58.33</v>
+        <v>91.67</v>
       </c>
       <c r="H5">
-        <v>57.14</v>
+        <v>66.67</v>
       </c>
       <c r="I5">
-        <v>8.33</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="6">
@@ -514,7 +514,7 @@
         <v>24</v>
       </c>
       <c r="C6">
-        <v>60.23</v>
+        <v>62.99</v>
       </c>
       <c r="D6">
         <v>6</v>
@@ -523,16 +523,16 @@
         <v>4</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6">
         <v>50.0</v>
       </c>
       <c r="H6">
-        <v>57.14</v>
+        <v>66.67</v>
       </c>
       <c r="I6">
-        <v>8.33</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="7">
@@ -543,25 +543,25 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>59.81</v>
+        <v>62.07</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>58.33</v>
+        <v>66.67</v>
       </c>
       <c r="H7">
-        <v>42.86</v>
+        <v>66.67</v>
       </c>
       <c r="I7">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8">
@@ -572,7 +572,7 @@
         <v>25</v>
       </c>
       <c r="C8">
-        <v>58.3</v>
+        <v>60.43</v>
       </c>
       <c r="D8">
         <v>10</v>
@@ -581,16 +581,16 @@
         <v>3</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8">
         <v>83.33</v>
       </c>
       <c r="H8">
-        <v>42.86</v>
+        <v>50.0</v>
       </c>
       <c r="I8">
-        <v>13.89</v>
+        <v>16.22</v>
       </c>
     </row>
     <row r="9">
@@ -601,7 +601,7 @@
         <v>34</v>
       </c>
       <c r="C9">
-        <v>57.92</v>
+        <v>60.04</v>
       </c>
       <c r="D9">
         <v>6</v>
@@ -610,16 +610,16 @@
         <v>3</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G9">
         <v>50.0</v>
       </c>
       <c r="H9">
-        <v>42.86</v>
+        <v>50.0</v>
       </c>
       <c r="I9">
-        <v>16.67</v>
+        <v>18.92</v>
       </c>
     </row>
     <row r="10">
@@ -627,28 +627,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C10">
-        <v>57.73</v>
+        <v>59.12</v>
       </c>
       <c r="D10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>58.33</v>
+        <v>66.67</v>
       </c>
       <c r="H10">
-        <v>42.86</v>
+        <v>50.0</v>
       </c>
       <c r="I10">
-        <v>11.11</v>
+        <v>8.11</v>
       </c>
     </row>
     <row r="11">
@@ -656,13 +656,13 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C11">
-        <v>56.95</v>
+        <v>58.91</v>
       </c>
       <c r="D11">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -671,13 +671,13 @@
         <v>2</v>
       </c>
       <c r="G11">
-        <v>66.67</v>
+        <v>100.0</v>
       </c>
       <c r="H11">
-        <v>42.86</v>
+        <v>50.0</v>
       </c>
       <c r="I11">
-        <v>5.56</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="12">
@@ -685,28 +685,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C12">
-        <v>56.73</v>
+        <v>58.71</v>
       </c>
       <c r="D12">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12">
-        <v>100.0</v>
+        <v>66.67</v>
       </c>
       <c r="H12">
-        <v>42.86</v>
+        <v>50.0</v>
       </c>
       <c r="I12">
-        <v>2.78</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="13">
@@ -714,28 +714,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="C13">
-        <v>56.53</v>
+        <v>56.11</v>
       </c>
       <c r="D13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G13">
-        <v>66.67</v>
+        <v>58.33</v>
       </c>
       <c r="H13">
-        <v>42.86</v>
+        <v>33.33</v>
       </c>
       <c r="I13">
-        <v>2.78</v>
+        <v>16.22</v>
       </c>
     </row>
     <row r="14">
@@ -743,28 +743,28 @@
         <v>13</v>
       </c>
       <c r="B14">
+        <v>33</v>
+      </c>
+      <c r="C14">
+        <v>55.87</v>
+      </c>
+      <c r="D14">
         <v>6</v>
       </c>
-      <c r="C14">
-        <v>54.75</v>
-      </c>
-      <c r="D14">
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
         <v>7</v>
       </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14">
-        <v>14</v>
-      </c>
       <c r="G14">
-        <v>58.33</v>
+        <v>50.0</v>
       </c>
       <c r="H14">
-        <v>14.29</v>
+        <v>33.33</v>
       </c>
       <c r="I14">
-        <v>38.89</v>
+        <v>18.92</v>
       </c>
     </row>
     <row r="15">
@@ -772,10 +772,10 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="C15">
-        <v>54.58</v>
+        <v>55.71</v>
       </c>
       <c r="D15">
         <v>7</v>
@@ -790,10 +790,10 @@
         <v>58.33</v>
       </c>
       <c r="H15">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="I15">
-        <v>13.89</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="16">
@@ -801,28 +801,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C16">
-        <v>54.34</v>
+        <v>54.95</v>
       </c>
       <c r="D16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E16">
         <v>2</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G16">
-        <v>50.0</v>
+        <v>66.67</v>
       </c>
       <c r="H16">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="I16">
-        <v>16.67</v>
+        <v>8.11</v>
       </c>
     </row>
     <row r="17">
@@ -830,28 +830,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C17">
-        <v>53.93</v>
+        <v>54.9</v>
       </c>
       <c r="D17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G17">
-        <v>50.0</v>
+        <v>58.33</v>
       </c>
       <c r="H17">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="I17">
-        <v>13.89</v>
+        <v>8.11</v>
       </c>
     </row>
     <row r="18">
@@ -859,13 +859,13 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C18">
-        <v>53.38</v>
+        <v>54.64</v>
       </c>
       <c r="D18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -874,13 +874,13 @@
         <v>2</v>
       </c>
       <c r="G18">
-        <v>66.67</v>
+        <v>83.33</v>
       </c>
       <c r="H18">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="I18">
-        <v>5.56</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="19">
@@ -888,28 +888,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C19">
-        <v>53.33</v>
+        <v>53.98</v>
       </c>
       <c r="D19">
         <v>7</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G19">
         <v>58.33</v>
       </c>
       <c r="H19">
-        <v>28.57</v>
+        <v>16.67</v>
       </c>
       <c r="I19">
-        <v>5.56</v>
+        <v>29.73</v>
       </c>
     </row>
     <row r="20">
@@ -917,28 +917,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="C20">
-        <v>53.09</v>
+        <v>53.68</v>
       </c>
       <c r="D20">
         <v>7</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G20">
         <v>58.33</v>
       </c>
       <c r="H20">
-        <v>14.29</v>
+        <v>33.33</v>
       </c>
       <c r="I20">
-        <v>27.78</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="21">
@@ -946,28 +946,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C21">
-        <v>53.06</v>
+        <v>53.67</v>
       </c>
       <c r="D21">
+        <v>9</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
         <v>10</v>
       </c>
-      <c r="E21">
-        <v>2</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
       <c r="G21">
-        <v>83.33</v>
+        <v>75.0</v>
       </c>
       <c r="H21">
-        <v>28.57</v>
+        <v>16.67</v>
       </c>
       <c r="I21">
-        <v>2.78</v>
+        <v>27.03</v>
       </c>
     </row>
     <row r="22">
@@ -975,28 +975,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="C22">
-        <v>52.77</v>
+        <v>53.47</v>
       </c>
       <c r="D22">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G22">
-        <v>75.0</v>
+        <v>41.67</v>
       </c>
       <c r="H22">
-        <v>14.29</v>
+        <v>50.0</v>
       </c>
       <c r="I22">
-        <v>25.0</v>
+        <v>8.11</v>
       </c>
     </row>
     <row r="23">
@@ -1004,28 +1004,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C23">
-        <v>51.3</v>
+        <v>53.03</v>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>41.67</v>
+        <v>50.0</v>
       </c>
       <c r="H23">
-        <v>42.86</v>
+        <v>33.33</v>
       </c>
       <c r="I23">
-        <v>5.56</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="24">
@@ -1036,7 +1036,7 @@
         <v>27</v>
       </c>
       <c r="C24">
-        <v>50.47</v>
+        <v>52.66</v>
       </c>
       <c r="D24">
         <v>5</v>
@@ -1045,16 +1045,16 @@
         <v>3</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24">
         <v>41.67</v>
       </c>
       <c r="H24">
-        <v>42.86</v>
+        <v>50.0</v>
       </c>
       <c r="I24">
-        <v>0.0</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="25">
@@ -1062,28 +1062,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25">
-        <v>50.23</v>
+        <v>52.25</v>
       </c>
       <c r="D25">
         <v>5</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G25">
         <v>41.67</v>
       </c>
       <c r="H25">
-        <v>28.57</v>
+        <v>50.0</v>
       </c>
       <c r="I25">
-        <v>22.22</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -1091,28 +1091,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>50.17</v>
+        <v>51.3</v>
       </c>
       <c r="D26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G26">
-        <v>58.33</v>
+        <v>50.0</v>
       </c>
       <c r="H26">
-        <v>14.29</v>
+        <v>16.67</v>
       </c>
       <c r="I26">
-        <v>8.33</v>
+        <v>16.22</v>
       </c>
     </row>
     <row r="27">
@@ -1120,28 +1120,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="C27">
-        <v>49.94</v>
+        <v>50.78</v>
       </c>
       <c r="D27">
         <v>6</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G27">
         <v>50.0</v>
       </c>
       <c r="H27">
-        <v>14.29</v>
+        <v>0.0</v>
       </c>
       <c r="I27">
-        <v>11.11</v>
+        <v>40.54</v>
       </c>
     </row>
     <row r="28">
@@ -1149,28 +1149,28 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="C28">
-        <v>49.39</v>
+        <v>50.49</v>
       </c>
       <c r="D28">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E28">
         <v>1</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G28">
-        <v>66.67</v>
+        <v>50.0</v>
       </c>
       <c r="H28">
-        <v>14.29</v>
+        <v>16.67</v>
       </c>
       <c r="I28">
-        <v>2.78</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="29">
@@ -1178,10 +1178,10 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="C29">
-        <v>49.34</v>
+        <v>50.33</v>
       </c>
       <c r="D29">
         <v>7</v>
@@ -1190,16 +1190,16 @@
         <v>1</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29">
         <v>58.33</v>
       </c>
       <c r="H29">
-        <v>14.29</v>
+        <v>16.67</v>
       </c>
       <c r="I29">
-        <v>2.78</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="30">
@@ -1207,28 +1207,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="C30">
-        <v>48.97</v>
+        <v>50.33</v>
       </c>
       <c r="D30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30">
-        <v>66.67</v>
+        <v>58.33</v>
       </c>
       <c r="H30">
-        <v>14.29</v>
+        <v>16.67</v>
       </c>
       <c r="I30">
-        <v>0.0</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="31">
@@ -1236,28 +1236,28 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C31">
-        <v>48.92</v>
+        <v>49.97</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="G31">
-        <v>41.67</v>
+        <v>66.67</v>
       </c>
       <c r="H31">
-        <v>0.0</v>
+        <v>16.67</v>
       </c>
       <c r="I31">
-        <v>61.11</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="32">
@@ -1265,28 +1265,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C32">
-        <v>48.27</v>
+        <v>49.7</v>
       </c>
       <c r="D32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G32">
-        <v>50.0</v>
+        <v>41.67</v>
       </c>
       <c r="H32">
-        <v>14.29</v>
+        <v>33.33</v>
       </c>
       <c r="I32">
-        <v>0.0</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="33">
@@ -1294,28 +1294,28 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C33">
-        <v>48.14</v>
+        <v>49.27</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G33">
-        <v>41.67</v>
+        <v>50.0</v>
       </c>
       <c r="H33">
-        <v>28.57</v>
+        <v>16.67</v>
       </c>
       <c r="I33">
-        <v>8.33</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="34">
@@ -1323,28 +1323,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C34">
-        <v>47.72</v>
+        <v>48.87</v>
       </c>
       <c r="D34">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34">
         <v>0</v>
       </c>
-      <c r="F34">
-        <v>31</v>
-      </c>
       <c r="G34">
-        <v>33.33</v>
+        <v>50.0</v>
       </c>
       <c r="H34">
+        <v>16.67</v>
+      </c>
+      <c r="I34">
         <v>0.0</v>
-      </c>
-      <c r="I34">
-        <v>86.11</v>
       </c>
     </row>
     <row r="35">
@@ -1355,7 +1355,7 @@
         <v>39</v>
       </c>
       <c r="C35">
-        <v>47.25</v>
+        <v>47.45</v>
       </c>
       <c r="D35">
         <v>5</v>
@@ -1364,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="F35">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G35">
         <v>41.67</v>
@@ -1373,7 +1373,7 @@
         <v>0.0</v>
       </c>
       <c r="I35">
-        <v>50.0</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="36">
@@ -1381,28 +1381,28 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="C36">
-        <v>47.07</v>
+        <v>46.78</v>
       </c>
       <c r="D36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36">
         <v>9</v>
       </c>
       <c r="G36">
-        <v>41.67</v>
+        <v>33.33</v>
       </c>
       <c r="H36">
-        <v>14.29</v>
+        <v>33.33</v>
       </c>
       <c r="I36">
-        <v>25.0</v>
+        <v>24.32</v>
       </c>
     </row>
     <row r="37">
@@ -1410,28 +1410,28 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="C37">
-        <v>46.89</v>
+        <v>46.37</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E37">
         <v>2</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G37">
-        <v>41.67</v>
+        <v>33.33</v>
       </c>
       <c r="H37">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="I37">
-        <v>0.0</v>
+        <v>21.62</v>
       </c>
     </row>
     <row r="38">
@@ -1439,28 +1439,28 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C38">
-        <v>46.0</v>
+        <v>44.85</v>
       </c>
       <c r="D38">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E38">
         <v>0</v>
       </c>
       <c r="F38">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="G38">
-        <v>41.67</v>
+        <v>25.0</v>
       </c>
       <c r="H38">
         <v>0.0</v>
       </c>
       <c r="I38">
-        <v>41.67</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="39">
@@ -1468,10 +1468,10 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="C39">
-        <v>44.86</v>
+        <v>44.35</v>
       </c>
       <c r="D39">
         <v>4</v>
@@ -1480,16 +1480,16 @@
         <v>2</v>
       </c>
       <c r="F39">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G39">
         <v>33.33</v>
       </c>
       <c r="H39">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="I39">
-        <v>19.44</v>
+        <v>8.11</v>
       </c>
     </row>
     <row r="40">
@@ -1497,28 +1497,28 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C40">
-        <v>44.85</v>
+        <v>44.32</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="G40">
-        <v>25.0</v>
+        <v>41.67</v>
       </c>
       <c r="H40">
-        <v>0.0</v>
+        <v>16.67</v>
       </c>
       <c r="I40">
-        <v>100.0</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="41">
@@ -1526,10 +1526,10 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C41">
-        <v>43.32</v>
+        <v>44.32</v>
       </c>
       <c r="D41">
         <v>5</v>
@@ -1538,16 +1538,16 @@
         <v>1</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41">
         <v>41.67</v>
       </c>
       <c r="H41">
-        <v>14.29</v>
+        <v>16.67</v>
       </c>
       <c r="I41">
-        <v>0.0</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="42">
@@ -1555,28 +1555,28 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C42">
-        <v>42.78</v>
+        <v>42.82</v>
       </c>
       <c r="D42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="G42">
-        <v>33.33</v>
+        <v>25.0</v>
       </c>
       <c r="H42">
-        <v>28.57</v>
+        <v>0.0</v>
       </c>
       <c r="I42">
-        <v>5.56</v>
+        <v>86.49</v>
       </c>
     </row>
     <row r="43">
@@ -1584,28 +1584,28 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C43">
-        <v>41.94</v>
+        <v>42.61</v>
       </c>
       <c r="D43">
         <v>4</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G43">
         <v>33.33</v>
       </c>
       <c r="H43">
-        <v>28.57</v>
+        <v>16.67</v>
       </c>
       <c r="I43">
-        <v>0.0</v>
+        <v>24.32</v>
       </c>
     </row>
     <row r="44">
@@ -1613,10 +1613,10 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C44">
-        <v>41.7</v>
+        <v>42.61</v>
       </c>
       <c r="D44">
         <v>4</v>
@@ -1625,16 +1625,16 @@
         <v>1</v>
       </c>
       <c r="F44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G44">
         <v>33.33</v>
       </c>
       <c r="H44">
-        <v>14.29</v>
+        <v>16.67</v>
       </c>
       <c r="I44">
-        <v>22.22</v>
+        <v>24.32</v>
       </c>
     </row>
     <row r="45">
@@ -1642,28 +1642,28 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C45">
-        <v>41.7</v>
+        <v>41.28</v>
       </c>
       <c r="D45">
         <v>4</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G45">
         <v>33.33</v>
       </c>
       <c r="H45">
-        <v>14.29</v>
+        <v>0.0</v>
       </c>
       <c r="I45">
-        <v>22.22</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="46">
@@ -1671,28 +1671,28 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C46">
-        <v>37.82</v>
+        <v>38.07</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="G46">
+        <v>25.0</v>
+      </c>
+      <c r="H46">
         <v>16.67</v>
       </c>
-      <c r="H46">
-        <v>0.0</v>
-      </c>
       <c r="I46">
-        <v>86.11</v>
+        <v>27.03</v>
       </c>
     </row>
     <row r="47">
@@ -1700,28 +1700,28 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C47">
-        <v>37.17</v>
+        <v>37.87</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="G47">
-        <v>25.0</v>
+        <v>16.67</v>
       </c>
       <c r="H47">
-        <v>14.29</v>
+        <v>0.0</v>
       </c>
       <c r="I47">
-        <v>25.0</v>
+        <v>86.49</v>
       </c>
     </row>
     <row r="48">
@@ -1732,7 +1732,7 @@
         <v>42</v>
       </c>
       <c r="C48">
-        <v>36.93</v>
+        <v>37.15</v>
       </c>
       <c r="D48">
         <v>3</v>
@@ -1741,7 +1741,7 @@
         <v>0</v>
       </c>
       <c r="F48">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G48">
         <v>25.0</v>
@@ -1750,7 +1750,7 @@
         <v>0.0</v>
       </c>
       <c r="I48">
-        <v>47.22</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="49">
@@ -1761,7 +1761,7 @@
         <v>5</v>
       </c>
       <c r="C49">
-        <v>35.92</v>
+        <v>36.86</v>
       </c>
       <c r="D49">
         <v>3</v>
@@ -1770,16 +1770,16 @@
         <v>1</v>
       </c>
       <c r="F49">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G49">
         <v>25.0</v>
       </c>
       <c r="H49">
-        <v>14.29</v>
+        <v>16.67</v>
       </c>
       <c r="I49">
-        <v>16.67</v>
+        <v>18.92</v>
       </c>
     </row>
     <row r="50">
@@ -1790,7 +1790,7 @@
         <v>31</v>
       </c>
       <c r="C50">
-        <v>31.62</v>
+        <v>31.71</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G50">
         <v>8.33</v>
@@ -1808,7 +1808,7 @@
         <v>0.0</v>
       </c>
       <c r="I50">
-        <v>77.78</v>
+        <v>78.38</v>
       </c>
     </row>
   </sheetData>
@@ -1867,545 +1867,545 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000085</v>
+        <v>115000086</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G2">
+        <v>47</v>
+      </c>
+      <c r="H2">
+        <v>49</v>
+      </c>
+      <c r="I2">
         <v>27</v>
-      </c>
-      <c r="H2">
-        <v>37</v>
-      </c>
-      <c r="I2">
-        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000084</v>
+        <v>115000085</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E3">
+        <v>17</v>
+      </c>
+      <c r="F3">
+        <v>18</v>
+      </c>
+      <c r="G3">
+        <v>27</v>
+      </c>
+      <c r="H3">
+        <v>37</v>
+      </c>
+      <c r="I3">
         <v>19</v>
-      </c>
-      <c r="F3">
-        <v>26</v>
-      </c>
-      <c r="G3">
-        <v>29</v>
-      </c>
-      <c r="H3">
-        <v>48</v>
-      </c>
-      <c r="I3">
-        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000083</v>
+        <v>115000084</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F4">
         <v>26</v>
       </c>
       <c r="G4">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H4">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C5">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E5">
+        <v>23</v>
+      </c>
+      <c r="F5">
         <v>26</v>
       </c>
-      <c r="F5">
-        <v>32</v>
-      </c>
       <c r="G5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H5">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G6">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H6">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I6">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D7">
         <v>14</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G7">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H7">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E8">
         <v>25</v>
       </c>
       <c r="F8">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G8">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H8">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I8">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D9">
         <v>12</v>
       </c>
       <c r="E9">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G9">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H9">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D10">
         <v>12</v>
       </c>
       <c r="E10">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F10">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G10">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H10">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I10">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E11">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F11">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G11">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H11">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I11">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C12">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D12">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E12">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F12">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G12">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H12">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I12">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C13">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D13">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F13">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G13">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H13">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I13">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F14">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G14">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H14">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I14">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E15">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F15">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G15">
         <v>35</v>
       </c>
       <c r="H15">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I15">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E16">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F16">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G16">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H16">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I16">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C17">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E17">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F17">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G17">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H17">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I17">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C18">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D18">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E18">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F18">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G18">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H18">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I18">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C19">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D19">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E19">
         <v>15</v>
@@ -2414,345 +2414,345 @@
         <v>18</v>
       </c>
       <c r="G19">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H19">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I19">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C20">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D20">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E20">
+        <v>15</v>
+      </c>
+      <c r="F20">
+        <v>18</v>
+      </c>
+      <c r="G20">
         <v>19</v>
       </c>
-      <c r="F20">
-        <v>23</v>
-      </c>
-      <c r="G20">
-        <v>39</v>
-      </c>
       <c r="H20">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I20">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D21">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E21">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F21">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G21">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H21">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I21">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C22">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D22">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E22">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F22">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G22">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H22">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C23">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D23">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E23">
+        <v>23</v>
+      </c>
+      <c r="F23">
+        <v>24</v>
+      </c>
+      <c r="G23">
         <v>29</v>
       </c>
-      <c r="F23">
-        <v>33</v>
-      </c>
-      <c r="G23">
-        <v>34</v>
-      </c>
       <c r="H23">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I23">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D24">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F24">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G24">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H24">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I24">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E25">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F25">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G25">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H25">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I25">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E26">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F26">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G26">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H26">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I26">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C27">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E27">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F27">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G27">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H27">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I27">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C28">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D28">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E28">
         <v>25</v>
       </c>
       <c r="F28">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G28">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H28">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I28">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C29">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D29">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E29">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F29">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G29">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H29">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I29">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C30">
+        <v>8</v>
+      </c>
+      <c r="D30">
+        <v>9</v>
+      </c>
+      <c r="E30">
+        <v>16</v>
+      </c>
+      <c r="F30">
         <v>20</v>
-      </c>
-      <c r="D30">
-        <v>26</v>
-      </c>
-      <c r="E30">
-        <v>29</v>
-      </c>
-      <c r="F30">
-        <v>31</v>
       </c>
       <c r="G30">
         <v>37</v>
@@ -2761,658 +2761,658 @@
         <v>49</v>
       </c>
       <c r="I30">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C31">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D31">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E31">
         <v>29</v>
       </c>
       <c r="F31">
+        <v>31</v>
+      </c>
+      <c r="G31">
         <v>37</v>
       </c>
-      <c r="G31">
-        <v>47</v>
-      </c>
       <c r="H31">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I31">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C32">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D32">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E32">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F32">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G32">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="H32">
         <v>48</v>
       </c>
       <c r="I32">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C33">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D33">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E33">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F33">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G33">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H33">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I33">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C34">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D34">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E34">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F34">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G34">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H34">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I34">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C35">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D35">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E35">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F35">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G35">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H35">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I35">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C36">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D36">
+        <v>12</v>
+      </c>
+      <c r="E36">
         <v>18</v>
       </c>
-      <c r="E36">
-        <v>25</v>
-      </c>
       <c r="F36">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G36">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H36">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I36">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C37">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D37">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E37">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F37">
         <v>28</v>
       </c>
       <c r="G37">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H37">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I37">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D38">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E38">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F38">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G38">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H38">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I38">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D39">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E39">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F39">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G39">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H39">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I39">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C40">
+        <v>6</v>
+      </c>
+      <c r="D40">
+        <v>10</v>
+      </c>
+      <c r="E40">
+        <v>14</v>
+      </c>
+      <c r="F40">
+        <v>25</v>
+      </c>
+      <c r="G40">
+        <v>26</v>
+      </c>
+      <c r="H40">
+        <v>32</v>
+      </c>
+      <c r="I40">
         <v>7</v>
-      </c>
-      <c r="D40">
-        <v>14</v>
-      </c>
-      <c r="E40">
-        <v>16</v>
-      </c>
-      <c r="F40">
-        <v>37</v>
-      </c>
-      <c r="G40">
-        <v>39</v>
-      </c>
-      <c r="H40">
-        <v>47</v>
-      </c>
-      <c r="I40">
-        <v>34</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D41">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E41">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F41">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G41">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H41">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I41">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C42">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D42">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E42">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F42">
+        <v>19</v>
+      </c>
+      <c r="G42">
+        <v>20</v>
+      </c>
+      <c r="H42">
+        <v>40</v>
+      </c>
+      <c r="I42">
         <v>22</v>
-      </c>
-      <c r="G42">
-        <v>40</v>
-      </c>
-      <c r="H42">
-        <v>45</v>
-      </c>
-      <c r="I42">
-        <v>18</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C43">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D43">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E43">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F43">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G43">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H43">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I43">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C44">
         <v>4</v>
       </c>
       <c r="D44">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E44">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F44">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G44">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H44">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I44">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E45">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F45">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G45">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H45">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I45">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C46">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D46">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E46">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F46">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G46">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H46">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I46">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C47">
         <v>5</v>
       </c>
       <c r="D47">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E47">
+        <v>13</v>
+      </c>
+      <c r="F47">
         <v>25</v>
       </c>
-      <c r="F47">
-        <v>40</v>
-      </c>
       <c r="G47">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H47">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I47">
-        <v>39</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D48">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E48">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F48">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G48">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H48">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I48">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C49">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D49">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E49">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F49">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G49">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H49">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I49">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C50">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D50">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E50">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F50">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G50">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H50">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I50">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C51">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D51">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E51">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F51">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G51">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H51">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I51">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-09-08 第 115000086 期；威力彩 2026-09-07 第 115000072 期</t>
+          <t>大樂透 2026-09-08 第 115000086 期；威力彩 2026-09-10 第 115000073 期</t>
         </is>
       </c>
     </row>
@@ -112,7 +112,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -121,7 +121,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -161,7 +161,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.357 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.381 碼/期</t>
         </is>
       </c>
     </row>
@@ -3464,10 +3464,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>1.024</v>
+        <v>1.048</v>
       </c>
       <c r="D2">
-        <v>31.0</v>
+        <v>33.3</v>
       </c>
       <c r="E2">
         <v>4.8</v>
@@ -3486,10 +3486,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>1.024</v>
+        <v>1.048</v>
       </c>
       <c r="D3">
-        <v>31.0</v>
+        <v>33.3</v>
       </c>
       <c r="E3">
         <v>4.8</v>
@@ -3552,7 +3552,7 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.976</v>
+        <v>0.952</v>
       </c>
       <c r="D6">
         <v>31.0</v>
@@ -3648,7 +3648,7 @@
         <v>19</v>
       </c>
       <c r="C2">
-        <v>73.32</v>
+        <v>73.7</v>
       </c>
       <c r="D2">
         <v>12</v>
@@ -3657,7 +3657,7 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>85.71</v>
@@ -3666,7 +3666,7 @@
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>2.7</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="3">
@@ -3677,7 +3677,7 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>72.43</v>
+        <v>72.82</v>
       </c>
       <c r="D3">
         <v>10</v>
@@ -3686,7 +3686,7 @@
         <v>6</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
         <v>71.43</v>
@@ -3695,7 +3695,7 @@
         <v>100.0</v>
       </c>
       <c r="I3">
-        <v>0.0</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="4">
@@ -3703,28 +3703,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>67.1</v>
+        <v>68.26</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>64.29</v>
+        <v>71.43</v>
       </c>
       <c r="H4">
-        <v>66.67</v>
+        <v>83.33</v>
       </c>
       <c r="I4">
-        <v>21.62</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="5">
@@ -3732,28 +3732,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C5">
-        <v>65.07</v>
+        <v>65.46</v>
       </c>
       <c r="D5">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>64.29</v>
+        <v>100.0</v>
       </c>
       <c r="H5">
         <v>66.67</v>
       </c>
       <c r="I5">
-        <v>8.11</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="6">
@@ -3761,28 +3761,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C6">
-        <v>65.07</v>
+        <v>65.43</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E6">
         <v>4</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>100.0</v>
+        <v>64.29</v>
       </c>
       <c r="H6">
         <v>66.67</v>
       </c>
       <c r="I6">
-        <v>0.0</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="7">
@@ -3793,10 +3793,10 @@
         <v>29</v>
       </c>
       <c r="C7">
-        <v>64.83</v>
+        <v>65.07</v>
       </c>
       <c r="D7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -3805,7 +3805,7 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>92.86</v>
+        <v>100.0</v>
       </c>
       <c r="H7">
         <v>66.67</v>
@@ -3819,28 +3819,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="C8">
-        <v>64.67</v>
+        <v>64.1</v>
       </c>
       <c r="D8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8">
         <v>4</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>64.29</v>
+        <v>71.43</v>
       </c>
       <c r="H8">
         <v>66.67</v>
       </c>
       <c r="I8">
-        <v>5.41</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="9">
@@ -3848,28 +3848,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C9">
-        <v>61.87</v>
+        <v>62.99</v>
       </c>
       <c r="D9">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>92.86</v>
+        <v>57.14</v>
       </c>
       <c r="H9">
         <v>50.0</v>
       </c>
       <c r="I9">
-        <v>8.11</v>
+        <v>23.68</v>
       </c>
     </row>
     <row r="10">
@@ -3877,13 +3877,13 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C10">
-        <v>61.06</v>
+        <v>61.99</v>
       </c>
       <c r="D10">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -3892,13 +3892,13 @@
         <v>4</v>
       </c>
       <c r="G10">
-        <v>57.14</v>
+        <v>85.71</v>
       </c>
       <c r="H10">
         <v>50.0</v>
       </c>
       <c r="I10">
-        <v>10.81</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="11">
@@ -3906,28 +3906,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>61.03</v>
+        <v>60.63</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G11">
-        <v>71.43</v>
+        <v>57.14</v>
       </c>
       <c r="H11">
-        <v>33.33</v>
+        <v>50.0</v>
       </c>
       <c r="I11">
-        <v>35.14</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="12">
@@ -3935,28 +3935,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C12">
-        <v>60.25</v>
+        <v>60.57</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>57.14</v>
+        <v>78.57</v>
       </c>
       <c r="H12">
         <v>50.0</v>
       </c>
       <c r="I12">
-        <v>5.41</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="13">
@@ -3964,28 +3964,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
-        <v>60.17</v>
+        <v>60.01</v>
       </c>
       <c r="D13">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G13">
-        <v>78.57</v>
+        <v>57.14</v>
       </c>
       <c r="H13">
-        <v>50.0</v>
+        <v>33.33</v>
       </c>
       <c r="I13">
-        <v>0.0</v>
+        <v>31.58</v>
       </c>
     </row>
     <row r="14">
@@ -3993,10 +3993,10 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C14">
-        <v>60.09</v>
+        <v>59.69</v>
       </c>
       <c r="D14">
         <v>9</v>
@@ -4005,7 +4005,7 @@
         <v>3</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14">
         <v>64.29</v>
@@ -4014,7 +4014,7 @@
         <v>50.0</v>
       </c>
       <c r="I14">
-        <v>2.7</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="15">
@@ -4022,28 +4022,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C15">
-        <v>60.09</v>
+        <v>59.07</v>
       </c>
       <c r="D15">
         <v>9</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G15">
         <v>64.29</v>
       </c>
       <c r="H15">
-        <v>50.0</v>
+        <v>33.33</v>
       </c>
       <c r="I15">
-        <v>2.7</v>
+        <v>23.68</v>
       </c>
     </row>
     <row r="16">
@@ -4051,28 +4051,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C16">
-        <v>59.73</v>
+        <v>57.51</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F16">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G16">
-        <v>57.14</v>
+        <v>42.86</v>
       </c>
       <c r="H16">
-        <v>33.33</v>
+        <v>66.67</v>
       </c>
       <c r="I16">
-        <v>29.73</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="17">
@@ -4080,28 +4080,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="C17">
-        <v>58.76</v>
+        <v>57.38</v>
       </c>
       <c r="D17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G17">
-        <v>64.29</v>
+        <v>50.0</v>
       </c>
       <c r="H17">
-        <v>33.33</v>
+        <v>50.0</v>
       </c>
       <c r="I17">
-        <v>21.62</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="18">
@@ -4109,28 +4109,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C18">
+        <v>57.25</v>
+      </c>
+      <c r="D18">
+        <v>8</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18">
+        <v>5</v>
+      </c>
+      <c r="G18">
         <v>57.14</v>
       </c>
-      <c r="D18">
-        <v>6</v>
-      </c>
-      <c r="E18">
-        <v>4</v>
-      </c>
-      <c r="F18">
-        <v>3</v>
-      </c>
-      <c r="G18">
-        <v>42.86</v>
-      </c>
       <c r="H18">
-        <v>66.67</v>
+        <v>33.33</v>
       </c>
       <c r="I18">
-        <v>8.11</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="19">
@@ -4138,28 +4138,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C19">
-        <v>57.02</v>
+        <v>56.88</v>
       </c>
       <c r="D19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G19">
-        <v>50.0</v>
+        <v>64.29</v>
       </c>
       <c r="H19">
-        <v>50.0</v>
+        <v>16.67</v>
       </c>
       <c r="I19">
-        <v>8.11</v>
+        <v>36.84</v>
       </c>
     </row>
     <row r="20">
@@ -4167,28 +4167,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C20">
-        <v>55.65</v>
+        <v>56.73</v>
       </c>
       <c r="D20">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>71.43</v>
+        <v>100.0</v>
       </c>
       <c r="H20">
-        <v>16.67</v>
+        <v>33.33</v>
       </c>
       <c r="I20">
-        <v>27.03</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="21">
@@ -4196,10 +4196,10 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C21">
-        <v>55.52</v>
+        <v>56.31</v>
       </c>
       <c r="D21">
         <v>9</v>
@@ -4208,7 +4208,7 @@
         <v>2</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G21">
         <v>64.29</v>
@@ -4217,7 +4217,7 @@
         <v>33.33</v>
       </c>
       <c r="I21">
-        <v>0.0</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="22">
@@ -4228,7 +4228,7 @@
         <v>15</v>
       </c>
       <c r="C22">
-        <v>55.41</v>
+        <v>55.7</v>
       </c>
       <c r="D22">
         <v>9</v>
@@ -4237,7 +4237,7 @@
         <v>1</v>
       </c>
       <c r="F22">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G22">
         <v>64.29</v>
@@ -4246,7 +4246,7 @@
         <v>16.67</v>
       </c>
       <c r="I22">
-        <v>27.03</v>
+        <v>28.95</v>
       </c>
     </row>
     <row r="23">
@@ -4254,28 +4254,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C23">
-        <v>55.27</v>
+        <v>55.7</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G23">
-        <v>57.14</v>
+        <v>64.29</v>
       </c>
       <c r="H23">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="I23">
-        <v>0.0</v>
+        <v>28.95</v>
       </c>
     </row>
     <row r="24">
@@ -4283,28 +4283,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="C24">
-        <v>54.76</v>
+        <v>55.67</v>
       </c>
       <c r="D24">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E24">
+        <v>2</v>
+      </c>
+      <c r="F24">
         <v>1</v>
       </c>
-      <c r="F24">
-        <v>6</v>
-      </c>
       <c r="G24">
-        <v>92.86</v>
+        <v>57.14</v>
       </c>
       <c r="H24">
-        <v>16.67</v>
+        <v>33.33</v>
       </c>
       <c r="I24">
-        <v>16.22</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="25">
@@ -4315,7 +4315,7 @@
         <v>24</v>
       </c>
       <c r="C25">
-        <v>53.05</v>
+        <v>53.42</v>
       </c>
       <c r="D25">
         <v>11</v>
@@ -4324,7 +4324,7 @@
         <v>1</v>
       </c>
       <c r="F25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G25">
         <v>78.57</v>
@@ -4333,7 +4333,7 @@
         <v>16.67</v>
       </c>
       <c r="I25">
-        <v>8.11</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="26">
@@ -4344,7 +4344,7 @@
         <v>1</v>
       </c>
       <c r="C26">
-        <v>52.16</v>
+        <v>52.55</v>
       </c>
       <c r="D26">
         <v>6</v>
@@ -4353,7 +4353,7 @@
         <v>3</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26">
         <v>42.86</v>
@@ -4362,7 +4362,7 @@
         <v>50.0</v>
       </c>
       <c r="I26">
-        <v>2.7</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="27">
@@ -4373,7 +4373,7 @@
         <v>25</v>
       </c>
       <c r="C27">
-        <v>50.71</v>
+        <v>51.02</v>
       </c>
       <c r="D27">
         <v>7</v>
@@ -4382,7 +4382,7 @@
         <v>1</v>
       </c>
       <c r="F27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G27">
         <v>50.0</v>
@@ -4391,7 +4391,7 @@
         <v>16.67</v>
       </c>
       <c r="I27">
-        <v>21.62</v>
+        <v>23.68</v>
       </c>
     </row>
     <row r="28">
@@ -4402,7 +4402,7 @@
         <v>10</v>
       </c>
       <c r="C28">
-        <v>50.43</v>
+        <v>50.75</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -4411,7 +4411,7 @@
         <v>2</v>
       </c>
       <c r="F28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G28">
         <v>42.86</v>
@@ -4420,7 +4420,7 @@
         <v>33.33</v>
       </c>
       <c r="I28">
-        <v>18.92</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="29">
@@ -4440,7 +4440,7 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G29">
         <v>35.71</v>
@@ -4460,7 +4460,7 @@
         <v>26</v>
       </c>
       <c r="C30">
-        <v>49.33</v>
+        <v>49.69</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -4469,7 +4469,7 @@
         <v>3</v>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G30">
         <v>35.71</v>
@@ -4478,7 +4478,7 @@
         <v>50.0</v>
       </c>
       <c r="I30">
-        <v>10.81</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="31">
@@ -4489,7 +4489,7 @@
         <v>30</v>
       </c>
       <c r="C31">
-        <v>43.95</v>
+        <v>44.33</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -4498,7 +4498,7 @@
         <v>2</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31">
         <v>35.71</v>
@@ -4507,7 +4507,7 @@
         <v>33.33</v>
       </c>
       <c r="I31">
-        <v>2.7</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="32">
@@ -4515,28 +4515,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C32">
-        <v>41.81</v>
+        <v>43.55</v>
       </c>
       <c r="D32">
         <v>5</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G32">
         <v>35.71</v>
       </c>
       <c r="H32">
-        <v>16.67</v>
+        <v>33.33</v>
       </c>
       <c r="I32">
-        <v>16.22</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="33">
@@ -4544,10 +4544,10 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C33">
-        <v>41.81</v>
+        <v>42.14</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -4556,7 +4556,7 @@
         <v>1</v>
       </c>
       <c r="F33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G33">
         <v>35.71</v>
@@ -4565,7 +4565,7 @@
         <v>16.67</v>
       </c>
       <c r="I33">
-        <v>16.22</v>
+        <v>18.42</v>
       </c>
     </row>
     <row r="34">
@@ -4573,28 +4573,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C34">
-        <v>40.31</v>
+        <v>39.46</v>
       </c>
       <c r="D34">
         <v>4</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G34">
         <v>28.57</v>
       </c>
       <c r="H34">
-        <v>33.33</v>
+        <v>0.0</v>
       </c>
       <c r="I34">
-        <v>5.41</v>
+        <v>55.26</v>
       </c>
     </row>
     <row r="35">
@@ -4602,28 +4602,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C35">
-        <v>39.28</v>
+        <v>38.5</v>
       </c>
       <c r="D35">
         <v>4</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G35">
         <v>28.57</v>
       </c>
       <c r="H35">
-        <v>0.0</v>
+        <v>16.67</v>
       </c>
       <c r="I35">
-        <v>54.05</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="36">
@@ -4631,10 +4631,10 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C36">
-        <v>38.18</v>
+        <v>36.52</v>
       </c>
       <c r="D36">
         <v>4</v>
@@ -4643,7 +4643,7 @@
         <v>1</v>
       </c>
       <c r="F36">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G36">
         <v>28.57</v>
@@ -4652,7 +4652,7 @@
         <v>16.67</v>
       </c>
       <c r="I36">
-        <v>18.92</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="37">
@@ -4663,7 +4663,7 @@
         <v>32</v>
       </c>
       <c r="C37">
-        <v>36.15</v>
+        <v>36.52</v>
       </c>
       <c r="D37">
         <v>4</v>
@@ -4672,7 +4672,7 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G37">
         <v>28.57</v>
@@ -4681,7 +4681,7 @@
         <v>16.67</v>
       </c>
       <c r="I37">
-        <v>5.41</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="38">
@@ -4692,7 +4692,7 @@
         <v>20</v>
       </c>
       <c r="C38">
-        <v>34.94</v>
+        <v>35.24</v>
       </c>
       <c r="D38">
         <v>3</v>
@@ -4701,7 +4701,7 @@
         <v>1</v>
       </c>
       <c r="F38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G38">
         <v>21.43</v>
@@ -4710,7 +4710,7 @@
         <v>16.67</v>
       </c>
       <c r="I38">
-        <v>24.32</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="39">
@@ -4721,7 +4721,7 @@
         <v>37</v>
       </c>
       <c r="C39">
-        <v>32.11</v>
+        <v>32.48</v>
       </c>
       <c r="D39">
         <v>3</v>
@@ -4730,7 +4730,7 @@
         <v>1</v>
       </c>
       <c r="F39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G39">
         <v>21.43</v>
@@ -4739,7 +4739,7 @@
         <v>16.67</v>
       </c>
       <c r="I39">
-        <v>5.41</v>
+        <v>7.89</v>
       </c>
     </row>
   </sheetData>
@@ -4798,30 +4798,30 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -4829,108 +4829,108 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H3">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F4">
         <v>19</v>
       </c>
       <c r="G4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H4">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <v>19</v>
+      </c>
+      <c r="G5">
+        <v>32</v>
+      </c>
+      <c r="H5">
+        <v>37</v>
+      </c>
+      <c r="I5">
         <v>2</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>24</v>
-      </c>
-      <c r="H5">
-        <v>36</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D6">
         <v>7</v>
@@ -4939,230 +4939,230 @@
         <v>9</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H6">
         <v>36</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E7">
         <v>9</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G7">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>9</v>
+      </c>
+      <c r="F8">
         <v>11</v>
       </c>
-      <c r="E8">
-        <v>18</v>
-      </c>
-      <c r="F8">
-        <v>19</v>
-      </c>
       <c r="G8">
+        <v>29</v>
+      </c>
+      <c r="H8">
         <v>35</v>
       </c>
-      <c r="H8">
-        <v>38</v>
-      </c>
       <c r="I8">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F9">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G9">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H9">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="I9">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C10">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E10">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F10">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G10">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H10">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I10">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D11">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E11">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F11">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G11">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H11">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I11">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>7</v>
+      </c>
+      <c r="E12">
+        <v>8</v>
+      </c>
+      <c r="F12">
+        <v>20</v>
+      </c>
+      <c r="G12">
+        <v>26</v>
+      </c>
+      <c r="H12">
+        <v>33</v>
+      </c>
+      <c r="I12">
         <v>4</v>
-      </c>
-      <c r="D12">
-        <v>15</v>
-      </c>
-      <c r="E12">
-        <v>22</v>
-      </c>
-      <c r="F12">
-        <v>26</v>
-      </c>
-      <c r="G12">
-        <v>34</v>
-      </c>
-      <c r="H12">
-        <v>36</v>
-      </c>
-      <c r="I12">
-        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C13">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D13">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F13">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G13">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H13">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I13">
         <v>7</v>
@@ -5170,30 +5170,30 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C14">
+        <v>8</v>
+      </c>
+      <c r="D14">
+        <v>14</v>
+      </c>
+      <c r="E14">
+        <v>17</v>
+      </c>
+      <c r="F14">
         <v>19</v>
       </c>
-      <c r="D14">
-        <v>22</v>
-      </c>
-      <c r="E14">
-        <v>28</v>
-      </c>
-      <c r="F14">
-        <v>31</v>
-      </c>
       <c r="G14">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H14">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I14">
         <v>7</v>
@@ -5201,30 +5201,30 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C15">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D15">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E15">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F15">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G15">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H15">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I15">
         <v>7</v>
@@ -5232,24 +5232,24 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D16">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E16">
         <v>13</v>
       </c>
       <c r="F16">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G16">
         <v>29</v>
@@ -5258,97 +5258,97 @@
         <v>31</v>
       </c>
       <c r="I16">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C17">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D17">
+        <v>12</v>
+      </c>
+      <c r="E17">
+        <v>13</v>
+      </c>
+      <c r="F17">
         <v>23</v>
       </c>
-      <c r="E17">
-        <v>25</v>
-      </c>
-      <c r="F17">
+      <c r="G17">
         <v>29</v>
       </c>
-      <c r="G17">
-        <v>34</v>
-      </c>
       <c r="H17">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I17">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C18">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D18">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E18">
+        <v>25</v>
+      </c>
+      <c r="F18">
         <v>29</v>
       </c>
-      <c r="F18">
-        <v>32</v>
-      </c>
       <c r="G18">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H18">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C19">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E19">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F19">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G19">
         <v>35</v>
       </c>
       <c r="H19">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I19">
         <v>6</v>
@@ -5356,402 +5356,402 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C20">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D20">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E20">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F20">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G20">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H20">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D21">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E21">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F21">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G21">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H21">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I21">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C22">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D22">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E22">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F22">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G22">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H22">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I22">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C23">
+        <v>5</v>
+      </c>
+      <c r="D23">
         <v>6</v>
       </c>
-      <c r="D23">
-        <v>10</v>
-      </c>
       <c r="E23">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F23">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G23">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H23">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C24">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D24">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E24">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F24">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G24">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H24">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I24">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D25">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E25">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F25">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G25">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H25">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I25">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26">
+        <v>8</v>
+      </c>
+      <c r="E26">
+        <v>9</v>
+      </c>
+      <c r="F26">
+        <v>15</v>
+      </c>
+      <c r="G26">
+        <v>18</v>
+      </c>
+      <c r="H26">
+        <v>23</v>
+      </c>
+      <c r="I26">
         <v>4</v>
-      </c>
-      <c r="D26">
-        <v>17</v>
-      </c>
-      <c r="E26">
-        <v>19</v>
-      </c>
-      <c r="F26">
-        <v>25</v>
-      </c>
-      <c r="G26">
-        <v>28</v>
-      </c>
-      <c r="H26">
-        <v>29</v>
-      </c>
-      <c r="I26">
-        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D27">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E27">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F27">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G27">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H27">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I27">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D28">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E28">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F28">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G28">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H28">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I28">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C29">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D29">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E29">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F29">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G29">
         <v>28</v>
       </c>
       <c r="H29">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I29">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C30">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D30">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E30">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F30">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G30">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H30">
         <v>35</v>
       </c>
       <c r="I30">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E31">
+        <v>9</v>
+      </c>
+      <c r="F31">
+        <v>15</v>
+      </c>
+      <c r="G31">
         <v>24</v>
       </c>
-      <c r="F31">
-        <v>31</v>
-      </c>
-      <c r="G31">
-        <v>34</v>
-      </c>
       <c r="H31">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I31">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C32">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D32">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E32">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F32">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G32">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I32">
         <v>3</v>
@@ -5759,554 +5759,554 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C33">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D33">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E33">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F33">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G33">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H33">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I33">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C34">
         <v>6</v>
       </c>
       <c r="D34">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E34">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F34">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G34">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H34">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I34">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C35">
         <v>6</v>
       </c>
       <c r="D35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E35">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F35">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G35">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H35">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I35">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C36">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D36">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E36">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F36">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G36">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H36">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I36">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C37">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D37">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E37">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F37">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G37">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H37">
         <v>38</v>
       </c>
       <c r="I37">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C38">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D38">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E38">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F38">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G38">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H38">
         <v>38</v>
       </c>
       <c r="I38">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D39">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E39">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F39">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G39">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H39">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I39">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C40">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D40">
+        <v>4</v>
+      </c>
+      <c r="E40">
+        <v>13</v>
+      </c>
+      <c r="F40">
+        <v>19</v>
+      </c>
+      <c r="G40">
+        <v>27</v>
+      </c>
+      <c r="H40">
+        <v>30</v>
+      </c>
+      <c r="I40">
         <v>8</v>
-      </c>
-      <c r="E40">
-        <v>27</v>
-      </c>
-      <c r="F40">
-        <v>33</v>
-      </c>
-      <c r="G40">
-        <v>35</v>
-      </c>
-      <c r="H40">
-        <v>38</v>
-      </c>
-      <c r="I40">
-        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C41">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D41">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E41">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F41">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G41">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H41">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I41">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C42">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D42">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E42">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F42">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G42">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H42">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I42">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C43">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D43">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E43">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F43">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G43">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H43">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I43">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000030</v>
+        <v>115000031</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D44">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E44">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F44">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G44">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H44">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="I44">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000029</v>
+        <v>115000030</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D45">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E45">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F45">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G45">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H45">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I45">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000028</v>
+        <v>115000029</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D46">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E46">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F46">
         <v>27</v>
       </c>
       <c r="G46">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H46">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I46">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000027</v>
+        <v>115000028</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C47">
         <v>5</v>
       </c>
       <c r="D47">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E47">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F47">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G47">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H47">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I47">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000026</v>
+        <v>115000027</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C48">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D48">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E48">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F48">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G48">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H48">
         <v>34</v>
       </c>
       <c r="I48">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000025</v>
+        <v>115000026</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C49">
+        <v>2</v>
+      </c>
+      <c r="D49">
         <v>13</v>
       </c>
-      <c r="D49">
-        <v>14</v>
-      </c>
       <c r="E49">
+        <v>21</v>
+      </c>
+      <c r="F49">
         <v>22</v>
       </c>
-      <c r="F49">
-        <v>28</v>
-      </c>
       <c r="G49">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H49">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I49">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000024</v>
+        <v>115000025</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D50">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E50">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F50">
         <v>28</v>
       </c>
       <c r="G50">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H50">
         <v>38</v>
@@ -6317,33 +6317,33 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000023</v>
+        <v>115000024</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51">
         <v>9</v>
       </c>
-      <c r="D51">
-        <v>13</v>
-      </c>
       <c r="E51">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F51">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G51">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H51">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I51">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-09-08 第 115000086 期；威力彩 2026-09-10 第 115000073 期</t>
+          <t>大樂透 2026-09-11 第 115000087 期；威力彩 2026-09-10 第 115000073 期</t>
         </is>
       </c>
     </row>
@@ -47,7 +47,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>115000086</v>
+        <v>115000087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -56,7 +56,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -96,7 +96,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.333 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.309 碼/期</t>
         </is>
       </c>
     </row>
@@ -302,10 +302,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.643</v>
+        <v>0.667</v>
       </c>
       <c r="D6">
-        <v>9.5</v>
+        <v>11.9</v>
       </c>
       <c r="E6">
         <v>0.0</v>
@@ -398,16 +398,16 @@
         <v>26</v>
       </c>
       <c r="C2">
-        <v>71.41</v>
+        <v>71.78</v>
       </c>
       <c r="D2">
         <v>12</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>100.0</v>
@@ -416,7 +416,7 @@
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>5.41</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="3">
@@ -424,13 +424,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C3">
-        <v>66.23</v>
+        <v>70.6</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -439,10 +439,10 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>66.67</v>
+        <v>100.0</v>
       </c>
       <c r="H3">
-        <v>83.33</v>
+        <v>100.0</v>
       </c>
       <c r="I3">
         <v>0.0</v>
@@ -453,13 +453,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C4">
-        <v>64.09</v>
+        <v>66.67</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -468,13 +468,13 @@
         <v>5</v>
       </c>
       <c r="G4">
-        <v>66.67</v>
+        <v>50.0</v>
       </c>
       <c r="H4">
-        <v>66.67</v>
+        <v>80.0</v>
       </c>
       <c r="I4">
-        <v>13.51</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="5">
@@ -482,28 +482,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C5">
-        <v>63.84</v>
+        <v>65.8</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>91.67</v>
+        <v>66.67</v>
       </c>
       <c r="H5">
-        <v>66.67</v>
+        <v>80.0</v>
       </c>
       <c r="I5">
-        <v>10.81</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="6">
@@ -511,28 +511,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C6">
-        <v>62.99</v>
+        <v>65.45</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E6">
         <v>4</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>50.0</v>
+        <v>75.0</v>
       </c>
       <c r="H6">
-        <v>66.67</v>
+        <v>80.0</v>
       </c>
       <c r="I6">
-        <v>10.81</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>62.07</v>
+        <v>65.4</v>
       </c>
       <c r="D7">
         <v>8</v>
@@ -558,7 +558,7 @@
         <v>66.67</v>
       </c>
       <c r="H7">
-        <v>66.67</v>
+        <v>80.0</v>
       </c>
       <c r="I7">
         <v>0.0</v>
@@ -569,28 +569,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C8">
-        <v>60.43</v>
+        <v>64.7</v>
       </c>
       <c r="D8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>83.33</v>
+        <v>50.0</v>
       </c>
       <c r="H8">
-        <v>50.0</v>
+        <v>80.0</v>
       </c>
       <c r="I8">
-        <v>16.22</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="9">
@@ -598,13 +598,13 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C9">
-        <v>60.04</v>
+        <v>63.26</v>
       </c>
       <c r="D9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -613,13 +613,13 @@
         <v>7</v>
       </c>
       <c r="G9">
-        <v>50.0</v>
+        <v>83.33</v>
       </c>
       <c r="H9">
-        <v>50.0</v>
+        <v>60.0</v>
       </c>
       <c r="I9">
-        <v>18.92</v>
+        <v>18.42</v>
       </c>
     </row>
     <row r="10">
@@ -627,28 +627,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C10">
-        <v>59.12</v>
+        <v>62.86</v>
       </c>
       <c r="D10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G10">
-        <v>66.67</v>
+        <v>50.0</v>
       </c>
       <c r="H10">
-        <v>50.0</v>
+        <v>60.0</v>
       </c>
       <c r="I10">
-        <v>8.11</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="11">
@@ -656,28 +656,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C11">
-        <v>58.91</v>
+        <v>62.77</v>
       </c>
       <c r="D11">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G11">
-        <v>100.0</v>
+        <v>66.67</v>
       </c>
       <c r="H11">
-        <v>50.0</v>
+        <v>60.0</v>
       </c>
       <c r="I11">
-        <v>5.41</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="12">
@@ -685,10 +685,10 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C12">
-        <v>58.71</v>
+        <v>61.98</v>
       </c>
       <c r="D12">
         <v>8</v>
@@ -697,16 +697,16 @@
         <v>3</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G12">
         <v>66.67</v>
       </c>
       <c r="H12">
-        <v>50.0</v>
+        <v>60.0</v>
       </c>
       <c r="I12">
-        <v>5.41</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="13">
@@ -714,28 +714,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C13">
-        <v>56.11</v>
+        <v>61.78</v>
       </c>
       <c r="D13">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G13">
-        <v>58.33</v>
+        <v>100.0</v>
       </c>
       <c r="H13">
-        <v>33.33</v>
+        <v>60.0</v>
       </c>
       <c r="I13">
-        <v>16.22</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="14">
@@ -743,28 +743,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C14">
-        <v>55.87</v>
+        <v>60.35</v>
       </c>
       <c r="D14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>50.0</v>
+        <v>58.33</v>
       </c>
       <c r="H14">
-        <v>33.33</v>
+        <v>60.0</v>
       </c>
       <c r="I14">
-        <v>18.92</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="15">
@@ -775,7 +775,7 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>55.71</v>
+        <v>57.72</v>
       </c>
       <c r="D15">
         <v>7</v>
@@ -784,16 +784,16 @@
         <v>2</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15">
         <v>58.33</v>
       </c>
       <c r="H15">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I15">
-        <v>13.51</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="16">
@@ -804,7 +804,7 @@
         <v>36</v>
       </c>
       <c r="C16">
-        <v>54.95</v>
+        <v>56.98</v>
       </c>
       <c r="D16">
         <v>8</v>
@@ -813,16 +813,16 @@
         <v>2</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16">
         <v>66.67</v>
       </c>
       <c r="H16">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I16">
-        <v>8.11</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="17">
@@ -833,7 +833,7 @@
         <v>20</v>
       </c>
       <c r="C17">
-        <v>54.9</v>
+        <v>56.93</v>
       </c>
       <c r="D17">
         <v>7</v>
@@ -842,16 +842,16 @@
         <v>2</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17">
         <v>58.33</v>
       </c>
       <c r="H17">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I17">
-        <v>8.11</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="18">
@@ -862,7 +862,7 @@
         <v>16</v>
       </c>
       <c r="C18">
-        <v>54.64</v>
+        <v>56.68</v>
       </c>
       <c r="D18">
         <v>10</v>
@@ -871,16 +871,16 @@
         <v>2</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18">
         <v>83.33</v>
       </c>
       <c r="H18">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I18">
-        <v>5.41</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="19">
@@ -888,28 +888,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="C19">
-        <v>53.98</v>
+        <v>56.33</v>
       </c>
       <c r="D19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G19">
-        <v>58.33</v>
+        <v>41.67</v>
       </c>
       <c r="H19">
-        <v>16.67</v>
+        <v>60.0</v>
       </c>
       <c r="I19">
-        <v>29.73</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="20">
@@ -920,7 +920,7 @@
         <v>47</v>
       </c>
       <c r="C20">
-        <v>53.68</v>
+        <v>55.74</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -929,16 +929,16 @@
         <v>2</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20">
         <v>58.33</v>
       </c>
       <c r="H20">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I20">
-        <v>0.0</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="21">
@@ -946,28 +946,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="C21">
-        <v>53.67</v>
+        <v>55.4</v>
       </c>
       <c r="D21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>75.0</v>
+        <v>66.67</v>
       </c>
       <c r="H21">
-        <v>16.67</v>
+        <v>40.0</v>
       </c>
       <c r="I21">
-        <v>27.03</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="22">
@@ -975,10 +975,10 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="C22">
-        <v>53.47</v>
+        <v>55.15</v>
       </c>
       <c r="D22">
         <v>5</v>
@@ -987,16 +987,16 @@
         <v>3</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22">
         <v>41.67</v>
       </c>
       <c r="H22">
-        <v>50.0</v>
+        <v>60.0</v>
       </c>
       <c r="I22">
-        <v>8.11</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="23">
@@ -1007,7 +1007,7 @@
         <v>49</v>
       </c>
       <c r="C23">
-        <v>53.03</v>
+        <v>55.09</v>
       </c>
       <c r="D23">
         <v>6</v>
@@ -1016,16 +1016,16 @@
         <v>2</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23">
         <v>50.0</v>
       </c>
       <c r="H23">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I23">
-        <v>0.0</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="24">
@@ -1033,28 +1033,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C24">
-        <v>52.66</v>
+        <v>54.79</v>
       </c>
       <c r="D24">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G24">
-        <v>41.67</v>
+        <v>75.0</v>
       </c>
       <c r="H24">
-        <v>50.0</v>
+        <v>20.0</v>
       </c>
       <c r="I24">
-        <v>2.7</v>
+        <v>28.95</v>
       </c>
     </row>
     <row r="25">
@@ -1062,28 +1062,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C25">
-        <v>52.25</v>
+        <v>54.44</v>
       </c>
       <c r="D25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G25">
-        <v>41.67</v>
+        <v>50.0</v>
       </c>
       <c r="H25">
-        <v>50.0</v>
+        <v>20.0</v>
       </c>
       <c r="I25">
-        <v>0.0</v>
+        <v>31.58</v>
       </c>
     </row>
     <row r="26">
@@ -1091,28 +1091,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="C26">
-        <v>51.3</v>
+        <v>52.91</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G26">
-        <v>50.0</v>
+        <v>41.67</v>
       </c>
       <c r="H26">
-        <v>16.67</v>
+        <v>40.0</v>
       </c>
       <c r="I26">
-        <v>16.22</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="27">
@@ -1120,28 +1120,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C27">
-        <v>50.78</v>
+        <v>52.46</v>
       </c>
       <c r="D27">
         <v>6</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G27">
         <v>50.0</v>
       </c>
       <c r="H27">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I27">
-        <v>40.54</v>
+        <v>18.42</v>
       </c>
     </row>
     <row r="28">
@@ -1149,28 +1149,28 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C28">
-        <v>50.49</v>
+        <v>51.72</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28">
-        <v>50.0</v>
+        <v>41.67</v>
       </c>
       <c r="H28">
-        <v>16.67</v>
+        <v>40.0</v>
       </c>
       <c r="I28">
-        <v>10.81</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="29">
@@ -1178,28 +1178,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="C29">
-        <v>50.33</v>
+        <v>51.67</v>
       </c>
       <c r="D29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G29">
-        <v>58.33</v>
+        <v>50.0</v>
       </c>
       <c r="H29">
-        <v>16.67</v>
+        <v>20.0</v>
       </c>
       <c r="I29">
-        <v>5.41</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="30">
@@ -1207,10 +1207,10 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="C30">
-        <v>50.33</v>
+        <v>51.53</v>
       </c>
       <c r="D30">
         <v>7</v>
@@ -1219,16 +1219,16 @@
         <v>1</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30">
         <v>58.33</v>
       </c>
       <c r="H30">
-        <v>16.67</v>
+        <v>20.0</v>
       </c>
       <c r="I30">
-        <v>5.41</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="31">
@@ -1239,7 +1239,7 @@
         <v>18</v>
       </c>
       <c r="C31">
-        <v>49.97</v>
+        <v>51.19</v>
       </c>
       <c r="D31">
         <v>8</v>
@@ -1248,16 +1248,16 @@
         <v>1</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31">
         <v>66.67</v>
       </c>
       <c r="H31">
-        <v>16.67</v>
+        <v>20.0</v>
       </c>
       <c r="I31">
-        <v>2.7</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="32">
@@ -1265,28 +1265,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C32">
-        <v>49.7</v>
+        <v>51.02</v>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G32">
-        <v>41.67</v>
+        <v>50.0</v>
       </c>
       <c r="H32">
-        <v>33.33</v>
+        <v>0.0</v>
       </c>
       <c r="I32">
-        <v>10.81</v>
+        <v>42.11</v>
       </c>
     </row>
     <row r="33">
@@ -1297,7 +1297,7 @@
         <v>37</v>
       </c>
       <c r="C33">
-        <v>49.27</v>
+        <v>50.49</v>
       </c>
       <c r="D33">
         <v>6</v>
@@ -1306,16 +1306,16 @@
         <v>1</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33">
         <v>50.0</v>
       </c>
       <c r="H33">
-        <v>16.67</v>
+        <v>20.0</v>
       </c>
       <c r="I33">
-        <v>2.7</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="34">
@@ -1326,7 +1326,7 @@
         <v>28</v>
       </c>
       <c r="C34">
-        <v>48.87</v>
+        <v>50.09</v>
       </c>
       <c r="D34">
         <v>6</v>
@@ -1335,16 +1335,16 @@
         <v>1</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34">
         <v>50.0</v>
       </c>
       <c r="H34">
-        <v>16.67</v>
+        <v>20.0</v>
       </c>
       <c r="I34">
-        <v>0.0</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="35">
@@ -1355,7 +1355,7 @@
         <v>39</v>
       </c>
       <c r="C35">
-        <v>47.45</v>
+        <v>47.65</v>
       </c>
       <c r="D35">
         <v>5</v>
@@ -1364,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="F35">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G35">
         <v>41.67</v>
@@ -1373,7 +1373,7 @@
         <v>0.0</v>
       </c>
       <c r="I35">
-        <v>51.35</v>
+        <v>52.63</v>
       </c>
     </row>
     <row r="36">
@@ -1381,10 +1381,10 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C36">
-        <v>46.78</v>
+        <v>46.38</v>
       </c>
       <c r="D36">
         <v>4</v>
@@ -1393,16 +1393,16 @@
         <v>2</v>
       </c>
       <c r="F36">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G36">
         <v>33.33</v>
       </c>
       <c r="H36">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I36">
-        <v>24.32</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="37">
@@ -1410,28 +1410,28 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="C37">
-        <v>46.37</v>
+        <v>45.54</v>
       </c>
       <c r="D37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37">
         <v>2</v>
       </c>
-      <c r="F37">
-        <v>8</v>
-      </c>
       <c r="G37">
-        <v>33.33</v>
+        <v>41.67</v>
       </c>
       <c r="H37">
-        <v>33.33</v>
+        <v>20.0</v>
       </c>
       <c r="I37">
-        <v>21.62</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="38">
@@ -1439,28 +1439,28 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C38">
-        <v>44.85</v>
+        <v>45.54</v>
       </c>
       <c r="D38">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="G38">
-        <v>25.0</v>
+        <v>41.67</v>
       </c>
       <c r="H38">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I38">
-        <v>100.0</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="39">
@@ -1468,28 +1468,28 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C39">
-        <v>44.35</v>
+        <v>44.85</v>
       </c>
       <c r="D39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="G39">
-        <v>33.33</v>
+        <v>25.0</v>
       </c>
       <c r="H39">
-        <v>33.33</v>
+        <v>0.0</v>
       </c>
       <c r="I39">
-        <v>8.11</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="40">
@@ -1497,28 +1497,28 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C40">
-        <v>44.32</v>
+        <v>43.75</v>
       </c>
       <c r="D40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E40">
         <v>1</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G40">
-        <v>41.67</v>
+        <v>33.33</v>
       </c>
       <c r="H40">
-        <v>16.67</v>
+        <v>20.0</v>
       </c>
       <c r="I40">
-        <v>2.7</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="41">
@@ -1526,28 +1526,28 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C41">
-        <v>44.32</v>
+        <v>43.75</v>
       </c>
       <c r="D41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E41">
         <v>1</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G41">
-        <v>41.67</v>
+        <v>33.33</v>
       </c>
       <c r="H41">
-        <v>16.67</v>
+        <v>20.0</v>
       </c>
       <c r="I41">
-        <v>2.7</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="42">
@@ -1555,28 +1555,28 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="C42">
-        <v>42.82</v>
+        <v>43.35</v>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="G42">
-        <v>25.0</v>
+        <v>33.33</v>
       </c>
       <c r="H42">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I42">
-        <v>86.49</v>
+        <v>23.68</v>
       </c>
     </row>
     <row r="43">
@@ -1584,28 +1584,28 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C43">
-        <v>42.61</v>
+        <v>42.88</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="G43">
-        <v>33.33</v>
+        <v>25.0</v>
       </c>
       <c r="H43">
-        <v>16.67</v>
+        <v>0.0</v>
       </c>
       <c r="I43">
-        <v>24.32</v>
+        <v>86.84</v>
       </c>
     </row>
     <row r="44">
@@ -1613,28 +1613,28 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C44">
-        <v>42.61</v>
+        <v>41.51</v>
       </c>
       <c r="D44">
         <v>4</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G44">
         <v>33.33</v>
       </c>
       <c r="H44">
-        <v>16.67</v>
+        <v>0.0</v>
       </c>
       <c r="I44">
-        <v>24.32</v>
+        <v>44.74</v>
       </c>
     </row>
     <row r="45">
@@ -1642,28 +1642,28 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C45">
-        <v>41.28</v>
+        <v>39.19</v>
       </c>
       <c r="D45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G45">
-        <v>33.33</v>
+        <v>25.0</v>
       </c>
       <c r="H45">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I45">
-        <v>43.24</v>
+        <v>28.95</v>
       </c>
     </row>
     <row r="46">
@@ -1671,10 +1671,10 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C46">
-        <v>38.07</v>
+        <v>38.8</v>
       </c>
       <c r="D46">
         <v>3</v>
@@ -1689,10 +1689,10 @@
         <v>25.0</v>
       </c>
       <c r="H46">
-        <v>16.67</v>
+        <v>20.0</v>
       </c>
       <c r="I46">
-        <v>27.03</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="47">
@@ -1700,28 +1700,28 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="C47">
-        <v>37.87</v>
+        <v>38.01</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G47">
-        <v>16.67</v>
+        <v>25.0</v>
       </c>
       <c r="H47">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I47">
-        <v>86.49</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="48">
@@ -1732,7 +1732,7 @@
         <v>42</v>
       </c>
       <c r="C48">
-        <v>37.15</v>
+        <v>37.35</v>
       </c>
       <c r="D48">
         <v>3</v>
@@ -1741,7 +1741,7 @@
         <v>0</v>
       </c>
       <c r="F48">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G48">
         <v>25.0</v>
@@ -1750,7 +1750,7 @@
         <v>0.0</v>
       </c>
       <c r="I48">
-        <v>48.65</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="49">
@@ -1758,28 +1758,28 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="C49">
-        <v>36.86</v>
+        <v>32.98</v>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="G49">
-        <v>25.0</v>
+        <v>8.33</v>
       </c>
       <c r="H49">
-        <v>16.67</v>
+        <v>0.0</v>
       </c>
       <c r="I49">
-        <v>18.92</v>
+        <v>86.84</v>
       </c>
     </row>
     <row r="50">
@@ -1790,7 +1790,7 @@
         <v>31</v>
       </c>
       <c r="C50">
-        <v>31.71</v>
+        <v>31.79</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G50">
         <v>8.33</v>
@@ -1808,7 +1808,7 @@
         <v>0.0</v>
       </c>
       <c r="I50">
-        <v>78.38</v>
+        <v>78.95</v>
       </c>
     </row>
   </sheetData>
@@ -1867,576 +1867,576 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000086</v>
+        <v>115000087</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>15</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I2">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000085</v>
+        <v>115000086</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G3">
+        <v>47</v>
+      </c>
+      <c r="H3">
+        <v>49</v>
+      </c>
+      <c r="I3">
         <v>27</v>
-      </c>
-      <c r="H3">
-        <v>37</v>
-      </c>
-      <c r="I3">
-        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000084</v>
+        <v>115000085</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E4">
+        <v>17</v>
+      </c>
+      <c r="F4">
+        <v>18</v>
+      </c>
+      <c r="G4">
+        <v>27</v>
+      </c>
+      <c r="H4">
+        <v>37</v>
+      </c>
+      <c r="I4">
         <v>19</v>
-      </c>
-      <c r="F4">
-        <v>26</v>
-      </c>
-      <c r="G4">
-        <v>29</v>
-      </c>
-      <c r="H4">
-        <v>48</v>
-      </c>
-      <c r="I4">
-        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000083</v>
+        <v>115000084</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E5">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F5">
         <v>26</v>
       </c>
       <c r="G5">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H5">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E6">
+        <v>23</v>
+      </c>
+      <c r="F6">
         <v>26</v>
       </c>
-      <c r="F6">
-        <v>32</v>
-      </c>
       <c r="G6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H6">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F7">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G7">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H7">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I7">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D8">
         <v>14</v>
       </c>
       <c r="E8">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G8">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H8">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E9">
         <v>25</v>
       </c>
       <c r="F9">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G9">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H9">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I9">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C10">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>12</v>
       </c>
       <c r="E10">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F10">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G10">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H10">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="I10">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D11">
         <v>12</v>
       </c>
       <c r="E11">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F11">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G11">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H11">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I11">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E12">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F12">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G12">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H12">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I12">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C13">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D13">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E13">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F13">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G13">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H13">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I13">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F14">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H14">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I14">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D15">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E15">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F15">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G15">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H15">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I15">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E16">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F16">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G16">
         <v>35</v>
       </c>
       <c r="H16">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I16">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E17">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F17">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G17">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H17">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I17">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C18">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E18">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F18">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G18">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H18">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I18">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D19">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E19">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F19">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G19">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H19">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I19">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C20">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D20">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E20">
         <v>15</v>
@@ -2445,345 +2445,345 @@
         <v>18</v>
       </c>
       <c r="G20">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H20">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I20">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C21">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D21">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E21">
+        <v>15</v>
+      </c>
+      <c r="F21">
+        <v>18</v>
+      </c>
+      <c r="G21">
         <v>19</v>
       </c>
-      <c r="F21">
-        <v>23</v>
-      </c>
-      <c r="G21">
-        <v>39</v>
-      </c>
       <c r="H21">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I21">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D22">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E22">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F22">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G22">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H22">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I22">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C23">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D23">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E23">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F23">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G23">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H23">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C24">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E24">
+        <v>23</v>
+      </c>
+      <c r="F24">
+        <v>24</v>
+      </c>
+      <c r="G24">
         <v>29</v>
       </c>
-      <c r="F24">
-        <v>33</v>
-      </c>
-      <c r="G24">
-        <v>34</v>
-      </c>
       <c r="H24">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I24">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D25">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E25">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F25">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G25">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H25">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I25">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E26">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F26">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G26">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H26">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I26">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E27">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F27">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G27">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H27">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I27">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C28">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D28">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E28">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F28">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G28">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H28">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I28">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C29">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D29">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E29">
         <v>25</v>
       </c>
       <c r="F29">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G29">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H29">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I29">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C30">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D30">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E30">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F30">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G30">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H30">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I30">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C31">
+        <v>8</v>
+      </c>
+      <c r="D31">
+        <v>9</v>
+      </c>
+      <c r="E31">
+        <v>16</v>
+      </c>
+      <c r="F31">
         <v>20</v>
-      </c>
-      <c r="D31">
-        <v>26</v>
-      </c>
-      <c r="E31">
-        <v>29</v>
-      </c>
-      <c r="F31">
-        <v>31</v>
       </c>
       <c r="G31">
         <v>37</v>
@@ -2792,627 +2792,627 @@
         <v>49</v>
       </c>
       <c r="I31">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D32">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E32">
         <v>29</v>
       </c>
       <c r="F32">
+        <v>31</v>
+      </c>
+      <c r="G32">
         <v>37</v>
       </c>
-      <c r="G32">
-        <v>47</v>
-      </c>
       <c r="H32">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I32">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C33">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D33">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E33">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F33">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G33">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="H33">
         <v>48</v>
       </c>
       <c r="I33">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C34">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D34">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E34">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F34">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G34">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H34">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I34">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C35">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D35">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E35">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F35">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G35">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H35">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I35">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C36">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D36">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E36">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F36">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G36">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H36">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I36">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D37">
+        <v>12</v>
+      </c>
+      <c r="E37">
         <v>18</v>
       </c>
-      <c r="E37">
-        <v>25</v>
-      </c>
       <c r="F37">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G37">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H37">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I37">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D38">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E38">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F38">
         <v>28</v>
       </c>
       <c r="G38">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H38">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I38">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C39">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D39">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E39">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F39">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G39">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H39">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I39">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D40">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E40">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F40">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G40">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H40">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I40">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C41">
+        <v>6</v>
+      </c>
+      <c r="D41">
+        <v>10</v>
+      </c>
+      <c r="E41">
+        <v>14</v>
+      </c>
+      <c r="F41">
+        <v>25</v>
+      </c>
+      <c r="G41">
+        <v>26</v>
+      </c>
+      <c r="H41">
+        <v>32</v>
+      </c>
+      <c r="I41">
         <v>7</v>
-      </c>
-      <c r="D41">
-        <v>14</v>
-      </c>
-      <c r="E41">
-        <v>16</v>
-      </c>
-      <c r="F41">
-        <v>37</v>
-      </c>
-      <c r="G41">
-        <v>39</v>
-      </c>
-      <c r="H41">
-        <v>47</v>
-      </c>
-      <c r="I41">
-        <v>34</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D42">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E42">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F42">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G42">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H42">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I42">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C43">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D43">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E43">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F43">
+        <v>19</v>
+      </c>
+      <c r="G43">
+        <v>20</v>
+      </c>
+      <c r="H43">
+        <v>40</v>
+      </c>
+      <c r="I43">
         <v>22</v>
-      </c>
-      <c r="G43">
-        <v>40</v>
-      </c>
-      <c r="H43">
-        <v>45</v>
-      </c>
-      <c r="I43">
-        <v>18</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C44">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D44">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E44">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F44">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G44">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H44">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I44">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C45">
         <v>4</v>
       </c>
       <c r="D45">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E45">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F45">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G45">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H45">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I45">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E46">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F46">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G46">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H46">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I46">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C47">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D47">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E47">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F47">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G47">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H47">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I47">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C48">
         <v>5</v>
       </c>
       <c r="D48">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E48">
+        <v>13</v>
+      </c>
+      <c r="F48">
         <v>25</v>
       </c>
-      <c r="F48">
-        <v>40</v>
-      </c>
       <c r="G48">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H48">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I48">
-        <v>39</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D49">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E49">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F49">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G49">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H49">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I49">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C50">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D50">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E50">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F50">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G50">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H50">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I50">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C51">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D51">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E51">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F51">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G51">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H51">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I51">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-09-11 第 115000087 期；威力彩 2026-09-10 第 115000073 期</t>
+          <t>大樂透 2026-09-11 第 115000087 期；威力彩 2026-09-14 第 115000074 期</t>
         </is>
       </c>
     </row>
@@ -112,7 +112,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -121,7 +121,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3530,7 +3530,7 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>0.976</v>
+        <v>0.952</v>
       </c>
       <c r="D5">
         <v>21.4</v>
@@ -3552,10 +3552,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.952</v>
+        <v>0.929</v>
       </c>
       <c r="D6">
-        <v>31.0</v>
+        <v>28.6</v>
       </c>
       <c r="E6">
         <v>2.4</v>
@@ -3648,7 +3648,7 @@
         <v>19</v>
       </c>
       <c r="C2">
-        <v>73.7</v>
+        <v>72.35</v>
       </c>
       <c r="D2">
         <v>12</v>
@@ -3657,16 +3657,16 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>85.71</v>
+        <v>80.0</v>
       </c>
       <c r="H2">
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>5.26</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="3">
@@ -3677,7 +3677,7 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>72.82</v>
+        <v>71.77</v>
       </c>
       <c r="D3">
         <v>10</v>
@@ -3686,16 +3686,16 @@
         <v>6</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>71.43</v>
+        <v>66.67</v>
       </c>
       <c r="H3">
         <v>100.0</v>
       </c>
       <c r="I3">
-        <v>2.63</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="4">
@@ -3703,28 +3703,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>68.26</v>
+        <v>64.49</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
         <v>5</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>71.43</v>
+        <v>60.0</v>
       </c>
       <c r="H4">
-        <v>83.33</v>
+        <v>66.67</v>
       </c>
       <c r="I4">
-        <v>0.0</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="5">
@@ -3735,7 +3735,7 @@
         <v>35</v>
       </c>
       <c r="C5">
-        <v>65.46</v>
+        <v>63.84</v>
       </c>
       <c r="D5">
         <v>14</v>
@@ -3744,16 +3744,16 @@
         <v>4</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>100.0</v>
+        <v>93.33</v>
       </c>
       <c r="H5">
         <v>66.67</v>
       </c>
       <c r="I5">
-        <v>2.63</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="6">
@@ -3761,28 +3761,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C6">
-        <v>65.43</v>
+        <v>63.17</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E6">
         <v>4</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>64.29</v>
+        <v>100.0</v>
       </c>
       <c r="H6">
         <v>66.67</v>
       </c>
       <c r="I6">
-        <v>10.53</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7">
@@ -3790,25 +3790,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C7">
-        <v>65.07</v>
+        <v>63.13</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>100.0</v>
+        <v>46.67</v>
       </c>
       <c r="H7">
-        <v>66.67</v>
+        <v>83.33</v>
       </c>
       <c r="I7">
         <v>0.0</v>
@@ -3819,10 +3819,10 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>64.1</v>
+        <v>63.05</v>
       </c>
       <c r="D8">
         <v>10</v>
@@ -3831,16 +3831,16 @@
         <v>4</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>71.43</v>
+        <v>66.67</v>
       </c>
       <c r="H8">
         <v>66.67</v>
       </c>
       <c r="I8">
-        <v>0.0</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="9">
@@ -3848,28 +3848,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C9">
-        <v>62.99</v>
+        <v>62.95</v>
       </c>
       <c r="D9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>57.14</v>
+        <v>60.0</v>
       </c>
       <c r="H9">
-        <v>50.0</v>
+        <v>66.67</v>
       </c>
       <c r="I9">
-        <v>23.68</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="10">
@@ -3880,25 +3880,25 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>61.99</v>
+        <v>60.52</v>
       </c>
       <c r="D10">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10">
-        <v>85.71</v>
+        <v>73.33</v>
       </c>
       <c r="H10">
         <v>50.0</v>
       </c>
       <c r="I10">
-        <v>10.53</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="11">
@@ -3909,7 +3909,7 @@
         <v>4</v>
       </c>
       <c r="C11">
-        <v>60.63</v>
+        <v>59.84</v>
       </c>
       <c r="D11">
         <v>8</v>
@@ -3918,16 +3918,16 @@
         <v>3</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="H11">
         <v>50.0</v>
       </c>
       <c r="I11">
-        <v>7.89</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="12">
@@ -3938,7 +3938,7 @@
         <v>22</v>
       </c>
       <c r="C12">
-        <v>60.57</v>
+        <v>59.37</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -3947,16 +3947,16 @@
         <v>3</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12">
-        <v>78.57</v>
+        <v>73.33</v>
       </c>
       <c r="H12">
         <v>50.0</v>
       </c>
       <c r="I12">
-        <v>2.63</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="13">
@@ -3964,28 +3964,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C13">
-        <v>60.01</v>
+        <v>58.78</v>
       </c>
       <c r="D13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>57.14</v>
+        <v>60.0</v>
       </c>
       <c r="H13">
-        <v>33.33</v>
+        <v>50.0</v>
       </c>
       <c r="I13">
-        <v>31.58</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="14">
@@ -3993,10 +3993,10 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C14">
-        <v>59.69</v>
+        <v>58.4</v>
       </c>
       <c r="D14">
         <v>9</v>
@@ -4008,7 +4008,7 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>64.29</v>
+        <v>60.0</v>
       </c>
       <c r="H14">
         <v>50.0</v>
@@ -4025,25 +4025,25 @@
         <v>28</v>
       </c>
       <c r="C15">
-        <v>59.07</v>
+        <v>57.98</v>
       </c>
       <c r="D15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E15">
         <v>2</v>
       </c>
       <c r="F15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G15">
-        <v>64.29</v>
+        <v>53.33</v>
       </c>
       <c r="H15">
         <v>33.33</v>
       </c>
       <c r="I15">
-        <v>23.68</v>
+        <v>25.64</v>
       </c>
     </row>
     <row r="16">
@@ -4051,28 +4051,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C16">
-        <v>57.51</v>
+        <v>57.98</v>
       </c>
       <c r="D16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G16">
-        <v>42.86</v>
+        <v>53.33</v>
       </c>
       <c r="H16">
-        <v>66.67</v>
+        <v>33.33</v>
       </c>
       <c r="I16">
-        <v>10.53</v>
+        <v>25.64</v>
       </c>
     </row>
     <row r="17">
@@ -4083,7 +4083,7 @@
         <v>2</v>
       </c>
       <c r="C17">
-        <v>57.38</v>
+        <v>56.72</v>
       </c>
       <c r="D17">
         <v>7</v>
@@ -4092,16 +4092,16 @@
         <v>3</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G17">
-        <v>50.0</v>
+        <v>46.67</v>
       </c>
       <c r="H17">
         <v>50.0</v>
       </c>
       <c r="I17">
-        <v>10.53</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="18">
@@ -4112,7 +4112,7 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>57.25</v>
+        <v>56.44</v>
       </c>
       <c r="D18">
         <v>8</v>
@@ -4121,16 +4121,16 @@
         <v>2</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="H18">
         <v>33.33</v>
       </c>
       <c r="I18">
-        <v>13.16</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="19">
@@ -4138,28 +4138,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C19">
-        <v>56.88</v>
+        <v>55.39</v>
       </c>
       <c r="D19">
         <v>9</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G19">
-        <v>64.29</v>
+        <v>60.0</v>
       </c>
       <c r="H19">
-        <v>16.67</v>
+        <v>33.33</v>
       </c>
       <c r="I19">
-        <v>36.84</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="20">
@@ -4170,25 +4170,25 @@
         <v>38</v>
       </c>
       <c r="C20">
-        <v>56.73</v>
+        <v>55.02</v>
       </c>
       <c r="D20">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20">
-        <v>100.0</v>
+        <v>86.67</v>
       </c>
       <c r="H20">
         <v>33.33</v>
       </c>
       <c r="I20">
-        <v>0.0</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="21">
@@ -4196,28 +4196,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C21">
-        <v>56.31</v>
+        <v>54.97</v>
       </c>
       <c r="D21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G21">
-        <v>64.29</v>
+        <v>53.33</v>
       </c>
       <c r="H21">
+        <v>16.67</v>
+      </c>
+      <c r="I21">
         <v>33.33</v>
-      </c>
-      <c r="I21">
-        <v>5.26</v>
       </c>
     </row>
     <row r="22">
@@ -4228,7 +4228,7 @@
         <v>15</v>
       </c>
       <c r="C22">
-        <v>55.7</v>
+        <v>54.68</v>
       </c>
       <c r="D22">
         <v>9</v>
@@ -4237,16 +4237,16 @@
         <v>1</v>
       </c>
       <c r="F22">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G22">
-        <v>64.29</v>
+        <v>60.0</v>
       </c>
       <c r="H22">
         <v>16.67</v>
       </c>
       <c r="I22">
-        <v>28.95</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="23">
@@ -4257,7 +4257,7 @@
         <v>34</v>
       </c>
       <c r="C23">
-        <v>55.7</v>
+        <v>54.68</v>
       </c>
       <c r="D23">
         <v>9</v>
@@ -4266,16 +4266,16 @@
         <v>1</v>
       </c>
       <c r="F23">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G23">
-        <v>64.29</v>
+        <v>60.0</v>
       </c>
       <c r="H23">
         <v>16.67</v>
       </c>
       <c r="I23">
-        <v>28.95</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="24">
@@ -4283,28 +4283,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C24">
-        <v>55.67</v>
+        <v>52.19</v>
       </c>
       <c r="D24">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G24">
-        <v>57.14</v>
+        <v>73.33</v>
       </c>
       <c r="H24">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="I24">
-        <v>2.63</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="25">
@@ -4312,28 +4312,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C25">
-        <v>53.42</v>
+        <v>51.67</v>
       </c>
       <c r="D25">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G25">
-        <v>78.57</v>
+        <v>60.0</v>
       </c>
       <c r="H25">
-        <v>16.67</v>
+        <v>0.0</v>
       </c>
       <c r="I25">
-        <v>10.53</v>
+        <v>38.46</v>
       </c>
     </row>
     <row r="26">
@@ -4341,28 +4341,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C26">
-        <v>52.55</v>
+        <v>50.63</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="H26">
-        <v>50.0</v>
+        <v>33.33</v>
       </c>
       <c r="I26">
-        <v>5.26</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
@@ -4373,7 +4373,7 @@
         <v>25</v>
       </c>
       <c r="C27">
-        <v>51.02</v>
+        <v>50.31</v>
       </c>
       <c r="D27">
         <v>7</v>
@@ -4382,16 +4382,16 @@
         <v>1</v>
       </c>
       <c r="F27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G27">
-        <v>50.0</v>
+        <v>46.67</v>
       </c>
       <c r="H27">
         <v>16.67</v>
       </c>
       <c r="I27">
-        <v>23.68</v>
+        <v>25.64</v>
       </c>
     </row>
     <row r="28">
@@ -4399,28 +4399,28 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C28">
-        <v>50.75</v>
+        <v>49.5</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="G28">
-        <v>42.86</v>
+        <v>33.33</v>
       </c>
       <c r="H28">
-        <v>33.33</v>
+        <v>0.0</v>
       </c>
       <c r="I28">
-        <v>21.05</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="29">
@@ -4428,28 +4428,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C29">
-        <v>50.21</v>
+        <v>49.31</v>
       </c>
       <c r="D29">
         <v>5</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F29">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="G29">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="H29">
-        <v>0.0</v>
+        <v>50.0</v>
       </c>
       <c r="I29">
-        <v>100.0</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="30">
@@ -4457,10 +4457,10 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>49.69</v>
+        <v>48.15</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -4469,16 +4469,16 @@
         <v>3</v>
       </c>
       <c r="F30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G30">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="H30">
         <v>50.0</v>
       </c>
       <c r="I30">
-        <v>13.16</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="31">
@@ -4489,7 +4489,7 @@
         <v>30</v>
       </c>
       <c r="C31">
-        <v>44.33</v>
+        <v>43.98</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -4498,16 +4498,16 @@
         <v>2</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="H31">
         <v>33.33</v>
       </c>
       <c r="I31">
-        <v>5.26</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="32">
@@ -4515,10 +4515,10 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C32">
-        <v>43.55</v>
+        <v>42.83</v>
       </c>
       <c r="D32">
         <v>5</v>
@@ -4530,7 +4530,7 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="H32">
         <v>33.33</v>
@@ -4547,7 +4547,7 @@
         <v>5</v>
       </c>
       <c r="C33">
-        <v>42.14</v>
+        <v>41.74</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -4556,16 +4556,16 @@
         <v>1</v>
       </c>
       <c r="F33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G33">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="H33">
         <v>16.67</v>
       </c>
       <c r="I33">
-        <v>18.42</v>
+        <v>20.51</v>
       </c>
     </row>
     <row r="34">
@@ -4573,28 +4573,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C34">
-        <v>39.46</v>
+        <v>39.32</v>
       </c>
       <c r="D34">
         <v>4</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F34">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G34">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="H34">
-        <v>0.0</v>
+        <v>33.33</v>
       </c>
       <c r="I34">
-        <v>55.26</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="35">
@@ -4602,28 +4602,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C35">
-        <v>38.5</v>
+        <v>38.67</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
       <c r="F35">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="H35">
         <v>16.67</v>
       </c>
       <c r="I35">
-        <v>21.05</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="36">
@@ -4631,10 +4631,10 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C36">
-        <v>36.52</v>
+        <v>38.23</v>
       </c>
       <c r="D36">
         <v>4</v>
@@ -4643,16 +4643,16 @@
         <v>1</v>
       </c>
       <c r="F36">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G36">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="H36">
         <v>16.67</v>
       </c>
       <c r="I36">
-        <v>7.89</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="37">
@@ -4663,7 +4663,7 @@
         <v>32</v>
       </c>
       <c r="C37">
-        <v>36.52</v>
+        <v>36.31</v>
       </c>
       <c r="D37">
         <v>4</v>
@@ -4672,16 +4672,16 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G37">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="H37">
         <v>16.67</v>
       </c>
       <c r="I37">
-        <v>7.89</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="38">
@@ -4692,7 +4692,7 @@
         <v>20</v>
       </c>
       <c r="C38">
-        <v>35.24</v>
+        <v>35.1</v>
       </c>
       <c r="D38">
         <v>3</v>
@@ -4701,16 +4701,16 @@
         <v>1</v>
       </c>
       <c r="F38">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G38">
-        <v>21.43</v>
+        <v>20.0</v>
       </c>
       <c r="H38">
         <v>16.67</v>
       </c>
       <c r="I38">
-        <v>26.32</v>
+        <v>28.21</v>
       </c>
     </row>
     <row r="39">
@@ -4721,7 +4721,7 @@
         <v>37</v>
       </c>
       <c r="C39">
-        <v>32.48</v>
+        <v>32.41</v>
       </c>
       <c r="D39">
         <v>3</v>
@@ -4730,16 +4730,16 @@
         <v>1</v>
       </c>
       <c r="F39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G39">
-        <v>21.43</v>
+        <v>20.0</v>
       </c>
       <c r="H39">
         <v>16.67</v>
       </c>
       <c r="I39">
-        <v>7.89</v>
+        <v>10.26</v>
       </c>
     </row>
   </sheetData>
@@ -4798,61 +4798,61 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C2">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>14</v>
+      </c>
+      <c r="F2">
+        <v>16</v>
+      </c>
+      <c r="G2">
+        <v>29</v>
+      </c>
+      <c r="H2">
+        <v>36</v>
+      </c>
+      <c r="I2">
         <v>8</v>
-      </c>
-      <c r="D2">
-        <v>17</v>
-      </c>
-      <c r="E2">
-        <v>18</v>
-      </c>
-      <c r="F2">
-        <v>29</v>
-      </c>
-      <c r="G2">
-        <v>33</v>
-      </c>
-      <c r="H2">
-        <v>38</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H3">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I3">
         <v>2</v>
@@ -4860,108 +4860,108 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H4">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F5">
         <v>19</v>
       </c>
       <c r="G5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H5">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>19</v>
+      </c>
+      <c r="G6">
+        <v>32</v>
+      </c>
+      <c r="H6">
+        <v>37</v>
+      </c>
+      <c r="I6">
         <v>2</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
-      <c r="F6">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>24</v>
-      </c>
-      <c r="H6">
-        <v>36</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D7">
         <v>7</v>
@@ -4970,230 +4970,230 @@
         <v>9</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H7">
         <v>36</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E8">
         <v>9</v>
       </c>
       <c r="F8">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G8">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H8">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>9</v>
+      </c>
+      <c r="F9">
         <v>11</v>
       </c>
-      <c r="E9">
-        <v>18</v>
-      </c>
-      <c r="F9">
-        <v>19</v>
-      </c>
       <c r="G9">
+        <v>29</v>
+      </c>
+      <c r="H9">
         <v>35</v>
       </c>
-      <c r="H9">
-        <v>38</v>
-      </c>
       <c r="I9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F10">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G10">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H10">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="I10">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C11">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E11">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F11">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G11">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H11">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D12">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F12">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G12">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H12">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I12">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>7</v>
+      </c>
+      <c r="E13">
+        <v>8</v>
+      </c>
+      <c r="F13">
+        <v>20</v>
+      </c>
+      <c r="G13">
+        <v>26</v>
+      </c>
+      <c r="H13">
+        <v>33</v>
+      </c>
+      <c r="I13">
         <v>4</v>
-      </c>
-      <c r="D13">
-        <v>15</v>
-      </c>
-      <c r="E13">
-        <v>22</v>
-      </c>
-      <c r="F13">
-        <v>26</v>
-      </c>
-      <c r="G13">
-        <v>34</v>
-      </c>
-      <c r="H13">
-        <v>36</v>
-      </c>
-      <c r="I13">
-        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E14">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F14">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G14">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H14">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I14">
         <v>7</v>
@@ -5201,30 +5201,30 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C15">
+        <v>8</v>
+      </c>
+      <c r="D15">
+        <v>14</v>
+      </c>
+      <c r="E15">
+        <v>17</v>
+      </c>
+      <c r="F15">
         <v>19</v>
       </c>
-      <c r="D15">
-        <v>22</v>
-      </c>
-      <c r="E15">
-        <v>28</v>
-      </c>
-      <c r="F15">
-        <v>31</v>
-      </c>
       <c r="G15">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H15">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I15">
         <v>7</v>
@@ -5232,30 +5232,30 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C16">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D16">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E16">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F16">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G16">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H16">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I16">
         <v>7</v>
@@ -5263,24 +5263,24 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D17">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E17">
         <v>13</v>
       </c>
       <c r="F17">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G17">
         <v>29</v>
@@ -5289,97 +5289,97 @@
         <v>31</v>
       </c>
       <c r="I17">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C18">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D18">
+        <v>12</v>
+      </c>
+      <c r="E18">
+        <v>13</v>
+      </c>
+      <c r="F18">
         <v>23</v>
       </c>
-      <c r="E18">
-        <v>25</v>
-      </c>
-      <c r="F18">
+      <c r="G18">
         <v>29</v>
       </c>
-      <c r="G18">
-        <v>34</v>
-      </c>
       <c r="H18">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I18">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C19">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E19">
+        <v>25</v>
+      </c>
+      <c r="F19">
         <v>29</v>
       </c>
-      <c r="F19">
-        <v>32</v>
-      </c>
       <c r="G19">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H19">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I19">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C20">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D20">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E20">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F20">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G20">
         <v>35</v>
       </c>
       <c r="H20">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I20">
         <v>6</v>
@@ -5387,402 +5387,402 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D21">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E21">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F21">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G21">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H21">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D22">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E22">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F22">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G22">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H22">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I22">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C23">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D23">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E23">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F23">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G23">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H23">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I23">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C24">
+        <v>5</v>
+      </c>
+      <c r="D24">
         <v>6</v>
       </c>
-      <c r="D24">
-        <v>10</v>
-      </c>
       <c r="E24">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F24">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G24">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H24">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C25">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D25">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E25">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F25">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G25">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H25">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I25">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D26">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E26">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F26">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G26">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H26">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I26">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27">
+        <v>8</v>
+      </c>
+      <c r="E27">
+        <v>9</v>
+      </c>
+      <c r="F27">
+        <v>15</v>
+      </c>
+      <c r="G27">
+        <v>18</v>
+      </c>
+      <c r="H27">
+        <v>23</v>
+      </c>
+      <c r="I27">
         <v>4</v>
-      </c>
-      <c r="D27">
-        <v>17</v>
-      </c>
-      <c r="E27">
-        <v>19</v>
-      </c>
-      <c r="F27">
-        <v>25</v>
-      </c>
-      <c r="G27">
-        <v>28</v>
-      </c>
-      <c r="H27">
-        <v>29</v>
-      </c>
-      <c r="I27">
-        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C28">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D28">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E28">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F28">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G28">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H28">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I28">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D29">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E29">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F29">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G29">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H29">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I29">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C30">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D30">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E30">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F30">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G30">
         <v>28</v>
       </c>
       <c r="H30">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I30">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C31">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D31">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E31">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F31">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G31">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H31">
         <v>35</v>
       </c>
       <c r="I31">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E32">
+        <v>9</v>
+      </c>
+      <c r="F32">
+        <v>15</v>
+      </c>
+      <c r="G32">
         <v>24</v>
       </c>
-      <c r="F32">
-        <v>31</v>
-      </c>
-      <c r="G32">
-        <v>34</v>
-      </c>
       <c r="H32">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I32">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C33">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E33">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F33">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G33">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I33">
         <v>3</v>
@@ -5790,554 +5790,554 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C34">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D34">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E34">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F34">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G34">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H34">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I34">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C35">
         <v>6</v>
       </c>
       <c r="D35">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E35">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F35">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G35">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H35">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I35">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C36">
         <v>6</v>
       </c>
       <c r="D36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E36">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F36">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G36">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H36">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I36">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C37">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D37">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E37">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F37">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G37">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H37">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I37">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C38">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D38">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E38">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F38">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G38">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H38">
         <v>38</v>
       </c>
       <c r="I38">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C39">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D39">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E39">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F39">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G39">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H39">
         <v>38</v>
       </c>
       <c r="I39">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D40">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E40">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F40">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G40">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H40">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I40">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C41">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D41">
+        <v>4</v>
+      </c>
+      <c r="E41">
+        <v>13</v>
+      </c>
+      <c r="F41">
+        <v>19</v>
+      </c>
+      <c r="G41">
+        <v>27</v>
+      </c>
+      <c r="H41">
+        <v>30</v>
+      </c>
+      <c r="I41">
         <v>8</v>
-      </c>
-      <c r="E41">
-        <v>27</v>
-      </c>
-      <c r="F41">
-        <v>33</v>
-      </c>
-      <c r="G41">
-        <v>35</v>
-      </c>
-      <c r="H41">
-        <v>38</v>
-      </c>
-      <c r="I41">
-        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C42">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D42">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E42">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F42">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G42">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H42">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I42">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C43">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D43">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E43">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F43">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G43">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H43">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I43">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C44">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D44">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E44">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F44">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G44">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H44">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I44">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000030</v>
+        <v>115000031</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D45">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E45">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F45">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G45">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H45">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="I45">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000029</v>
+        <v>115000030</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D46">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E46">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F46">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G46">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H46">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I46">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000028</v>
+        <v>115000029</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D47">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E47">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F47">
         <v>27</v>
       </c>
       <c r="G47">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H47">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I47">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000027</v>
+        <v>115000028</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C48">
         <v>5</v>
       </c>
       <c r="D48">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E48">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F48">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G48">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H48">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I48">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000026</v>
+        <v>115000027</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C49">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D49">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E49">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F49">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G49">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H49">
         <v>34</v>
       </c>
       <c r="I49">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000025</v>
+        <v>115000026</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C50">
+        <v>2</v>
+      </c>
+      <c r="D50">
         <v>13</v>
       </c>
-      <c r="D50">
-        <v>14</v>
-      </c>
       <c r="E50">
+        <v>21</v>
+      </c>
+      <c r="F50">
         <v>22</v>
       </c>
-      <c r="F50">
-        <v>28</v>
-      </c>
       <c r="G50">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H50">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I50">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000024</v>
+        <v>115000025</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D51">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E51">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F51">
         <v>28</v>
       </c>
       <c r="G51">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H51">
         <v>38</v>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-09-11 第 115000087 期；威力彩 2026-09-14 第 115000074 期</t>
+          <t>大樂透 2026-09-15 第 115000088 期；威力彩 2026-09-14 第 115000074 期</t>
         </is>
       </c>
     </row>
@@ -47,7 +47,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>115000087</v>
+        <v>115000088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -56,7 +56,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -96,7 +96,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.309 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.262 碼/期</t>
         </is>
       </c>
     </row>
@@ -214,7 +214,7 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>0.976</v>
+        <v>0.952</v>
       </c>
       <c r="D2">
         <v>28.6</v>
@@ -236,7 +236,7 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>0.952</v>
+        <v>0.929</v>
       </c>
       <c r="D3">
         <v>26.2</v>
@@ -258,7 +258,7 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>0.81</v>
+        <v>0.786</v>
       </c>
       <c r="D4">
         <v>19.0</v>
@@ -280,7 +280,7 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>0.786</v>
+        <v>0.762</v>
       </c>
       <c r="D5">
         <v>19.0</v>
@@ -302,7 +302,7 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.667</v>
+        <v>0.69</v>
       </c>
       <c r="D6">
         <v>11.9</v>
@@ -324,10 +324,10 @@
         <v>42</v>
       </c>
       <c r="C7">
-        <v>0.619</v>
+        <v>0.643</v>
       </c>
       <c r="D7">
-        <v>9.5</v>
+        <v>11.9</v>
       </c>
       <c r="E7">
         <v>0.0</v>
@@ -398,7 +398,7 @@
         <v>26</v>
       </c>
       <c r="C2">
-        <v>71.78</v>
+        <v>72.14</v>
       </c>
       <c r="D2">
         <v>12</v>
@@ -407,7 +407,7 @@
         <v>5</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
         <v>100.0</v>
@@ -416,7 +416,7 @@
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>7.89</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="3">
@@ -427,7 +427,7 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>70.6</v>
+        <v>70.98</v>
       </c>
       <c r="D3">
         <v>12</v>
@@ -436,7 +436,7 @@
         <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
         <v>100.0</v>
@@ -445,7 +445,7 @@
         <v>100.0</v>
       </c>
       <c r="I3">
-        <v>0.0</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="4">
@@ -456,7 +456,7 @@
         <v>24</v>
       </c>
       <c r="C4">
-        <v>66.67</v>
+        <v>67.01</v>
       </c>
       <c r="D4">
         <v>6</v>
@@ -465,7 +465,7 @@
         <v>4</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4">
         <v>50.0</v>
@@ -474,7 +474,7 @@
         <v>80.0</v>
       </c>
       <c r="I4">
-        <v>13.16</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="5">
@@ -482,13 +482,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C5">
-        <v>65.8</v>
+        <v>65.83</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -497,13 +497,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>66.67</v>
+        <v>75.0</v>
       </c>
       <c r="H5">
         <v>80.0</v>
       </c>
       <c r="I5">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="6">
@@ -511,28 +511,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C6">
-        <v>65.45</v>
+        <v>63.58</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G6">
-        <v>75.0</v>
+        <v>83.33</v>
       </c>
       <c r="H6">
-        <v>80.0</v>
+        <v>60.0</v>
       </c>
       <c r="I6">
-        <v>0.0</v>
+        <v>20.51</v>
       </c>
     </row>
     <row r="7">
@@ -540,28 +540,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>65.4</v>
+        <v>63.09</v>
       </c>
       <c r="D7">
         <v>8</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G7">
         <v>66.67</v>
       </c>
       <c r="H7">
-        <v>80.0</v>
+        <v>60.0</v>
       </c>
       <c r="I7">
-        <v>0.0</v>
+        <v>17.95</v>
       </c>
     </row>
     <row r="8">
@@ -569,28 +569,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C8">
-        <v>64.7</v>
+        <v>62.32</v>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G8">
-        <v>50.0</v>
+        <v>66.67</v>
       </c>
       <c r="H8">
-        <v>80.0</v>
+        <v>60.0</v>
       </c>
       <c r="I8">
-        <v>0.0</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="9">
@@ -598,28 +598,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C9">
-        <v>63.26</v>
+        <v>62.14</v>
       </c>
       <c r="D9">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>83.33</v>
+        <v>100.0</v>
       </c>
       <c r="H9">
         <v>60.0</v>
       </c>
       <c r="I9">
-        <v>18.42</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="10">
@@ -627,28 +627,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10">
-        <v>62.86</v>
+        <v>61.17</v>
       </c>
       <c r="D10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G10">
-        <v>50.0</v>
+        <v>66.67</v>
       </c>
       <c r="H10">
         <v>60.0</v>
       </c>
       <c r="I10">
-        <v>21.05</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="11">
@@ -656,10 +656,10 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C11">
-        <v>62.77</v>
+        <v>60.79</v>
       </c>
       <c r="D11">
         <v>8</v>
@@ -668,7 +668,7 @@
         <v>3</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G11">
         <v>66.67</v>
@@ -677,7 +677,7 @@
         <v>60.0</v>
       </c>
       <c r="I11">
-        <v>15.79</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="12">
@@ -685,28 +685,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="C12">
-        <v>61.98</v>
+        <v>60.73</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>66.67</v>
+        <v>58.33</v>
       </c>
       <c r="H12">
         <v>60.0</v>
       </c>
       <c r="I12">
-        <v>10.53</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="13">
@@ -714,28 +714,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C13">
-        <v>61.78</v>
+        <v>60.08</v>
       </c>
       <c r="D13">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>100.0</v>
+        <v>50.0</v>
       </c>
       <c r="H13">
         <v>60.0</v>
       </c>
       <c r="I13">
-        <v>7.89</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="14">
@@ -743,13 +743,13 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="C14">
-        <v>60.35</v>
+        <v>59.7</v>
       </c>
       <c r="D14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -758,7 +758,7 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>58.33</v>
+        <v>50.0</v>
       </c>
       <c r="H14">
         <v>60.0</v>
@@ -772,28 +772,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C15">
-        <v>57.72</v>
+        <v>58.16</v>
       </c>
       <c r="D15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E15">
         <v>2</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G15">
-        <v>58.33</v>
+        <v>50.0</v>
       </c>
       <c r="H15">
         <v>40.0</v>
       </c>
       <c r="I15">
-        <v>15.79</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="16">
@@ -801,28 +801,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C16">
-        <v>56.98</v>
+        <v>57.39</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E16">
         <v>2</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G16">
-        <v>66.67</v>
+        <v>50.0</v>
       </c>
       <c r="H16">
         <v>40.0</v>
       </c>
       <c r="I16">
-        <v>10.53</v>
+        <v>17.95</v>
       </c>
     </row>
     <row r="17">
@@ -830,28 +830,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C17">
-        <v>56.93</v>
+        <v>57.32</v>
       </c>
       <c r="D17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G17">
-        <v>58.33</v>
+        <v>66.67</v>
       </c>
       <c r="H17">
         <v>40.0</v>
       </c>
       <c r="I17">
-        <v>10.53</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="18">
@@ -859,28 +859,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C18">
-        <v>56.68</v>
+        <v>57.27</v>
       </c>
       <c r="D18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18">
-        <v>83.33</v>
+        <v>58.33</v>
       </c>
       <c r="H18">
         <v>40.0</v>
       </c>
       <c r="I18">
-        <v>7.89</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="19">
@@ -888,28 +888,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="C19">
-        <v>56.33</v>
+        <v>57.04</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F19">
         <v>4</v>
       </c>
       <c r="G19">
-        <v>41.67</v>
+        <v>83.33</v>
       </c>
       <c r="H19">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="I19">
-        <v>10.53</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="20">
@@ -920,7 +920,7 @@
         <v>47</v>
       </c>
       <c r="C20">
-        <v>55.74</v>
+        <v>56.12</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -929,7 +929,7 @@
         <v>2</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20">
         <v>58.33</v>
@@ -938,7 +938,7 @@
         <v>40.0</v>
       </c>
       <c r="I20">
-        <v>2.63</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="21">
@@ -949,25 +949,25 @@
         <v>48</v>
       </c>
       <c r="C21">
-        <v>55.4</v>
+        <v>55.73</v>
       </c>
       <c r="D21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E21">
         <v>2</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>66.67</v>
+        <v>58.33</v>
       </c>
       <c r="H21">
         <v>40.0</v>
       </c>
       <c r="I21">
-        <v>0.0</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="22">
@@ -975,28 +975,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="C22">
-        <v>55.15</v>
+        <v>55.47</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>41.67</v>
+        <v>50.0</v>
       </c>
       <c r="H22">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="I22">
-        <v>2.63</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="23">
@@ -1004,28 +1004,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="C23">
-        <v>55.09</v>
+        <v>55.45</v>
       </c>
       <c r="D23">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E23">
         <v>2</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>50.0</v>
+        <v>75.0</v>
       </c>
       <c r="H23">
         <v>40.0</v>
       </c>
       <c r="I23">
-        <v>2.63</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="24">
@@ -1036,7 +1036,7 @@
         <v>4</v>
       </c>
       <c r="C24">
-        <v>54.79</v>
+        <v>55.07</v>
       </c>
       <c r="D24">
         <v>9</v>
@@ -1045,7 +1045,7 @@
         <v>1</v>
       </c>
       <c r="F24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G24">
         <v>75.0</v>
@@ -1054,7 +1054,7 @@
         <v>20.0</v>
       </c>
       <c r="I24">
-        <v>28.95</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="25">
@@ -1065,7 +1065,7 @@
         <v>11</v>
       </c>
       <c r="C25">
-        <v>54.44</v>
+        <v>54.7</v>
       </c>
       <c r="D25">
         <v>6</v>
@@ -1074,7 +1074,7 @@
         <v>1</v>
       </c>
       <c r="F25">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G25">
         <v>50.0</v>
@@ -1083,7 +1083,7 @@
         <v>20.0</v>
       </c>
       <c r="I25">
-        <v>31.58</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="26">
@@ -1091,28 +1091,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>52.91</v>
+        <v>52.78</v>
       </c>
       <c r="D26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26">
         <v>8</v>
       </c>
       <c r="G26">
-        <v>41.67</v>
+        <v>50.0</v>
       </c>
       <c r="H26">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I26">
-        <v>21.05</v>
+        <v>20.51</v>
       </c>
     </row>
     <row r="27">
@@ -1120,28 +1120,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C27">
-        <v>52.46</v>
+        <v>52.06</v>
       </c>
       <c r="D27">
+        <v>5</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="F27">
         <v>6</v>
       </c>
-      <c r="E27">
-        <v>1</v>
-      </c>
-      <c r="F27">
-        <v>7</v>
-      </c>
       <c r="G27">
-        <v>50.0</v>
+        <v>41.67</v>
       </c>
       <c r="H27">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I27">
-        <v>18.42</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="28">
@@ -1149,28 +1149,28 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C28">
-        <v>51.72</v>
+        <v>52.01</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28">
-        <v>41.67</v>
+        <v>50.0</v>
       </c>
       <c r="H28">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I28">
-        <v>13.16</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="29">
@@ -1178,28 +1178,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="C29">
-        <v>51.67</v>
+        <v>51.89</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G29">
-        <v>50.0</v>
+        <v>58.33</v>
       </c>
       <c r="H29">
         <v>20.0</v>
       </c>
       <c r="I29">
-        <v>13.16</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="30">
@@ -1207,28 +1207,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C30">
-        <v>51.53</v>
+        <v>51.24</v>
       </c>
       <c r="D30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G30">
-        <v>58.33</v>
+        <v>50.0</v>
       </c>
       <c r="H30">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I30">
-        <v>7.89</v>
+        <v>43.59</v>
       </c>
     </row>
     <row r="31">
@@ -1236,28 +1236,28 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C31">
-        <v>51.19</v>
+        <v>50.85</v>
       </c>
       <c r="D31">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31">
-        <v>66.67</v>
+        <v>50.0</v>
       </c>
       <c r="H31">
         <v>20.0</v>
       </c>
       <c r="I31">
-        <v>5.26</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="32">
@@ -1265,28 +1265,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C32">
-        <v>51.02</v>
+        <v>50.47</v>
       </c>
       <c r="D32">
         <v>6</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G32">
         <v>50.0</v>
       </c>
       <c r="H32">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I32">
-        <v>42.11</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="33">
@@ -1294,28 +1294,28 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>50.49</v>
+        <v>49.75</v>
       </c>
       <c r="D33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>50.0</v>
+        <v>41.67</v>
       </c>
       <c r="H33">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I33">
-        <v>5.26</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="34">
@@ -1323,28 +1323,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C34">
-        <v>50.09</v>
+        <v>49.75</v>
       </c>
       <c r="D34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34">
-        <v>50.0</v>
+        <v>41.67</v>
       </c>
       <c r="H34">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I34">
-        <v>2.63</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="35">
@@ -1355,25 +1355,25 @@
         <v>39</v>
       </c>
       <c r="C35">
-        <v>47.65</v>
+        <v>49.7</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35">
         <v>0</v>
       </c>
-      <c r="F35">
-        <v>20</v>
-      </c>
       <c r="G35">
-        <v>41.67</v>
+        <v>50.0</v>
       </c>
       <c r="H35">
+        <v>20.0</v>
+      </c>
+      <c r="I35">
         <v>0.0</v>
-      </c>
-      <c r="I35">
-        <v>52.63</v>
       </c>
     </row>
     <row r="36">
@@ -1381,10 +1381,10 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C36">
-        <v>46.38</v>
+        <v>48.26</v>
       </c>
       <c r="D36">
         <v>4</v>
@@ -1393,7 +1393,7 @@
         <v>2</v>
       </c>
       <c r="F36">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G36">
         <v>33.33</v>
@@ -1402,7 +1402,7 @@
         <v>40.0</v>
       </c>
       <c r="I36">
-        <v>10.53</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="37">
@@ -1410,28 +1410,28 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C37">
-        <v>45.54</v>
+        <v>46.72</v>
       </c>
       <c r="D37">
+        <v>4</v>
+      </c>
+      <c r="E37">
+        <v>2</v>
+      </c>
+      <c r="F37">
         <v>5</v>
       </c>
-      <c r="E37">
-        <v>1</v>
-      </c>
-      <c r="F37">
-        <v>2</v>
-      </c>
       <c r="G37">
-        <v>41.67</v>
+        <v>33.33</v>
       </c>
       <c r="H37">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I37">
-        <v>5.26</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="38">
@@ -1439,28 +1439,28 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="C38">
-        <v>45.54</v>
+        <v>46.72</v>
       </c>
       <c r="D38">
+        <v>4</v>
+      </c>
+      <c r="E38">
+        <v>2</v>
+      </c>
+      <c r="F38">
         <v>5</v>
       </c>
-      <c r="E38">
-        <v>1</v>
-      </c>
-      <c r="F38">
-        <v>2</v>
-      </c>
       <c r="G38">
-        <v>41.67</v>
+        <v>33.33</v>
       </c>
       <c r="H38">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I38">
-        <v>5.26</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="39">
@@ -1468,28 +1468,28 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C39">
-        <v>44.85</v>
+        <v>45.9</v>
       </c>
       <c r="D39">
+        <v>5</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="F39">
         <v>3</v>
       </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-      <c r="F39">
-        <v>38</v>
-      </c>
       <c r="G39">
-        <v>25.0</v>
+        <v>41.67</v>
       </c>
       <c r="H39">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I39">
-        <v>100.0</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="40">
@@ -1497,28 +1497,28 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C40">
-        <v>43.75</v>
+        <v>45.9</v>
       </c>
       <c r="D40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E40">
         <v>1</v>
       </c>
       <c r="F40">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G40">
-        <v>33.33</v>
+        <v>41.67</v>
       </c>
       <c r="H40">
         <v>20.0</v>
       </c>
       <c r="I40">
-        <v>26.32</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="41">
@@ -1526,28 +1526,28 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C41">
-        <v>43.75</v>
+        <v>44.85</v>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="G41">
-        <v>33.33</v>
+        <v>25.0</v>
       </c>
       <c r="H41">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I41">
-        <v>26.32</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="42">
@@ -1558,7 +1558,7 @@
         <v>46</v>
       </c>
       <c r="C42">
-        <v>43.35</v>
+        <v>43.64</v>
       </c>
       <c r="D42">
         <v>4</v>
@@ -1567,7 +1567,7 @@
         <v>1</v>
       </c>
       <c r="F42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G42">
         <v>33.33</v>
@@ -1576,7 +1576,7 @@
         <v>20.0</v>
       </c>
       <c r="I42">
-        <v>23.68</v>
+        <v>25.64</v>
       </c>
     </row>
     <row r="43">
@@ -1584,28 +1584,28 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C43">
-        <v>42.88</v>
+        <v>41.72</v>
       </c>
       <c r="D43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E43">
         <v>0</v>
       </c>
       <c r="F43">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G43">
-        <v>25.0</v>
+        <v>33.33</v>
       </c>
       <c r="H43">
         <v>0.0</v>
       </c>
       <c r="I43">
-        <v>86.84</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="44">
@@ -1613,28 +1613,28 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="C44">
-        <v>41.51</v>
+        <v>39.8</v>
       </c>
       <c r="D44">
         <v>4</v>
       </c>
       <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="F44">
         <v>0</v>
-      </c>
-      <c r="F44">
-        <v>17</v>
       </c>
       <c r="G44">
         <v>33.33</v>
       </c>
       <c r="H44">
+        <v>20.0</v>
+      </c>
+      <c r="I44">
         <v>0.0</v>
-      </c>
-      <c r="I44">
-        <v>44.74</v>
       </c>
     </row>
     <row r="45">
@@ -1645,7 +1645,7 @@
         <v>30</v>
       </c>
       <c r="C45">
-        <v>39.19</v>
+        <v>39.47</v>
       </c>
       <c r="D45">
         <v>3</v>
@@ -1654,7 +1654,7 @@
         <v>1</v>
       </c>
       <c r="F45">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G45">
         <v>25.0</v>
@@ -1663,7 +1663,7 @@
         <v>20.0</v>
       </c>
       <c r="I45">
-        <v>28.95</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="46">
@@ -1671,10 +1671,10 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="C46">
-        <v>38.8</v>
+        <v>38.31</v>
       </c>
       <c r="D46">
         <v>3</v>
@@ -1683,7 +1683,7 @@
         <v>1</v>
       </c>
       <c r="F46">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G46">
         <v>25.0</v>
@@ -1692,7 +1692,7 @@
         <v>20.0</v>
       </c>
       <c r="I46">
-        <v>26.32</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="47">
@@ -1700,28 +1700,28 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="C47">
-        <v>38.01</v>
+        <v>34.13</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47">
         <v>1</v>
       </c>
       <c r="F47">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G47">
-        <v>25.0</v>
+        <v>16.67</v>
       </c>
       <c r="H47">
         <v>20.0</v>
       </c>
       <c r="I47">
-        <v>21.05</v>
+        <v>28.21</v>
       </c>
     </row>
     <row r="48">
@@ -1729,28 +1729,28 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C48">
-        <v>37.35</v>
+        <v>33.03</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="G48">
-        <v>25.0</v>
+        <v>8.33</v>
       </c>
       <c r="H48">
         <v>0.0</v>
       </c>
       <c r="I48">
-        <v>50.0</v>
+        <v>87.18</v>
       </c>
     </row>
     <row r="49">
@@ -1758,28 +1758,28 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C49">
-        <v>32.98</v>
+        <v>32.59</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49">
         <v>0</v>
       </c>
       <c r="F49">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G49">
-        <v>8.33</v>
+        <v>16.67</v>
       </c>
       <c r="H49">
         <v>0.0</v>
       </c>
       <c r="I49">
-        <v>86.84</v>
+        <v>51.28</v>
       </c>
     </row>
     <row r="50">
@@ -1790,7 +1790,7 @@
         <v>31</v>
       </c>
       <c r="C50">
-        <v>31.79</v>
+        <v>31.87</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G50">
         <v>8.33</v>
@@ -1808,7 +1808,7 @@
         <v>0.0</v>
       </c>
       <c r="I50">
-        <v>78.95</v>
+        <v>79.49</v>
       </c>
     </row>
   </sheetData>
@@ -1867,607 +1867,607 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000087</v>
+        <v>115000088</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I2">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000086</v>
+        <v>115000087</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D3">
         <v>15</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F3">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H3">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I3">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000085</v>
+        <v>115000086</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G4">
+        <v>47</v>
+      </c>
+      <c r="H4">
+        <v>49</v>
+      </c>
+      <c r="I4">
         <v>27</v>
-      </c>
-      <c r="H4">
-        <v>37</v>
-      </c>
-      <c r="I4">
-        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000084</v>
+        <v>115000085</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E5">
+        <v>17</v>
+      </c>
+      <c r="F5">
+        <v>18</v>
+      </c>
+      <c r="G5">
+        <v>27</v>
+      </c>
+      <c r="H5">
+        <v>37</v>
+      </c>
+      <c r="I5">
         <v>19</v>
-      </c>
-      <c r="F5">
-        <v>26</v>
-      </c>
-      <c r="G5">
-        <v>29</v>
-      </c>
-      <c r="H5">
-        <v>48</v>
-      </c>
-      <c r="I5">
-        <v>30</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000083</v>
+        <v>115000084</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F6">
         <v>26</v>
       </c>
       <c r="G6">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H6">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C7">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E7">
+        <v>23</v>
+      </c>
+      <c r="F7">
         <v>26</v>
       </c>
-      <c r="F7">
-        <v>32</v>
-      </c>
       <c r="G7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H7">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C8">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D8">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F8">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G8">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H8">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I8">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D9">
         <v>14</v>
       </c>
       <c r="E9">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F9">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G9">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H9">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E10">
         <v>25</v>
       </c>
       <c r="F10">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G10">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H10">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I10">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D11">
         <v>12</v>
       </c>
       <c r="E11">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F11">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G11">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H11">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="I11">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D12">
         <v>12</v>
       </c>
       <c r="E12">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F12">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G12">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H12">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I12">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D13">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E13">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F13">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G13">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H13">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I13">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C14">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D14">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E14">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F14">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H14">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I14">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E15">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F15">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G15">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H15">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I15">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D16">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E16">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F16">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G16">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H16">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I16">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E17">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F17">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G17">
         <v>35</v>
       </c>
       <c r="H17">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I17">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E18">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F18">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G18">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H18">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I18">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C19">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E19">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F19">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G19">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H19">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I19">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C20">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D20">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E20">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F20">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G20">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H20">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I20">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C21">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D21">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E21">
         <v>15</v>
@@ -2476,345 +2476,345 @@
         <v>18</v>
       </c>
       <c r="G21">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H21">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I21">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C22">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D22">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E22">
+        <v>15</v>
+      </c>
+      <c r="F22">
+        <v>18</v>
+      </c>
+      <c r="G22">
         <v>19</v>
       </c>
-      <c r="F22">
-        <v>23</v>
-      </c>
-      <c r="G22">
-        <v>39</v>
-      </c>
       <c r="H22">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I22">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D23">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E23">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F23">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G23">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H23">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I23">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C24">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D24">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E24">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F24">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G24">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H24">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C25">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D25">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E25">
+        <v>23</v>
+      </c>
+      <c r="F25">
+        <v>24</v>
+      </c>
+      <c r="G25">
         <v>29</v>
       </c>
-      <c r="F25">
-        <v>33</v>
-      </c>
-      <c r="G25">
-        <v>34</v>
-      </c>
       <c r="H25">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I25">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C26">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D26">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E26">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F26">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G26">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H26">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I26">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E27">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F27">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G27">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H27">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I27">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E28">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F28">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G28">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H28">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I28">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C29">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D29">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E29">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F29">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G29">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H29">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I29">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C30">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D30">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E30">
         <v>25</v>
       </c>
       <c r="F30">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G30">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H30">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I30">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C31">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D31">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E31">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F31">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G31">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H31">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I31">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C32">
+        <v>8</v>
+      </c>
+      <c r="D32">
+        <v>9</v>
+      </c>
+      <c r="E32">
+        <v>16</v>
+      </c>
+      <c r="F32">
         <v>20</v>
-      </c>
-      <c r="D32">
-        <v>26</v>
-      </c>
-      <c r="E32">
-        <v>29</v>
-      </c>
-      <c r="F32">
-        <v>31</v>
       </c>
       <c r="G32">
         <v>37</v>
@@ -2823,596 +2823,596 @@
         <v>49</v>
       </c>
       <c r="I32">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C33">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D33">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E33">
         <v>29</v>
       </c>
       <c r="F33">
+        <v>31</v>
+      </c>
+      <c r="G33">
         <v>37</v>
       </c>
-      <c r="G33">
-        <v>47</v>
-      </c>
       <c r="H33">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I33">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C34">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D34">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E34">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F34">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G34">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="H34">
         <v>48</v>
       </c>
       <c r="I34">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C35">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D35">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E35">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F35">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G35">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H35">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I35">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C36">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D36">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E36">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F36">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G36">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H36">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I36">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C37">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D37">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E37">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F37">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G37">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H37">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I37">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D38">
+        <v>12</v>
+      </c>
+      <c r="E38">
         <v>18</v>
       </c>
-      <c r="E38">
-        <v>25</v>
-      </c>
       <c r="F38">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G38">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H38">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I38">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C39">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D39">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E39">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F39">
         <v>28</v>
       </c>
       <c r="G39">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H39">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I39">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C40">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D40">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E40">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F40">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G40">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H40">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I40">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D41">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E41">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F41">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G41">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H41">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I41">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C42">
+        <v>6</v>
+      </c>
+      <c r="D42">
+        <v>10</v>
+      </c>
+      <c r="E42">
+        <v>14</v>
+      </c>
+      <c r="F42">
+        <v>25</v>
+      </c>
+      <c r="G42">
+        <v>26</v>
+      </c>
+      <c r="H42">
+        <v>32</v>
+      </c>
+      <c r="I42">
         <v>7</v>
-      </c>
-      <c r="D42">
-        <v>14</v>
-      </c>
-      <c r="E42">
-        <v>16</v>
-      </c>
-      <c r="F42">
-        <v>37</v>
-      </c>
-      <c r="G42">
-        <v>39</v>
-      </c>
-      <c r="H42">
-        <v>47</v>
-      </c>
-      <c r="I42">
-        <v>34</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D43">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E43">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F43">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G43">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H43">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I43">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C44">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D44">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E44">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F44">
+        <v>19</v>
+      </c>
+      <c r="G44">
+        <v>20</v>
+      </c>
+      <c r="H44">
+        <v>40</v>
+      </c>
+      <c r="I44">
         <v>22</v>
-      </c>
-      <c r="G44">
-        <v>40</v>
-      </c>
-      <c r="H44">
-        <v>45</v>
-      </c>
-      <c r="I44">
-        <v>18</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D45">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E45">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F45">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G45">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H45">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I45">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C46">
         <v>4</v>
       </c>
       <c r="D46">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E46">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F46">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G46">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H46">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I46">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E47">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F47">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G47">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H47">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I47">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C48">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D48">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E48">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F48">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G48">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H48">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I48">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C49">
         <v>5</v>
       </c>
       <c r="D49">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E49">
+        <v>13</v>
+      </c>
+      <c r="F49">
         <v>25</v>
       </c>
-      <c r="F49">
-        <v>40</v>
-      </c>
       <c r="G49">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H49">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I49">
-        <v>39</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D50">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E50">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F50">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G50">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H50">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I50">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C51">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D51">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E51">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F51">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G51">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H51">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I51">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-09-15 第 115000088 期；威力彩 2026-09-14 第 115000074 期</t>
+          <t>大樂透 2026-09-15 第 115000088 期；威力彩 2026-09-17 第 115000075 期</t>
         </is>
       </c>
     </row>
@@ -112,7 +112,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -121,7 +121,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -143,7 +143,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9, 19, 22, 29, 35, 38</t>
+          <t>9, 19, 24, 29, 35, 38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -161,7 +161,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.381 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.31 碼/期</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>1.048</v>
+        <v>1.024</v>
       </c>
       <c r="D2">
         <v>33.3</v>
@@ -3486,7 +3486,7 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>1.048</v>
+        <v>1.024</v>
       </c>
       <c r="D3">
         <v>33.3</v>
@@ -3508,7 +3508,7 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>1.0</v>
+        <v>0.976</v>
       </c>
       <c r="D4">
         <v>23.8</v>
@@ -3523,7 +3523,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>均衡分散</t>
+          <t>冷號觀察</t>
         </is>
       </c>
       <c r="B5">
@@ -3533,10 +3533,10 @@
         <v>0.952</v>
       </c>
       <c r="D5">
-        <v>21.4</v>
+        <v>28.6</v>
       </c>
       <c r="E5">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -3545,7 +3545,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>冷號觀察</t>
+          <t>均衡分散</t>
         </is>
       </c>
       <c r="B6">
@@ -3555,10 +3555,10 @@
         <v>0.929</v>
       </c>
       <c r="D6">
-        <v>28.6</v>
+        <v>21.4</v>
       </c>
       <c r="E6">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -3574,10 +3574,10 @@
         <v>42</v>
       </c>
       <c r="C7">
-        <v>0.667</v>
+        <v>0.714</v>
       </c>
       <c r="D7">
-        <v>11.9</v>
+        <v>14.3</v>
       </c>
       <c r="E7">
         <v>0.0</v>
@@ -3645,13 +3645,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>72.35</v>
+        <v>73.81</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <v>6</v>
@@ -3660,13 +3660,13 @@
         <v>3</v>
       </c>
       <c r="G2">
-        <v>80.0</v>
+        <v>66.67</v>
       </c>
       <c r="H2">
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>7.69</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="3">
@@ -3674,28 +3674,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C3">
-        <v>71.77</v>
+        <v>70.78</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>66.67</v>
+        <v>80.0</v>
       </c>
       <c r="H3">
-        <v>100.0</v>
+        <v>83.33</v>
       </c>
       <c r="I3">
-        <v>5.13</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="4">
@@ -3706,7 +3706,7 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>64.49</v>
+        <v>68.19</v>
       </c>
       <c r="D4">
         <v>9</v>
@@ -3715,7 +3715,7 @@
         <v>4</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4">
         <v>60.0</v>
@@ -3724,7 +3724,7 @@
         <v>66.67</v>
       </c>
       <c r="I4">
-        <v>12.82</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="5">
@@ -3732,13 +3732,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>63.84</v>
+        <v>64.54</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -3747,13 +3747,13 @@
         <v>2</v>
       </c>
       <c r="G5">
-        <v>93.33</v>
+        <v>66.67</v>
       </c>
       <c r="H5">
         <v>66.67</v>
       </c>
       <c r="I5">
-        <v>5.13</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="6">
@@ -3761,28 +3761,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>63.17</v>
+        <v>64.22</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>100.0</v>
+        <v>73.33</v>
       </c>
       <c r="H6">
-        <v>66.67</v>
+        <v>50.0</v>
       </c>
       <c r="I6">
-        <v>0.0</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="7">
@@ -3790,28 +3790,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C7">
-        <v>63.13</v>
+        <v>64.11</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>46.67</v>
+        <v>100.0</v>
       </c>
       <c r="H7">
-        <v>83.33</v>
+        <v>66.67</v>
       </c>
       <c r="I7">
-        <v>0.0</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
@@ -3819,28 +3819,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="C8">
-        <v>63.05</v>
+        <v>64.07</v>
       </c>
       <c r="D8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8">
-        <v>66.67</v>
+        <v>46.67</v>
       </c>
       <c r="H8">
-        <v>66.67</v>
+        <v>83.33</v>
       </c>
       <c r="I8">
-        <v>2.56</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="9">
@@ -3848,28 +3848,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C9">
-        <v>62.95</v>
+        <v>63.09</v>
       </c>
       <c r="D9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G9">
-        <v>60.0</v>
+        <v>53.33</v>
       </c>
       <c r="H9">
-        <v>66.67</v>
+        <v>16.67</v>
       </c>
       <c r="I9">
-        <v>2.56</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="10">
@@ -3877,13 +3877,13 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>60.52</v>
+        <v>62.99</v>
       </c>
       <c r="D10">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -3892,13 +3892,13 @@
         <v>5</v>
       </c>
       <c r="G10">
-        <v>73.33</v>
+        <v>53.33</v>
       </c>
       <c r="H10">
         <v>50.0</v>
       </c>
       <c r="I10">
-        <v>12.82</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="11">
@@ -3906,28 +3906,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C11">
-        <v>59.84</v>
+        <v>62.26</v>
       </c>
       <c r="D11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G11">
-        <v>53.33</v>
+        <v>60.0</v>
       </c>
       <c r="H11">
-        <v>50.0</v>
+        <v>16.67</v>
       </c>
       <c r="I11">
-        <v>10.26</v>
+        <v>81.25</v>
       </c>
     </row>
     <row r="12">
@@ -3935,28 +3935,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C12">
-        <v>59.37</v>
+        <v>62.26</v>
       </c>
       <c r="D12">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G12">
-        <v>73.33</v>
+        <v>60.0</v>
       </c>
       <c r="H12">
-        <v>50.0</v>
+        <v>16.67</v>
       </c>
       <c r="I12">
-        <v>5.13</v>
+        <v>81.25</v>
       </c>
     </row>
     <row r="13">
@@ -3964,28 +3964,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C13">
-        <v>58.78</v>
+        <v>61.61</v>
       </c>
       <c r="D13">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G13">
-        <v>60.0</v>
+        <v>86.67</v>
       </c>
       <c r="H13">
         <v>50.0</v>
       </c>
       <c r="I13">
-        <v>2.56</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="14">
@@ -3993,28 +3993,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14">
-        <v>58.4</v>
+        <v>60.8</v>
       </c>
       <c r="D14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G14">
-        <v>60.0</v>
+        <v>53.33</v>
       </c>
       <c r="H14">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
       <c r="I14">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="15">
@@ -4022,28 +4022,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>57.98</v>
+        <v>60.43</v>
       </c>
       <c r="D15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G15">
-        <v>53.33</v>
+        <v>46.67</v>
       </c>
       <c r="H15">
-        <v>33.33</v>
+        <v>50.0</v>
       </c>
       <c r="I15">
-        <v>25.64</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="16">
@@ -4051,28 +4051,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C16">
-        <v>57.98</v>
+        <v>60.27</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G16">
-        <v>53.33</v>
+        <v>60.0</v>
       </c>
       <c r="H16">
-        <v>33.33</v>
+        <v>50.0</v>
       </c>
       <c r="I16">
-        <v>25.64</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="17">
@@ -4080,28 +4080,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="C17">
-        <v>56.72</v>
+        <v>60.27</v>
       </c>
       <c r="D17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E17">
         <v>3</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G17">
-        <v>46.67</v>
+        <v>60.0</v>
       </c>
       <c r="H17">
         <v>50.0</v>
       </c>
       <c r="I17">
-        <v>12.82</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="18">
@@ -4109,28 +4109,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C18">
-        <v>56.44</v>
+        <v>59.24</v>
       </c>
       <c r="D18">
         <v>8</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G18">
         <v>53.33</v>
       </c>
       <c r="H18">
-        <v>33.33</v>
+        <v>50.0</v>
       </c>
       <c r="I18">
-        <v>15.38</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="19">
@@ -4138,28 +4138,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C19">
-        <v>55.39</v>
+        <v>58.4</v>
       </c>
       <c r="D19">
         <v>9</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G19">
         <v>60.0</v>
       </c>
       <c r="H19">
-        <v>33.33</v>
+        <v>50.0</v>
       </c>
       <c r="I19">
-        <v>7.69</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="20">
@@ -4167,28 +4167,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C20">
-        <v>55.02</v>
+        <v>57.98</v>
       </c>
       <c r="D20">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G20">
-        <v>86.67</v>
+        <v>60.0</v>
       </c>
       <c r="H20">
         <v>33.33</v>
       </c>
       <c r="I20">
-        <v>2.56</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="21">
@@ -4196,28 +4196,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C21">
-        <v>54.97</v>
+        <v>57.15</v>
       </c>
       <c r="D21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G21">
-        <v>53.33</v>
+        <v>66.67</v>
       </c>
       <c r="H21">
-        <v>16.67</v>
+        <v>33.33</v>
       </c>
       <c r="I21">
-        <v>33.33</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="22">
@@ -4225,28 +4225,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C22">
-        <v>54.68</v>
+        <v>56.78</v>
       </c>
       <c r="D22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G22">
-        <v>60.0</v>
+        <v>46.67</v>
       </c>
       <c r="H22">
         <v>16.67</v>
       </c>
       <c r="I22">
-        <v>30.77</v>
+        <v>68.75</v>
       </c>
     </row>
     <row r="23">
@@ -4254,28 +4254,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C23">
-        <v>54.68</v>
+        <v>56.41</v>
       </c>
       <c r="D23">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>60.0</v>
+        <v>80.0</v>
       </c>
       <c r="H23">
-        <v>16.67</v>
+        <v>33.33</v>
       </c>
       <c r="I23">
-        <v>30.77</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="24">
@@ -4286,7 +4286,7 @@
         <v>24</v>
       </c>
       <c r="C24">
-        <v>52.19</v>
+        <v>55.89</v>
       </c>
       <c r="D24">
         <v>11</v>
@@ -4295,7 +4295,7 @@
         <v>1</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G24">
         <v>73.33</v>
@@ -4304,7 +4304,7 @@
         <v>16.67</v>
       </c>
       <c r="I24">
-        <v>12.82</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="25">
@@ -4312,28 +4312,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C25">
-        <v>51.67</v>
+        <v>55.07</v>
       </c>
       <c r="D25">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E25">
+        <v>4</v>
+      </c>
+      <c r="F25">
         <v>0</v>
       </c>
-      <c r="F25">
-        <v>15</v>
-      </c>
       <c r="G25">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="H25">
+        <v>66.67</v>
+      </c>
+      <c r="I25">
         <v>0.0</v>
-      </c>
-      <c r="I25">
-        <v>38.46</v>
       </c>
     </row>
     <row r="26">
@@ -4341,13 +4341,13 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C26">
-        <v>50.63</v>
+        <v>54.23</v>
       </c>
       <c r="D26">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E26">
         <v>2</v>
@@ -4356,7 +4356,7 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>46.67</v>
+        <v>60.0</v>
       </c>
       <c r="H26">
         <v>33.33</v>
@@ -4370,28 +4370,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C27">
-        <v>50.31</v>
+        <v>54.13</v>
       </c>
       <c r="D27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>46.67</v>
+        <v>53.33</v>
       </c>
       <c r="H27">
-        <v>16.67</v>
+        <v>33.33</v>
       </c>
       <c r="I27">
-        <v>25.64</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="28">
@@ -4399,28 +4399,28 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="C28">
-        <v>49.5</v>
+        <v>51.57</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F28">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="G28">
+        <v>46.67</v>
+      </c>
+      <c r="H28">
         <v>33.33</v>
       </c>
-      <c r="H28">
-        <v>0.0</v>
-      </c>
       <c r="I28">
-        <v>100.0</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="29">
@@ -4428,10 +4428,10 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>49.31</v>
+        <v>50.75</v>
       </c>
       <c r="D29">
         <v>5</v>
@@ -4440,7 +4440,7 @@
         <v>3</v>
       </c>
       <c r="F29">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G29">
         <v>33.33</v>
@@ -4449,7 +4449,7 @@
         <v>50.0</v>
       </c>
       <c r="I29">
-        <v>15.38</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="30">
@@ -4457,28 +4457,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C30">
-        <v>48.15</v>
+        <v>47.1</v>
       </c>
       <c r="D30">
         <v>5</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G30">
         <v>33.33</v>
       </c>
       <c r="H30">
-        <v>50.0</v>
+        <v>16.67</v>
       </c>
       <c r="I30">
-        <v>7.69</v>
+        <v>56.25</v>
       </c>
     </row>
     <row r="31">
@@ -4489,7 +4489,7 @@
         <v>30</v>
       </c>
       <c r="C31">
-        <v>43.98</v>
+        <v>46.58</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -4498,7 +4498,7 @@
         <v>2</v>
       </c>
       <c r="F31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31">
         <v>33.33</v>
@@ -4507,7 +4507,7 @@
         <v>33.33</v>
       </c>
       <c r="I31">
-        <v>7.69</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="32">
@@ -4515,28 +4515,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C32">
-        <v>42.83</v>
+        <v>44.14</v>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G32">
-        <v>33.33</v>
+        <v>26.67</v>
       </c>
       <c r="H32">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="I32">
-        <v>0.0</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="33">
@@ -4544,28 +4544,28 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C33">
-        <v>41.74</v>
+        <v>43.77</v>
       </c>
       <c r="D33">
         <v>5</v>
       </c>
       <c r="E33">
+        <v>2</v>
+      </c>
+      <c r="F33">
         <v>1</v>
-      </c>
-      <c r="F33">
-        <v>8</v>
       </c>
       <c r="G33">
         <v>33.33</v>
       </c>
       <c r="H33">
-        <v>16.67</v>
+        <v>33.33</v>
       </c>
       <c r="I33">
-        <v>20.51</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="34">
@@ -4573,28 +4573,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C34">
-        <v>39.32</v>
+        <v>42.57</v>
       </c>
       <c r="D34">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34">
-        <v>26.67</v>
+        <v>40.0</v>
       </c>
       <c r="H34">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="I34">
-        <v>2.56</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="35">
@@ -4602,28 +4602,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C35">
-        <v>38.67</v>
+        <v>42.12</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G35">
-        <v>33.33</v>
+        <v>20.0</v>
       </c>
       <c r="H35">
         <v>16.67</v>
       </c>
       <c r="I35">
-        <v>0.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="36">
@@ -4631,28 +4631,28 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C36">
-        <v>38.23</v>
+        <v>40.81</v>
       </c>
       <c r="D36">
         <v>4</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G36">
         <v>26.67</v>
       </c>
       <c r="H36">
-        <v>16.67</v>
+        <v>33.33</v>
       </c>
       <c r="I36">
-        <v>23.08</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="37">
@@ -4660,28 +4660,28 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C37">
-        <v>36.31</v>
+        <v>39.6</v>
       </c>
       <c r="D37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E37">
         <v>1</v>
       </c>
       <c r="F37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G37">
-        <v>26.67</v>
+        <v>33.33</v>
       </c>
       <c r="H37">
         <v>16.67</v>
       </c>
       <c r="I37">
-        <v>10.26</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="38">
@@ -4689,28 +4689,28 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C38">
-        <v>35.1</v>
+        <v>39.46</v>
       </c>
       <c r="D38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
       <c r="F38">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G38">
-        <v>20.0</v>
+        <v>26.67</v>
       </c>
       <c r="H38">
         <v>16.67</v>
       </c>
       <c r="I38">
-        <v>28.21</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="39">
@@ -4721,25 +4721,25 @@
         <v>37</v>
       </c>
       <c r="C39">
-        <v>32.41</v>
+        <v>38.93</v>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>20.0</v>
+        <v>26.67</v>
       </c>
       <c r="H39">
-        <v>16.67</v>
+        <v>33.33</v>
       </c>
       <c r="I39">
-        <v>10.26</v>
+        <v>0.0</v>
       </c>
     </row>
   </sheetData>
@@ -4798,92 +4798,92 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <v>14</v>
+      </c>
+      <c r="F3">
+        <v>16</v>
+      </c>
+      <c r="G3">
+        <v>29</v>
+      </c>
+      <c r="H3">
+        <v>36</v>
+      </c>
+      <c r="I3">
         <v>8</v>
-      </c>
-      <c r="D3">
-        <v>17</v>
-      </c>
-      <c r="E3">
-        <v>18</v>
-      </c>
-      <c r="F3">
-        <v>29</v>
-      </c>
-      <c r="G3">
-        <v>33</v>
-      </c>
-      <c r="H3">
-        <v>38</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H4">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -4891,108 +4891,108 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H5">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F6">
         <v>19</v>
       </c>
       <c r="G6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H6">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G7">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -5001,230 +5001,230 @@
         <v>9</v>
       </c>
       <c r="F8">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H8">
         <v>36</v>
       </c>
       <c r="I8">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E9">
         <v>9</v>
       </c>
       <c r="F9">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G9">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H9">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>9</v>
+      </c>
+      <c r="F10">
         <v>11</v>
       </c>
-      <c r="E10">
-        <v>18</v>
-      </c>
-      <c r="F10">
-        <v>19</v>
-      </c>
       <c r="G10">
+        <v>29</v>
+      </c>
+      <c r="H10">
         <v>35</v>
       </c>
-      <c r="H10">
-        <v>38</v>
-      </c>
       <c r="I10">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G11">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H11">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="I11">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C12">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E12">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F12">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G12">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H12">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I12">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D13">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E13">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F13">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G13">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H13">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I13">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>7</v>
+      </c>
+      <c r="E14">
+        <v>8</v>
+      </c>
+      <c r="F14">
+        <v>20</v>
+      </c>
+      <c r="G14">
+        <v>26</v>
+      </c>
+      <c r="H14">
+        <v>33</v>
+      </c>
+      <c r="I14">
         <v>4</v>
-      </c>
-      <c r="D14">
-        <v>15</v>
-      </c>
-      <c r="E14">
-        <v>22</v>
-      </c>
-      <c r="F14">
-        <v>26</v>
-      </c>
-      <c r="G14">
-        <v>34</v>
-      </c>
-      <c r="H14">
-        <v>36</v>
-      </c>
-      <c r="I14">
-        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C15">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E15">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F15">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G15">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H15">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I15">
         <v>7</v>
@@ -5232,30 +5232,30 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C16">
+        <v>8</v>
+      </c>
+      <c r="D16">
+        <v>14</v>
+      </c>
+      <c r="E16">
+        <v>17</v>
+      </c>
+      <c r="F16">
         <v>19</v>
       </c>
-      <c r="D16">
-        <v>22</v>
-      </c>
-      <c r="E16">
-        <v>28</v>
-      </c>
-      <c r="F16">
-        <v>31</v>
-      </c>
       <c r="G16">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H16">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I16">
         <v>7</v>
@@ -5263,30 +5263,30 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C17">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D17">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E17">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F17">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G17">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H17">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I17">
         <v>7</v>
@@ -5294,24 +5294,24 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D18">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E18">
         <v>13</v>
       </c>
       <c r="F18">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G18">
         <v>29</v>
@@ -5320,97 +5320,97 @@
         <v>31</v>
       </c>
       <c r="I18">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C19">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D19">
+        <v>12</v>
+      </c>
+      <c r="E19">
+        <v>13</v>
+      </c>
+      <c r="F19">
         <v>23</v>
       </c>
-      <c r="E19">
-        <v>25</v>
-      </c>
-      <c r="F19">
+      <c r="G19">
         <v>29</v>
       </c>
-      <c r="G19">
-        <v>34</v>
-      </c>
       <c r="H19">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I19">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C20">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D20">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E20">
+        <v>25</v>
+      </c>
+      <c r="F20">
         <v>29</v>
       </c>
-      <c r="F20">
-        <v>32</v>
-      </c>
       <c r="G20">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H20">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I20">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C21">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D21">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E21">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F21">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G21">
         <v>35</v>
       </c>
       <c r="H21">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I21">
         <v>6</v>
@@ -5418,402 +5418,402 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D22">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E22">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F22">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G22">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H22">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D23">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E23">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F23">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G23">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H23">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I23">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C24">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D24">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E24">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F24">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G24">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H24">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I24">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C25">
+        <v>5</v>
+      </c>
+      <c r="D25">
         <v>6</v>
       </c>
-      <c r="D25">
-        <v>10</v>
-      </c>
       <c r="E25">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F25">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G25">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H25">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C26">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D26">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E26">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F26">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G26">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H26">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I26">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D27">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E27">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F27">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G27">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H27">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I27">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28">
+        <v>8</v>
+      </c>
+      <c r="E28">
+        <v>9</v>
+      </c>
+      <c r="F28">
+        <v>15</v>
+      </c>
+      <c r="G28">
+        <v>18</v>
+      </c>
+      <c r="H28">
+        <v>23</v>
+      </c>
+      <c r="I28">
         <v>4</v>
-      </c>
-      <c r="D28">
-        <v>17</v>
-      </c>
-      <c r="E28">
-        <v>19</v>
-      </c>
-      <c r="F28">
-        <v>25</v>
-      </c>
-      <c r="G28">
-        <v>28</v>
-      </c>
-      <c r="H28">
-        <v>29</v>
-      </c>
-      <c r="I28">
-        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C29">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D29">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E29">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F29">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G29">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H29">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I29">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D30">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E30">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F30">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G30">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H30">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I30">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C31">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D31">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E31">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F31">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G31">
         <v>28</v>
       </c>
       <c r="H31">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I31">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D32">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E32">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F32">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G32">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H32">
         <v>35</v>
       </c>
       <c r="I32">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E33">
+        <v>9</v>
+      </c>
+      <c r="F33">
+        <v>15</v>
+      </c>
+      <c r="G33">
         <v>24</v>
       </c>
-      <c r="F33">
-        <v>31</v>
-      </c>
-      <c r="G33">
-        <v>34</v>
-      </c>
       <c r="H33">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I33">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C34">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D34">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E34">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F34">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G34">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H34">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I34">
         <v>3</v>
@@ -5821,529 +5821,529 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C35">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D35">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E35">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F35">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G35">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H35">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I35">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C36">
         <v>6</v>
       </c>
       <c r="D36">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E36">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F36">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G36">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H36">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I36">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C37">
         <v>6</v>
       </c>
       <c r="D37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E37">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F37">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G37">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H37">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I37">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C38">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D38">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E38">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F38">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G38">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H38">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I38">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C39">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D39">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E39">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F39">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G39">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H39">
         <v>38</v>
       </c>
       <c r="I39">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C40">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D40">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E40">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F40">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G40">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H40">
         <v>38</v>
       </c>
       <c r="I40">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E41">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F41">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G41">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H41">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I41">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C42">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D42">
+        <v>4</v>
+      </c>
+      <c r="E42">
+        <v>13</v>
+      </c>
+      <c r="F42">
+        <v>19</v>
+      </c>
+      <c r="G42">
+        <v>27</v>
+      </c>
+      <c r="H42">
+        <v>30</v>
+      </c>
+      <c r="I42">
         <v>8</v>
-      </c>
-      <c r="E42">
-        <v>27</v>
-      </c>
-      <c r="F42">
-        <v>33</v>
-      </c>
-      <c r="G42">
-        <v>35</v>
-      </c>
-      <c r="H42">
-        <v>38</v>
-      </c>
-      <c r="I42">
-        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C43">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D43">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E43">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F43">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G43">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H43">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I43">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C44">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D44">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E44">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F44">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G44">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H44">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I44">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D45">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E45">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F45">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G45">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H45">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I45">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000030</v>
+        <v>115000031</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D46">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E46">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F46">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G46">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H46">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="I46">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000029</v>
+        <v>115000030</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D47">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E47">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F47">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G47">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H47">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I47">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000028</v>
+        <v>115000029</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D48">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E48">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F48">
         <v>27</v>
       </c>
       <c r="G48">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H48">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I48">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000027</v>
+        <v>115000028</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C49">
         <v>5</v>
       </c>
       <c r="D49">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E49">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F49">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G49">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H49">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I49">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000026</v>
+        <v>115000027</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C50">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D50">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E50">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F50">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G50">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H50">
         <v>34</v>
       </c>
       <c r="I50">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000025</v>
+        <v>115000026</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C51">
+        <v>2</v>
+      </c>
+      <c r="D51">
         <v>13</v>
       </c>
-      <c r="D51">
-        <v>14</v>
-      </c>
       <c r="E51">
+        <v>21</v>
+      </c>
+      <c r="F51">
         <v>22</v>
       </c>
-      <c r="F51">
-        <v>28</v>
-      </c>
       <c r="G51">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H51">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I51">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-09-15 第 115000088 期；威力彩 2026-09-17 第 115000075 期</t>
+          <t>大樂透 2026-09-18 第 115000089 期；威力彩 2026-09-17 第 115000075 期</t>
         </is>
       </c>
     </row>
@@ -47,7 +47,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>115000088</v>
+        <v>115000089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -56,7 +56,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -78,7 +78,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4, 12, 16, 25, 26, 29</t>
+          <t>12, 16, 18, 25, 26, 29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -96,7 +96,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.262 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.239 碼/期</t>
         </is>
       </c>
     </row>
@@ -214,7 +214,7 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>0.952</v>
+        <v>0.929</v>
       </c>
       <c r="D2">
         <v>28.6</v>
@@ -236,7 +236,7 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>0.929</v>
+        <v>0.905</v>
       </c>
       <c r="D3">
         <v>26.2</v>
@@ -324,10 +324,10 @@
         <v>42</v>
       </c>
       <c r="C7">
-        <v>0.643</v>
+        <v>0.69</v>
       </c>
       <c r="D7">
-        <v>11.9</v>
+        <v>14.3</v>
       </c>
       <c r="E7">
         <v>0.0</v>
@@ -395,10 +395,10 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C2">
-        <v>72.14</v>
+        <v>71.35</v>
       </c>
       <c r="D2">
         <v>12</v>
@@ -407,7 +407,7 @@
         <v>5</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>100.0</v>
@@ -416,7 +416,7 @@
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>10.26</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="3">
@@ -424,28 +424,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C3">
-        <v>70.98</v>
+        <v>67.43</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
         <v>5</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
       <c r="G3">
-        <v>100.0</v>
+        <v>91.67</v>
       </c>
       <c r="H3">
-        <v>100.0</v>
+        <v>80.0</v>
       </c>
       <c r="I3">
-        <v>2.56</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="4">
@@ -453,28 +453,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C4">
-        <v>67.01</v>
+        <v>65.45</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E4">
         <v>4</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>50.0</v>
+        <v>75.0</v>
       </c>
       <c r="H4">
         <v>80.0</v>
       </c>
       <c r="I4">
-        <v>15.38</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="5">
@@ -482,28 +482,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C5">
-        <v>65.83</v>
+        <v>63.87</v>
       </c>
       <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
         <v>9</v>
       </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
       <c r="G5">
-        <v>75.0</v>
+        <v>83.33</v>
       </c>
       <c r="H5">
-        <v>80.0</v>
+        <v>60.0</v>
       </c>
       <c r="I5">
-        <v>2.56</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="6">
@@ -511,28 +511,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C6">
-        <v>63.58</v>
+        <v>62.6</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>83.33</v>
+        <v>58.33</v>
       </c>
       <c r="H6">
         <v>60.0</v>
       </c>
       <c r="I6">
-        <v>20.51</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="7">
@@ -540,28 +540,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C7">
-        <v>63.09</v>
+        <v>62.43</v>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G7">
-        <v>66.67</v>
+        <v>91.67</v>
       </c>
       <c r="H7">
         <v>60.0</v>
       </c>
       <c r="I7">
-        <v>17.95</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="8">
@@ -569,28 +569,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8">
-        <v>62.32</v>
+        <v>62.33</v>
       </c>
       <c r="D8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G8">
-        <v>66.67</v>
+        <v>50.0</v>
       </c>
       <c r="H8">
         <v>60.0</v>
       </c>
       <c r="I8">
-        <v>12.82</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="9">
@@ -598,28 +598,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C9">
-        <v>62.14</v>
+        <v>61.2</v>
       </c>
       <c r="D9">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>100.0</v>
+        <v>75.0</v>
       </c>
       <c r="H9">
         <v>60.0</v>
       </c>
       <c r="I9">
-        <v>10.26</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="10">
@@ -627,10 +627,10 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C10">
-        <v>61.17</v>
+        <v>61.15</v>
       </c>
       <c r="D10">
         <v>8</v>
@@ -648,7 +648,7 @@
         <v>60.0</v>
       </c>
       <c r="I10">
-        <v>5.13</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="11">
@@ -656,28 +656,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C11">
-        <v>60.79</v>
+        <v>60.45</v>
       </c>
       <c r="D11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11">
-        <v>66.67</v>
+        <v>50.0</v>
       </c>
       <c r="H11">
         <v>60.0</v>
       </c>
       <c r="I11">
-        <v>2.56</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="12">
@@ -685,10 +685,10 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="C12">
-        <v>60.73</v>
+        <v>60.35</v>
       </c>
       <c r="D12">
         <v>7</v>
@@ -697,7 +697,7 @@
         <v>3</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12">
         <v>58.33</v>
@@ -706,7 +706,7 @@
         <v>60.0</v>
       </c>
       <c r="I12">
-        <v>2.56</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="13">
@@ -714,7 +714,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="C13">
         <v>60.08</v>
@@ -735,7 +735,7 @@
         <v>60.0</v>
       </c>
       <c r="I13">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14">
@@ -743,7 +743,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C14">
         <v>59.7</v>
@@ -775,7 +775,7 @@
         <v>34</v>
       </c>
       <c r="C15">
-        <v>58.16</v>
+        <v>58.45</v>
       </c>
       <c r="D15">
         <v>6</v>
@@ -784,7 +784,7 @@
         <v>2</v>
       </c>
       <c r="F15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>50.0</v>
@@ -793,7 +793,7 @@
         <v>40.0</v>
       </c>
       <c r="I15">
-        <v>23.08</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="16">
@@ -801,28 +801,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C16">
-        <v>57.39</v>
+        <v>58.35</v>
       </c>
       <c r="D16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16">
         <v>2</v>
       </c>
       <c r="F16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G16">
-        <v>50.0</v>
+        <v>58.33</v>
       </c>
       <c r="H16">
         <v>40.0</v>
       </c>
       <c r="I16">
-        <v>17.95</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="17">
@@ -830,28 +830,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C17">
-        <v>57.32</v>
+        <v>57.6</v>
       </c>
       <c r="D17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G17">
-        <v>66.67</v>
+        <v>58.33</v>
       </c>
       <c r="H17">
         <v>40.0</v>
       </c>
       <c r="I17">
-        <v>12.82</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="18">
@@ -859,10 +859,10 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C18">
-        <v>57.27</v>
+        <v>57.6</v>
       </c>
       <c r="D18">
         <v>7</v>
@@ -871,7 +871,7 @@
         <v>2</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18">
         <v>58.33</v>
@@ -880,7 +880,7 @@
         <v>40.0</v>
       </c>
       <c r="I18">
-        <v>12.82</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="19">
@@ -891,7 +891,7 @@
         <v>16</v>
       </c>
       <c r="C19">
-        <v>57.04</v>
+        <v>57.37</v>
       </c>
       <c r="D19">
         <v>10</v>
@@ -900,7 +900,7 @@
         <v>2</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G19">
         <v>83.33</v>
@@ -909,7 +909,7 @@
         <v>40.0</v>
       </c>
       <c r="I19">
-        <v>10.26</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="20">
@@ -920,7 +920,7 @@
         <v>47</v>
       </c>
       <c r="C20">
-        <v>56.12</v>
+        <v>56.47</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -929,7 +929,7 @@
         <v>2</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20">
         <v>58.33</v>
@@ -938,7 +938,7 @@
         <v>40.0</v>
       </c>
       <c r="I20">
-        <v>5.13</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="21">
@@ -946,10 +946,10 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C21">
-        <v>55.73</v>
+        <v>56.1</v>
       </c>
       <c r="D21">
         <v>7</v>
@@ -958,7 +958,7 @@
         <v>2</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21">
         <v>58.33</v>
@@ -967,7 +967,7 @@
         <v>40.0</v>
       </c>
       <c r="I21">
-        <v>2.56</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="22">
@@ -975,13 +975,13 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C22">
-        <v>55.47</v>
+        <v>56.1</v>
       </c>
       <c r="D22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E22">
         <v>2</v>
@@ -990,13 +990,13 @@
         <v>2</v>
       </c>
       <c r="G22">
-        <v>50.0</v>
+        <v>58.33</v>
       </c>
       <c r="H22">
         <v>40.0</v>
       </c>
       <c r="I22">
-        <v>5.13</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="23">
@@ -1004,28 +1004,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="C23">
-        <v>55.45</v>
+        <v>55.83</v>
       </c>
       <c r="D23">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E23">
         <v>2</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G23">
-        <v>75.0</v>
+        <v>50.0</v>
       </c>
       <c r="H23">
         <v>40.0</v>
       </c>
       <c r="I23">
-        <v>0.0</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="24">
@@ -1033,28 +1033,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C24">
-        <v>55.07</v>
+        <v>55.82</v>
       </c>
       <c r="D24">
         <v>9</v>
       </c>
       <c r="E24">
+        <v>2</v>
+      </c>
+      <c r="F24">
         <v>1</v>
-      </c>
-      <c r="F24">
-        <v>12</v>
       </c>
       <c r="G24">
         <v>75.0</v>
       </c>
       <c r="H24">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I24">
-        <v>30.77</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="25">
@@ -1062,28 +1062,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>54.7</v>
+        <v>55.35</v>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>50.0</v>
+        <v>58.33</v>
       </c>
       <c r="H25">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I25">
-        <v>33.33</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -1091,28 +1091,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C26">
-        <v>52.78</v>
+        <v>55.28</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G26">
-        <v>50.0</v>
+        <v>66.67</v>
       </c>
       <c r="H26">
         <v>20.0</v>
       </c>
       <c r="I26">
-        <v>20.51</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="27">
@@ -1120,28 +1120,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C27">
-        <v>52.06</v>
+        <v>54.95</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G27">
-        <v>41.67</v>
+        <v>50.0</v>
       </c>
       <c r="H27">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I27">
-        <v>15.38</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="28">
@@ -1152,7 +1152,7 @@
         <v>40</v>
       </c>
       <c r="C28">
-        <v>52.01</v>
+        <v>52.33</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -1161,7 +1161,7 @@
         <v>1</v>
       </c>
       <c r="F28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G28">
         <v>50.0</v>
@@ -1170,7 +1170,7 @@
         <v>20.0</v>
       </c>
       <c r="I28">
-        <v>15.38</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="29">
@@ -1181,7 +1181,7 @@
         <v>10</v>
       </c>
       <c r="C29">
-        <v>51.89</v>
+        <v>52.22</v>
       </c>
       <c r="D29">
         <v>7</v>
@@ -1190,7 +1190,7 @@
         <v>1</v>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G29">
         <v>58.33</v>
@@ -1199,7 +1199,7 @@
         <v>20.0</v>
       </c>
       <c r="I29">
-        <v>10.26</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="30">
@@ -1207,28 +1207,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="C30">
-        <v>51.24</v>
+        <v>51.2</v>
       </c>
       <c r="D30">
         <v>6</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G30">
         <v>50.0</v>
       </c>
       <c r="H30">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I30">
-        <v>43.59</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="31">
@@ -1236,10 +1236,10 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C31">
-        <v>50.85</v>
+        <v>50.83</v>
       </c>
       <c r="D31">
         <v>6</v>
@@ -1257,7 +1257,7 @@
         <v>20.0</v>
       </c>
       <c r="I31">
-        <v>7.69</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="32">
@@ -1265,28 +1265,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="C32">
-        <v>50.47</v>
+        <v>50.35</v>
       </c>
       <c r="D32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E32">
         <v>1</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>50.0</v>
+        <v>58.33</v>
       </c>
       <c r="H32">
         <v>20.0</v>
       </c>
       <c r="I32">
-        <v>5.13</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="33">
@@ -1297,7 +1297,7 @@
         <v>2</v>
       </c>
       <c r="C33">
-        <v>49.75</v>
+        <v>50.13</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -1306,7 +1306,7 @@
         <v>2</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33">
         <v>41.67</v>
@@ -1315,7 +1315,7 @@
         <v>40.0</v>
       </c>
       <c r="I33">
-        <v>0.0</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="34">
@@ -1323,28 +1323,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C34">
-        <v>49.75</v>
+        <v>50.08</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34">
-        <v>41.67</v>
+        <v>50.0</v>
       </c>
       <c r="H34">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I34">
-        <v>0.0</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="35">
@@ -1352,28 +1352,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C35">
-        <v>49.7</v>
+        <v>48.55</v>
       </c>
       <c r="D35">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G35">
-        <v>50.0</v>
+        <v>33.33</v>
       </c>
       <c r="H35">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I35">
-        <v>0.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="36">
@@ -1381,28 +1381,28 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C36">
-        <v>48.26</v>
+        <v>47.38</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G36">
-        <v>33.33</v>
+        <v>41.67</v>
       </c>
       <c r="H36">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I36">
-        <v>23.08</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="37">
@@ -1413,7 +1413,7 @@
         <v>9</v>
       </c>
       <c r="C37">
-        <v>46.72</v>
+        <v>47.05</v>
       </c>
       <c r="D37">
         <v>4</v>
@@ -1422,7 +1422,7 @@
         <v>2</v>
       </c>
       <c r="F37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G37">
         <v>33.33</v>
@@ -1431,7 +1431,7 @@
         <v>40.0</v>
       </c>
       <c r="I37">
-        <v>12.82</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="38">
@@ -1442,7 +1442,7 @@
         <v>44</v>
       </c>
       <c r="C38">
-        <v>46.72</v>
+        <v>47.05</v>
       </c>
       <c r="D38">
         <v>4</v>
@@ -1451,7 +1451,7 @@
         <v>2</v>
       </c>
       <c r="F38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G38">
         <v>33.33</v>
@@ -1460,7 +1460,7 @@
         <v>40.0</v>
       </c>
       <c r="I38">
-        <v>12.82</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="39">
@@ -1471,7 +1471,7 @@
         <v>13</v>
       </c>
       <c r="C39">
-        <v>45.9</v>
+        <v>46.25</v>
       </c>
       <c r="D39">
         <v>5</v>
@@ -1480,7 +1480,7 @@
         <v>1</v>
       </c>
       <c r="F39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G39">
         <v>41.67</v>
@@ -1489,7 +1489,7 @@
         <v>20.0</v>
       </c>
       <c r="I39">
-        <v>7.69</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="40">
@@ -1500,7 +1500,7 @@
         <v>17</v>
       </c>
       <c r="C40">
-        <v>45.9</v>
+        <v>46.25</v>
       </c>
       <c r="D40">
         <v>5</v>
@@ -1509,7 +1509,7 @@
         <v>1</v>
       </c>
       <c r="F40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G40">
         <v>41.67</v>
@@ -1518,7 +1518,7 @@
         <v>20.0</v>
       </c>
       <c r="I40">
-        <v>7.69</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="41">
@@ -1538,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="F41">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G41">
         <v>25.0</v>
@@ -1558,7 +1558,7 @@
         <v>46</v>
       </c>
       <c r="C42">
-        <v>43.64</v>
+        <v>43.92</v>
       </c>
       <c r="D42">
         <v>4</v>
@@ -1567,7 +1567,7 @@
         <v>1</v>
       </c>
       <c r="F42">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G42">
         <v>33.33</v>
@@ -1576,7 +1576,7 @@
         <v>20.0</v>
       </c>
       <c r="I42">
-        <v>25.64</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="43">
@@ -1587,7 +1587,7 @@
         <v>45</v>
       </c>
       <c r="C43">
-        <v>41.72</v>
+        <v>41.92</v>
       </c>
       <c r="D43">
         <v>4</v>
@@ -1596,7 +1596,7 @@
         <v>0</v>
       </c>
       <c r="F43">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G43">
         <v>33.33</v>
@@ -1605,7 +1605,7 @@
         <v>0.0</v>
       </c>
       <c r="I43">
-        <v>46.15</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="44">
@@ -1616,7 +1616,7 @@
         <v>22</v>
       </c>
       <c r="C44">
-        <v>39.8</v>
+        <v>40.17</v>
       </c>
       <c r="D44">
         <v>4</v>
@@ -1625,7 +1625,7 @@
         <v>1</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44">
         <v>33.33</v>
@@ -1634,7 +1634,7 @@
         <v>20.0</v>
       </c>
       <c r="I44">
-        <v>0.0</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="45">
@@ -1645,7 +1645,7 @@
         <v>30</v>
       </c>
       <c r="C45">
-        <v>39.47</v>
+        <v>39.73</v>
       </c>
       <c r="D45">
         <v>3</v>
@@ -1654,7 +1654,7 @@
         <v>1</v>
       </c>
       <c r="F45">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G45">
         <v>25.0</v>
@@ -1663,7 +1663,7 @@
         <v>20.0</v>
       </c>
       <c r="I45">
-        <v>30.77</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="46">
@@ -1674,7 +1674,7 @@
         <v>5</v>
       </c>
       <c r="C46">
-        <v>38.31</v>
+        <v>38.6</v>
       </c>
       <c r="D46">
         <v>3</v>
@@ -1683,7 +1683,7 @@
         <v>1</v>
       </c>
       <c r="F46">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G46">
         <v>25.0</v>
@@ -1692,7 +1692,7 @@
         <v>20.0</v>
       </c>
       <c r="I46">
-        <v>23.08</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="47">
@@ -1703,7 +1703,7 @@
         <v>41</v>
       </c>
       <c r="C47">
-        <v>34.13</v>
+        <v>34.4</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -1712,7 +1712,7 @@
         <v>1</v>
       </c>
       <c r="F47">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G47">
         <v>16.67</v>
@@ -1721,7 +1721,7 @@
         <v>20.0</v>
       </c>
       <c r="I47">
-        <v>28.21</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="48">
@@ -1732,7 +1732,7 @@
         <v>38</v>
       </c>
       <c r="C48">
-        <v>33.03</v>
+        <v>33.07</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -1741,7 +1741,7 @@
         <v>0</v>
       </c>
       <c r="F48">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G48">
         <v>8.33</v>
@@ -1750,7 +1750,7 @@
         <v>0.0</v>
       </c>
       <c r="I48">
-        <v>87.18</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="49">
@@ -1761,7 +1761,7 @@
         <v>42</v>
       </c>
       <c r="C49">
-        <v>32.59</v>
+        <v>32.78</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -1770,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="F49">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G49">
         <v>16.67</v>
@@ -1779,7 +1779,7 @@
         <v>0.0</v>
       </c>
       <c r="I49">
-        <v>51.28</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="50">
@@ -1790,25 +1790,25 @@
         <v>31</v>
       </c>
       <c r="C50">
-        <v>31.87</v>
+        <v>29.9</v>
       </c>
       <c r="D50">
+        <v>2</v>
+      </c>
+      <c r="E50">
         <v>1</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>0</v>
       </c>
-      <c r="F50">
-        <v>31</v>
-      </c>
       <c r="G50">
-        <v>8.33</v>
+        <v>16.67</v>
       </c>
       <c r="H50">
+        <v>20.0</v>
+      </c>
+      <c r="I50">
         <v>0.0</v>
-      </c>
-      <c r="I50">
-        <v>79.49</v>
       </c>
     </row>
   </sheetData>
@@ -1867,638 +1867,638 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000088</v>
+        <v>115000089</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F2">
         <v>21</v>
       </c>
       <c r="G2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H2">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000087</v>
+        <v>115000088</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H3">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I3">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000086</v>
+        <v>115000087</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D4">
         <v>15</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F4">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H4">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I4">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000085</v>
+        <v>115000086</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
       <c r="D5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G5">
+        <v>47</v>
+      </c>
+      <c r="H5">
+        <v>49</v>
+      </c>
+      <c r="I5">
         <v>27</v>
-      </c>
-      <c r="H5">
-        <v>37</v>
-      </c>
-      <c r="I5">
-        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000084</v>
+        <v>115000085</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E6">
+        <v>17</v>
+      </c>
+      <c r="F6">
+        <v>18</v>
+      </c>
+      <c r="G6">
+        <v>27</v>
+      </c>
+      <c r="H6">
+        <v>37</v>
+      </c>
+      <c r="I6">
         <v>19</v>
-      </c>
-      <c r="F6">
-        <v>26</v>
-      </c>
-      <c r="G6">
-        <v>29</v>
-      </c>
-      <c r="H6">
-        <v>48</v>
-      </c>
-      <c r="I6">
-        <v>30</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000083</v>
+        <v>115000084</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F7">
         <v>26</v>
       </c>
       <c r="G7">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H7">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C8">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D8">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E8">
+        <v>23</v>
+      </c>
+      <c r="F8">
         <v>26</v>
       </c>
-      <c r="F8">
-        <v>32</v>
-      </c>
       <c r="G8">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H8">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I8">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D9">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E9">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F9">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G9">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H9">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I9">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D10">
         <v>14</v>
       </c>
       <c r="E10">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F10">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G10">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H10">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E11">
         <v>25</v>
       </c>
       <c r="F11">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G11">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H11">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I11">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C12">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <v>12</v>
       </c>
       <c r="E12">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F12">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G12">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H12">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="I12">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D13">
         <v>12</v>
       </c>
       <c r="E13">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F13">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G13">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H13">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I13">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F14">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G14">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H14">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I14">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C15">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D15">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E15">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F15">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G15">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H15">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I15">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C16">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D16">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E16">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F16">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G16">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H16">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I16">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C17">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D17">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E17">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F17">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G17">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H17">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I17">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E18">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F18">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G18">
         <v>35</v>
       </c>
       <c r="H18">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I18">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E19">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F19">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G19">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H19">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I19">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C20">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E20">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F20">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G20">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H20">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I20">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C21">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D21">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E21">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F21">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G21">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H21">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I21">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C22">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D22">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E22">
         <v>15</v>
@@ -2507,345 +2507,345 @@
         <v>18</v>
       </c>
       <c r="G22">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H22">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I22">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C23">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D23">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E23">
+        <v>15</v>
+      </c>
+      <c r="F23">
+        <v>18</v>
+      </c>
+      <c r="G23">
         <v>19</v>
       </c>
-      <c r="F23">
-        <v>23</v>
-      </c>
-      <c r="G23">
-        <v>39</v>
-      </c>
       <c r="H23">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I23">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D24">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E24">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F24">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G24">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H24">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I24">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C25">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D25">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E25">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F25">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G25">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H25">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C26">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D26">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E26">
+        <v>23</v>
+      </c>
+      <c r="F26">
+        <v>24</v>
+      </c>
+      <c r="G26">
         <v>29</v>
       </c>
-      <c r="F26">
-        <v>33</v>
-      </c>
-      <c r="G26">
-        <v>34</v>
-      </c>
       <c r="H26">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I26">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D27">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E27">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F27">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G27">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H27">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I27">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E28">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F28">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G28">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H28">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I28">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E29">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F29">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G29">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H29">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I29">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C30">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D30">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E30">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F30">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G30">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H30">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I30">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C31">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D31">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E31">
         <v>25</v>
       </c>
       <c r="F31">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G31">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H31">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I31">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C32">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D32">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E32">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F32">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G32">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H32">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I32">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C33">
+        <v>8</v>
+      </c>
+      <c r="D33">
+        <v>9</v>
+      </c>
+      <c r="E33">
+        <v>16</v>
+      </c>
+      <c r="F33">
         <v>20</v>
-      </c>
-      <c r="D33">
-        <v>26</v>
-      </c>
-      <c r="E33">
-        <v>29</v>
-      </c>
-      <c r="F33">
-        <v>31</v>
       </c>
       <c r="G33">
         <v>37</v>
@@ -2854,565 +2854,565 @@
         <v>49</v>
       </c>
       <c r="I33">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C34">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D34">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E34">
         <v>29</v>
       </c>
       <c r="F34">
+        <v>31</v>
+      </c>
+      <c r="G34">
         <v>37</v>
       </c>
-      <c r="G34">
-        <v>47</v>
-      </c>
       <c r="H34">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I34">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C35">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D35">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E35">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F35">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G35">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="H35">
         <v>48</v>
       </c>
       <c r="I35">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D36">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E36">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F36">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G36">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H36">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I36">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C37">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D37">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E37">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F37">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G37">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H37">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I37">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C38">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D38">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E38">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F38">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G38">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H38">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I38">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D39">
+        <v>12</v>
+      </c>
+      <c r="E39">
         <v>18</v>
       </c>
-      <c r="E39">
-        <v>25</v>
-      </c>
       <c r="F39">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G39">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H39">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I39">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C40">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D40">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E40">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F40">
         <v>28</v>
       </c>
       <c r="G40">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H40">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I40">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D41">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E41">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F41">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G41">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H41">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I41">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D42">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E42">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F42">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G42">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H42">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I42">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C43">
+        <v>6</v>
+      </c>
+      <c r="D43">
+        <v>10</v>
+      </c>
+      <c r="E43">
+        <v>14</v>
+      </c>
+      <c r="F43">
+        <v>25</v>
+      </c>
+      <c r="G43">
+        <v>26</v>
+      </c>
+      <c r="H43">
+        <v>32</v>
+      </c>
+      <c r="I43">
         <v>7</v>
-      </c>
-      <c r="D43">
-        <v>14</v>
-      </c>
-      <c r="E43">
-        <v>16</v>
-      </c>
-      <c r="F43">
-        <v>37</v>
-      </c>
-      <c r="G43">
-        <v>39</v>
-      </c>
-      <c r="H43">
-        <v>47</v>
-      </c>
-      <c r="I43">
-        <v>34</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D44">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E44">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F44">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G44">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H44">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I44">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D45">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E45">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F45">
+        <v>19</v>
+      </c>
+      <c r="G45">
+        <v>20</v>
+      </c>
+      <c r="H45">
+        <v>40</v>
+      </c>
+      <c r="I45">
         <v>22</v>
-      </c>
-      <c r="G45">
-        <v>40</v>
-      </c>
-      <c r="H45">
-        <v>45</v>
-      </c>
-      <c r="I45">
-        <v>18</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C46">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D46">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E46">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F46">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G46">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H46">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I46">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C47">
         <v>4</v>
       </c>
       <c r="D47">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E47">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F47">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G47">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H47">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I47">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E48">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F48">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G48">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H48">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I48">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C49">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D49">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E49">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F49">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G49">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H49">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I49">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C50">
         <v>5</v>
       </c>
       <c r="D50">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E50">
+        <v>13</v>
+      </c>
+      <c r="F50">
         <v>25</v>
       </c>
-      <c r="F50">
-        <v>40</v>
-      </c>
       <c r="G50">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H50">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I50">
-        <v>39</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D51">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E51">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F51">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G51">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H51">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I51">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-09-18 第 115000089 期；威力彩 2026-09-17 第 115000075 期</t>
+          <t>大樂透 2026-09-18 第 115000089 期；威力彩 2026-09-21 第 115000076 期</t>
         </is>
       </c>
     </row>
@@ -112,7 +112,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -121,7 +121,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -143,7 +143,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9, 19, 24, 29, 35, 38</t>
+          <t>8, 19, 24, 29, 35, 38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -161,7 +161,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.31 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.286 碼/期</t>
         </is>
       </c>
     </row>
@@ -3574,10 +3574,10 @@
         <v>42</v>
       </c>
       <c r="C7">
-        <v>0.714</v>
+        <v>0.738</v>
       </c>
       <c r="D7">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="E7">
         <v>0.0</v>
@@ -3648,7 +3648,7 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>73.81</v>
+        <v>75.96</v>
       </c>
       <c r="D2">
         <v>10</v>
@@ -3657,16 +3657,16 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>66.67</v>
+        <v>71.43</v>
       </c>
       <c r="H2">
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>18.75</v>
+        <v>23.53</v>
       </c>
     </row>
     <row r="3">
@@ -3674,28 +3674,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C3">
-        <v>70.78</v>
+        <v>70.03</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G3">
-        <v>80.0</v>
+        <v>64.29</v>
       </c>
       <c r="H3">
-        <v>83.33</v>
+        <v>66.67</v>
       </c>
       <c r="I3">
-        <v>25.0</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="4">
@@ -3703,28 +3703,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C4">
-        <v>68.19</v>
+        <v>68.99</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E4">
         <v>4</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G4">
-        <v>60.0</v>
+        <v>85.71</v>
       </c>
       <c r="H4">
         <v>66.67</v>
       </c>
       <c r="I4">
-        <v>37.5</v>
+        <v>29.41</v>
       </c>
     </row>
     <row r="5">
@@ -3732,13 +3732,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C5">
-        <v>64.54</v>
+        <v>66.83</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -3747,13 +3747,13 @@
         <v>2</v>
       </c>
       <c r="G5">
-        <v>66.67</v>
+        <v>100.0</v>
       </c>
       <c r="H5">
         <v>66.67</v>
       </c>
       <c r="I5">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="6">
@@ -3764,7 +3764,7 @@
         <v>9</v>
       </c>
       <c r="C6">
-        <v>64.22</v>
+        <v>66.35</v>
       </c>
       <c r="D6">
         <v>11</v>
@@ -3773,16 +3773,16 @@
         <v>3</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>73.33</v>
+        <v>78.57</v>
       </c>
       <c r="H6">
         <v>50.0</v>
       </c>
       <c r="I6">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="7">
@@ -3790,28 +3790,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C7">
-        <v>64.11</v>
+        <v>65.9</v>
       </c>
       <c r="D7">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>100.0</v>
+        <v>50.0</v>
       </c>
       <c r="H7">
-        <v>66.67</v>
+        <v>83.33</v>
       </c>
       <c r="I7">
-        <v>6.25</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="8">
@@ -3819,28 +3819,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>64.07</v>
+        <v>64.74</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G8">
-        <v>46.67</v>
+        <v>57.14</v>
       </c>
       <c r="H8">
-        <v>83.33</v>
+        <v>50.0</v>
       </c>
       <c r="I8">
-        <v>6.25</v>
+        <v>35.29</v>
       </c>
     </row>
     <row r="9">
@@ -3848,28 +3848,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>63.09</v>
+        <v>64.34</v>
       </c>
       <c r="D9">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>53.33</v>
+        <v>78.57</v>
       </c>
       <c r="H9">
-        <v>16.67</v>
+        <v>66.67</v>
       </c>
       <c r="I9">
-        <v>87.5</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="10">
@@ -3877,28 +3877,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="C10">
-        <v>62.99</v>
+        <v>64.19</v>
       </c>
       <c r="D10">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>53.33</v>
+        <v>92.86</v>
       </c>
       <c r="H10">
         <v>50.0</v>
       </c>
       <c r="I10">
-        <v>31.25</v>
+        <v>23.53</v>
       </c>
     </row>
     <row r="11">
@@ -3909,7 +3909,7 @@
         <v>15</v>
       </c>
       <c r="C11">
-        <v>62.26</v>
+        <v>63.71</v>
       </c>
       <c r="D11">
         <v>9</v>
@@ -3918,16 +3918,16 @@
         <v>1</v>
       </c>
       <c r="F11">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11">
-        <v>60.0</v>
+        <v>64.29</v>
       </c>
       <c r="H11">
         <v>16.67</v>
       </c>
       <c r="I11">
-        <v>81.25</v>
+        <v>82.35</v>
       </c>
     </row>
     <row r="12">
@@ -3938,25 +3938,25 @@
         <v>34</v>
       </c>
       <c r="C12">
-        <v>62.26</v>
+        <v>63.46</v>
       </c>
       <c r="D12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12">
-        <v>60.0</v>
+        <v>57.14</v>
       </c>
       <c r="H12">
         <v>16.67</v>
       </c>
       <c r="I12">
-        <v>81.25</v>
+        <v>82.35</v>
       </c>
     </row>
     <row r="13">
@@ -3964,13 +3964,13 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C13">
-        <v>61.61</v>
+        <v>62.33</v>
       </c>
       <c r="D13">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -3979,13 +3979,13 @@
         <v>3</v>
       </c>
       <c r="G13">
-        <v>86.67</v>
+        <v>64.29</v>
       </c>
       <c r="H13">
         <v>50.0</v>
       </c>
       <c r="I13">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="14">
@@ -3993,28 +3993,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>60.8</v>
+        <v>59.93</v>
       </c>
       <c r="D14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G14">
-        <v>53.33</v>
+        <v>64.29</v>
       </c>
       <c r="H14">
-        <v>0.0</v>
+        <v>33.33</v>
       </c>
       <c r="I14">
-        <v>100.0</v>
+        <v>29.41</v>
       </c>
     </row>
     <row r="15">
@@ -4022,28 +4022,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C15">
-        <v>60.43</v>
+        <v>59.93</v>
       </c>
       <c r="D15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E15">
         <v>3</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>46.67</v>
+        <v>71.43</v>
       </c>
       <c r="H15">
         <v>50.0</v>
       </c>
       <c r="I15">
-        <v>37.5</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="16">
@@ -4051,28 +4051,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C16">
-        <v>60.27</v>
+        <v>59.05</v>
       </c>
       <c r="D16">
         <v>9</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G16">
-        <v>60.0</v>
+        <v>64.29</v>
       </c>
       <c r="H16">
-        <v>50.0</v>
+        <v>33.33</v>
       </c>
       <c r="I16">
-        <v>12.5</v>
+        <v>23.53</v>
       </c>
     </row>
     <row r="17">
@@ -4080,28 +4080,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C17">
-        <v>60.27</v>
+        <v>58.89</v>
       </c>
       <c r="D17">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17">
         <v>3</v>
       </c>
-      <c r="F17">
-        <v>2</v>
-      </c>
       <c r="G17">
-        <v>60.0</v>
+        <v>85.71</v>
       </c>
       <c r="H17">
-        <v>50.0</v>
+        <v>33.33</v>
       </c>
       <c r="I17">
-        <v>12.5</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="18">
@@ -4109,28 +4109,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18">
-        <v>59.24</v>
+        <v>58.3</v>
       </c>
       <c r="D18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G18">
-        <v>53.33</v>
+        <v>50.0</v>
       </c>
       <c r="H18">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
       <c r="I18">
-        <v>6.25</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="19">
@@ -4138,28 +4138,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>58.4</v>
+        <v>57.93</v>
       </c>
       <c r="D19">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E19">
         <v>3</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G19">
-        <v>60.0</v>
+        <v>42.86</v>
       </c>
       <c r="H19">
         <v>50.0</v>
       </c>
       <c r="I19">
-        <v>0.0</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="20">
@@ -4167,28 +4167,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C20">
-        <v>57.98</v>
+        <v>57.04</v>
       </c>
       <c r="D20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G20">
-        <v>60.0</v>
+        <v>57.14</v>
       </c>
       <c r="H20">
         <v>33.33</v>
       </c>
       <c r="I20">
-        <v>25.0</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="21">
@@ -4196,28 +4196,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C21">
-        <v>57.15</v>
+        <v>56.81</v>
       </c>
       <c r="D21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G21">
+        <v>42.86</v>
+      </c>
+      <c r="H21">
         <v>66.67</v>
       </c>
-      <c r="H21">
-        <v>33.33</v>
-      </c>
       <c r="I21">
-        <v>18.75</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="22">
@@ -4225,28 +4225,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C22">
-        <v>56.78</v>
+        <v>56.54</v>
       </c>
       <c r="D22">
         <v>7</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G22">
-        <v>46.67</v>
+        <v>50.0</v>
       </c>
       <c r="H22">
-        <v>16.67</v>
+        <v>0.0</v>
       </c>
       <c r="I22">
-        <v>68.75</v>
+        <v>88.24</v>
       </c>
     </row>
     <row r="23">
@@ -4254,28 +4254,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C23">
-        <v>56.41</v>
+        <v>56.4</v>
       </c>
       <c r="D23">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E23">
         <v>2</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>80.0</v>
+        <v>64.29</v>
       </c>
       <c r="H23">
         <v>33.33</v>
       </c>
       <c r="I23">
-        <v>12.5</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="24">
@@ -4283,28 +4283,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C24">
-        <v>55.89</v>
+        <v>56.4</v>
       </c>
       <c r="D24">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E24">
+        <v>2</v>
+      </c>
+      <c r="F24">
         <v>1</v>
       </c>
-      <c r="F24">
-        <v>6</v>
-      </c>
       <c r="G24">
-        <v>73.33</v>
+        <v>64.29</v>
       </c>
       <c r="H24">
-        <v>16.67</v>
+        <v>33.33</v>
       </c>
       <c r="I24">
-        <v>37.5</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="25">
@@ -4312,25 +4312,25 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C25">
-        <v>55.07</v>
+        <v>56.25</v>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>40.0</v>
+        <v>85.71</v>
       </c>
       <c r="H25">
-        <v>66.67</v>
+        <v>33.33</v>
       </c>
       <c r="I25">
         <v>0.0</v>
@@ -4341,28 +4341,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C26">
-        <v>54.23</v>
+        <v>56.16</v>
       </c>
       <c r="D26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E26">
         <v>2</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26">
-        <v>60.0</v>
+        <v>57.14</v>
       </c>
       <c r="H26">
         <v>33.33</v>
       </c>
       <c r="I26">
-        <v>0.0</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="27">
@@ -4370,10 +4370,10 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C27">
-        <v>54.13</v>
+        <v>55.27</v>
       </c>
       <c r="D27">
         <v>8</v>
@@ -4385,7 +4385,7 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>53.33</v>
+        <v>57.14</v>
       </c>
       <c r="H27">
         <v>33.33</v>
@@ -4402,7 +4402,7 @@
         <v>10</v>
       </c>
       <c r="C28">
-        <v>51.57</v>
+        <v>53.4</v>
       </c>
       <c r="D28">
         <v>7</v>
@@ -4411,16 +4411,16 @@
         <v>2</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28">
-        <v>46.67</v>
+        <v>50.0</v>
       </c>
       <c r="H28">
         <v>33.33</v>
       </c>
       <c r="I28">
-        <v>6.25</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="29">
@@ -4431,7 +4431,7 @@
         <v>1</v>
       </c>
       <c r="C29">
-        <v>50.75</v>
+        <v>52.12</v>
       </c>
       <c r="D29">
         <v>5</v>
@@ -4440,16 +4440,16 @@
         <v>3</v>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G29">
-        <v>33.33</v>
+        <v>35.71</v>
       </c>
       <c r="H29">
         <v>50.0</v>
       </c>
       <c r="I29">
-        <v>25.0</v>
+        <v>29.41</v>
       </c>
     </row>
     <row r="30">
@@ -4460,7 +4460,7 @@
         <v>5</v>
       </c>
       <c r="C30">
-        <v>47.1</v>
+        <v>48.2</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -4469,16 +4469,16 @@
         <v>1</v>
       </c>
       <c r="F30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G30">
-        <v>33.33</v>
+        <v>35.71</v>
       </c>
       <c r="H30">
         <v>16.67</v>
       </c>
       <c r="I30">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
     </row>
     <row r="31">
@@ -4489,7 +4489,7 @@
         <v>30</v>
       </c>
       <c r="C31">
-        <v>46.58</v>
+        <v>47.96</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -4498,16 +4498,16 @@
         <v>2</v>
       </c>
       <c r="F31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G31">
-        <v>33.33</v>
+        <v>35.71</v>
       </c>
       <c r="H31">
         <v>33.33</v>
       </c>
       <c r="I31">
-        <v>25.0</v>
+        <v>29.41</v>
       </c>
     </row>
     <row r="32">
@@ -4515,28 +4515,28 @@
         <v>31</v>
       </c>
       <c r="B32">
+        <v>37</v>
+      </c>
+      <c r="C32">
+        <v>47.71</v>
+      </c>
+      <c r="D32">
+        <v>5</v>
+      </c>
+      <c r="E32">
         <v>3</v>
       </c>
-      <c r="C32">
-        <v>44.14</v>
-      </c>
-      <c r="D32">
-        <v>4</v>
-      </c>
-      <c r="E32">
-        <v>1</v>
-      </c>
       <c r="F32">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>26.67</v>
+        <v>35.71</v>
       </c>
       <c r="H32">
-        <v>16.67</v>
+        <v>50.0</v>
       </c>
       <c r="I32">
-        <v>62.5</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="33">
@@ -4547,7 +4547,7 @@
         <v>12</v>
       </c>
       <c r="C33">
-        <v>43.77</v>
+        <v>45.31</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -4556,16 +4556,16 @@
         <v>2</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33">
-        <v>33.33</v>
+        <v>35.71</v>
       </c>
       <c r="H33">
         <v>33.33</v>
       </c>
       <c r="I33">
-        <v>6.25</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="34">
@@ -4576,7 +4576,7 @@
         <v>27</v>
       </c>
       <c r="C34">
-        <v>42.57</v>
+        <v>44.31</v>
       </c>
       <c r="D34">
         <v>6</v>
@@ -4585,16 +4585,16 @@
         <v>1</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34">
-        <v>40.0</v>
+        <v>42.86</v>
       </c>
       <c r="H34">
         <v>16.67</v>
       </c>
       <c r="I34">
-        <v>0.0</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="35">
@@ -4602,28 +4602,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C35">
-        <v>42.12</v>
+        <v>43.55</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>20.0</v>
+        <v>35.71</v>
       </c>
       <c r="H35">
-        <v>16.67</v>
+        <v>33.33</v>
       </c>
       <c r="I35">
-        <v>75.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="36">
@@ -4631,28 +4631,28 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C36">
-        <v>40.81</v>
+        <v>42.77</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G36">
-        <v>26.67</v>
+        <v>21.43</v>
       </c>
       <c r="H36">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="I36">
-        <v>12.5</v>
+        <v>76.47</v>
       </c>
     </row>
     <row r="37">
@@ -4660,28 +4660,28 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C37">
-        <v>39.6</v>
+        <v>42.15</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G37">
+        <v>28.57</v>
+      </c>
+      <c r="H37">
         <v>33.33</v>
       </c>
-      <c r="H37">
-        <v>16.67</v>
-      </c>
       <c r="I37">
-        <v>6.25</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="38">
@@ -4689,28 +4689,28 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C38">
-        <v>39.46</v>
+        <v>41.14</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
       <c r="F38">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G38">
-        <v>26.67</v>
+        <v>35.71</v>
       </c>
       <c r="H38">
         <v>16.67</v>
       </c>
       <c r="I38">
-        <v>31.25</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="39">
@@ -4718,28 +4718,28 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C39">
-        <v>38.93</v>
+        <v>40.63</v>
       </c>
       <c r="D39">
         <v>4</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G39">
-        <v>26.67</v>
+        <v>28.57</v>
       </c>
       <c r="H39">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="I39">
-        <v>0.0</v>
+        <v>35.29</v>
       </c>
     </row>
   </sheetData>
@@ -4798,123 +4798,123 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C2">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H2">
         <v>37</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F3">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>12</v>
+      </c>
+      <c r="E4">
+        <v>14</v>
+      </c>
+      <c r="F4">
+        <v>16</v>
+      </c>
+      <c r="G4">
+        <v>29</v>
+      </c>
+      <c r="H4">
+        <v>36</v>
+      </c>
+      <c r="I4">
         <v>8</v>
-      </c>
-      <c r="D4">
-        <v>17</v>
-      </c>
-      <c r="E4">
-        <v>18</v>
-      </c>
-      <c r="F4">
-        <v>29</v>
-      </c>
-      <c r="G4">
-        <v>33</v>
-      </c>
-      <c r="H4">
-        <v>38</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G5">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H5">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -4922,108 +4922,108 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F7">
         <v>19</v>
       </c>
       <c r="G7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H7">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G8">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H8">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D9">
         <v>7</v>
@@ -5032,230 +5032,230 @@
         <v>9</v>
       </c>
       <c r="F9">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H9">
         <v>36</v>
       </c>
       <c r="I9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E10">
         <v>9</v>
       </c>
       <c r="F10">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G10">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H10">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>9</v>
+      </c>
+      <c r="F11">
         <v>11</v>
       </c>
-      <c r="E11">
-        <v>18</v>
-      </c>
-      <c r="F11">
-        <v>19</v>
-      </c>
       <c r="G11">
+        <v>29</v>
+      </c>
+      <c r="H11">
         <v>35</v>
       </c>
-      <c r="H11">
-        <v>38</v>
-      </c>
       <c r="I11">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G12">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H12">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="I12">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C13">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E13">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F13">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G13">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H13">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I13">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D14">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E14">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G14">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I14">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>7</v>
+      </c>
+      <c r="E15">
+        <v>8</v>
+      </c>
+      <c r="F15">
+        <v>20</v>
+      </c>
+      <c r="G15">
+        <v>26</v>
+      </c>
+      <c r="H15">
+        <v>33</v>
+      </c>
+      <c r="I15">
         <v>4</v>
-      </c>
-      <c r="D15">
-        <v>15</v>
-      </c>
-      <c r="E15">
-        <v>22</v>
-      </c>
-      <c r="F15">
-        <v>26</v>
-      </c>
-      <c r="G15">
-        <v>34</v>
-      </c>
-      <c r="H15">
-        <v>36</v>
-      </c>
-      <c r="I15">
-        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C16">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E16">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F16">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G16">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H16">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I16">
         <v>7</v>
@@ -5263,30 +5263,30 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C17">
+        <v>8</v>
+      </c>
+      <c r="D17">
+        <v>14</v>
+      </c>
+      <c r="E17">
+        <v>17</v>
+      </c>
+      <c r="F17">
         <v>19</v>
       </c>
-      <c r="D17">
-        <v>22</v>
-      </c>
-      <c r="E17">
-        <v>28</v>
-      </c>
-      <c r="F17">
-        <v>31</v>
-      </c>
       <c r="G17">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H17">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I17">
         <v>7</v>
@@ -5294,30 +5294,30 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C18">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D18">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E18">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F18">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G18">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H18">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I18">
         <v>7</v>
@@ -5325,24 +5325,24 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D19">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E19">
         <v>13</v>
       </c>
       <c r="F19">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G19">
         <v>29</v>
@@ -5351,97 +5351,97 @@
         <v>31</v>
       </c>
       <c r="I19">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C20">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D20">
+        <v>12</v>
+      </c>
+      <c r="E20">
+        <v>13</v>
+      </c>
+      <c r="F20">
         <v>23</v>
       </c>
-      <c r="E20">
-        <v>25</v>
-      </c>
-      <c r="F20">
+      <c r="G20">
         <v>29</v>
       </c>
-      <c r="G20">
-        <v>34</v>
-      </c>
       <c r="H20">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I20">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C21">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D21">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E21">
+        <v>25</v>
+      </c>
+      <c r="F21">
         <v>29</v>
       </c>
-      <c r="F21">
-        <v>32</v>
-      </c>
       <c r="G21">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H21">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I21">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C22">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D22">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E22">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F22">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G22">
         <v>35</v>
       </c>
       <c r="H22">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I22">
         <v>6</v>
@@ -5449,402 +5449,402 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D23">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E23">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F23">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G23">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H23">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E24">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F24">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G24">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H24">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I24">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E25">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F25">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G25">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H25">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I25">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C26">
+        <v>5</v>
+      </c>
+      <c r="D26">
         <v>6</v>
       </c>
-      <c r="D26">
-        <v>10</v>
-      </c>
       <c r="E26">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F26">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G26">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H26">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C27">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D27">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E27">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F27">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G27">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H27">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I27">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D28">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E28">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F28">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G28">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H28">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I28">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29">
+        <v>8</v>
+      </c>
+      <c r="E29">
+        <v>9</v>
+      </c>
+      <c r="F29">
+        <v>15</v>
+      </c>
+      <c r="G29">
+        <v>18</v>
+      </c>
+      <c r="H29">
+        <v>23</v>
+      </c>
+      <c r="I29">
         <v>4</v>
-      </c>
-      <c r="D29">
-        <v>17</v>
-      </c>
-      <c r="E29">
-        <v>19</v>
-      </c>
-      <c r="F29">
-        <v>25</v>
-      </c>
-      <c r="G29">
-        <v>28</v>
-      </c>
-      <c r="H29">
-        <v>29</v>
-      </c>
-      <c r="I29">
-        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C30">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D30">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E30">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F30">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G30">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H30">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I30">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D31">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E31">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F31">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G31">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H31">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I31">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C32">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D32">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E32">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F32">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G32">
         <v>28</v>
       </c>
       <c r="H32">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I32">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C33">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D33">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E33">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F33">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G33">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H33">
         <v>35</v>
       </c>
       <c r="I33">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E34">
+        <v>9</v>
+      </c>
+      <c r="F34">
+        <v>15</v>
+      </c>
+      <c r="G34">
         <v>24</v>
       </c>
-      <c r="F34">
-        <v>31</v>
-      </c>
-      <c r="G34">
-        <v>34</v>
-      </c>
       <c r="H34">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I34">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C35">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D35">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E35">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F35">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G35">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H35">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I35">
         <v>3</v>
@@ -5852,498 +5852,498 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C36">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D36">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E36">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F36">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G36">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H36">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I36">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C37">
         <v>6</v>
       </c>
       <c r="D37">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E37">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F37">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G37">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H37">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I37">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C38">
         <v>6</v>
       </c>
       <c r="D38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E38">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F38">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G38">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H38">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I38">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C39">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D39">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E39">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F39">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G39">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H39">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I39">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D40">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E40">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F40">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G40">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H40">
         <v>38</v>
       </c>
       <c r="I40">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C41">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D41">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E41">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F41">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G41">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H41">
         <v>38</v>
       </c>
       <c r="I41">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D42">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E42">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F42">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G42">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H42">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I42">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C43">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D43">
+        <v>4</v>
+      </c>
+      <c r="E43">
+        <v>13</v>
+      </c>
+      <c r="F43">
+        <v>19</v>
+      </c>
+      <c r="G43">
+        <v>27</v>
+      </c>
+      <c r="H43">
+        <v>30</v>
+      </c>
+      <c r="I43">
         <v>8</v>
-      </c>
-      <c r="E43">
-        <v>27</v>
-      </c>
-      <c r="F43">
-        <v>33</v>
-      </c>
-      <c r="G43">
-        <v>35</v>
-      </c>
-      <c r="H43">
-        <v>38</v>
-      </c>
-      <c r="I43">
-        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C44">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D44">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E44">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F44">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G44">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H44">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I44">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D45">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E45">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F45">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G45">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H45">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I45">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C46">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D46">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E46">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F46">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G46">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H46">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I46">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000030</v>
+        <v>115000031</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D47">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E47">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F47">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G47">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H47">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="I47">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000029</v>
+        <v>115000030</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D48">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E48">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F48">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G48">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H48">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I48">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000028</v>
+        <v>115000029</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D49">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E49">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F49">
         <v>27</v>
       </c>
       <c r="G49">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H49">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I49">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000027</v>
+        <v>115000028</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C50">
         <v>5</v>
       </c>
       <c r="D50">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E50">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F50">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G50">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H50">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I50">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000026</v>
+        <v>115000027</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D51">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E51">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F51">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G51">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H51">
         <v>34</v>
       </c>
       <c r="I51">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-09-18 第 115000089 期；威力彩 2026-09-21 第 115000076 期</t>
+          <t>大樂透 2026-09-22 第 115000090 期；威力彩 2026-09-21 第 115000076 期</t>
         </is>
       </c>
     </row>
@@ -47,7 +47,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>115000089</v>
+        <v>115000090</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -56,7 +56,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -78,7 +78,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12, 16, 18, 25, 26, 29</t>
+          <t>12, 16, 18, 26, 29, 35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -398,7 +398,7 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>71.35</v>
+        <v>71.7</v>
       </c>
       <c r="D2">
         <v>12</v>
@@ -407,7 +407,7 @@
         <v>5</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>100.0</v>
@@ -416,7 +416,7 @@
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>5.0</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="3">
@@ -424,28 +424,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C3">
-        <v>67.43</v>
+        <v>70.5</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>91.67</v>
+        <v>83.33</v>
       </c>
       <c r="H3">
-        <v>80.0</v>
+        <v>100.0</v>
       </c>
       <c r="I3">
-        <v>12.5</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="4">
@@ -453,28 +453,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C4">
-        <v>65.45</v>
+        <v>67.75</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E4">
         <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G4">
-        <v>75.0</v>
+        <v>91.67</v>
       </c>
       <c r="H4">
         <v>80.0</v>
       </c>
       <c r="I4">
-        <v>0.0</v>
+        <v>14.63</v>
       </c>
     </row>
     <row r="5">
@@ -482,28 +482,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>63.87</v>
+        <v>65.45</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>83.33</v>
+        <v>75.0</v>
       </c>
       <c r="H5">
-        <v>60.0</v>
+        <v>80.0</v>
       </c>
       <c r="I5">
-        <v>22.5</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
@@ -511,28 +511,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>62.6</v>
+        <v>65.4</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>58.33</v>
+        <v>66.67</v>
       </c>
       <c r="H6">
-        <v>60.0</v>
+        <v>80.0</v>
       </c>
       <c r="I6">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7">
@@ -540,28 +540,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C7">
-        <v>62.43</v>
+        <v>64.11</v>
       </c>
       <c r="D7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>91.67</v>
+        <v>75.0</v>
       </c>
       <c r="H7">
         <v>60.0</v>
       </c>
       <c r="I7">
-        <v>12.5</v>
+        <v>24.39</v>
       </c>
     </row>
     <row r="8">
@@ -569,28 +569,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C8">
-        <v>62.33</v>
+        <v>62.75</v>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G8">
-        <v>50.0</v>
+        <v>91.67</v>
       </c>
       <c r="H8">
         <v>60.0</v>
       </c>
       <c r="I8">
-        <v>17.5</v>
+        <v>14.63</v>
       </c>
     </row>
     <row r="9">
@@ -598,28 +598,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C9">
-        <v>61.2</v>
+        <v>62.63</v>
       </c>
       <c r="D9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G9">
-        <v>75.0</v>
+        <v>50.0</v>
       </c>
       <c r="H9">
         <v>60.0</v>
       </c>
       <c r="I9">
-        <v>5.0</v>
+        <v>19.51</v>
       </c>
     </row>
     <row r="10">
@@ -627,28 +627,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C10">
-        <v>61.15</v>
+        <v>61.55</v>
       </c>
       <c r="D10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>66.67</v>
+        <v>75.0</v>
       </c>
       <c r="H10">
         <v>60.0</v>
       </c>
       <c r="I10">
-        <v>5.0</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="11">
@@ -659,7 +659,7 @@
         <v>27</v>
       </c>
       <c r="C11">
-        <v>60.45</v>
+        <v>60.8</v>
       </c>
       <c r="D11">
         <v>6</v>
@@ -668,7 +668,7 @@
         <v>3</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11">
         <v>50.0</v>
@@ -677,7 +677,7 @@
         <v>60.0</v>
       </c>
       <c r="I11">
-        <v>5.0</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="12">
@@ -685,13 +685,13 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C12">
-        <v>60.35</v>
+        <v>60.5</v>
       </c>
       <c r="D12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>58.33</v>
+        <v>83.33</v>
       </c>
       <c r="H12">
         <v>60.0</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="C13">
-        <v>60.08</v>
+        <v>60.43</v>
       </c>
       <c r="D13">
         <v>6</v>
@@ -726,7 +726,7 @@
         <v>3</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13">
         <v>50.0</v>
@@ -735,7 +735,7 @@
         <v>60.0</v>
       </c>
       <c r="I13">
-        <v>2.5</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="14">
@@ -746,7 +746,7 @@
         <v>21</v>
       </c>
       <c r="C14">
-        <v>59.7</v>
+        <v>60.07</v>
       </c>
       <c r="D14">
         <v>6</v>
@@ -755,7 +755,7 @@
         <v>3</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14">
         <v>50.0</v>
@@ -764,7 +764,7 @@
         <v>60.0</v>
       </c>
       <c r="I14">
-        <v>0.0</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="15">
@@ -772,28 +772,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="C15">
-        <v>58.45</v>
+        <v>58.64</v>
       </c>
       <c r="D15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15">
         <v>2</v>
       </c>
       <c r="F15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G15">
-        <v>50.0</v>
+        <v>58.33</v>
       </c>
       <c r="H15">
         <v>40.0</v>
       </c>
       <c r="I15">
-        <v>25.0</v>
+        <v>21.95</v>
       </c>
     </row>
     <row r="16">
@@ -801,10 +801,10 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C16">
-        <v>58.35</v>
+        <v>57.91</v>
       </c>
       <c r="D16">
         <v>7</v>
@@ -813,7 +813,7 @@
         <v>2</v>
       </c>
       <c r="F16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G16">
         <v>58.33</v>
@@ -822,7 +822,7 @@
         <v>40.0</v>
       </c>
       <c r="I16">
-        <v>20.0</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="17">
@@ -830,10 +830,10 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C17">
-        <v>57.6</v>
+        <v>57.91</v>
       </c>
       <c r="D17">
         <v>7</v>
@@ -842,7 +842,7 @@
         <v>2</v>
       </c>
       <c r="F17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G17">
         <v>58.33</v>
@@ -851,7 +851,7 @@
         <v>40.0</v>
       </c>
       <c r="I17">
-        <v>15.0</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="18">
@@ -859,13 +859,13 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C18">
-        <v>57.6</v>
+        <v>57.69</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -874,13 +874,13 @@
         <v>6</v>
       </c>
       <c r="G18">
-        <v>58.33</v>
+        <v>83.33</v>
       </c>
       <c r="H18">
         <v>40.0</v>
       </c>
       <c r="I18">
-        <v>15.0</v>
+        <v>14.63</v>
       </c>
     </row>
     <row r="19">
@@ -888,28 +888,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="C19">
-        <v>57.37</v>
+        <v>56.45</v>
       </c>
       <c r="D19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G19">
-        <v>83.33</v>
+        <v>58.33</v>
       </c>
       <c r="H19">
         <v>40.0</v>
       </c>
       <c r="I19">
-        <v>12.5</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="20">
@@ -917,10 +917,10 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C20">
-        <v>56.47</v>
+        <v>56.45</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -938,7 +938,7 @@
         <v>40.0</v>
       </c>
       <c r="I20">
-        <v>7.5</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="21">
@@ -946,28 +946,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C21">
-        <v>56.1</v>
+        <v>56.16</v>
       </c>
       <c r="D21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E21">
         <v>2</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G21">
-        <v>58.33</v>
+        <v>50.0</v>
       </c>
       <c r="H21">
         <v>40.0</v>
       </c>
       <c r="I21">
-        <v>5.0</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="22">
@@ -975,28 +975,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C22">
-        <v>56.1</v>
+        <v>56.16</v>
       </c>
       <c r="D22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E22">
         <v>2</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G22">
-        <v>58.33</v>
+        <v>50.0</v>
       </c>
       <c r="H22">
         <v>40.0</v>
       </c>
       <c r="I22">
-        <v>5.0</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="23">
@@ -1004,28 +1004,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>55.83</v>
+        <v>55.71</v>
       </c>
       <c r="D23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E23">
         <v>2</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>50.0</v>
+        <v>58.33</v>
       </c>
       <c r="H23">
         <v>40.0</v>
       </c>
       <c r="I23">
-        <v>7.5</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="24">
@@ -1033,28 +1033,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C24">
-        <v>55.82</v>
+        <v>55.52</v>
       </c>
       <c r="D24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G24">
-        <v>75.0</v>
+        <v>66.67</v>
       </c>
       <c r="H24">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I24">
-        <v>2.5</v>
+        <v>34.15</v>
       </c>
     </row>
     <row r="25">
@@ -1062,28 +1062,28 @@
         <v>24</v>
       </c>
       <c r="B25">
+        <v>34</v>
+      </c>
+      <c r="C25">
+        <v>53.72</v>
+      </c>
+      <c r="D25">
+        <v>6</v>
+      </c>
+      <c r="E25">
         <v>1</v>
       </c>
-      <c r="C25">
-        <v>55.35</v>
-      </c>
-      <c r="D25">
-        <v>7</v>
-      </c>
-      <c r="E25">
-        <v>2</v>
-      </c>
       <c r="F25">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G25">
-        <v>58.33</v>
+        <v>50.0</v>
       </c>
       <c r="H25">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I25">
-        <v>0.0</v>
+        <v>26.83</v>
       </c>
     </row>
     <row r="26">
@@ -1091,28 +1091,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C26">
-        <v>55.28</v>
+        <v>52.91</v>
       </c>
       <c r="D26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G26">
-        <v>66.67</v>
+        <v>58.33</v>
       </c>
       <c r="H26">
         <v>20.0</v>
       </c>
       <c r="I26">
-        <v>32.5</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="27">
@@ -1120,28 +1120,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C27">
-        <v>54.95</v>
+        <v>52.54</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G27">
-        <v>50.0</v>
+        <v>58.33</v>
       </c>
       <c r="H27">
         <v>20.0</v>
       </c>
       <c r="I27">
-        <v>35.0</v>
+        <v>14.63</v>
       </c>
     </row>
     <row r="28">
@@ -1149,10 +1149,10 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C28">
-        <v>52.33</v>
+        <v>51.53</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -1161,7 +1161,7 @@
         <v>1</v>
       </c>
       <c r="F28">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G28">
         <v>50.0</v>
@@ -1170,7 +1170,7 @@
         <v>20.0</v>
       </c>
       <c r="I28">
-        <v>17.5</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="29">
@@ -1178,28 +1178,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C29">
-        <v>52.22</v>
+        <v>51.16</v>
       </c>
       <c r="D29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G29">
-        <v>58.33</v>
+        <v>50.0</v>
       </c>
       <c r="H29">
         <v>20.0</v>
       </c>
       <c r="I29">
-        <v>12.5</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="30">
@@ -1207,28 +1207,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="C30">
-        <v>51.2</v>
+        <v>50.71</v>
       </c>
       <c r="D30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G30">
-        <v>50.0</v>
+        <v>58.33</v>
       </c>
       <c r="H30">
         <v>20.0</v>
       </c>
       <c r="I30">
-        <v>10.0</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="31">
@@ -1236,28 +1236,28 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="C31">
-        <v>50.83</v>
+        <v>50.48</v>
       </c>
       <c r="D31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G31">
-        <v>50.0</v>
+        <v>41.67</v>
       </c>
       <c r="H31">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I31">
-        <v>7.5</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="32">
@@ -1265,28 +1265,28 @@
         <v>31</v>
       </c>
       <c r="B32">
+        <v>39</v>
+      </c>
+      <c r="C32">
+        <v>50.43</v>
+      </c>
+      <c r="D32">
         <v>6</v>
-      </c>
-      <c r="C32">
-        <v>50.35</v>
-      </c>
-      <c r="D32">
-        <v>7</v>
       </c>
       <c r="E32">
         <v>1</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G32">
-        <v>58.33</v>
+        <v>50.0</v>
       </c>
       <c r="H32">
         <v>20.0</v>
       </c>
       <c r="I32">
-        <v>0.0</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="33">
@@ -1294,28 +1294,28 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="C33">
-        <v>50.13</v>
+        <v>47.68</v>
       </c>
       <c r="D33">
         <v>5</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G33">
         <v>41.67</v>
       </c>
       <c r="H33">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I33">
-        <v>2.5</v>
+        <v>19.51</v>
       </c>
     </row>
     <row r="34">
@@ -1323,28 +1323,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C34">
-        <v>50.08</v>
+        <v>47.68</v>
       </c>
       <c r="D34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E34">
         <v>1</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G34">
-        <v>50.0</v>
+        <v>41.67</v>
       </c>
       <c r="H34">
         <v>20.0</v>
       </c>
       <c r="I34">
-        <v>2.5</v>
+        <v>19.51</v>
       </c>
     </row>
     <row r="35">
@@ -1352,10 +1352,10 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C35">
-        <v>48.55</v>
+        <v>47.36</v>
       </c>
       <c r="D35">
         <v>4</v>
@@ -1364,7 +1364,7 @@
         <v>2</v>
       </c>
       <c r="F35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G35">
         <v>33.33</v>
@@ -1373,7 +1373,7 @@
         <v>40.0</v>
       </c>
       <c r="I35">
-        <v>25.0</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="36">
@@ -1381,10 +1381,10 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C36">
-        <v>47.38</v>
+        <v>46.58</v>
       </c>
       <c r="D36">
         <v>5</v>
@@ -1393,7 +1393,7 @@
         <v>1</v>
       </c>
       <c r="F36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G36">
         <v>41.67</v>
@@ -1402,7 +1402,7 @@
         <v>20.0</v>
       </c>
       <c r="I36">
-        <v>17.5</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="37">
@@ -1410,28 +1410,28 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C37">
-        <v>47.05</v>
+        <v>46.58</v>
       </c>
       <c r="D37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G37">
-        <v>33.33</v>
+        <v>41.67</v>
       </c>
       <c r="H37">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I37">
-        <v>15.0</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="38">
@@ -1439,28 +1439,28 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="C38">
-        <v>47.05</v>
+        <v>45.24</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G38">
-        <v>33.33</v>
+        <v>41.67</v>
       </c>
       <c r="H38">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="I38">
-        <v>15.0</v>
+        <v>36.59</v>
       </c>
     </row>
     <row r="39">
@@ -1468,28 +1468,28 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C39">
-        <v>46.25</v>
+        <v>44.85</v>
       </c>
       <c r="D39">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="G39">
-        <v>41.67</v>
+        <v>25.0</v>
       </c>
       <c r="H39">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I39">
-        <v>10.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="40">
@@ -1497,28 +1497,28 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C40">
-        <v>46.25</v>
+        <v>44.8</v>
       </c>
       <c r="D40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G40">
-        <v>41.67</v>
+        <v>33.33</v>
       </c>
       <c r="H40">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I40">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="41">
@@ -1526,28 +1526,28 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="C41">
-        <v>44.85</v>
+        <v>44.19</v>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="G41">
-        <v>25.0</v>
+        <v>33.33</v>
       </c>
       <c r="H41">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I41">
-        <v>100.0</v>
+        <v>29.27</v>
       </c>
     </row>
     <row r="42">
@@ -1555,10 +1555,10 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="C42">
-        <v>43.92</v>
+        <v>43.82</v>
       </c>
       <c r="D42">
         <v>4</v>
@@ -1576,7 +1576,7 @@
         <v>20.0</v>
       </c>
       <c r="I42">
-        <v>27.5</v>
+        <v>26.83</v>
       </c>
     </row>
     <row r="43">
@@ -1584,28 +1584,28 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C43">
-        <v>41.92</v>
+        <v>42.36</v>
       </c>
       <c r="D43">
         <v>4</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G43">
         <v>33.33</v>
       </c>
       <c r="H43">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I43">
-        <v>47.5</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="44">
@@ -1616,7 +1616,7 @@
         <v>22</v>
       </c>
       <c r="C44">
-        <v>40.17</v>
+        <v>40.53</v>
       </c>
       <c r="D44">
         <v>4</v>
@@ -1625,7 +1625,7 @@
         <v>1</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44">
         <v>33.33</v>
@@ -1634,7 +1634,7 @@
         <v>20.0</v>
       </c>
       <c r="I44">
-        <v>2.5</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="45">
@@ -1642,28 +1642,28 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C45">
-        <v>39.73</v>
+        <v>39.8</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E45">
         <v>1</v>
       </c>
       <c r="F45">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G45">
-        <v>25.0</v>
+        <v>33.33</v>
       </c>
       <c r="H45">
         <v>20.0</v>
       </c>
       <c r="I45">
-        <v>32.5</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="46">
@@ -1671,28 +1671,28 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="C46">
-        <v>38.6</v>
+        <v>34.66</v>
       </c>
       <c r="D46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46">
         <v>1</v>
       </c>
       <c r="F46">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G46">
-        <v>25.0</v>
+        <v>16.67</v>
       </c>
       <c r="H46">
         <v>20.0</v>
       </c>
       <c r="I46">
-        <v>25.0</v>
+        <v>31.71</v>
       </c>
     </row>
     <row r="47">
@@ -1700,10 +1700,10 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="C47">
-        <v>34.4</v>
+        <v>33.93</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -1712,7 +1712,7 @@
         <v>1</v>
       </c>
       <c r="F47">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G47">
         <v>16.67</v>
@@ -1721,7 +1721,7 @@
         <v>20.0</v>
       </c>
       <c r="I47">
-        <v>30.0</v>
+        <v>26.83</v>
       </c>
     </row>
     <row r="48">
@@ -1732,7 +1732,7 @@
         <v>38</v>
       </c>
       <c r="C48">
-        <v>33.07</v>
+        <v>33.12</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -1741,7 +1741,7 @@
         <v>0</v>
       </c>
       <c r="F48">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G48">
         <v>8.33</v>
@@ -1750,7 +1750,7 @@
         <v>0.0</v>
       </c>
       <c r="I48">
-        <v>87.5</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="49">
@@ -1761,7 +1761,7 @@
         <v>42</v>
       </c>
       <c r="C49">
-        <v>32.78</v>
+        <v>32.95</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -1770,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="F49">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G49">
         <v>16.67</v>
@@ -1779,7 +1779,7 @@
         <v>0.0</v>
       </c>
       <c r="I49">
-        <v>52.5</v>
+        <v>53.66</v>
       </c>
     </row>
     <row r="50">
@@ -1790,7 +1790,7 @@
         <v>31</v>
       </c>
       <c r="C50">
-        <v>29.9</v>
+        <v>30.27</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -1799,7 +1799,7 @@
         <v>1</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50">
         <v>16.67</v>
@@ -1808,7 +1808,7 @@
         <v>20.0</v>
       </c>
       <c r="I50">
-        <v>0.0</v>
+        <v>2.44</v>
       </c>
     </row>
   </sheetData>
@@ -1867,669 +1867,669 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000089</v>
+        <v>115000090</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H2">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="I2">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000088</v>
+        <v>115000089</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F3">
         <v>21</v>
       </c>
       <c r="G3">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H3">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000087</v>
+        <v>115000088</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C4">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H4">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I4">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000086</v>
+        <v>115000087</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D5">
         <v>15</v>
       </c>
       <c r="E5">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G5">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H5">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I5">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000085</v>
+        <v>115000086</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G6">
+        <v>47</v>
+      </c>
+      <c r="H6">
+        <v>49</v>
+      </c>
+      <c r="I6">
         <v>27</v>
-      </c>
-      <c r="H6">
-        <v>37</v>
-      </c>
-      <c r="I6">
-        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000084</v>
+        <v>115000085</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E7">
+        <v>17</v>
+      </c>
+      <c r="F7">
+        <v>18</v>
+      </c>
+      <c r="G7">
+        <v>27</v>
+      </c>
+      <c r="H7">
+        <v>37</v>
+      </c>
+      <c r="I7">
         <v>19</v>
-      </c>
-      <c r="F7">
-        <v>26</v>
-      </c>
-      <c r="G7">
-        <v>29</v>
-      </c>
-      <c r="H7">
-        <v>48</v>
-      </c>
-      <c r="I7">
-        <v>30</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000083</v>
+        <v>115000084</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F8">
         <v>26</v>
       </c>
       <c r="G8">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H8">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I8">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C9">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D9">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E9">
+        <v>23</v>
+      </c>
+      <c r="F9">
         <v>26</v>
       </c>
-      <c r="F9">
-        <v>32</v>
-      </c>
       <c r="G9">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H9">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I9">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C10">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D10">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E10">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F10">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G10">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H10">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I10">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D11">
         <v>14</v>
       </c>
       <c r="E11">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F11">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G11">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H11">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I11">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E12">
         <v>25</v>
       </c>
       <c r="F12">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G12">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H12">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I12">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C13">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D13">
         <v>12</v>
       </c>
       <c r="E13">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F13">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G13">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H13">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="I13">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D14">
         <v>12</v>
       </c>
       <c r="E14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H14">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I14">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E15">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F15">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G15">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H15">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I15">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C16">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D16">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E16">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F16">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G16">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H16">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I16">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C17">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D17">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E17">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F17">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G17">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H17">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I17">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C18">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D18">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E18">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F18">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G18">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H18">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I18">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E19">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F19">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G19">
         <v>35</v>
       </c>
       <c r="H19">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I19">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E20">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F20">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G20">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H20">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I20">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C21">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E21">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F21">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G21">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H21">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I21">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D22">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E22">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F22">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G22">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H22">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I22">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C23">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D23">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E23">
         <v>15</v>
@@ -2538,345 +2538,345 @@
         <v>18</v>
       </c>
       <c r="G23">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H23">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I23">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C24">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D24">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E24">
+        <v>15</v>
+      </c>
+      <c r="F24">
+        <v>18</v>
+      </c>
+      <c r="G24">
         <v>19</v>
       </c>
-      <c r="F24">
-        <v>23</v>
-      </c>
-      <c r="G24">
-        <v>39</v>
-      </c>
       <c r="H24">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I24">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D25">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E25">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F25">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G25">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H25">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I25">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C26">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D26">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E26">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F26">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G26">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H26">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C27">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D27">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E27">
+        <v>23</v>
+      </c>
+      <c r="F27">
+        <v>24</v>
+      </c>
+      <c r="G27">
         <v>29</v>
       </c>
-      <c r="F27">
-        <v>33</v>
-      </c>
-      <c r="G27">
-        <v>34</v>
-      </c>
       <c r="H27">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I27">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C28">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D28">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E28">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F28">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G28">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H28">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I28">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E29">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F29">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G29">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H29">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I29">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C30">
         <v>1</v>
       </c>
       <c r="D30">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E30">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F30">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G30">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H30">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I30">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C31">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D31">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E31">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F31">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G31">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H31">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I31">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C32">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D32">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E32">
         <v>25</v>
       </c>
       <c r="F32">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G32">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H32">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I32">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C33">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D33">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E33">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F33">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G33">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H33">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I33">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C34">
+        <v>8</v>
+      </c>
+      <c r="D34">
+        <v>9</v>
+      </c>
+      <c r="E34">
+        <v>16</v>
+      </c>
+      <c r="F34">
         <v>20</v>
-      </c>
-      <c r="D34">
-        <v>26</v>
-      </c>
-      <c r="E34">
-        <v>29</v>
-      </c>
-      <c r="F34">
-        <v>31</v>
       </c>
       <c r="G34">
         <v>37</v>
@@ -2885,534 +2885,534 @@
         <v>49</v>
       </c>
       <c r="I34">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C35">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D35">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E35">
         <v>29</v>
       </c>
       <c r="F35">
+        <v>31</v>
+      </c>
+      <c r="G35">
         <v>37</v>
       </c>
-      <c r="G35">
-        <v>47</v>
-      </c>
       <c r="H35">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I35">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C36">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D36">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E36">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F36">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G36">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="H36">
         <v>48</v>
       </c>
       <c r="I36">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C37">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D37">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E37">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F37">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G37">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H37">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I37">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C38">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D38">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E38">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F38">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G38">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H38">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I38">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C39">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D39">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E39">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F39">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G39">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H39">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I39">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C40">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D40">
+        <v>12</v>
+      </c>
+      <c r="E40">
         <v>18</v>
       </c>
-      <c r="E40">
-        <v>25</v>
-      </c>
       <c r="F40">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G40">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H40">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I40">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D41">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E41">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F41">
         <v>28</v>
       </c>
       <c r="G41">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H41">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I41">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C42">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D42">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E42">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F42">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G42">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H42">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I42">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D43">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E43">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F43">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G43">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H43">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I43">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C44">
+        <v>6</v>
+      </c>
+      <c r="D44">
+        <v>10</v>
+      </c>
+      <c r="E44">
+        <v>14</v>
+      </c>
+      <c r="F44">
+        <v>25</v>
+      </c>
+      <c r="G44">
+        <v>26</v>
+      </c>
+      <c r="H44">
+        <v>32</v>
+      </c>
+      <c r="I44">
         <v>7</v>
-      </c>
-      <c r="D44">
-        <v>14</v>
-      </c>
-      <c r="E44">
-        <v>16</v>
-      </c>
-      <c r="F44">
-        <v>37</v>
-      </c>
-      <c r="G44">
-        <v>39</v>
-      </c>
-      <c r="H44">
-        <v>47</v>
-      </c>
-      <c r="I44">
-        <v>34</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D45">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E45">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F45">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G45">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H45">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I45">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C46">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D46">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E46">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F46">
+        <v>19</v>
+      </c>
+      <c r="G46">
+        <v>20</v>
+      </c>
+      <c r="H46">
+        <v>40</v>
+      </c>
+      <c r="I46">
         <v>22</v>
-      </c>
-      <c r="G46">
-        <v>40</v>
-      </c>
-      <c r="H46">
-        <v>45</v>
-      </c>
-      <c r="I46">
-        <v>18</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C47">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D47">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E47">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F47">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G47">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H47">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I47">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C48">
         <v>4</v>
       </c>
       <c r="D48">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E48">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F48">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G48">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H48">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I48">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E49">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F49">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G49">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H49">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I49">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C50">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D50">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E50">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F50">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G50">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H50">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I50">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C51">
         <v>5</v>
       </c>
       <c r="D51">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E51">
+        <v>13</v>
+      </c>
+      <c r="F51">
         <v>25</v>
       </c>
-      <c r="F51">
-        <v>40</v>
-      </c>
       <c r="G51">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H51">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I51">
-        <v>39</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-09-22 第 115000090 期；威力彩 2026-09-21 第 115000076 期</t>
+          <t>大樂透 2026-09-22 第 115000090 期；威力彩 2026-09-24 第 115000077 期</t>
         </is>
       </c>
     </row>
@@ -112,7 +112,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -121,7 +121,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -161,7 +161,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.286 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.31 碼/期</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>1.024</v>
+        <v>1.048</v>
       </c>
       <c r="D2">
         <v>33.3</v>
@@ -3486,7 +3486,7 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>1.024</v>
+        <v>1.048</v>
       </c>
       <c r="D3">
         <v>33.3</v>
@@ -3508,10 +3508,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>0.976</v>
+        <v>0.952</v>
       </c>
       <c r="D4">
-        <v>23.8</v>
+        <v>21.4</v>
       </c>
       <c r="E4">
         <v>4.8</v>
@@ -3552,10 +3552,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.929</v>
+        <v>0.881</v>
       </c>
       <c r="D6">
-        <v>21.4</v>
+        <v>19.0</v>
       </c>
       <c r="E6">
         <v>4.8</v>
@@ -3648,7 +3648,7 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>75.96</v>
+        <v>76.6</v>
       </c>
       <c r="D2">
         <v>10</v>
@@ -3657,7 +3657,7 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>71.43</v>
@@ -3666,7 +3666,7 @@
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>23.53</v>
+        <v>27.78</v>
       </c>
     </row>
     <row r="3">
@@ -3677,7 +3677,7 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>70.03</v>
+        <v>70.52</v>
       </c>
       <c r="D3">
         <v>9</v>
@@ -3686,7 +3686,7 @@
         <v>4</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G3">
         <v>64.29</v>
@@ -3695,7 +3695,7 @@
         <v>66.67</v>
       </c>
       <c r="I3">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
     </row>
     <row r="4">
@@ -3706,7 +3706,7 @@
         <v>19</v>
       </c>
       <c r="C4">
-        <v>68.99</v>
+        <v>69.58</v>
       </c>
       <c r="D4">
         <v>12</v>
@@ -3715,7 +3715,7 @@
         <v>4</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4">
         <v>85.71</v>
@@ -3724,7 +3724,7 @@
         <v>66.67</v>
       </c>
       <c r="I4">
-        <v>29.41</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="5">
@@ -3732,28 +3732,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>66.83</v>
+        <v>68.75</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>100.0</v>
+        <v>85.71</v>
       </c>
       <c r="H5">
-        <v>66.67</v>
+        <v>83.33</v>
       </c>
       <c r="I5">
-        <v>11.76</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
@@ -3761,28 +3761,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C6">
-        <v>66.35</v>
+        <v>67.57</v>
       </c>
       <c r="D6">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>78.57</v>
+        <v>100.0</v>
       </c>
       <c r="H6">
-        <v>50.0</v>
+        <v>66.67</v>
       </c>
       <c r="I6">
-        <v>41.18</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="7">
@@ -3790,28 +3790,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>65.9</v>
+        <v>66.84</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G7">
+        <v>78.57</v>
+      </c>
+      <c r="H7">
         <v>50.0</v>
       </c>
-      <c r="H7">
-        <v>83.33</v>
-      </c>
       <c r="I7">
-        <v>11.76</v>
+        <v>44.44</v>
       </c>
     </row>
     <row r="8">
@@ -3819,28 +3819,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="C8">
-        <v>64.74</v>
+        <v>64.83</v>
       </c>
       <c r="D8">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G8">
-        <v>57.14</v>
+        <v>92.86</v>
       </c>
       <c r="H8">
         <v>50.0</v>
       </c>
       <c r="I8">
-        <v>35.29</v>
+        <v>27.78</v>
       </c>
     </row>
     <row r="9">
@@ -3848,28 +3848,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="C9">
-        <v>64.34</v>
+        <v>63.02</v>
       </c>
       <c r="D9">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9">
         <v>4</v>
       </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
       <c r="G9">
-        <v>78.57</v>
+        <v>64.29</v>
       </c>
       <c r="H9">
-        <v>66.67</v>
+        <v>50.0</v>
       </c>
       <c r="I9">
-        <v>0.0</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="10">
@@ -3877,28 +3877,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10">
-        <v>64.19</v>
+        <v>62.47</v>
       </c>
       <c r="D10">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>92.86</v>
+        <v>50.0</v>
       </c>
       <c r="H10">
-        <v>50.0</v>
+        <v>66.67</v>
       </c>
       <c r="I10">
-        <v>23.53</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="11">
@@ -3906,28 +3906,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>63.71</v>
+        <v>61.11</v>
       </c>
       <c r="D11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G11">
-        <v>64.29</v>
+        <v>57.14</v>
       </c>
       <c r="H11">
-        <v>16.67</v>
+        <v>33.33</v>
       </c>
       <c r="I11">
-        <v>82.35</v>
+        <v>38.89</v>
       </c>
     </row>
     <row r="12">
@@ -3935,28 +3935,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="C12">
-        <v>63.46</v>
+        <v>60.52</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G12">
-        <v>57.14</v>
+        <v>64.29</v>
       </c>
       <c r="H12">
-        <v>16.67</v>
+        <v>33.33</v>
       </c>
       <c r="I12">
-        <v>82.35</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="13">
@@ -3964,10 +3964,10 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C13">
-        <v>62.33</v>
+        <v>60.52</v>
       </c>
       <c r="D13">
         <v>9</v>
@@ -3976,7 +3976,7 @@
         <v>3</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13">
         <v>64.29</v>
@@ -3985,7 +3985,7 @@
         <v>50.0</v>
       </c>
       <c r="I13">
-        <v>17.65</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="14">
@@ -3993,28 +3993,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C14">
         <v>59.93</v>
       </c>
       <c r="D14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>64.29</v>
+        <v>71.43</v>
       </c>
       <c r="H14">
-        <v>33.33</v>
+        <v>50.0</v>
       </c>
       <c r="I14">
-        <v>29.41</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="15">
@@ -4022,28 +4022,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C15">
-        <v>59.93</v>
+        <v>59.58</v>
       </c>
       <c r="D15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G15">
-        <v>71.43</v>
+        <v>85.71</v>
       </c>
       <c r="H15">
-        <v>50.0</v>
+        <v>33.33</v>
       </c>
       <c r="I15">
-        <v>0.0</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="16">
@@ -4051,28 +4051,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C16">
-        <v>59.05</v>
+        <v>59.44</v>
       </c>
       <c r="D16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G16">
-        <v>64.29</v>
+        <v>57.14</v>
       </c>
       <c r="H16">
-        <v>33.33</v>
+        <v>0.0</v>
       </c>
       <c r="I16">
-        <v>23.53</v>
+        <v>83.33</v>
       </c>
     </row>
     <row r="17">
@@ -4080,28 +4080,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C17">
-        <v>58.89</v>
+        <v>59.44</v>
       </c>
       <c r="D17">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>85.71</v>
+        <v>57.14</v>
       </c>
       <c r="H17">
-        <v>33.33</v>
+        <v>50.0</v>
       </c>
       <c r="I17">
-        <v>17.65</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="18">
@@ -4109,28 +4109,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>58.3</v>
+        <v>58.42</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F18">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G18">
+        <v>42.86</v>
+      </c>
+      <c r="H18">
         <v>50.0</v>
       </c>
-      <c r="H18">
-        <v>0.0</v>
-      </c>
       <c r="I18">
-        <v>100.0</v>
+        <v>44.44</v>
       </c>
     </row>
     <row r="19">
@@ -4138,28 +4138,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C19">
-        <v>57.93</v>
+        <v>58.3</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G19">
-        <v>42.86</v>
+        <v>50.0</v>
       </c>
       <c r="H19">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
       <c r="I19">
-        <v>41.18</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="20">
@@ -4170,7 +4170,7 @@
         <v>14</v>
       </c>
       <c r="C20">
-        <v>57.04</v>
+        <v>57.77</v>
       </c>
       <c r="D20">
         <v>8</v>
@@ -4179,7 +4179,7 @@
         <v>2</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20">
         <v>57.14</v>
@@ -4188,7 +4188,7 @@
         <v>33.33</v>
       </c>
       <c r="I20">
-        <v>11.76</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="21">
@@ -4196,28 +4196,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C21">
-        <v>56.81</v>
+        <v>57.08</v>
       </c>
       <c r="D21">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="G21">
-        <v>42.86</v>
+        <v>85.71</v>
       </c>
       <c r="H21">
-        <v>66.67</v>
+        <v>33.33</v>
       </c>
       <c r="I21">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="22">
@@ -4225,28 +4225,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C22">
-        <v>56.54</v>
+        <v>56.94</v>
       </c>
       <c r="D22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>50.0</v>
+        <v>57.14</v>
       </c>
       <c r="H22">
-        <v>0.0</v>
+        <v>33.33</v>
       </c>
       <c r="I22">
-        <v>88.24</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="23">
@@ -4254,28 +4254,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C23">
-        <v>56.4</v>
+        <v>56.94</v>
       </c>
       <c r="D23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E23">
         <v>2</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>64.29</v>
+        <v>57.14</v>
       </c>
       <c r="H23">
         <v>33.33</v>
       </c>
       <c r="I23">
-        <v>5.88</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="24">
@@ -4283,28 +4283,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C24">
-        <v>56.4</v>
+        <v>56.63</v>
       </c>
       <c r="D24">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G24">
-        <v>64.29</v>
+        <v>50.0</v>
       </c>
       <c r="H24">
-        <v>33.33</v>
+        <v>0.0</v>
       </c>
       <c r="I24">
-        <v>5.88</v>
+        <v>88.89</v>
       </c>
     </row>
     <row r="25">
@@ -4312,28 +4312,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C25">
-        <v>56.25</v>
+        <v>55.8</v>
       </c>
       <c r="D25">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G25">
-        <v>85.71</v>
+        <v>50.0</v>
       </c>
       <c r="H25">
-        <v>33.33</v>
+        <v>0.0</v>
       </c>
       <c r="I25">
-        <v>0.0</v>
+        <v>83.33</v>
       </c>
     </row>
     <row r="26">
@@ -4341,28 +4341,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C26">
-        <v>56.16</v>
+        <v>55.52</v>
       </c>
       <c r="D26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G26">
-        <v>57.14</v>
+        <v>64.29</v>
       </c>
       <c r="H26">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="I26">
-        <v>5.88</v>
+        <v>27.78</v>
       </c>
     </row>
     <row r="27">
@@ -4370,28 +4370,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C27">
-        <v>55.27</v>
+        <v>54.13</v>
       </c>
       <c r="D27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E27">
         <v>2</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G27">
-        <v>57.14</v>
+        <v>50.0</v>
       </c>
       <c r="H27">
         <v>33.33</v>
       </c>
       <c r="I27">
-        <v>0.0</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="28">
@@ -4399,28 +4399,28 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C28">
-        <v>53.4</v>
+        <v>53.42</v>
       </c>
       <c r="D28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28">
         <v>2</v>
       </c>
       <c r="G28">
+        <v>42.86</v>
+      </c>
+      <c r="H28">
         <v>50.0</v>
       </c>
-      <c r="H28">
-        <v>33.33</v>
-      </c>
       <c r="I28">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="29">
@@ -4431,7 +4431,7 @@
         <v>1</v>
       </c>
       <c r="C29">
-        <v>52.12</v>
+        <v>52.71</v>
       </c>
       <c r="D29">
         <v>5</v>
@@ -4440,7 +4440,7 @@
         <v>3</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G29">
         <v>35.71</v>
@@ -4449,7 +4449,7 @@
         <v>50.0</v>
       </c>
       <c r="I29">
-        <v>29.41</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="30">
@@ -4457,28 +4457,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C30">
-        <v>48.2</v>
+        <v>51.76</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F30">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>35.71</v>
+        <v>42.86</v>
       </c>
       <c r="H30">
-        <v>16.67</v>
+        <v>50.0</v>
       </c>
       <c r="I30">
-        <v>58.82</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="31">
@@ -4489,25 +4489,25 @@
         <v>30</v>
       </c>
       <c r="C31">
-        <v>47.96</v>
+        <v>51.76</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G31">
-        <v>35.71</v>
+        <v>42.86</v>
       </c>
       <c r="H31">
-        <v>33.33</v>
+        <v>50.0</v>
       </c>
       <c r="I31">
-        <v>29.41</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="32">
@@ -4515,25 +4515,25 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C32">
-        <v>47.71</v>
+        <v>51.63</v>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F32">
         <v>0</v>
       </c>
       <c r="G32">
-        <v>35.71</v>
+        <v>50.0</v>
       </c>
       <c r="H32">
-        <v>50.0</v>
+        <v>33.33</v>
       </c>
       <c r="I32">
         <v>0.0</v>
@@ -4544,28 +4544,28 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="C33">
-        <v>45.31</v>
+        <v>48.55</v>
       </c>
       <c r="D33">
         <v>5</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33">
         <v>35.71</v>
       </c>
       <c r="H33">
-        <v>33.33</v>
+        <v>50.0</v>
       </c>
       <c r="I33">
-        <v>11.76</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="34">
@@ -4573,28 +4573,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C34">
-        <v>44.31</v>
+        <v>46.05</v>
       </c>
       <c r="D34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G34">
-        <v>42.86</v>
+        <v>35.71</v>
       </c>
       <c r="H34">
+        <v>33.33</v>
+      </c>
+      <c r="I34">
         <v>16.67</v>
-      </c>
-      <c r="I34">
-        <v>5.88</v>
       </c>
     </row>
     <row r="35">
@@ -4602,28 +4602,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C35">
-        <v>43.55</v>
+        <v>44.51</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G35">
-        <v>35.71</v>
+        <v>28.57</v>
       </c>
       <c r="H35">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="I35">
-        <v>0.0</v>
+        <v>61.11</v>
       </c>
     </row>
     <row r="36">
@@ -4634,7 +4634,7 @@
         <v>20</v>
       </c>
       <c r="C36">
-        <v>42.77</v>
+        <v>42.96</v>
       </c>
       <c r="D36">
         <v>3</v>
@@ -4643,7 +4643,7 @@
         <v>1</v>
       </c>
       <c r="F36">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G36">
         <v>21.43</v>
@@ -4652,7 +4652,7 @@
         <v>16.67</v>
       </c>
       <c r="I36">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
     </row>
     <row r="37">
@@ -4663,7 +4663,7 @@
         <v>18</v>
       </c>
       <c r="C37">
-        <v>42.15</v>
+        <v>42.84</v>
       </c>
       <c r="D37">
         <v>4</v>
@@ -4672,7 +4672,7 @@
         <v>2</v>
       </c>
       <c r="F37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G37">
         <v>28.57</v>
@@ -4681,7 +4681,7 @@
         <v>33.33</v>
       </c>
       <c r="I37">
-        <v>17.65</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="38">
@@ -4692,7 +4692,7 @@
         <v>16</v>
       </c>
       <c r="C38">
-        <v>41.14</v>
+        <v>41.88</v>
       </c>
       <c r="D38">
         <v>5</v>
@@ -4701,7 +4701,7 @@
         <v>1</v>
       </c>
       <c r="F38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G38">
         <v>35.71</v>
@@ -4710,7 +4710,7 @@
         <v>16.67</v>
       </c>
       <c r="I38">
-        <v>11.76</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="39">
@@ -4721,7 +4721,7 @@
         <v>32</v>
       </c>
       <c r="C39">
-        <v>40.63</v>
+        <v>41.17</v>
       </c>
       <c r="D39">
         <v>4</v>
@@ -4730,7 +4730,7 @@
         <v>1</v>
       </c>
       <c r="F39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G39">
         <v>28.57</v>
@@ -4739,7 +4739,7 @@
         <v>16.67</v>
       </c>
       <c r="I39">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
     </row>
   </sheetData>
@@ -4798,11 +4798,11 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C2">
@@ -4812,140 +4812,140 @@
         <v>8</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H2">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C3">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H3">
         <v>37</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>14</v>
+      </c>
+      <c r="F5">
+        <v>16</v>
+      </c>
+      <c r="G5">
+        <v>29</v>
+      </c>
+      <c r="H5">
+        <v>36</v>
+      </c>
+      <c r="I5">
         <v>8</v>
-      </c>
-      <c r="D5">
-        <v>17</v>
-      </c>
-      <c r="E5">
-        <v>18</v>
-      </c>
-      <c r="F5">
-        <v>29</v>
-      </c>
-      <c r="G5">
-        <v>33</v>
-      </c>
-      <c r="H5">
-        <v>38</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G6">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H6">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I6">
         <v>2</v>
@@ -4953,108 +4953,108 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F7">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H7">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F8">
         <v>19</v>
       </c>
       <c r="G8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H8">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+      <c r="E9">
+        <v>12</v>
+      </c>
+      <c r="F9">
+        <v>19</v>
+      </c>
+      <c r="G9">
+        <v>32</v>
+      </c>
+      <c r="H9">
+        <v>37</v>
+      </c>
+      <c r="I9">
         <v>2</v>
-      </c>
-      <c r="D9">
-        <v>7</v>
-      </c>
-      <c r="E9">
-        <v>9</v>
-      </c>
-      <c r="F9">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>24</v>
-      </c>
-      <c r="H9">
-        <v>36</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D10">
         <v>7</v>
@@ -5063,230 +5063,230 @@
         <v>9</v>
       </c>
       <c r="F10">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G10">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H10">
         <v>36</v>
       </c>
       <c r="I10">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E11">
         <v>9</v>
       </c>
       <c r="F11">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G11">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H11">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I11">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12">
+        <v>9</v>
+      </c>
+      <c r="F12">
         <v>11</v>
       </c>
-      <c r="E12">
-        <v>18</v>
-      </c>
-      <c r="F12">
-        <v>19</v>
-      </c>
       <c r="G12">
+        <v>29</v>
+      </c>
+      <c r="H12">
         <v>35</v>
       </c>
-      <c r="H12">
-        <v>38</v>
-      </c>
       <c r="I12">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F13">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G13">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H13">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="I13">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C14">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E14">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F14">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G14">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H14">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I14">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D15">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E15">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F15">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G15">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H15">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I15">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>7</v>
+      </c>
+      <c r="E16">
+        <v>8</v>
+      </c>
+      <c r="F16">
+        <v>20</v>
+      </c>
+      <c r="G16">
+        <v>26</v>
+      </c>
+      <c r="H16">
+        <v>33</v>
+      </c>
+      <c r="I16">
         <v>4</v>
-      </c>
-      <c r="D16">
-        <v>15</v>
-      </c>
-      <c r="E16">
-        <v>22</v>
-      </c>
-      <c r="F16">
-        <v>26</v>
-      </c>
-      <c r="G16">
-        <v>34</v>
-      </c>
-      <c r="H16">
-        <v>36</v>
-      </c>
-      <c r="I16">
-        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C17">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D17">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F17">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G17">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H17">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I17">
         <v>7</v>
@@ -5294,30 +5294,30 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C18">
+        <v>8</v>
+      </c>
+      <c r="D18">
+        <v>14</v>
+      </c>
+      <c r="E18">
+        <v>17</v>
+      </c>
+      <c r="F18">
         <v>19</v>
       </c>
-      <c r="D18">
-        <v>22</v>
-      </c>
-      <c r="E18">
-        <v>28</v>
-      </c>
-      <c r="F18">
-        <v>31</v>
-      </c>
       <c r="G18">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H18">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I18">
         <v>7</v>
@@ -5325,30 +5325,30 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C19">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D19">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E19">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F19">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G19">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H19">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I19">
         <v>7</v>
@@ -5356,24 +5356,24 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D20">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E20">
         <v>13</v>
       </c>
       <c r="F20">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G20">
         <v>29</v>
@@ -5382,97 +5382,97 @@
         <v>31</v>
       </c>
       <c r="I20">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C21">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D21">
+        <v>12</v>
+      </c>
+      <c r="E21">
+        <v>13</v>
+      </c>
+      <c r="F21">
         <v>23</v>
       </c>
-      <c r="E21">
-        <v>25</v>
-      </c>
-      <c r="F21">
+      <c r="G21">
         <v>29</v>
       </c>
-      <c r="G21">
-        <v>34</v>
-      </c>
       <c r="H21">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I21">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C22">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D22">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E22">
+        <v>25</v>
+      </c>
+      <c r="F22">
         <v>29</v>
       </c>
-      <c r="F22">
-        <v>32</v>
-      </c>
       <c r="G22">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H22">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I22">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C23">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D23">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E23">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F23">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G23">
         <v>35</v>
       </c>
       <c r="H23">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I23">
         <v>6</v>
@@ -5480,402 +5480,402 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D24">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E24">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F24">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G24">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H24">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D25">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E25">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F25">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G25">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H25">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I25">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C26">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E26">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F26">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G26">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H26">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I26">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C27">
+        <v>5</v>
+      </c>
+      <c r="D27">
         <v>6</v>
       </c>
-      <c r="D27">
-        <v>10</v>
-      </c>
       <c r="E27">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F27">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G27">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H27">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C28">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D28">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E28">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F28">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G28">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H28">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I28">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D29">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E29">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F29">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G29">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H29">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I29">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30">
+        <v>8</v>
+      </c>
+      <c r="E30">
+        <v>9</v>
+      </c>
+      <c r="F30">
+        <v>15</v>
+      </c>
+      <c r="G30">
+        <v>18</v>
+      </c>
+      <c r="H30">
+        <v>23</v>
+      </c>
+      <c r="I30">
         <v>4</v>
-      </c>
-      <c r="D30">
-        <v>17</v>
-      </c>
-      <c r="E30">
-        <v>19</v>
-      </c>
-      <c r="F30">
-        <v>25</v>
-      </c>
-      <c r="G30">
-        <v>28</v>
-      </c>
-      <c r="H30">
-        <v>29</v>
-      </c>
-      <c r="I30">
-        <v>6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C31">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D31">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E31">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F31">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G31">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H31">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I31">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D32">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E32">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F32">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G32">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H32">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I32">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C33">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D33">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E33">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F33">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G33">
         <v>28</v>
       </c>
       <c r="H33">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I33">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C34">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D34">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E34">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F34">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G34">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H34">
         <v>35</v>
       </c>
       <c r="I34">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E35">
+        <v>9</v>
+      </c>
+      <c r="F35">
+        <v>15</v>
+      </c>
+      <c r="G35">
         <v>24</v>
       </c>
-      <c r="F35">
-        <v>31</v>
-      </c>
-      <c r="G35">
-        <v>34</v>
-      </c>
       <c r="H35">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I35">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C36">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D36">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E36">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F36">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G36">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H36">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I36">
         <v>3</v>
@@ -5883,467 +5883,467 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C37">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D37">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E37">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F37">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G37">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H37">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I37">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C38">
         <v>6</v>
       </c>
       <c r="D38">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E38">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F38">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G38">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H38">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I38">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C39">
         <v>6</v>
       </c>
       <c r="D39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E39">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F39">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G39">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H39">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I39">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C40">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D40">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E40">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F40">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G40">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H40">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I40">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C41">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D41">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E41">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F41">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G41">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H41">
         <v>38</v>
       </c>
       <c r="I41">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C42">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D42">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E42">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F42">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G42">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H42">
         <v>38</v>
       </c>
       <c r="I42">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E43">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F43">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G43">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H43">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I43">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C44">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D44">
+        <v>4</v>
+      </c>
+      <c r="E44">
+        <v>13</v>
+      </c>
+      <c r="F44">
+        <v>19</v>
+      </c>
+      <c r="G44">
+        <v>27</v>
+      </c>
+      <c r="H44">
+        <v>30</v>
+      </c>
+      <c r="I44">
         <v>8</v>
-      </c>
-      <c r="E44">
-        <v>27</v>
-      </c>
-      <c r="F44">
-        <v>33</v>
-      </c>
-      <c r="G44">
-        <v>35</v>
-      </c>
-      <c r="H44">
-        <v>38</v>
-      </c>
-      <c r="I44">
-        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C45">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D45">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E45">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F45">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G45">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H45">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I45">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C46">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D46">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E46">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F46">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G46">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H46">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I46">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C47">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D47">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E47">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F47">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G47">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H47">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I47">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000030</v>
+        <v>115000031</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D48">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E48">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F48">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G48">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H48">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="I48">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000029</v>
+        <v>115000030</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D49">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E49">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F49">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G49">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H49">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I49">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000028</v>
+        <v>115000029</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D50">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E50">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F50">
         <v>27</v>
       </c>
       <c r="G50">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H50">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I50">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000027</v>
+        <v>115000028</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C51">
         <v>5</v>
       </c>
       <c r="D51">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E51">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F51">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G51">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H51">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I51">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-09-22 第 115000090 期；威力彩 2026-09-24 第 115000077 期</t>
+          <t>大樂透 2026-09-25 第 115000091 期；威力彩 2026-09-24 第 115000077 期</t>
         </is>
       </c>
     </row>
@@ -47,7 +47,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>115000090</v>
+        <v>115000091</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -56,7 +56,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -96,7 +96,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.239 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.215 碼/期</t>
         </is>
       </c>
     </row>
@@ -214,7 +214,7 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>0.929</v>
+        <v>0.905</v>
       </c>
       <c r="D2">
         <v>28.6</v>
@@ -236,7 +236,7 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>0.905</v>
+        <v>0.881</v>
       </c>
       <c r="D3">
         <v>26.2</v>
@@ -258,7 +258,7 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>0.786</v>
+        <v>0.81</v>
       </c>
       <c r="D4">
         <v>19.0</v>
@@ -280,7 +280,7 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>0.762</v>
+        <v>0.786</v>
       </c>
       <c r="D5">
         <v>19.0</v>
@@ -398,16 +398,16 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>71.7</v>
+        <v>74.48</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
         <v>100.0</v>
@@ -416,7 +416,7 @@
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>7.32</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="3">
@@ -427,7 +427,7 @@
         <v>35</v>
       </c>
       <c r="C3">
-        <v>70.5</v>
+        <v>73.13</v>
       </c>
       <c r="D3">
         <v>10</v>
@@ -436,16 +436,16 @@
         <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>83.33</v>
+        <v>90.91</v>
       </c>
       <c r="H3">
         <v>100.0</v>
       </c>
       <c r="I3">
-        <v>0.0</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="4">
@@ -456,7 +456,7 @@
         <v>26</v>
       </c>
       <c r="C4">
-        <v>67.75</v>
+        <v>70.55</v>
       </c>
       <c r="D4">
         <v>11</v>
@@ -465,16 +465,16 @@
         <v>4</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4">
-        <v>91.67</v>
+        <v>100.0</v>
       </c>
       <c r="H4">
         <v>80.0</v>
       </c>
       <c r="I4">
-        <v>14.63</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="5">
@@ -482,28 +482,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5">
-        <v>65.45</v>
+        <v>67.58</v>
       </c>
       <c r="D5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>75.0</v>
+        <v>72.73</v>
       </c>
       <c r="H5">
         <v>80.0</v>
       </c>
       <c r="I5">
-        <v>0.0</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C6">
-        <v>65.4</v>
+        <v>67.5</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -526,7 +526,7 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>66.67</v>
+        <v>81.82</v>
       </c>
       <c r="H6">
         <v>80.0</v>
@@ -540,28 +540,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7">
-        <v>64.11</v>
+        <v>66.94</v>
       </c>
       <c r="D7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>75.0</v>
+        <v>63.64</v>
       </c>
       <c r="H7">
-        <v>60.0</v>
+        <v>80.0</v>
       </c>
       <c r="I7">
-        <v>24.39</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8">
@@ -572,7 +572,7 @@
         <v>29</v>
       </c>
       <c r="C8">
-        <v>62.75</v>
+        <v>65.55</v>
       </c>
       <c r="D8">
         <v>11</v>
@@ -581,16 +581,16 @@
         <v>3</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G8">
-        <v>91.67</v>
+        <v>100.0</v>
       </c>
       <c r="H8">
         <v>60.0</v>
       </c>
       <c r="I8">
-        <v>14.63</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="9">
@@ -598,28 +598,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C9">
-        <v>62.63</v>
+        <v>63.92</v>
       </c>
       <c r="D9">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>50.0</v>
+        <v>81.82</v>
       </c>
       <c r="H9">
         <v>60.0</v>
       </c>
       <c r="I9">
-        <v>19.51</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="10">
@@ -627,28 +627,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10">
-        <v>61.55</v>
+        <v>63.13</v>
       </c>
       <c r="D10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>75.0</v>
+        <v>90.91</v>
       </c>
       <c r="H10">
         <v>60.0</v>
       </c>
       <c r="I10">
-        <v>7.32</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="11">
@@ -656,28 +656,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11">
-        <v>60.8</v>
+        <v>62.85</v>
       </c>
       <c r="D11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>50.0</v>
+        <v>81.82</v>
       </c>
       <c r="H11">
         <v>60.0</v>
       </c>
       <c r="I11">
-        <v>7.32</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="12">
@@ -685,28 +685,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C12">
-        <v>60.5</v>
+        <v>62.49</v>
       </c>
       <c r="D12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G12">
-        <v>83.33</v>
+        <v>54.55</v>
       </c>
       <c r="H12">
         <v>60.0</v>
       </c>
       <c r="I12">
-        <v>0.0</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="13">
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="C13">
-        <v>60.43</v>
+        <v>62.14</v>
       </c>
       <c r="D13">
         <v>6</v>
@@ -726,16 +726,16 @@
         <v>3</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13">
-        <v>50.0</v>
+        <v>54.55</v>
       </c>
       <c r="H13">
         <v>60.0</v>
       </c>
       <c r="I13">
-        <v>4.88</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="14">
@@ -746,7 +746,7 @@
         <v>21</v>
       </c>
       <c r="C14">
-        <v>60.07</v>
+        <v>61.78</v>
       </c>
       <c r="D14">
         <v>6</v>
@@ -755,16 +755,16 @@
         <v>3</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14">
-        <v>50.0</v>
+        <v>54.55</v>
       </c>
       <c r="H14">
         <v>60.0</v>
       </c>
       <c r="I14">
-        <v>2.44</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="15">
@@ -775,7 +775,7 @@
         <v>8</v>
       </c>
       <c r="C15">
-        <v>58.64</v>
+        <v>60.51</v>
       </c>
       <c r="D15">
         <v>7</v>
@@ -784,16 +784,16 @@
         <v>2</v>
       </c>
       <c r="F15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G15">
-        <v>58.33</v>
+        <v>63.64</v>
       </c>
       <c r="H15">
         <v>40.0</v>
       </c>
       <c r="I15">
-        <v>21.95</v>
+        <v>23.81</v>
       </c>
     </row>
     <row r="16">
@@ -801,13 +801,13 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C16">
-        <v>57.91</v>
+        <v>60.27</v>
       </c>
       <c r="D16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -816,13 +816,13 @@
         <v>7</v>
       </c>
       <c r="G16">
-        <v>58.33</v>
+        <v>90.91</v>
       </c>
       <c r="H16">
         <v>40.0</v>
       </c>
       <c r="I16">
-        <v>17.07</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="17">
@@ -830,10 +830,10 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C17">
-        <v>57.91</v>
+        <v>59.8</v>
       </c>
       <c r="D17">
         <v>7</v>
@@ -842,16 +842,16 @@
         <v>2</v>
       </c>
       <c r="F17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G17">
-        <v>58.33</v>
+        <v>63.64</v>
       </c>
       <c r="H17">
         <v>40.0</v>
       </c>
       <c r="I17">
-        <v>17.07</v>
+        <v>19.05</v>
       </c>
     </row>
     <row r="18">
@@ -859,28 +859,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="C18">
-        <v>57.69</v>
+        <v>58.37</v>
       </c>
       <c r="D18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G18">
-        <v>83.33</v>
+        <v>63.64</v>
       </c>
       <c r="H18">
         <v>40.0</v>
       </c>
       <c r="I18">
-        <v>14.63</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="19">
@@ -888,28 +888,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C19">
-        <v>56.45</v>
+        <v>57.85</v>
       </c>
       <c r="D19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G19">
-        <v>58.33</v>
+        <v>54.55</v>
       </c>
       <c r="H19">
         <v>40.0</v>
       </c>
       <c r="I19">
-        <v>7.32</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="20">
@@ -917,10 +917,10 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>56.45</v>
+        <v>57.66</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -929,16 +929,16 @@
         <v>2</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20">
-        <v>58.33</v>
+        <v>63.64</v>
       </c>
       <c r="H20">
         <v>40.0</v>
       </c>
       <c r="I20">
-        <v>7.32</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="21">
@@ -946,10 +946,10 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C21">
-        <v>56.16</v>
+        <v>57.49</v>
       </c>
       <c r="D21">
         <v>6</v>
@@ -961,13 +961,13 @@
         <v>4</v>
       </c>
       <c r="G21">
-        <v>50.0</v>
+        <v>54.55</v>
       </c>
       <c r="H21">
         <v>40.0</v>
       </c>
       <c r="I21">
-        <v>9.76</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="22">
@@ -975,28 +975,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="C22">
-        <v>56.16</v>
+        <v>56.94</v>
       </c>
       <c r="D22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E22">
         <v>2</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>50.0</v>
+        <v>63.64</v>
       </c>
       <c r="H22">
         <v>40.0</v>
       </c>
       <c r="I22">
-        <v>9.76</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="23">
@@ -1004,28 +1004,28 @@
         <v>22</v>
       </c>
       <c r="B23">
+        <v>34</v>
+      </c>
+      <c r="C23">
+        <v>55.35</v>
+      </c>
+      <c r="D23">
+        <v>6</v>
+      </c>
+      <c r="E23">
         <v>1</v>
       </c>
-      <c r="C23">
-        <v>55.71</v>
-      </c>
-      <c r="D23">
-        <v>7</v>
-      </c>
-      <c r="E23">
-        <v>2</v>
-      </c>
       <c r="F23">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G23">
-        <v>58.33</v>
+        <v>54.55</v>
       </c>
       <c r="H23">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I23">
-        <v>2.44</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="24">
@@ -1033,28 +1033,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C24">
-        <v>55.52</v>
+        <v>54.8</v>
       </c>
       <c r="D24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G24">
-        <v>66.67</v>
+        <v>63.64</v>
       </c>
       <c r="H24">
         <v>20.0</v>
       </c>
       <c r="I24">
-        <v>34.15</v>
+        <v>19.05</v>
       </c>
     </row>
     <row r="25">
@@ -1062,28 +1062,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="C25">
-        <v>53.72</v>
+        <v>54.44</v>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G25">
-        <v>50.0</v>
+        <v>63.64</v>
       </c>
       <c r="H25">
         <v>20.0</v>
       </c>
       <c r="I25">
-        <v>26.83</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="26">
@@ -1091,28 +1091,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C26">
-        <v>52.91</v>
+        <v>53.92</v>
       </c>
       <c r="D26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G26">
-        <v>58.33</v>
+        <v>54.55</v>
       </c>
       <c r="H26">
         <v>20.0</v>
       </c>
       <c r="I26">
-        <v>17.07</v>
+        <v>19.05</v>
       </c>
     </row>
     <row r="27">
@@ -1120,13 +1120,13 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="C27">
-        <v>52.54</v>
+        <v>53.21</v>
       </c>
       <c r="D27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -1135,13 +1135,13 @@
         <v>6</v>
       </c>
       <c r="G27">
-        <v>58.33</v>
+        <v>54.55</v>
       </c>
       <c r="H27">
         <v>20.0</v>
       </c>
       <c r="I27">
-        <v>14.63</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="28">
@@ -1149,10 +1149,10 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C28">
-        <v>51.53</v>
+        <v>52.85</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -1164,13 +1164,13 @@
         <v>5</v>
       </c>
       <c r="G28">
-        <v>50.0</v>
+        <v>54.55</v>
       </c>
       <c r="H28">
         <v>20.0</v>
       </c>
       <c r="I28">
-        <v>12.2</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="29">
@@ -1178,28 +1178,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="C29">
-        <v>51.16</v>
+        <v>52.66</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G29">
-        <v>50.0</v>
+        <v>63.64</v>
       </c>
       <c r="H29">
         <v>20.0</v>
       </c>
       <c r="I29">
-        <v>9.76</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="30">
@@ -1207,28 +1207,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C30">
-        <v>50.71</v>
+        <v>52.58</v>
       </c>
       <c r="D30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G30">
-        <v>58.33</v>
+        <v>72.73</v>
       </c>
       <c r="H30">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I30">
-        <v>2.44</v>
+        <v>35.71</v>
       </c>
     </row>
     <row r="31">
@@ -1236,28 +1236,28 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="C31">
-        <v>50.48</v>
+        <v>52.14</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31">
-        <v>41.67</v>
+        <v>54.55</v>
       </c>
       <c r="H31">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I31">
-        <v>4.88</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="32">
@@ -1265,28 +1265,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="C32">
-        <v>50.43</v>
+        <v>51.96</v>
       </c>
       <c r="D32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G32">
-        <v>50.0</v>
+        <v>45.45</v>
       </c>
       <c r="H32">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I32">
-        <v>4.88</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="33">
@@ -1294,28 +1294,28 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C33">
-        <v>47.68</v>
+        <v>50.88</v>
       </c>
       <c r="D33">
         <v>5</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>41.67</v>
+        <v>45.45</v>
       </c>
       <c r="H33">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I33">
-        <v>19.51</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="34">
@@ -1323,28 +1323,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C34">
-        <v>47.68</v>
+        <v>50.88</v>
       </c>
       <c r="D34">
         <v>5</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G34">
-        <v>41.67</v>
+        <v>45.45</v>
       </c>
       <c r="H34">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I34">
-        <v>19.51</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="35">
@@ -1352,28 +1352,28 @@
         <v>34</v>
       </c>
       <c r="B35">
+        <v>32</v>
+      </c>
+      <c r="C35">
+        <v>49.1</v>
+      </c>
+      <c r="D35">
+        <v>5</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35">
         <v>9</v>
       </c>
-      <c r="C35">
-        <v>47.36</v>
-      </c>
-      <c r="D35">
-        <v>4</v>
-      </c>
-      <c r="E35">
-        <v>2</v>
-      </c>
-      <c r="F35">
-        <v>7</v>
-      </c>
       <c r="G35">
-        <v>33.33</v>
+        <v>45.45</v>
       </c>
       <c r="H35">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I35">
-        <v>17.07</v>
+        <v>21.43</v>
       </c>
     </row>
     <row r="36">
@@ -1381,10 +1381,10 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="C36">
-        <v>46.58</v>
+        <v>49.1</v>
       </c>
       <c r="D36">
         <v>5</v>
@@ -1393,16 +1393,16 @@
         <v>1</v>
       </c>
       <c r="F36">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G36">
-        <v>41.67</v>
+        <v>45.45</v>
       </c>
       <c r="H36">
         <v>20.0</v>
       </c>
       <c r="I36">
-        <v>12.2</v>
+        <v>21.43</v>
       </c>
     </row>
     <row r="37">
@@ -1413,7 +1413,7 @@
         <v>17</v>
       </c>
       <c r="C37">
-        <v>46.58</v>
+        <v>48.03</v>
       </c>
       <c r="D37">
         <v>5</v>
@@ -1422,16 +1422,16 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G37">
-        <v>41.67</v>
+        <v>45.45</v>
       </c>
       <c r="H37">
         <v>20.0</v>
       </c>
       <c r="I37">
-        <v>12.2</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="38">
@@ -1442,7 +1442,7 @@
         <v>11</v>
       </c>
       <c r="C38">
-        <v>45.24</v>
+        <v>46.6</v>
       </c>
       <c r="D38">
         <v>5</v>
@@ -1451,16 +1451,16 @@
         <v>0</v>
       </c>
       <c r="F38">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G38">
-        <v>41.67</v>
+        <v>45.45</v>
       </c>
       <c r="H38">
         <v>0.0</v>
       </c>
       <c r="I38">
-        <v>36.59</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="39">
@@ -1471,7 +1471,7 @@
         <v>7</v>
       </c>
       <c r="C39">
-        <v>44.85</v>
+        <v>45.53</v>
       </c>
       <c r="D39">
         <v>3</v>
@@ -1480,10 +1480,10 @@
         <v>0</v>
       </c>
       <c r="F39">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G39">
-        <v>25.0</v>
+        <v>27.27</v>
       </c>
       <c r="H39">
         <v>0.0</v>
@@ -1497,28 +1497,28 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="C40">
-        <v>44.8</v>
+        <v>45.35</v>
       </c>
       <c r="D40">
         <v>4</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G40">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="H40">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I40">
-        <v>0.0</v>
+        <v>30.95</v>
       </c>
     </row>
     <row r="41">
@@ -1526,10 +1526,10 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="C41">
-        <v>44.19</v>
+        <v>43.57</v>
       </c>
       <c r="D41">
         <v>4</v>
@@ -1538,16 +1538,16 @@
         <v>1</v>
       </c>
       <c r="F41">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G41">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="H41">
         <v>20.0</v>
       </c>
       <c r="I41">
-        <v>29.27</v>
+        <v>19.05</v>
       </c>
     </row>
     <row r="42">
@@ -1555,10 +1555,10 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C42">
-        <v>43.82</v>
+        <v>43.57</v>
       </c>
       <c r="D42">
         <v>4</v>
@@ -1567,16 +1567,16 @@
         <v>1</v>
       </c>
       <c r="F42">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G42">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="H42">
         <v>20.0</v>
       </c>
       <c r="I42">
-        <v>26.83</v>
+        <v>19.05</v>
       </c>
     </row>
     <row r="43">
@@ -1584,10 +1584,10 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="C43">
-        <v>42.36</v>
+        <v>41.78</v>
       </c>
       <c r="D43">
         <v>4</v>
@@ -1596,16 +1596,16 @@
         <v>1</v>
       </c>
       <c r="F43">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G43">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="H43">
         <v>20.0</v>
       </c>
       <c r="I43">
-        <v>17.07</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="44">
@@ -1613,10 +1613,10 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C44">
-        <v>40.53</v>
+        <v>41.06</v>
       </c>
       <c r="D44">
         <v>4</v>
@@ -1625,16 +1625,16 @@
         <v>1</v>
       </c>
       <c r="F44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G44">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="H44">
         <v>20.0</v>
       </c>
       <c r="I44">
-        <v>4.88</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="45">
@@ -1645,7 +1645,7 @@
         <v>45</v>
       </c>
       <c r="C45">
-        <v>39.8</v>
+        <v>41.06</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -1654,16 +1654,16 @@
         <v>1</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="H45">
         <v>20.0</v>
       </c>
       <c r="I45">
-        <v>0.0</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="46">
@@ -1671,28 +1671,28 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="C46">
-        <v>34.66</v>
+        <v>35.35</v>
       </c>
       <c r="D46">
         <v>2</v>
       </c>
       <c r="E46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G46">
-        <v>16.67</v>
+        <v>18.18</v>
       </c>
       <c r="H46">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I46">
-        <v>31.71</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="47">
@@ -1700,10 +1700,10 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="C47">
-        <v>33.93</v>
+        <v>35.35</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -1712,16 +1712,16 @@
         <v>1</v>
       </c>
       <c r="F47">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G47">
-        <v>16.67</v>
+        <v>18.18</v>
       </c>
       <c r="H47">
         <v>20.0</v>
       </c>
       <c r="I47">
-        <v>26.83</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="48">
@@ -1729,28 +1729,28 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C48">
-        <v>33.12</v>
+        <v>33.57</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G48">
-        <v>8.33</v>
+        <v>18.18</v>
       </c>
       <c r="H48">
         <v>0.0</v>
       </c>
       <c r="I48">
-        <v>87.8</v>
+        <v>54.76</v>
       </c>
     </row>
     <row r="49">
@@ -1758,28 +1758,28 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C49">
-        <v>32.95</v>
+        <v>33.39</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49">
         <v>0</v>
       </c>
       <c r="F49">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="G49">
-        <v>16.67</v>
+        <v>9.09</v>
       </c>
       <c r="H49">
         <v>0.0</v>
       </c>
       <c r="I49">
-        <v>53.66</v>
+        <v>88.1</v>
       </c>
     </row>
     <row r="50">
@@ -1790,7 +1790,7 @@
         <v>31</v>
       </c>
       <c r="C50">
-        <v>30.27</v>
+        <v>31.07</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -1799,16 +1799,16 @@
         <v>1</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G50">
-        <v>16.67</v>
+        <v>18.18</v>
       </c>
       <c r="H50">
         <v>20.0</v>
       </c>
       <c r="I50">
-        <v>2.44</v>
+        <v>4.76</v>
       </c>
     </row>
   </sheetData>
@@ -1867,700 +1867,700 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000090</v>
+        <v>115000091</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H2">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000089</v>
+        <v>115000090</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H3">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="I3">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000088</v>
+        <v>115000089</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F4">
         <v>21</v>
       </c>
       <c r="G4">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H4">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000087</v>
+        <v>115000088</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C5">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F5">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H5">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I5">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000086</v>
+        <v>115000087</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D6">
         <v>15</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H6">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I6">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000085</v>
+        <v>115000086</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C7">
         <v>3</v>
       </c>
       <c r="D7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G7">
+        <v>47</v>
+      </c>
+      <c r="H7">
+        <v>49</v>
+      </c>
+      <c r="I7">
         <v>27</v>
-      </c>
-      <c r="H7">
-        <v>37</v>
-      </c>
-      <c r="I7">
-        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000084</v>
+        <v>115000085</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D8">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E8">
+        <v>17</v>
+      </c>
+      <c r="F8">
+        <v>18</v>
+      </c>
+      <c r="G8">
+        <v>27</v>
+      </c>
+      <c r="H8">
+        <v>37</v>
+      </c>
+      <c r="I8">
         <v>19</v>
-      </c>
-      <c r="F8">
-        <v>26</v>
-      </c>
-      <c r="G8">
-        <v>29</v>
-      </c>
-      <c r="H8">
-        <v>48</v>
-      </c>
-      <c r="I8">
-        <v>30</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000083</v>
+        <v>115000084</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E9">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F9">
         <v>26</v>
       </c>
       <c r="G9">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H9">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I9">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C10">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D10">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E10">
+        <v>23</v>
+      </c>
+      <c r="F10">
         <v>26</v>
       </c>
-      <c r="F10">
-        <v>32</v>
-      </c>
       <c r="G10">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H10">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I10">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C11">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D11">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E11">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F11">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G11">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H11">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I11">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D12">
         <v>14</v>
       </c>
       <c r="E12">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F12">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G12">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H12">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I12">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E13">
         <v>25</v>
       </c>
       <c r="F13">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G13">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H13">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I13">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>12</v>
       </c>
       <c r="E14">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F14">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G14">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H14">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="I14">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D15">
         <v>12</v>
       </c>
       <c r="E15">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F15">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G15">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H15">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I15">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E16">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F16">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G16">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H16">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I16">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C17">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D17">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E17">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F17">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G17">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H17">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I17">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C18">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D18">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E18">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F18">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G18">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H18">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I18">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D19">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E19">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F19">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G19">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H19">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I19">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E20">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F20">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G20">
         <v>35</v>
       </c>
       <c r="H20">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I20">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E21">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F21">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G21">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H21">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I21">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C22">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E22">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F22">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G22">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H22">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I22">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C23">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E23">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F23">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G23">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H23">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I23">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C24">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D24">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E24">
         <v>15</v>
@@ -2569,345 +2569,345 @@
         <v>18</v>
       </c>
       <c r="G24">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H24">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I24">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C25">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D25">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E25">
+        <v>15</v>
+      </c>
+      <c r="F25">
+        <v>18</v>
+      </c>
+      <c r="G25">
         <v>19</v>
       </c>
-      <c r="F25">
-        <v>23</v>
-      </c>
-      <c r="G25">
-        <v>39</v>
-      </c>
       <c r="H25">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I25">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C26">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D26">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E26">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F26">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G26">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H26">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I26">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C27">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D27">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E27">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F27">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G27">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H27">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C28">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D28">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E28">
+        <v>23</v>
+      </c>
+      <c r="F28">
+        <v>24</v>
+      </c>
+      <c r="G28">
         <v>29</v>
       </c>
-      <c r="F28">
-        <v>33</v>
-      </c>
-      <c r="G28">
-        <v>34</v>
-      </c>
       <c r="H28">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I28">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C29">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D29">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E29">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F29">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G29">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H29">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I29">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E30">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F30">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G30">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H30">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I30">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C31">
         <v>1</v>
       </c>
       <c r="D31">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E31">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F31">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G31">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H31">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I31">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C32">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D32">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E32">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F32">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G32">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H32">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I32">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C33">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D33">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E33">
         <v>25</v>
       </c>
       <c r="F33">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G33">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H33">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I33">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C34">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D34">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E34">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F34">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G34">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H34">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I34">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C35">
+        <v>8</v>
+      </c>
+      <c r="D35">
+        <v>9</v>
+      </c>
+      <c r="E35">
+        <v>16</v>
+      </c>
+      <c r="F35">
         <v>20</v>
-      </c>
-      <c r="D35">
-        <v>26</v>
-      </c>
-      <c r="E35">
-        <v>29</v>
-      </c>
-      <c r="F35">
-        <v>31</v>
       </c>
       <c r="G35">
         <v>37</v>
@@ -2916,503 +2916,503 @@
         <v>49</v>
       </c>
       <c r="I35">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C36">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D36">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E36">
         <v>29</v>
       </c>
       <c r="F36">
+        <v>31</v>
+      </c>
+      <c r="G36">
         <v>37</v>
       </c>
-      <c r="G36">
-        <v>47</v>
-      </c>
       <c r="H36">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I36">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C37">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D37">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E37">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F37">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G37">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="H37">
         <v>48</v>
       </c>
       <c r="I37">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D38">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E38">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F38">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G38">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H38">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I38">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C39">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D39">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E39">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F39">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G39">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H39">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I39">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C40">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D40">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E40">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F40">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G40">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H40">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I40">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C41">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D41">
+        <v>12</v>
+      </c>
+      <c r="E41">
         <v>18</v>
       </c>
-      <c r="E41">
-        <v>25</v>
-      </c>
       <c r="F41">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G41">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H41">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I41">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C42">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D42">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E42">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F42">
         <v>28</v>
       </c>
       <c r="G42">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H42">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I42">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C43">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D43">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E43">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F43">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G43">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H43">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I43">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C44">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D44">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E44">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F44">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G44">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H44">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I44">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C45">
+        <v>6</v>
+      </c>
+      <c r="D45">
+        <v>10</v>
+      </c>
+      <c r="E45">
+        <v>14</v>
+      </c>
+      <c r="F45">
+        <v>25</v>
+      </c>
+      <c r="G45">
+        <v>26</v>
+      </c>
+      <c r="H45">
+        <v>32</v>
+      </c>
+      <c r="I45">
         <v>7</v>
-      </c>
-      <c r="D45">
-        <v>14</v>
-      </c>
-      <c r="E45">
-        <v>16</v>
-      </c>
-      <c r="F45">
-        <v>37</v>
-      </c>
-      <c r="G45">
-        <v>39</v>
-      </c>
-      <c r="H45">
-        <v>47</v>
-      </c>
-      <c r="I45">
-        <v>34</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D46">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E46">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F46">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G46">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H46">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I46">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C47">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D47">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E47">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F47">
+        <v>19</v>
+      </c>
+      <c r="G47">
+        <v>20</v>
+      </c>
+      <c r="H47">
+        <v>40</v>
+      </c>
+      <c r="I47">
         <v>22</v>
-      </c>
-      <c r="G47">
-        <v>40</v>
-      </c>
-      <c r="H47">
-        <v>45</v>
-      </c>
-      <c r="I47">
-        <v>18</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C48">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D48">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E48">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F48">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G48">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H48">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I48">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C49">
         <v>4</v>
       </c>
       <c r="D49">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E49">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F49">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G49">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H49">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I49">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E50">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F50">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G50">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H50">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I50">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C51">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D51">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E51">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F51">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G51">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H51">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I51">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-09-25 第 115000091 期；威力彩 2026-09-24 第 115000077 期</t>
+          <t>大樂透 2026-09-25 第 115000091 期；威力彩 2026-09-28 第 115000078 期</t>
         </is>
       </c>
     </row>
@@ -112,7 +112,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -121,7 +121,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -143,7 +143,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8, 19, 24, 29, 35, 38</t>
+          <t>8, 9, 19, 24, 29, 35</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -161,7 +161,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.31 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.286 碼/期</t>
         </is>
       </c>
     </row>
@@ -3464,10 +3464,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>1.048</v>
+        <v>1.024</v>
       </c>
       <c r="D2">
-        <v>33.3</v>
+        <v>31.0</v>
       </c>
       <c r="E2">
         <v>4.8</v>
@@ -3486,10 +3486,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>1.048</v>
+        <v>1.024</v>
       </c>
       <c r="D3">
-        <v>33.3</v>
+        <v>31.0</v>
       </c>
       <c r="E3">
         <v>4.8</v>
@@ -3508,10 +3508,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>0.952</v>
+        <v>0.929</v>
       </c>
       <c r="D4">
-        <v>21.4</v>
+        <v>19.0</v>
       </c>
       <c r="E4">
         <v>4.8</v>
@@ -3530,10 +3530,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>0.952</v>
+        <v>0.929</v>
       </c>
       <c r="D5">
-        <v>28.6</v>
+        <v>26.2</v>
       </c>
       <c r="E5">
         <v>2.4</v>
@@ -3552,10 +3552,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.881</v>
+        <v>0.857</v>
       </c>
       <c r="D6">
-        <v>19.0</v>
+        <v>16.7</v>
       </c>
       <c r="E6">
         <v>4.8</v>
@@ -3648,25 +3648,25 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>76.6</v>
+        <v>75.74</v>
       </c>
       <c r="D2">
         <v>10</v>
       </c>
       <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
         <v>6</v>
       </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
       <c r="G2">
-        <v>71.43</v>
+        <v>66.67</v>
       </c>
       <c r="H2">
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
     </row>
     <row r="3">
@@ -3677,7 +3677,7 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>70.52</v>
+        <v>73.01</v>
       </c>
       <c r="D3">
         <v>9</v>
@@ -3686,16 +3686,16 @@
         <v>4</v>
       </c>
       <c r="F3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>64.29</v>
+        <v>60.0</v>
       </c>
       <c r="H3">
-        <v>66.67</v>
+        <v>80.0</v>
       </c>
       <c r="I3">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
     </row>
     <row r="4">
@@ -3706,7 +3706,7 @@
         <v>19</v>
       </c>
       <c r="C4">
-        <v>69.58</v>
+        <v>71.73</v>
       </c>
       <c r="D4">
         <v>12</v>
@@ -3715,16 +3715,16 @@
         <v>4</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4">
-        <v>85.71</v>
+        <v>80.0</v>
       </c>
       <c r="H4">
-        <v>66.67</v>
+        <v>80.0</v>
       </c>
       <c r="I4">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
     </row>
     <row r="5">
@@ -3732,13 +3732,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C5">
-        <v>68.75</v>
+        <v>71.5</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -3747,10 +3747,10 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>85.71</v>
+        <v>100.0</v>
       </c>
       <c r="H5">
-        <v>83.33</v>
+        <v>100.0</v>
       </c>
       <c r="I5">
         <v>0.0</v>
@@ -3761,28 +3761,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>67.57</v>
+        <v>68.2</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>100.0</v>
+        <v>73.33</v>
       </c>
       <c r="H6">
-        <v>66.67</v>
+        <v>60.0</v>
       </c>
       <c r="I6">
-        <v>16.67</v>
+        <v>47.37</v>
       </c>
     </row>
     <row r="7">
@@ -3790,28 +3790,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>66.84</v>
+        <v>66.89</v>
       </c>
       <c r="D7">
         <v>11</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>78.57</v>
+        <v>73.33</v>
       </c>
       <c r="H7">
-        <v>50.0</v>
+        <v>80.0</v>
       </c>
       <c r="I7">
-        <v>44.44</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="8">
@@ -3819,28 +3819,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="C8">
-        <v>64.83</v>
+        <v>66.0</v>
       </c>
       <c r="D8">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>92.86</v>
+        <v>66.67</v>
       </c>
       <c r="H8">
-        <v>50.0</v>
+        <v>80.0</v>
       </c>
       <c r="I8">
-        <v>27.78</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="9">
@@ -3848,28 +3848,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C9">
-        <v>63.02</v>
+        <v>65.94</v>
       </c>
       <c r="D9">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G9">
-        <v>64.29</v>
+        <v>80.0</v>
       </c>
       <c r="H9">
-        <v>50.0</v>
+        <v>60.0</v>
       </c>
       <c r="I9">
-        <v>22.22</v>
+        <v>31.58</v>
       </c>
     </row>
     <row r="10">
@@ -3880,7 +3880,7 @@
         <v>36</v>
       </c>
       <c r="C10">
-        <v>62.47</v>
+        <v>65.46</v>
       </c>
       <c r="D10">
         <v>7</v>
@@ -3889,16 +3889,16 @@
         <v>4</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>50.0</v>
+        <v>46.67</v>
       </c>
       <c r="H10">
-        <v>66.67</v>
+        <v>80.0</v>
       </c>
       <c r="I10">
-        <v>16.67</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="11">
@@ -3906,28 +3906,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C11">
-        <v>61.11</v>
+        <v>61.79</v>
       </c>
       <c r="D11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>57.14</v>
+        <v>66.67</v>
       </c>
       <c r="H11">
-        <v>33.33</v>
+        <v>60.0</v>
       </c>
       <c r="I11">
-        <v>38.89</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="12">
@@ -3935,28 +3935,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C12">
-        <v>60.52</v>
+        <v>61.59</v>
       </c>
       <c r="D12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>64.29</v>
+        <v>53.33</v>
       </c>
       <c r="H12">
-        <v>33.33</v>
+        <v>60.0</v>
       </c>
       <c r="I12">
-        <v>33.33</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="13">
@@ -3964,28 +3964,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C13">
-        <v>60.52</v>
+        <v>61.43</v>
       </c>
       <c r="D13">
         <v>9</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G13">
-        <v>64.29</v>
+        <v>60.0</v>
       </c>
       <c r="H13">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="I13">
-        <v>5.56</v>
+        <v>36.84</v>
       </c>
     </row>
     <row r="14">
@@ -3993,13 +3993,13 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="C14">
-        <v>59.93</v>
+        <v>60.9</v>
       </c>
       <c r="D14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -4008,10 +4008,10 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>71.43</v>
+        <v>60.0</v>
       </c>
       <c r="H14">
-        <v>50.0</v>
+        <v>60.0</v>
       </c>
       <c r="I14">
         <v>0.0</v>
@@ -4025,25 +4025,25 @@
         <v>38</v>
       </c>
       <c r="C15">
-        <v>59.58</v>
+        <v>60.05</v>
       </c>
       <c r="D15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E15">
         <v>2</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G15">
-        <v>85.71</v>
+        <v>73.33</v>
       </c>
       <c r="H15">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I15">
-        <v>22.22</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="16">
@@ -4051,28 +4051,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C16">
-        <v>59.44</v>
+        <v>59.85</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G16">
-        <v>57.14</v>
+        <v>60.0</v>
       </c>
       <c r="H16">
-        <v>0.0</v>
+        <v>40.0</v>
       </c>
       <c r="I16">
-        <v>83.33</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="17">
@@ -4080,28 +4080,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C17">
-        <v>59.44</v>
+        <v>58.96</v>
       </c>
       <c r="D17">
         <v>8</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G17">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="H17">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="I17">
-        <v>0.0</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="18">
@@ -4109,28 +4109,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C18">
-        <v>58.42</v>
+        <v>58.43</v>
       </c>
       <c r="D18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G18">
-        <v>42.86</v>
+        <v>53.33</v>
       </c>
       <c r="H18">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
       <c r="I18">
-        <v>44.44</v>
+        <v>84.21</v>
       </c>
     </row>
     <row r="19">
@@ -4138,28 +4138,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
       <c r="D19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19">
+        <v>4</v>
+      </c>
+      <c r="F19">
         <v>0</v>
       </c>
-      <c r="F19">
-        <v>18</v>
-      </c>
       <c r="G19">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="H19">
+        <v>80.0</v>
+      </c>
+      <c r="I19">
         <v>0.0</v>
-      </c>
-      <c r="I19">
-        <v>100.0</v>
       </c>
     </row>
     <row r="20">
@@ -4167,10 +4167,10 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C20">
-        <v>57.77</v>
+        <v>58.17</v>
       </c>
       <c r="D20">
         <v>8</v>
@@ -4182,13 +4182,13 @@
         <v>3</v>
       </c>
       <c r="G20">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="H20">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I20">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="21">
@@ -4196,28 +4196,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C21">
-        <v>57.08</v>
+        <v>58.17</v>
       </c>
       <c r="D21">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E21">
         <v>2</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21">
-        <v>85.71</v>
+        <v>53.33</v>
       </c>
       <c r="H21">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I21">
-        <v>5.56</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="22">
@@ -4225,13 +4225,13 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C22">
-        <v>56.94</v>
+        <v>57.78</v>
       </c>
       <c r="D22">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E22">
         <v>2</v>
@@ -4240,13 +4240,13 @@
         <v>2</v>
       </c>
       <c r="G22">
-        <v>57.14</v>
+        <v>80.0</v>
       </c>
       <c r="H22">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I22">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="23">
@@ -4254,28 +4254,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="C23">
-        <v>56.94</v>
+        <v>57.3</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>57.14</v>
+        <v>46.67</v>
       </c>
       <c r="H23">
-        <v>33.33</v>
+        <v>60.0</v>
       </c>
       <c r="I23">
-        <v>11.11</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="24">
@@ -4283,10 +4283,10 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C24">
-        <v>56.63</v>
+        <v>57.3</v>
       </c>
       <c r="D24">
         <v>7</v>
@@ -4295,16 +4295,16 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G24">
-        <v>50.0</v>
+        <v>46.67</v>
       </c>
       <c r="H24">
         <v>0.0</v>
       </c>
       <c r="I24">
-        <v>88.89</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="25">
@@ -4312,10 +4312,10 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C25">
-        <v>55.8</v>
+        <v>55.72</v>
       </c>
       <c r="D25">
         <v>7</v>
@@ -4324,16 +4324,16 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G25">
-        <v>50.0</v>
+        <v>46.67</v>
       </c>
       <c r="H25">
         <v>0.0</v>
       </c>
       <c r="I25">
-        <v>83.33</v>
+        <v>89.47</v>
       </c>
     </row>
     <row r="26">
@@ -4344,25 +4344,25 @@
         <v>22</v>
       </c>
       <c r="C26">
-        <v>55.52</v>
+        <v>55.54</v>
       </c>
       <c r="D26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G26">
-        <v>64.29</v>
+        <v>53.33</v>
       </c>
       <c r="H26">
-        <v>16.67</v>
+        <v>20.0</v>
       </c>
       <c r="I26">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
     </row>
     <row r="27">
@@ -4373,7 +4373,7 @@
         <v>10</v>
       </c>
       <c r="C27">
-        <v>54.13</v>
+        <v>55.46</v>
       </c>
       <c r="D27">
         <v>7</v>
@@ -4382,16 +4382,16 @@
         <v>2</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27">
-        <v>50.0</v>
+        <v>46.67</v>
       </c>
       <c r="H27">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I27">
-        <v>16.67</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="28">
@@ -4399,10 +4399,10 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="C28">
-        <v>53.42</v>
+        <v>54.19</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -4411,16 +4411,16 @@
         <v>3</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28">
-        <v>42.86</v>
+        <v>40.0</v>
       </c>
       <c r="H28">
-        <v>50.0</v>
+        <v>60.0</v>
       </c>
       <c r="I28">
-        <v>11.11</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="29">
@@ -4428,28 +4428,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C29">
-        <v>52.71</v>
+        <v>54.19</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E29">
         <v>3</v>
       </c>
       <c r="F29">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G29">
-        <v>35.71</v>
+        <v>40.0</v>
       </c>
       <c r="H29">
-        <v>50.0</v>
+        <v>60.0</v>
       </c>
       <c r="I29">
-        <v>33.33</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="30">
@@ -4457,28 +4457,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="C30">
-        <v>51.76</v>
+        <v>51.08</v>
       </c>
       <c r="D30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30">
         <v>3</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30">
-        <v>42.86</v>
+        <v>33.33</v>
       </c>
       <c r="H30">
-        <v>50.0</v>
+        <v>60.0</v>
       </c>
       <c r="I30">
-        <v>0.0</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="31">
@@ -4486,25 +4486,25 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C31">
-        <v>51.76</v>
+        <v>50.8</v>
       </c>
       <c r="D31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
       <c r="G31">
-        <v>42.86</v>
+        <v>53.33</v>
       </c>
       <c r="H31">
-        <v>50.0</v>
+        <v>20.0</v>
       </c>
       <c r="I31">
         <v>0.0</v>
@@ -4515,28 +4515,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C32">
-        <v>51.63</v>
+        <v>50.77</v>
       </c>
       <c r="D32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E32">
         <v>2</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G32">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="H32">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I32">
-        <v>0.0</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="33">
@@ -4544,28 +4544,28 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C33">
-        <v>48.55</v>
+        <v>49.19</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
       <c r="G33">
-        <v>35.71</v>
+        <v>40.0</v>
       </c>
       <c r="H33">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="I33">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="34">
@@ -4576,7 +4576,7 @@
         <v>12</v>
       </c>
       <c r="C34">
-        <v>46.05</v>
+        <v>47.66</v>
       </c>
       <c r="D34">
         <v>5</v>
@@ -4585,16 +4585,16 @@
         <v>2</v>
       </c>
       <c r="F34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G34">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="H34">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I34">
-        <v>16.67</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="35">
@@ -4602,28 +4602,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C35">
-        <v>44.51</v>
+        <v>44.55</v>
       </c>
       <c r="D35">
         <v>4</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G35">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="H35">
-        <v>16.67</v>
+        <v>40.0</v>
       </c>
       <c r="I35">
-        <v>61.11</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="36">
@@ -4631,28 +4631,28 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C36">
-        <v>42.96</v>
+        <v>42.66</v>
       </c>
       <c r="D36">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E36">
         <v>1</v>
       </c>
       <c r="F36">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G36">
-        <v>21.43</v>
+        <v>33.33</v>
       </c>
       <c r="H36">
-        <v>16.67</v>
+        <v>20.0</v>
       </c>
       <c r="I36">
-        <v>77.78</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="37">
@@ -4660,28 +4660,28 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C37">
-        <v>42.84</v>
+        <v>41.92</v>
       </c>
       <c r="D37">
         <v>4</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G37">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="H37">
-        <v>33.33</v>
+        <v>20.0</v>
       </c>
       <c r="I37">
-        <v>22.22</v>
+        <v>42.11</v>
       </c>
     </row>
     <row r="38">
@@ -4689,28 +4689,28 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C38">
-        <v>41.88</v>
+        <v>41.17</v>
       </c>
       <c r="D38">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
       <c r="F38">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G38">
-        <v>35.71</v>
+        <v>20.0</v>
       </c>
       <c r="H38">
-        <v>16.67</v>
+        <v>20.0</v>
       </c>
       <c r="I38">
-        <v>16.67</v>
+        <v>63.16</v>
       </c>
     </row>
     <row r="39">
@@ -4718,28 +4718,28 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C39">
-        <v>41.17</v>
+        <v>38.54</v>
       </c>
       <c r="D39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G39">
-        <v>28.57</v>
+        <v>20.0</v>
       </c>
       <c r="H39">
-        <v>16.67</v>
+        <v>0.0</v>
       </c>
       <c r="I39">
-        <v>38.89</v>
+        <v>78.95</v>
       </c>
     </row>
   </sheetData>
@@ -4798,30 +4798,30 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -4829,11 +4829,11 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C3">
@@ -4843,140 +4843,140 @@
         <v>8</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H3">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C4">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E4">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H4">
         <v>37</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F5">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>16</v>
+      </c>
+      <c r="G6">
+        <v>29</v>
+      </c>
+      <c r="H6">
+        <v>36</v>
+      </c>
+      <c r="I6">
         <v>8</v>
-      </c>
-      <c r="D6">
-        <v>17</v>
-      </c>
-      <c r="E6">
-        <v>18</v>
-      </c>
-      <c r="F6">
-        <v>29</v>
-      </c>
-      <c r="G6">
-        <v>33</v>
-      </c>
-      <c r="H6">
-        <v>38</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H7">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I7">
         <v>2</v>
@@ -4984,108 +4984,108 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E8">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F8">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G8">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H8">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I8">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F9">
         <v>19</v>
       </c>
       <c r="G9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H9">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10">
+        <v>8</v>
+      </c>
+      <c r="E10">
+        <v>12</v>
+      </c>
+      <c r="F10">
+        <v>19</v>
+      </c>
+      <c r="G10">
+        <v>32</v>
+      </c>
+      <c r="H10">
+        <v>37</v>
+      </c>
+      <c r="I10">
         <v>2</v>
-      </c>
-      <c r="D10">
-        <v>7</v>
-      </c>
-      <c r="E10">
-        <v>9</v>
-      </c>
-      <c r="F10">
-        <v>11</v>
-      </c>
-      <c r="G10">
-        <v>24</v>
-      </c>
-      <c r="H10">
-        <v>36</v>
-      </c>
-      <c r="I10">
-        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C11">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D11">
         <v>7</v>
@@ -5094,230 +5094,230 @@
         <v>9</v>
       </c>
       <c r="F11">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G11">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H11">
         <v>36</v>
       </c>
       <c r="I11">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E12">
         <v>9</v>
       </c>
       <c r="F12">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G12">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H12">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I12">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>9</v>
+      </c>
+      <c r="F13">
         <v>11</v>
       </c>
-      <c r="E13">
-        <v>18</v>
-      </c>
-      <c r="F13">
-        <v>19</v>
-      </c>
       <c r="G13">
+        <v>29</v>
+      </c>
+      <c r="H13">
         <v>35</v>
       </c>
-      <c r="H13">
-        <v>38</v>
-      </c>
       <c r="I13">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F14">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G14">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H14">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="I14">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C15">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E15">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F15">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G15">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H15">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I15">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D16">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E16">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F16">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G16">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H16">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I16">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>7</v>
+      </c>
+      <c r="E17">
+        <v>8</v>
+      </c>
+      <c r="F17">
+        <v>20</v>
+      </c>
+      <c r="G17">
+        <v>26</v>
+      </c>
+      <c r="H17">
+        <v>33</v>
+      </c>
+      <c r="I17">
         <v>4</v>
-      </c>
-      <c r="D17">
-        <v>15</v>
-      </c>
-      <c r="E17">
-        <v>22</v>
-      </c>
-      <c r="F17">
-        <v>26</v>
-      </c>
-      <c r="G17">
-        <v>34</v>
-      </c>
-      <c r="H17">
-        <v>36</v>
-      </c>
-      <c r="I17">
-        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C18">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E18">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F18">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G18">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H18">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I18">
         <v>7</v>
@@ -5325,30 +5325,30 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C19">
+        <v>8</v>
+      </c>
+      <c r="D19">
+        <v>14</v>
+      </c>
+      <c r="E19">
+        <v>17</v>
+      </c>
+      <c r="F19">
         <v>19</v>
       </c>
-      <c r="D19">
-        <v>22</v>
-      </c>
-      <c r="E19">
-        <v>28</v>
-      </c>
-      <c r="F19">
-        <v>31</v>
-      </c>
       <c r="G19">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H19">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I19">
         <v>7</v>
@@ -5356,30 +5356,30 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C20">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D20">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E20">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F20">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G20">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H20">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I20">
         <v>7</v>
@@ -5387,24 +5387,24 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D21">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E21">
         <v>13</v>
       </c>
       <c r="F21">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G21">
         <v>29</v>
@@ -5413,97 +5413,97 @@
         <v>31</v>
       </c>
       <c r="I21">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C22">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D22">
+        <v>12</v>
+      </c>
+      <c r="E22">
+        <v>13</v>
+      </c>
+      <c r="F22">
         <v>23</v>
       </c>
-      <c r="E22">
-        <v>25</v>
-      </c>
-      <c r="F22">
+      <c r="G22">
         <v>29</v>
       </c>
-      <c r="G22">
-        <v>34</v>
-      </c>
       <c r="H22">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I22">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C23">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D23">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E23">
+        <v>25</v>
+      </c>
+      <c r="F23">
         <v>29</v>
       </c>
-      <c r="F23">
-        <v>32</v>
-      </c>
       <c r="G23">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H23">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I23">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D24">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E24">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F24">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G24">
         <v>35</v>
       </c>
       <c r="H24">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I24">
         <v>6</v>
@@ -5511,402 +5511,402 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D25">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E25">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F25">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G25">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H25">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D26">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E26">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F26">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G26">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H26">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I26">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C27">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E27">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F27">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G27">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H27">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I27">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C28">
+        <v>5</v>
+      </c>
+      <c r="D28">
         <v>6</v>
       </c>
-      <c r="D28">
-        <v>10</v>
-      </c>
       <c r="E28">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F28">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G28">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H28">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C29">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D29">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E29">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F29">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G29">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H29">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I29">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C30">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D30">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E30">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F30">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G30">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H30">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I30">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="D31">
+        <v>8</v>
+      </c>
+      <c r="E31">
+        <v>9</v>
+      </c>
+      <c r="F31">
+        <v>15</v>
+      </c>
+      <c r="G31">
+        <v>18</v>
+      </c>
+      <c r="H31">
+        <v>23</v>
+      </c>
+      <c r="I31">
         <v>4</v>
-      </c>
-      <c r="D31">
-        <v>17</v>
-      </c>
-      <c r="E31">
-        <v>19</v>
-      </c>
-      <c r="F31">
-        <v>25</v>
-      </c>
-      <c r="G31">
-        <v>28</v>
-      </c>
-      <c r="H31">
-        <v>29</v>
-      </c>
-      <c r="I31">
-        <v>6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D32">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E32">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F32">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G32">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H32">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I32">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D33">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E33">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F33">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G33">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H33">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I33">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C34">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D34">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E34">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F34">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G34">
         <v>28</v>
       </c>
       <c r="H34">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I34">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C35">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D35">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E35">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F35">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G35">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H35">
         <v>35</v>
       </c>
       <c r="I35">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E36">
+        <v>9</v>
+      </c>
+      <c r="F36">
+        <v>15</v>
+      </c>
+      <c r="G36">
         <v>24</v>
       </c>
-      <c r="F36">
-        <v>31</v>
-      </c>
-      <c r="G36">
-        <v>34</v>
-      </c>
       <c r="H36">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I36">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C37">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D37">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E37">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F37">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G37">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H37">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I37">
         <v>3</v>
@@ -5914,436 +5914,436 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C38">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D38">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E38">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F38">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G38">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H38">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I38">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C39">
         <v>6</v>
       </c>
       <c r="D39">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E39">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F39">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G39">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H39">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I39">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C40">
         <v>6</v>
       </c>
       <c r="D40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E40">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F40">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G40">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H40">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I40">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C41">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D41">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E41">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F41">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G41">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H41">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I41">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C42">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D42">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E42">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F42">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G42">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H42">
         <v>38</v>
       </c>
       <c r="I42">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C43">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D43">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E43">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F43">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G43">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H43">
         <v>38</v>
       </c>
       <c r="I43">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D44">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E44">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F44">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G44">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H44">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I44">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C45">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D45">
+        <v>4</v>
+      </c>
+      <c r="E45">
+        <v>13</v>
+      </c>
+      <c r="F45">
+        <v>19</v>
+      </c>
+      <c r="G45">
+        <v>27</v>
+      </c>
+      <c r="H45">
+        <v>30</v>
+      </c>
+      <c r="I45">
         <v>8</v>
-      </c>
-      <c r="E45">
-        <v>27</v>
-      </c>
-      <c r="F45">
-        <v>33</v>
-      </c>
-      <c r="G45">
-        <v>35</v>
-      </c>
-      <c r="H45">
-        <v>38</v>
-      </c>
-      <c r="I45">
-        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C46">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D46">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E46">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F46">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G46">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H46">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I46">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C47">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D47">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E47">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F47">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G47">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H47">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I47">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C48">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D48">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E48">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F48">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G48">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H48">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I48">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000030</v>
+        <v>115000031</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D49">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E49">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F49">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G49">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H49">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="I49">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000029</v>
+        <v>115000030</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D50">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E50">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F50">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G50">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H50">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I50">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000028</v>
+        <v>115000029</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D51">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E51">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F51">
         <v>27</v>
       </c>
       <c r="G51">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H51">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I51">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-09-25 第 115000091 期；威力彩 2026-09-28 第 115000078 期</t>
+          <t>大樂透 2026-09-29 第 115000092 期；威力彩 2026-09-28 第 115000078 期</t>
         </is>
       </c>
     </row>
@@ -47,7 +47,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>115000091</v>
+        <v>115000092</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -56,7 +56,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -78,7 +78,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12, 16, 18, 26, 29, 35</t>
+          <t>4, 12, 15, 26, 29, 35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -96,7 +96,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.215 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.238 碼/期</t>
         </is>
       </c>
     </row>
@@ -295,17 +295,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>隨機基準</t>
+          <t>冷號觀察</t>
         </is>
       </c>
       <c r="B6">
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.69</v>
+        <v>0.714</v>
       </c>
       <c r="D6">
-        <v>11.9</v>
+        <v>16.7</v>
       </c>
       <c r="E6">
         <v>0.0</v>
@@ -317,17 +317,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>冷號觀察</t>
+          <t>隨機基準</t>
         </is>
       </c>
       <c r="B7">
         <v>42</v>
       </c>
       <c r="C7">
-        <v>0.69</v>
+        <v>0.667</v>
       </c>
       <c r="D7">
-        <v>14.3</v>
+        <v>11.9</v>
       </c>
       <c r="E7">
         <v>0.0</v>
@@ -395,28 +395,28 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C2">
-        <v>74.48</v>
+        <v>73.47</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>100.0</v>
+        <v>90.91</v>
       </c>
       <c r="H2">
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>9.52</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="3">
@@ -424,28 +424,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C3">
-        <v>73.13</v>
+        <v>70.56</v>
       </c>
       <c r="D3">
         <v>10</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G3">
         <v>90.91</v>
       </c>
       <c r="H3">
-        <v>100.0</v>
+        <v>80.0</v>
       </c>
       <c r="I3">
-        <v>2.38</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="4">
@@ -453,10 +453,10 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C4">
-        <v>70.55</v>
+        <v>69.79</v>
       </c>
       <c r="D4">
         <v>11</v>
@@ -465,7 +465,7 @@
         <v>4</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G4">
         <v>100.0</v>
@@ -474,7 +474,7 @@
         <v>80.0</v>
       </c>
       <c r="I4">
-        <v>16.67</v>
+        <v>11.63</v>
       </c>
     </row>
     <row r="5">
@@ -485,7 +485,7 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>67.58</v>
+        <v>67.92</v>
       </c>
       <c r="D5">
         <v>8</v>
@@ -494,7 +494,7 @@
         <v>4</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5">
         <v>72.73</v>
@@ -503,7 +503,7 @@
         <v>80.0</v>
       </c>
       <c r="I5">
-        <v>2.38</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="6">
@@ -511,28 +511,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6">
-        <v>67.5</v>
+        <v>67.29</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E6">
         <v>4</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>81.82</v>
+        <v>63.64</v>
       </c>
       <c r="H6">
         <v>80.0</v>
       </c>
       <c r="I6">
-        <v>0.0</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="7">
@@ -540,28 +540,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C7">
-        <v>66.94</v>
+        <v>65.84</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G7">
-        <v>63.64</v>
+        <v>100.0</v>
       </c>
       <c r="H7">
-        <v>80.0</v>
+        <v>60.0</v>
       </c>
       <c r="I7">
-        <v>0.0</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="8">
@@ -569,28 +569,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>65.55</v>
+        <v>63.19</v>
       </c>
       <c r="D8">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>100.0</v>
+        <v>81.82</v>
       </c>
       <c r="H8">
         <v>60.0</v>
       </c>
       <c r="I8">
-        <v>16.67</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="9">
@@ -598,10 +598,10 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9">
-        <v>63.92</v>
+        <v>63.19</v>
       </c>
       <c r="D9">
         <v>9</v>
@@ -610,7 +610,7 @@
         <v>3</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G9">
         <v>81.82</v>
@@ -619,7 +619,7 @@
         <v>60.0</v>
       </c>
       <c r="I9">
-        <v>9.52</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="10">
@@ -627,13 +627,13 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C10">
-        <v>63.13</v>
+        <v>62.85</v>
       </c>
       <c r="D10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -642,13 +642,13 @@
         <v>1</v>
       </c>
       <c r="G10">
-        <v>90.91</v>
+        <v>81.82</v>
       </c>
       <c r="H10">
         <v>60.0</v>
       </c>
       <c r="I10">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="11">
@@ -656,28 +656,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C11">
-        <v>62.85</v>
+        <v>62.81</v>
       </c>
       <c r="D11">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G11">
-        <v>81.82</v>
+        <v>54.55</v>
       </c>
       <c r="H11">
         <v>60.0</v>
       </c>
       <c r="I11">
-        <v>2.38</v>
+        <v>11.63</v>
       </c>
     </row>
     <row r="12">
@@ -685,10 +685,10 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="C12">
-        <v>62.49</v>
+        <v>62.46</v>
       </c>
       <c r="D12">
         <v>6</v>
@@ -706,7 +706,7 @@
         <v>60.0</v>
       </c>
       <c r="I12">
-        <v>9.52</v>
+        <v>9.3</v>
       </c>
     </row>
     <row r="13">
@@ -714,28 +714,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C13">
-        <v>62.14</v>
+        <v>61.94</v>
       </c>
       <c r="D13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>54.55</v>
+        <v>63.64</v>
       </c>
       <c r="H13">
         <v>60.0</v>
       </c>
       <c r="I13">
-        <v>7.14</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="14">
@@ -743,10 +743,10 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C14">
-        <v>61.78</v>
+        <v>61.06</v>
       </c>
       <c r="D14">
         <v>6</v>
@@ -755,7 +755,7 @@
         <v>3</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G14">
         <v>54.55</v>
@@ -764,7 +764,7 @@
         <v>60.0</v>
       </c>
       <c r="I14">
-        <v>4.76</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="15">
@@ -775,7 +775,7 @@
         <v>8</v>
       </c>
       <c r="C15">
-        <v>60.51</v>
+        <v>60.78</v>
       </c>
       <c r="D15">
         <v>7</v>
@@ -784,7 +784,7 @@
         <v>2</v>
       </c>
       <c r="F15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15">
         <v>63.64</v>
@@ -793,7 +793,7 @@
         <v>40.0</v>
       </c>
       <c r="I15">
-        <v>23.81</v>
+        <v>25.58</v>
       </c>
     </row>
     <row r="16">
@@ -804,25 +804,25 @@
         <v>16</v>
       </c>
       <c r="C16">
-        <v>60.27</v>
+        <v>60.29</v>
       </c>
       <c r="D16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E16">
         <v>2</v>
       </c>
       <c r="F16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G16">
-        <v>90.91</v>
+        <v>81.82</v>
       </c>
       <c r="H16">
         <v>40.0</v>
       </c>
       <c r="I16">
-        <v>16.67</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="17">
@@ -833,7 +833,7 @@
         <v>23</v>
       </c>
       <c r="C17">
-        <v>59.8</v>
+        <v>60.08</v>
       </c>
       <c r="D17">
         <v>7</v>
@@ -842,7 +842,7 @@
         <v>2</v>
       </c>
       <c r="F17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G17">
         <v>63.64</v>
@@ -851,7 +851,7 @@
         <v>40.0</v>
       </c>
       <c r="I17">
-        <v>19.05</v>
+        <v>20.93</v>
       </c>
     </row>
     <row r="18">
@@ -859,28 +859,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="C18">
-        <v>58.37</v>
+        <v>59.24</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18">
-        <v>63.64</v>
+        <v>81.82</v>
       </c>
       <c r="H18">
         <v>40.0</v>
       </c>
       <c r="I18">
-        <v>9.52</v>
+        <v>11.63</v>
       </c>
     </row>
     <row r="19">
@@ -888,13 +888,13 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C19">
-        <v>57.85</v>
+        <v>58.69</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -903,13 +903,13 @@
         <v>5</v>
       </c>
       <c r="G19">
-        <v>54.55</v>
+        <v>63.64</v>
       </c>
       <c r="H19">
         <v>40.0</v>
       </c>
       <c r="I19">
-        <v>11.9</v>
+        <v>11.63</v>
       </c>
     </row>
     <row r="20">
@@ -917,28 +917,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="C20">
-        <v>57.66</v>
+        <v>58.16</v>
       </c>
       <c r="D20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G20">
-        <v>63.64</v>
+        <v>54.55</v>
       </c>
       <c r="H20">
         <v>40.0</v>
       </c>
       <c r="I20">
-        <v>4.76</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="21">
@@ -949,7 +949,7 @@
         <v>48</v>
       </c>
       <c r="C21">
-        <v>57.49</v>
+        <v>57.81</v>
       </c>
       <c r="D21">
         <v>6</v>
@@ -958,7 +958,7 @@
         <v>2</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G21">
         <v>54.55</v>
@@ -967,7 +967,7 @@
         <v>40.0</v>
       </c>
       <c r="I21">
-        <v>9.52</v>
+        <v>11.63</v>
       </c>
     </row>
     <row r="22">
@@ -978,7 +978,7 @@
         <v>28</v>
       </c>
       <c r="C22">
-        <v>56.94</v>
+        <v>57.29</v>
       </c>
       <c r="D22">
         <v>7</v>
@@ -987,7 +987,7 @@
         <v>2</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22">
         <v>63.64</v>
@@ -996,7 +996,7 @@
         <v>40.0</v>
       </c>
       <c r="I22">
-        <v>0.0</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="23">
@@ -1004,28 +1004,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C23">
-        <v>55.35</v>
+        <v>57.11</v>
       </c>
       <c r="D23">
         <v>6</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G23">
         <v>54.55</v>
       </c>
       <c r="H23">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I23">
-        <v>28.57</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="24">
@@ -1033,28 +1033,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C24">
-        <v>54.8</v>
+        <v>55.6</v>
       </c>
       <c r="D24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G24">
-        <v>63.64</v>
+        <v>54.55</v>
       </c>
       <c r="H24">
         <v>20.0</v>
       </c>
       <c r="I24">
-        <v>19.05</v>
+        <v>30.23</v>
       </c>
     </row>
     <row r="25">
@@ -1062,10 +1062,10 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C25">
-        <v>54.44</v>
+        <v>55.08</v>
       </c>
       <c r="D25">
         <v>7</v>
@@ -1074,7 +1074,7 @@
         <v>1</v>
       </c>
       <c r="F25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G25">
         <v>63.64</v>
@@ -1083,7 +1083,7 @@
         <v>20.0</v>
       </c>
       <c r="I25">
-        <v>16.67</v>
+        <v>20.93</v>
       </c>
     </row>
     <row r="26">
@@ -1091,13 +1091,13 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C26">
-        <v>53.92</v>
+        <v>54.73</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -1106,13 +1106,13 @@
         <v>8</v>
       </c>
       <c r="G26">
-        <v>54.55</v>
+        <v>63.64</v>
       </c>
       <c r="H26">
         <v>20.0</v>
       </c>
       <c r="I26">
-        <v>19.05</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="27">
@@ -1120,10 +1120,10 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C27">
-        <v>53.21</v>
+        <v>54.2</v>
       </c>
       <c r="D27">
         <v>6</v>
@@ -1132,7 +1132,7 @@
         <v>1</v>
       </c>
       <c r="F27">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G27">
         <v>54.55</v>
@@ -1141,7 +1141,7 @@
         <v>20.0</v>
       </c>
       <c r="I27">
-        <v>14.29</v>
+        <v>20.93</v>
       </c>
     </row>
     <row r="28">
@@ -1149,10 +1149,10 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C28">
-        <v>52.85</v>
+        <v>53.51</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -1161,7 +1161,7 @@
         <v>1</v>
       </c>
       <c r="F28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G28">
         <v>54.55</v>
@@ -1170,7 +1170,7 @@
         <v>20.0</v>
       </c>
       <c r="I28">
-        <v>11.9</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="29">
@@ -1178,28 +1178,28 @@
         <v>28</v>
       </c>
       <c r="B29">
+        <v>49</v>
+      </c>
+      <c r="C29">
+        <v>53.16</v>
+      </c>
+      <c r="D29">
         <v>6</v>
-      </c>
-      <c r="C29">
-        <v>52.66</v>
-      </c>
-      <c r="D29">
-        <v>7</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G29">
-        <v>63.64</v>
+        <v>54.55</v>
       </c>
       <c r="H29">
         <v>20.0</v>
       </c>
       <c r="I29">
-        <v>4.76</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="30">
@@ -1210,25 +1210,25 @@
         <v>4</v>
       </c>
       <c r="C30">
-        <v>52.58</v>
+        <v>52.5</v>
       </c>
       <c r="D30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
         <v>0</v>
       </c>
-      <c r="F30">
-        <v>15</v>
-      </c>
       <c r="G30">
-        <v>72.73</v>
+        <v>81.82</v>
       </c>
       <c r="H30">
+        <v>20.0</v>
+      </c>
+      <c r="I30">
         <v>0.0</v>
-      </c>
-      <c r="I30">
-        <v>35.71</v>
       </c>
     </row>
     <row r="31">
@@ -1239,7 +1239,7 @@
         <v>39</v>
       </c>
       <c r="C31">
-        <v>52.14</v>
+        <v>52.46</v>
       </c>
       <c r="D31">
         <v>6</v>
@@ -1248,7 +1248,7 @@
         <v>1</v>
       </c>
       <c r="F31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31">
         <v>54.55</v>
@@ -1257,7 +1257,7 @@
         <v>20.0</v>
       </c>
       <c r="I31">
-        <v>7.14</v>
+        <v>9.3</v>
       </c>
     </row>
     <row r="32">
@@ -1265,28 +1265,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C32">
-        <v>51.96</v>
+        <v>52.11</v>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32">
         <v>3</v>
       </c>
       <c r="G32">
-        <v>45.45</v>
+        <v>54.55</v>
       </c>
       <c r="H32">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I32">
-        <v>7.14</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="33">
@@ -1294,10 +1294,10 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C33">
-        <v>50.88</v>
+        <v>51.23</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -1306,7 +1306,7 @@
         <v>2</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33">
         <v>45.45</v>
@@ -1315,7 +1315,7 @@
         <v>40.0</v>
       </c>
       <c r="I33">
-        <v>0.0</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="34">
@@ -1323,7 +1323,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="C34">
         <v>50.88</v>
@@ -1352,28 +1352,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C35">
-        <v>49.1</v>
+        <v>50.88</v>
       </c>
       <c r="D35">
         <v>5</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G35">
         <v>45.45</v>
       </c>
       <c r="H35">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I35">
-        <v>21.43</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="36">
@@ -1381,10 +1381,10 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C36">
-        <v>49.1</v>
+        <v>49.37</v>
       </c>
       <c r="D36">
         <v>5</v>
@@ -1393,7 +1393,7 @@
         <v>1</v>
       </c>
       <c r="F36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G36">
         <v>45.45</v>
@@ -1402,7 +1402,7 @@
         <v>20.0</v>
       </c>
       <c r="I36">
-        <v>21.43</v>
+        <v>23.26</v>
       </c>
     </row>
     <row r="37">
@@ -1410,10 +1410,10 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C37">
-        <v>48.03</v>
+        <v>49.37</v>
       </c>
       <c r="D37">
         <v>5</v>
@@ -1422,7 +1422,7 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G37">
         <v>45.45</v>
@@ -1431,7 +1431,7 @@
         <v>20.0</v>
       </c>
       <c r="I37">
-        <v>14.29</v>
+        <v>23.26</v>
       </c>
     </row>
     <row r="38">
@@ -1439,28 +1439,28 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C38">
-        <v>46.6</v>
+        <v>48.33</v>
       </c>
       <c r="D38">
         <v>5</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G38">
         <v>45.45</v>
       </c>
       <c r="H38">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I38">
-        <v>38.1</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="39">
@@ -1468,28 +1468,28 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C39">
-        <v>45.53</v>
+        <v>46.81</v>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E39">
         <v>0</v>
       </c>
       <c r="F39">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="G39">
-        <v>27.27</v>
+        <v>45.45</v>
       </c>
       <c r="H39">
         <v>0.0</v>
       </c>
       <c r="I39">
-        <v>100.0</v>
+        <v>39.53</v>
       </c>
     </row>
     <row r="40">
@@ -1500,7 +1500,7 @@
         <v>46</v>
       </c>
       <c r="C40">
-        <v>45.35</v>
+        <v>45.59</v>
       </c>
       <c r="D40">
         <v>4</v>
@@ -1509,7 +1509,7 @@
         <v>1</v>
       </c>
       <c r="F40">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G40">
         <v>36.36</v>
@@ -1518,7 +1518,7 @@
         <v>20.0</v>
       </c>
       <c r="I40">
-        <v>30.95</v>
+        <v>32.56</v>
       </c>
     </row>
     <row r="41">
@@ -1526,28 +1526,28 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C41">
-        <v>43.57</v>
+        <v>45.53</v>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="G41">
-        <v>36.36</v>
+        <v>27.27</v>
       </c>
       <c r="H41">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I41">
-        <v>19.05</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="42">
@@ -1555,10 +1555,10 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="C42">
-        <v>43.57</v>
+        <v>43.85</v>
       </c>
       <c r="D42">
         <v>4</v>
@@ -1567,7 +1567,7 @@
         <v>1</v>
       </c>
       <c r="F42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G42">
         <v>36.36</v>
@@ -1576,7 +1576,7 @@
         <v>20.0</v>
       </c>
       <c r="I42">
-        <v>19.05</v>
+        <v>20.93</v>
       </c>
     </row>
     <row r="43">
@@ -1584,10 +1584,10 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C43">
-        <v>41.78</v>
+        <v>43.85</v>
       </c>
       <c r="D43">
         <v>4</v>
@@ -1596,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="F43">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G43">
         <v>36.36</v>
@@ -1605,7 +1605,7 @@
         <v>20.0</v>
       </c>
       <c r="I43">
-        <v>7.14</v>
+        <v>20.93</v>
       </c>
     </row>
     <row r="44">
@@ -1613,10 +1613,10 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C44">
-        <v>41.06</v>
+        <v>42.1</v>
       </c>
       <c r="D44">
         <v>4</v>
@@ -1625,7 +1625,7 @@
         <v>1</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G44">
         <v>36.36</v>
@@ -1634,7 +1634,7 @@
         <v>20.0</v>
       </c>
       <c r="I44">
-        <v>2.38</v>
+        <v>9.3</v>
       </c>
     </row>
     <row r="45">
@@ -1645,7 +1645,7 @@
         <v>45</v>
       </c>
       <c r="C45">
-        <v>41.06</v>
+        <v>41.41</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -1654,7 +1654,7 @@
         <v>1</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45">
         <v>36.36</v>
@@ -1663,7 +1663,7 @@
         <v>20.0</v>
       </c>
       <c r="I45">
-        <v>2.38</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="46">
@@ -1674,7 +1674,7 @@
         <v>5</v>
       </c>
       <c r="C46">
-        <v>35.35</v>
+        <v>35.7</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -1683,7 +1683,7 @@
         <v>2</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46">
         <v>18.18</v>
@@ -1692,7 +1692,7 @@
         <v>40.0</v>
       </c>
       <c r="I46">
-        <v>0.0</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="47">
@@ -1700,28 +1700,28 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C47">
-        <v>35.35</v>
+        <v>33.73</v>
       </c>
       <c r="D47">
         <v>2</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G47">
         <v>18.18</v>
       </c>
       <c r="H47">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I47">
-        <v>33.33</v>
+        <v>55.81</v>
       </c>
     </row>
     <row r="48">
@@ -1729,28 +1729,28 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C48">
-        <v>33.57</v>
+        <v>31.4</v>
       </c>
       <c r="D48">
         <v>2</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="G48">
         <v>18.18</v>
       </c>
       <c r="H48">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I48">
-        <v>54.76</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="49">
@@ -1758,28 +1758,28 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C49">
-        <v>33.39</v>
+        <v>30.59</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49">
         <v>0</v>
       </c>
       <c r="F49">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="G49">
-        <v>9.09</v>
+        <v>18.18</v>
       </c>
       <c r="H49">
         <v>0.0</v>
       </c>
       <c r="I49">
-        <v>88.1</v>
+        <v>34.88</v>
       </c>
     </row>
     <row r="50">
@@ -1787,10 +1787,10 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C50">
-        <v>31.07</v>
+        <v>30.35</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -1799,7 +1799,7 @@
         <v>1</v>
       </c>
       <c r="F50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G50">
         <v>18.18</v>
@@ -1808,7 +1808,7 @@
         <v>20.0</v>
       </c>
       <c r="I50">
-        <v>4.76</v>
+        <v>0.0</v>
       </c>
     </row>
   </sheetData>
@@ -1867,731 +1867,731 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000091</v>
+        <v>115000092</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
         <v>13</v>
       </c>
-      <c r="E2">
-        <v>24</v>
-      </c>
-      <c r="F2">
-        <v>25</v>
-      </c>
       <c r="G2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H2">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I2">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000090</v>
+        <v>115000091</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C3">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H3">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000089</v>
+        <v>115000090</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H4">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="I4">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000088</v>
+        <v>115000089</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F5">
         <v>21</v>
       </c>
       <c r="G5">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H5">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000087</v>
+        <v>115000088</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G6">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H6">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I6">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000086</v>
+        <v>115000087</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D7">
         <v>15</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F7">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G7">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H7">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I7">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000085</v>
+        <v>115000086</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C8">
         <v>3</v>
       </c>
       <c r="D8">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E8">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G8">
+        <v>47</v>
+      </c>
+      <c r="H8">
+        <v>49</v>
+      </c>
+      <c r="I8">
         <v>27</v>
-      </c>
-      <c r="H8">
-        <v>37</v>
-      </c>
-      <c r="I8">
-        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000084</v>
+        <v>115000085</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C9">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D9">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E9">
+        <v>17</v>
+      </c>
+      <c r="F9">
+        <v>18</v>
+      </c>
+      <c r="G9">
+        <v>27</v>
+      </c>
+      <c r="H9">
+        <v>37</v>
+      </c>
+      <c r="I9">
         <v>19</v>
-      </c>
-      <c r="F9">
-        <v>26</v>
-      </c>
-      <c r="G9">
-        <v>29</v>
-      </c>
-      <c r="H9">
-        <v>48</v>
-      </c>
-      <c r="I9">
-        <v>30</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000083</v>
+        <v>115000084</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E10">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F10">
         <v>26</v>
       </c>
       <c r="G10">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H10">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I10">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C11">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D11">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E11">
+        <v>23</v>
+      </c>
+      <c r="F11">
         <v>26</v>
       </c>
-      <c r="F11">
-        <v>32</v>
-      </c>
       <c r="G11">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H11">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I11">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C12">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D12">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E12">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F12">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G12">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H12">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I12">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D13">
         <v>14</v>
       </c>
       <c r="E13">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F13">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G13">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H13">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I13">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E14">
         <v>25</v>
       </c>
       <c r="F14">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G14">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H14">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I14">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D15">
         <v>12</v>
       </c>
       <c r="E15">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F15">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G15">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H15">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="I15">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D16">
         <v>12</v>
       </c>
       <c r="E16">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F16">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G16">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H16">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I16">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E17">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F17">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G17">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H17">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I17">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C18">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D18">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E18">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F18">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G18">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H18">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I18">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C19">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D19">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F19">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G19">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H19">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I19">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C20">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D20">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E20">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F20">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G20">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H20">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I20">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E21">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F21">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G21">
         <v>35</v>
       </c>
       <c r="H21">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I21">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E22">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F22">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G22">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H22">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I22">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C23">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E23">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F23">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G23">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H23">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I23">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D24">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E24">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F24">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G24">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H24">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I24">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C25">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D25">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E25">
         <v>15</v>
@@ -2600,345 +2600,345 @@
         <v>18</v>
       </c>
       <c r="G25">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H25">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I25">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C26">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D26">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E26">
+        <v>15</v>
+      </c>
+      <c r="F26">
+        <v>18</v>
+      </c>
+      <c r="G26">
         <v>19</v>
       </c>
-      <c r="F26">
-        <v>23</v>
-      </c>
-      <c r="G26">
-        <v>39</v>
-      </c>
       <c r="H26">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I26">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D27">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E27">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F27">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G27">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H27">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I27">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C28">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D28">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E28">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F28">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G28">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H28">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C29">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D29">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E29">
+        <v>23</v>
+      </c>
+      <c r="F29">
+        <v>24</v>
+      </c>
+      <c r="G29">
         <v>29</v>
       </c>
-      <c r="F29">
-        <v>33</v>
-      </c>
-      <c r="G29">
-        <v>34</v>
-      </c>
       <c r="H29">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I29">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C30">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D30">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E30">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F30">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G30">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H30">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I30">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E31">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F31">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G31">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H31">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I31">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E32">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F32">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G32">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H32">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I32">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C33">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E33">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F33">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G33">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H33">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I33">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C34">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D34">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E34">
         <v>25</v>
       </c>
       <c r="F34">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G34">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H34">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I34">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C35">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D35">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E35">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F35">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G35">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H35">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I35">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C36">
+        <v>8</v>
+      </c>
+      <c r="D36">
+        <v>9</v>
+      </c>
+      <c r="E36">
+        <v>16</v>
+      </c>
+      <c r="F36">
         <v>20</v>
-      </c>
-      <c r="D36">
-        <v>26</v>
-      </c>
-      <c r="E36">
-        <v>29</v>
-      </c>
-      <c r="F36">
-        <v>31</v>
       </c>
       <c r="G36">
         <v>37</v>
@@ -2947,472 +2947,472 @@
         <v>49</v>
       </c>
       <c r="I36">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C37">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D37">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E37">
         <v>29</v>
       </c>
       <c r="F37">
+        <v>31</v>
+      </c>
+      <c r="G37">
         <v>37</v>
       </c>
-      <c r="G37">
-        <v>47</v>
-      </c>
       <c r="H37">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I37">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C38">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D38">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E38">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F38">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G38">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="H38">
         <v>48</v>
       </c>
       <c r="I38">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C39">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D39">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E39">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F39">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G39">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H39">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I39">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C40">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D40">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E40">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F40">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G40">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H40">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I40">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C41">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D41">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E41">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F41">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G41">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H41">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I41">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C42">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D42">
+        <v>12</v>
+      </c>
+      <c r="E42">
         <v>18</v>
       </c>
-      <c r="E42">
-        <v>25</v>
-      </c>
       <c r="F42">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G42">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H42">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I42">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C43">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D43">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E43">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F43">
         <v>28</v>
       </c>
       <c r="G43">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H43">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I43">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C44">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D44">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E44">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F44">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G44">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H44">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I44">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C45">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D45">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E45">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F45">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G45">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H45">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I45">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C46">
+        <v>6</v>
+      </c>
+      <c r="D46">
+        <v>10</v>
+      </c>
+      <c r="E46">
+        <v>14</v>
+      </c>
+      <c r="F46">
+        <v>25</v>
+      </c>
+      <c r="G46">
+        <v>26</v>
+      </c>
+      <c r="H46">
+        <v>32</v>
+      </c>
+      <c r="I46">
         <v>7</v>
-      </c>
-      <c r="D46">
-        <v>14</v>
-      </c>
-      <c r="E46">
-        <v>16</v>
-      </c>
-      <c r="F46">
-        <v>37</v>
-      </c>
-      <c r="G46">
-        <v>39</v>
-      </c>
-      <c r="H46">
-        <v>47</v>
-      </c>
-      <c r="I46">
-        <v>34</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D47">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E47">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F47">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G47">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H47">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I47">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C48">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D48">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E48">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F48">
+        <v>19</v>
+      </c>
+      <c r="G48">
+        <v>20</v>
+      </c>
+      <c r="H48">
+        <v>40</v>
+      </c>
+      <c r="I48">
         <v>22</v>
-      </c>
-      <c r="G48">
-        <v>40</v>
-      </c>
-      <c r="H48">
-        <v>45</v>
-      </c>
-      <c r="I48">
-        <v>18</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D49">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E49">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F49">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G49">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H49">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I49">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C50">
         <v>4</v>
       </c>
       <c r="D50">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E50">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F50">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G50">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H50">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I50">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E51">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F51">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G51">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H51">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I51">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-09-29 第 115000092 期；威力彩 2026-09-28 第 115000078 期</t>
+          <t>大樂透 2026-09-29 第 115000092 期；威力彩 2026-10-01 第 115000079 期</t>
         </is>
       </c>
     </row>
@@ -112,7 +112,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -121,7 +121,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -143,7 +143,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8, 9, 19, 24, 29, 35</t>
+          <t>8, 19, 24, 29, 35, 38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -161,7 +161,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.286 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.166 碼/期</t>
         </is>
       </c>
     </row>
@@ -3464,13 +3464,13 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>1.024</v>
+        <v>0.952</v>
       </c>
       <c r="D2">
-        <v>31.0</v>
+        <v>28.6</v>
       </c>
       <c r="E2">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="F2">
         <v>3</v>
@@ -3486,13 +3486,13 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>1.024</v>
+        <v>0.952</v>
       </c>
       <c r="D3">
-        <v>31.0</v>
+        <v>28.6</v>
       </c>
       <c r="E3">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="F3">
         <v>3</v>
@@ -3501,7 +3501,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>近期趨勢</t>
+          <t>冷號觀察</t>
         </is>
       </c>
       <c r="B4">
@@ -3511,10 +3511,10 @@
         <v>0.929</v>
       </c>
       <c r="D4">
-        <v>19.0</v>
+        <v>26.2</v>
       </c>
       <c r="E4">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -3523,17 +3523,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>冷號觀察</t>
+          <t>近期趨勢</t>
         </is>
       </c>
       <c r="B5">
         <v>42</v>
       </c>
       <c r="C5">
-        <v>0.929</v>
+        <v>0.857</v>
       </c>
       <c r="D5">
-        <v>26.2</v>
+        <v>16.7</v>
       </c>
       <c r="E5">
         <v>2.4</v>
@@ -3552,13 +3552,13 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.857</v>
+        <v>0.786</v>
       </c>
       <c r="D6">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="E6">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -3574,10 +3574,10 @@
         <v>42</v>
       </c>
       <c r="C7">
-        <v>0.738</v>
+        <v>0.786</v>
       </c>
       <c r="D7">
-        <v>16.7</v>
+        <v>19.0</v>
       </c>
       <c r="E7">
         <v>0.0</v>
@@ -3648,7 +3648,7 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>75.74</v>
+        <v>77.68</v>
       </c>
       <c r="D2">
         <v>10</v>
@@ -3657,16 +3657,16 @@
         <v>5</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>66.67</v>
+        <v>71.43</v>
       </c>
       <c r="H2">
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>31.58</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="3">
@@ -3674,28 +3674,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C3">
-        <v>73.01</v>
+        <v>74.15</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>60.0</v>
+        <v>100.0</v>
       </c>
       <c r="H3">
-        <v>80.0</v>
+        <v>100.0</v>
       </c>
       <c r="I3">
-        <v>47.37</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="4">
@@ -3706,7 +3706,7 @@
         <v>19</v>
       </c>
       <c r="C4">
-        <v>71.73</v>
+        <v>73.91</v>
       </c>
       <c r="D4">
         <v>12</v>
@@ -3715,16 +3715,16 @@
         <v>4</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G4">
-        <v>80.0</v>
+        <v>85.71</v>
       </c>
       <c r="H4">
         <v>80.0</v>
       </c>
       <c r="I4">
-        <v>36.84</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="5">
@@ -3732,28 +3732,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>71.5</v>
+        <v>69.93</v>
       </c>
       <c r="D5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>100.0</v>
+        <v>71.43</v>
       </c>
       <c r="H5">
-        <v>100.0</v>
+        <v>60.0</v>
       </c>
       <c r="I5">
-        <v>0.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="6">
@@ -3761,28 +3761,28 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>69.69</v>
+      </c>
+      <c r="D6">
         <v>9</v>
-      </c>
-      <c r="C6">
-        <v>68.2</v>
-      </c>
-      <c r="D6">
-        <v>11</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>73.33</v>
+        <v>64.29</v>
       </c>
       <c r="H6">
         <v>60.0</v>
       </c>
       <c r="I6">
-        <v>47.37</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="7">
@@ -3793,7 +3793,7 @@
         <v>8</v>
       </c>
       <c r="C7">
-        <v>66.89</v>
+        <v>69.17</v>
       </c>
       <c r="D7">
         <v>11</v>
@@ -3802,16 +3802,16 @@
         <v>4</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>73.33</v>
+        <v>78.57</v>
       </c>
       <c r="H7">
         <v>80.0</v>
       </c>
       <c r="I7">
-        <v>5.26</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="8">
@@ -3822,7 +3822,7 @@
         <v>17</v>
       </c>
       <c r="C8">
-        <v>66.0</v>
+        <v>68.18</v>
       </c>
       <c r="D8">
         <v>10</v>
@@ -3831,16 +3831,16 @@
         <v>4</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>66.67</v>
+        <v>71.43</v>
       </c>
       <c r="H8">
         <v>80.0</v>
       </c>
       <c r="I8">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="9">
@@ -3851,7 +3851,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>65.94</v>
+        <v>68.16</v>
       </c>
       <c r="D9">
         <v>12</v>
@@ -3860,16 +3860,16 @@
         <v>3</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G9">
-        <v>80.0</v>
+        <v>85.71</v>
       </c>
       <c r="H9">
         <v>60.0</v>
       </c>
       <c r="I9">
-        <v>31.58</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="10">
@@ -3877,28 +3877,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>65.46</v>
+        <v>67.19</v>
       </c>
       <c r="D10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E10">
         <v>4</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>46.67</v>
+        <v>64.29</v>
       </c>
       <c r="H10">
         <v>80.0</v>
       </c>
       <c r="I10">
-        <v>21.05</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="11">
@@ -3906,28 +3906,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="C11">
-        <v>61.79</v>
+        <v>66.94</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="H11">
-        <v>60.0</v>
+        <v>80.0</v>
       </c>
       <c r="I11">
-        <v>5.26</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="12">
@@ -3935,28 +3935,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="C12">
-        <v>61.59</v>
+        <v>63.19</v>
       </c>
       <c r="D12">
+        <v>9</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
         <v>8</v>
       </c>
-      <c r="E12">
-        <v>3</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
       <c r="G12">
-        <v>53.33</v>
+        <v>64.29</v>
       </c>
       <c r="H12">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="I12">
-        <v>5.26</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="13">
@@ -3964,28 +3964,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C13">
-        <v>61.43</v>
+        <v>62.43</v>
       </c>
       <c r="D13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G13">
+        <v>71.43</v>
+      </c>
+      <c r="H13">
         <v>60.0</v>
       </c>
-      <c r="H13">
-        <v>40.0</v>
-      </c>
       <c r="I13">
-        <v>36.84</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="14">
@@ -3993,28 +3993,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="C14">
-        <v>60.9</v>
+        <v>62.17</v>
       </c>
       <c r="D14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G14">
-        <v>60.0</v>
+        <v>78.57</v>
       </c>
       <c r="H14">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="I14">
-        <v>0.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="15">
@@ -4022,28 +4022,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C15">
-        <v>60.05</v>
+        <v>62.05</v>
       </c>
       <c r="D15">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15">
         <v>5</v>
       </c>
       <c r="G15">
-        <v>73.33</v>
+        <v>50.0</v>
       </c>
       <c r="H15">
-        <v>40.0</v>
+        <v>60.0</v>
       </c>
       <c r="I15">
-        <v>26.32</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="16">
@@ -4051,13 +4051,13 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="C16">
-        <v>59.85</v>
+        <v>60.69</v>
       </c>
       <c r="D16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -4066,13 +4066,13 @@
         <v>5</v>
       </c>
       <c r="G16">
-        <v>60.0</v>
+        <v>57.14</v>
       </c>
       <c r="H16">
         <v>40.0</v>
       </c>
       <c r="I16">
-        <v>26.32</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="17">
@@ -4080,28 +4080,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C17">
-        <v>58.96</v>
+        <v>60.16</v>
       </c>
       <c r="D17">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17">
-        <v>53.33</v>
+        <v>85.71</v>
       </c>
       <c r="H17">
         <v>40.0</v>
       </c>
       <c r="I17">
-        <v>21.05</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="18">
@@ -4109,28 +4109,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>58.43</v>
+        <v>60.01</v>
       </c>
       <c r="D18">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F18">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>53.33</v>
+        <v>42.86</v>
       </c>
       <c r="H18">
-        <v>0.0</v>
+        <v>80.0</v>
       </c>
       <c r="I18">
-        <v>84.21</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="19">
@@ -4138,28 +4138,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C19">
-        <v>58.4</v>
+        <v>59.94</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19">
         <v>4</v>
       </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
       <c r="G19">
+        <v>57.14</v>
+      </c>
+      <c r="H19">
         <v>40.0</v>
       </c>
-      <c r="H19">
-        <v>80.0</v>
-      </c>
       <c r="I19">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="20">
@@ -4167,28 +4167,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C20">
-        <v>58.17</v>
+        <v>59.69</v>
       </c>
       <c r="D20">
         <v>8</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G20">
-        <v>53.33</v>
+        <v>57.14</v>
       </c>
       <c r="H20">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="I20">
-        <v>15.79</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="21">
@@ -4196,28 +4196,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C21">
-        <v>58.17</v>
+        <v>59.26</v>
       </c>
       <c r="D21">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>53.33</v>
+        <v>42.86</v>
       </c>
       <c r="H21">
-        <v>40.0</v>
+        <v>80.0</v>
       </c>
       <c r="I21">
-        <v>15.79</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="22">
@@ -4225,13 +4225,13 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C22">
-        <v>57.78</v>
+        <v>58.93</v>
       </c>
       <c r="D22">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E22">
         <v>2</v>
@@ -4240,13 +4240,13 @@
         <v>2</v>
       </c>
       <c r="G22">
-        <v>80.0</v>
+        <v>71.43</v>
       </c>
       <c r="H22">
         <v>40.0</v>
       </c>
       <c r="I22">
-        <v>10.53</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="23">
@@ -4254,28 +4254,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C23">
-        <v>57.3</v>
+        <v>58.44</v>
       </c>
       <c r="D23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>46.67</v>
+        <v>57.14</v>
       </c>
       <c r="H23">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="I23">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="24">
@@ -4283,28 +4283,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C24">
-        <v>57.3</v>
+        <v>58.3</v>
       </c>
       <c r="D24">
         <v>7</v>
       </c>
       <c r="E24">
+        <v>3</v>
+      </c>
+      <c r="F24">
         <v>0</v>
       </c>
-      <c r="F24">
-        <v>19</v>
-      </c>
       <c r="G24">
-        <v>46.67</v>
+        <v>50.0</v>
       </c>
       <c r="H24">
+        <v>60.0</v>
+      </c>
+      <c r="I24">
         <v>0.0</v>
-      </c>
-      <c r="I24">
-        <v>100.0</v>
       </c>
     </row>
     <row r="25">
@@ -4312,28 +4312,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C25">
-        <v>55.72</v>
+        <v>57.19</v>
       </c>
       <c r="D25">
+        <v>8</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
         <v>7</v>
       </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>17</v>
-      </c>
       <c r="G25">
-        <v>46.67</v>
+        <v>57.14</v>
       </c>
       <c r="H25">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I25">
-        <v>89.47</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="26">
@@ -4341,28 +4341,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C26">
-        <v>55.54</v>
+        <v>57.05</v>
       </c>
       <c r="D26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G26">
-        <v>53.33</v>
+        <v>50.0</v>
       </c>
       <c r="H26">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I26">
-        <v>31.58</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="27">
@@ -4370,28 +4370,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C27">
-        <v>55.46</v>
+        <v>56.8</v>
       </c>
       <c r="D27">
         <v>7</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G27">
-        <v>46.67</v>
+        <v>50.0</v>
       </c>
       <c r="H27">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="I27">
-        <v>21.05</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="28">
@@ -4402,7 +4402,7 @@
         <v>3</v>
       </c>
       <c r="C28">
-        <v>54.19</v>
+        <v>55.76</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -4411,16 +4411,16 @@
         <v>3</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28">
-        <v>40.0</v>
+        <v>42.86</v>
       </c>
       <c r="H28">
         <v>60.0</v>
       </c>
       <c r="I28">
-        <v>5.26</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="29">
@@ -4428,28 +4428,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C29">
-        <v>54.19</v>
+        <v>54.94</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G29">
-        <v>40.0</v>
+        <v>57.14</v>
       </c>
       <c r="H29">
-        <v>60.0</v>
+        <v>20.0</v>
       </c>
       <c r="I29">
-        <v>5.26</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="30">
@@ -4457,28 +4457,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C30">
-        <v>51.08</v>
+        <v>54.26</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G30">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="H30">
-        <v>60.0</v>
+        <v>0.0</v>
       </c>
       <c r="I30">
-        <v>10.53</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="31">
@@ -4486,28 +4486,28 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C31">
-        <v>50.8</v>
+        <v>50.76</v>
       </c>
       <c r="D31">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G31">
-        <v>53.33</v>
+        <v>42.86</v>
       </c>
       <c r="H31">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I31">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="32">
@@ -4515,28 +4515,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C32">
-        <v>50.77</v>
+        <v>50.21</v>
       </c>
       <c r="D32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F32">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>40.0</v>
+        <v>35.71</v>
       </c>
       <c r="H32">
-        <v>40.0</v>
+        <v>60.0</v>
       </c>
       <c r="I32">
-        <v>15.79</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="33">
@@ -4544,28 +4544,28 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C33">
-        <v>49.19</v>
+        <v>49.05</v>
       </c>
       <c r="D33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
       <c r="G33">
-        <v>40.0</v>
+        <v>50.0</v>
       </c>
       <c r="H33">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I33">
-        <v>5.26</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="34">
@@ -4576,7 +4576,7 @@
         <v>12</v>
       </c>
       <c r="C34">
-        <v>47.66</v>
+        <v>48.96</v>
       </c>
       <c r="D34">
         <v>5</v>
@@ -4585,16 +4585,16 @@
         <v>2</v>
       </c>
       <c r="F34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G34">
-        <v>33.33</v>
+        <v>35.71</v>
       </c>
       <c r="H34">
         <v>40.0</v>
       </c>
       <c r="I34">
-        <v>21.05</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="35">
@@ -4602,28 +4602,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C35">
-        <v>44.55</v>
+        <v>46.71</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E35">
         <v>2</v>
       </c>
       <c r="F35">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G35">
-        <v>26.67</v>
+        <v>35.71</v>
       </c>
       <c r="H35">
         <v>40.0</v>
       </c>
       <c r="I35">
-        <v>26.32</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="36">
@@ -4634,7 +4634,7 @@
         <v>16</v>
       </c>
       <c r="C36">
-        <v>42.66</v>
+        <v>43.96</v>
       </c>
       <c r="D36">
         <v>5</v>
@@ -4643,16 +4643,16 @@
         <v>1</v>
       </c>
       <c r="F36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G36">
-        <v>33.33</v>
+        <v>35.71</v>
       </c>
       <c r="H36">
         <v>20.0</v>
       </c>
       <c r="I36">
-        <v>21.05</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="37">
@@ -4663,7 +4663,7 @@
         <v>32</v>
       </c>
       <c r="C37">
-        <v>41.92</v>
+        <v>42.92</v>
       </c>
       <c r="D37">
         <v>4</v>
@@ -4672,16 +4672,16 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G37">
-        <v>26.67</v>
+        <v>28.57</v>
       </c>
       <c r="H37">
         <v>20.0</v>
       </c>
       <c r="I37">
-        <v>42.11</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="38">
@@ -4692,7 +4692,7 @@
         <v>5</v>
       </c>
       <c r="C38">
-        <v>41.17</v>
+        <v>41.88</v>
       </c>
       <c r="D38">
         <v>3</v>
@@ -4701,16 +4701,16 @@
         <v>1</v>
       </c>
       <c r="F38">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G38">
-        <v>20.0</v>
+        <v>21.43</v>
       </c>
       <c r="H38">
         <v>20.0</v>
       </c>
       <c r="I38">
-        <v>63.16</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="39">
@@ -4721,7 +4721,7 @@
         <v>20</v>
       </c>
       <c r="C39">
-        <v>38.54</v>
+        <v>39.13</v>
       </c>
       <c r="D39">
         <v>3</v>
@@ -4730,16 +4730,16 @@
         <v>0</v>
       </c>
       <c r="F39">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G39">
-        <v>20.0</v>
+        <v>21.43</v>
       </c>
       <c r="H39">
         <v>0.0</v>
       </c>
       <c r="I39">
-        <v>78.95</v>
+        <v>80.0</v>
       </c>
     </row>
   </sheetData>
@@ -4798,61 +4798,61 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H3">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -4860,11 +4860,11 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C4">
@@ -4874,140 +4874,140 @@
         <v>8</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H4">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C5">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E5">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F5">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H5">
         <v>37</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7">
+        <v>12</v>
+      </c>
+      <c r="E7">
+        <v>14</v>
+      </c>
+      <c r="F7">
+        <v>16</v>
+      </c>
+      <c r="G7">
+        <v>29</v>
+      </c>
+      <c r="H7">
+        <v>36</v>
+      </c>
+      <c r="I7">
         <v>8</v>
-      </c>
-      <c r="D7">
-        <v>17</v>
-      </c>
-      <c r="E7">
-        <v>18</v>
-      </c>
-      <c r="F7">
-        <v>29</v>
-      </c>
-      <c r="G7">
-        <v>33</v>
-      </c>
-      <c r="H7">
-        <v>38</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E8">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F8">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G8">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H8">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I8">
         <v>2</v>
@@ -5015,108 +5015,108 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D9">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E9">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F9">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H9">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F10">
         <v>19</v>
       </c>
       <c r="G10">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H10">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G11">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H11">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C12">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D12">
         <v>7</v>
@@ -5125,230 +5125,230 @@
         <v>9</v>
       </c>
       <c r="F12">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G12">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H12">
         <v>36</v>
       </c>
       <c r="I12">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E13">
         <v>9</v>
       </c>
       <c r="F13">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G13">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H13">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I13">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14">
+        <v>9</v>
+      </c>
+      <c r="F14">
         <v>11</v>
       </c>
-      <c r="E14">
-        <v>18</v>
-      </c>
-      <c r="F14">
-        <v>19</v>
-      </c>
       <c r="G14">
+        <v>29</v>
+      </c>
+      <c r="H14">
         <v>35</v>
       </c>
-      <c r="H14">
-        <v>38</v>
-      </c>
       <c r="I14">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D15">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F15">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G15">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H15">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="I15">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C16">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E16">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F16">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G16">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H16">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I16">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D17">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E17">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F17">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G17">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H17">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I17">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>7</v>
+      </c>
+      <c r="E18">
+        <v>8</v>
+      </c>
+      <c r="F18">
+        <v>20</v>
+      </c>
+      <c r="G18">
+        <v>26</v>
+      </c>
+      <c r="H18">
+        <v>33</v>
+      </c>
+      <c r="I18">
         <v>4</v>
-      </c>
-      <c r="D18">
-        <v>15</v>
-      </c>
-      <c r="E18">
-        <v>22</v>
-      </c>
-      <c r="F18">
-        <v>26</v>
-      </c>
-      <c r="G18">
-        <v>34</v>
-      </c>
-      <c r="H18">
-        <v>36</v>
-      </c>
-      <c r="I18">
-        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C19">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D19">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E19">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F19">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G19">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H19">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I19">
         <v>7</v>
@@ -5356,30 +5356,30 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C20">
+        <v>8</v>
+      </c>
+      <c r="D20">
+        <v>14</v>
+      </c>
+      <c r="E20">
+        <v>17</v>
+      </c>
+      <c r="F20">
         <v>19</v>
       </c>
-      <c r="D20">
-        <v>22</v>
-      </c>
-      <c r="E20">
-        <v>28</v>
-      </c>
-      <c r="F20">
-        <v>31</v>
-      </c>
       <c r="G20">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H20">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I20">
         <v>7</v>
@@ -5387,30 +5387,30 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C21">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D21">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E21">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F21">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G21">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H21">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I21">
         <v>7</v>
@@ -5418,24 +5418,24 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D22">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E22">
         <v>13</v>
       </c>
       <c r="F22">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G22">
         <v>29</v>
@@ -5444,97 +5444,97 @@
         <v>31</v>
       </c>
       <c r="I22">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C23">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D23">
+        <v>12</v>
+      </c>
+      <c r="E23">
+        <v>13</v>
+      </c>
+      <c r="F23">
         <v>23</v>
       </c>
-      <c r="E23">
-        <v>25</v>
-      </c>
-      <c r="F23">
+      <c r="G23">
         <v>29</v>
       </c>
-      <c r="G23">
-        <v>34</v>
-      </c>
       <c r="H23">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I23">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C24">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D24">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E24">
+        <v>25</v>
+      </c>
+      <c r="F24">
         <v>29</v>
       </c>
-      <c r="F24">
-        <v>32</v>
-      </c>
       <c r="G24">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H24">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I24">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C25">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D25">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E25">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F25">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G25">
         <v>35</v>
       </c>
       <c r="H25">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I25">
         <v>6</v>
@@ -5542,402 +5542,402 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C26">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D26">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E26">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F26">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G26">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H26">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D27">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E27">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F27">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G27">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H27">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I27">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E28">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F28">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G28">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H28">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I28">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C29">
+        <v>5</v>
+      </c>
+      <c r="D29">
         <v>6</v>
       </c>
-      <c r="D29">
-        <v>10</v>
-      </c>
       <c r="E29">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F29">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G29">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H29">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I29">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C30">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D30">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E30">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F30">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G30">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H30">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I30">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D31">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E31">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F31">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G31">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H31">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I31">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C32">
+        <v>2</v>
+      </c>
+      <c r="D32">
+        <v>8</v>
+      </c>
+      <c r="E32">
+        <v>9</v>
+      </c>
+      <c r="F32">
+        <v>15</v>
+      </c>
+      <c r="G32">
+        <v>18</v>
+      </c>
+      <c r="H32">
+        <v>23</v>
+      </c>
+      <c r="I32">
         <v>4</v>
-      </c>
-      <c r="D32">
-        <v>17</v>
-      </c>
-      <c r="E32">
-        <v>19</v>
-      </c>
-      <c r="F32">
-        <v>25</v>
-      </c>
-      <c r="G32">
-        <v>28</v>
-      </c>
-      <c r="H32">
-        <v>29</v>
-      </c>
-      <c r="I32">
-        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C33">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D33">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E33">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F33">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G33">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H33">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I33">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D34">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E34">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F34">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G34">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H34">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I34">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C35">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D35">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E35">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F35">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G35">
         <v>28</v>
       </c>
       <c r="H35">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I35">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C36">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D36">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E36">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F36">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G36">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H36">
         <v>35</v>
       </c>
       <c r="I36">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E37">
+        <v>9</v>
+      </c>
+      <c r="F37">
+        <v>15</v>
+      </c>
+      <c r="G37">
         <v>24</v>
       </c>
-      <c r="F37">
-        <v>31</v>
-      </c>
-      <c r="G37">
-        <v>34</v>
-      </c>
       <c r="H37">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I37">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C38">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D38">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E38">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F38">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G38">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H38">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I38">
         <v>3</v>
@@ -5945,405 +5945,405 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C39">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D39">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E39">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F39">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G39">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H39">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I39">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C40">
         <v>6</v>
       </c>
       <c r="D40">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E40">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F40">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G40">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H40">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I40">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C41">
         <v>6</v>
       </c>
       <c r="D41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E41">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F41">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G41">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H41">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I41">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C42">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D42">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E42">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F42">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G42">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H42">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I42">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C43">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D43">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E43">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F43">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G43">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H43">
         <v>38</v>
       </c>
       <c r="I43">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C44">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D44">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E44">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F44">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G44">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H44">
         <v>38</v>
       </c>
       <c r="I44">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D45">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E45">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F45">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G45">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H45">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I45">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C46">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D46">
+        <v>4</v>
+      </c>
+      <c r="E46">
+        <v>13</v>
+      </c>
+      <c r="F46">
+        <v>19</v>
+      </c>
+      <c r="G46">
+        <v>27</v>
+      </c>
+      <c r="H46">
+        <v>30</v>
+      </c>
+      <c r="I46">
         <v>8</v>
-      </c>
-      <c r="E46">
-        <v>27</v>
-      </c>
-      <c r="F46">
-        <v>33</v>
-      </c>
-      <c r="G46">
-        <v>35</v>
-      </c>
-      <c r="H46">
-        <v>38</v>
-      </c>
-      <c r="I46">
-        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C47">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D47">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E47">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F47">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G47">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H47">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I47">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C48">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D48">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E48">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F48">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G48">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H48">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I48">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C49">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D49">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E49">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F49">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G49">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H49">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I49">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000030</v>
+        <v>115000031</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D50">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E50">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F50">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G50">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H50">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="I50">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000029</v>
+        <v>115000030</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E51">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F51">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G51">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H51">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I51">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-09-29 第 115000092 期；威力彩 2026-10-01 第 115000079 期</t>
+          <t>大樂透 2026-10-02 第 115000093 期；威力彩 2026-10-01 第 115000079 期</t>
         </is>
       </c>
     </row>
@@ -47,7 +47,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>115000092</v>
+        <v>115000093</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -56,7 +56,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -78,7 +78,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4, 12, 15, 26, 29, 35</t>
+          <t>4, 12, 14, 26, 29, 35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -96,7 +96,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.238 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.262 碼/期</t>
         </is>
       </c>
     </row>
@@ -258,10 +258,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>0.81</v>
+        <v>0.833</v>
       </c>
       <c r="D4">
-        <v>19.0</v>
+        <v>21.4</v>
       </c>
       <c r="E4">
         <v>2.4</v>
@@ -280,10 +280,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>0.786</v>
+        <v>0.81</v>
       </c>
       <c r="D5">
-        <v>19.0</v>
+        <v>21.4</v>
       </c>
       <c r="E5">
         <v>2.4</v>
@@ -324,7 +324,7 @@
         <v>42</v>
       </c>
       <c r="C7">
-        <v>0.667</v>
+        <v>0.643</v>
       </c>
       <c r="D7">
         <v>11.9</v>
@@ -398,7 +398,7 @@
         <v>35</v>
       </c>
       <c r="C2">
-        <v>73.47</v>
+        <v>73.8</v>
       </c>
       <c r="D2">
         <v>10</v>
@@ -407,7 +407,7 @@
         <v>5</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>90.91</v>
@@ -416,7 +416,7 @@
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>4.65</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="3">
@@ -427,25 +427,25 @@
         <v>26</v>
       </c>
       <c r="C3">
-        <v>70.56</v>
+        <v>73.05</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>90.91</v>
+        <v>100.0</v>
       </c>
       <c r="H3">
-        <v>80.0</v>
+        <v>100.0</v>
       </c>
       <c r="I3">
-        <v>18.6</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="4">
@@ -453,28 +453,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4">
-        <v>69.79</v>
+        <v>72.5</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G4">
+        <v>81.82</v>
+      </c>
+      <c r="H4">
         <v>100.0</v>
       </c>
-      <c r="H4">
-        <v>80.0</v>
-      </c>
       <c r="I4">
-        <v>11.63</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="5">
@@ -482,28 +482,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>67.92</v>
+        <v>65.1</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>72.73</v>
+        <v>100.0</v>
       </c>
       <c r="H5">
-        <v>80.0</v>
+        <v>60.0</v>
       </c>
       <c r="I5">
-        <v>4.65</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="6">
@@ -511,28 +511,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C6">
-        <v>67.29</v>
+        <v>63.52</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>63.64</v>
+        <v>81.82</v>
       </c>
       <c r="H6">
-        <v>80.0</v>
+        <v>60.0</v>
       </c>
       <c r="I6">
-        <v>2.33</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="7">
@@ -540,28 +540,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C7">
-        <v>65.84</v>
+        <v>63.24</v>
       </c>
       <c r="D7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>100.0</v>
+        <v>72.73</v>
       </c>
       <c r="H7">
         <v>60.0</v>
       </c>
       <c r="I7">
-        <v>18.6</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="8">
@@ -569,10 +569,10 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C8">
-        <v>63.19</v>
+        <v>63.18</v>
       </c>
       <c r="D8">
         <v>9</v>
@@ -590,7 +590,7 @@
         <v>60.0</v>
       </c>
       <c r="I8">
-        <v>4.65</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="9">
@@ -598,28 +598,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C9">
-        <v>63.19</v>
+        <v>63.11</v>
       </c>
       <c r="D9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G9">
-        <v>81.82</v>
+        <v>54.55</v>
       </c>
       <c r="H9">
         <v>60.0</v>
       </c>
       <c r="I9">
-        <v>4.65</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="10">
@@ -627,28 +627,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>62.85</v>
+        <v>62.77</v>
       </c>
       <c r="D10">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G10">
-        <v>81.82</v>
+        <v>54.55</v>
       </c>
       <c r="H10">
         <v>60.0</v>
       </c>
       <c r="I10">
-        <v>2.33</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="11">
@@ -656,28 +656,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C11">
-        <v>62.81</v>
+        <v>62.62</v>
       </c>
       <c r="D11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G11">
-        <v>54.55</v>
+        <v>63.64</v>
       </c>
       <c r="H11">
         <v>60.0</v>
       </c>
       <c r="I11">
-        <v>11.63</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="12">
@@ -685,28 +685,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>62.46</v>
+        <v>62.28</v>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>54.55</v>
+        <v>63.64</v>
       </c>
       <c r="H12">
         <v>60.0</v>
       </c>
       <c r="I12">
-        <v>9.3</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="13">
@@ -714,7 +714,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="C13">
         <v>61.94</v>
@@ -746,7 +746,7 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>61.06</v>
+        <v>61.41</v>
       </c>
       <c r="D14">
         <v>6</v>
@@ -755,7 +755,7 @@
         <v>3</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14">
         <v>54.55</v>
@@ -764,7 +764,7 @@
         <v>60.0</v>
       </c>
       <c r="I14">
-        <v>0.0</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="15">
@@ -772,28 +772,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C15">
-        <v>60.78</v>
+        <v>61.12</v>
       </c>
       <c r="D15">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E15">
         <v>2</v>
       </c>
       <c r="F15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G15">
-        <v>63.64</v>
+        <v>100.0</v>
       </c>
       <c r="H15">
         <v>40.0</v>
       </c>
       <c r="I15">
-        <v>25.58</v>
+        <v>20.45</v>
       </c>
     </row>
     <row r="16">
@@ -801,28 +801,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C16">
-        <v>60.29</v>
+        <v>60.35</v>
       </c>
       <c r="D16">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E16">
         <v>2</v>
       </c>
       <c r="F16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G16">
-        <v>81.82</v>
+        <v>63.64</v>
       </c>
       <c r="H16">
         <v>40.0</v>
       </c>
       <c r="I16">
-        <v>18.6</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="17">
@@ -830,28 +830,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C17">
-        <v>60.08</v>
+        <v>59.54</v>
       </c>
       <c r="D17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
       <c r="F17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G17">
-        <v>63.64</v>
+        <v>81.82</v>
       </c>
       <c r="H17">
         <v>40.0</v>
       </c>
       <c r="I17">
-        <v>20.93</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="18">
@@ -859,28 +859,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="C18">
-        <v>59.24</v>
+        <v>58.99</v>
       </c>
       <c r="D18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18">
-        <v>81.82</v>
+        <v>63.64</v>
       </c>
       <c r="H18">
         <v>40.0</v>
       </c>
       <c r="I18">
-        <v>11.63</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="19">
@@ -888,28 +888,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C19">
-        <v>58.69</v>
+        <v>58.11</v>
       </c>
       <c r="D19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G19">
-        <v>63.64</v>
+        <v>54.55</v>
       </c>
       <c r="H19">
         <v>40.0</v>
       </c>
       <c r="I19">
-        <v>11.63</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="20">
@@ -917,28 +917,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="C20">
-        <v>58.16</v>
+        <v>57.62</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
       <c r="F20">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G20">
-        <v>54.55</v>
+        <v>63.64</v>
       </c>
       <c r="H20">
         <v>40.0</v>
       </c>
       <c r="I20">
-        <v>13.95</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="21">
@@ -946,28 +946,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="C21">
-        <v>57.81</v>
+        <v>57.5</v>
       </c>
       <c r="D21">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E21">
         <v>2</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>54.55</v>
+        <v>81.82</v>
       </c>
       <c r="H21">
         <v>40.0</v>
       </c>
       <c r="I21">
-        <v>11.63</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="22">
@@ -975,28 +975,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C22">
-        <v>57.29</v>
+        <v>57.22</v>
       </c>
       <c r="D22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E22">
         <v>2</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>63.64</v>
+        <v>72.73</v>
       </c>
       <c r="H22">
         <v>40.0</v>
       </c>
       <c r="I22">
-        <v>2.33</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="23">
@@ -1004,28 +1004,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C23">
-        <v>57.11</v>
+        <v>56.03</v>
       </c>
       <c r="D23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G23">
-        <v>54.55</v>
+        <v>63.64</v>
       </c>
       <c r="H23">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I23">
-        <v>6.98</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="24">
@@ -1036,7 +1036,7 @@
         <v>34</v>
       </c>
       <c r="C24">
-        <v>55.6</v>
+        <v>55.84</v>
       </c>
       <c r="D24">
         <v>6</v>
@@ -1045,7 +1045,7 @@
         <v>1</v>
       </c>
       <c r="F24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G24">
         <v>54.55</v>
@@ -1054,7 +1054,7 @@
         <v>20.0</v>
       </c>
       <c r="I24">
-        <v>30.23</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="25">
@@ -1062,13 +1062,13 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C25">
-        <v>55.08</v>
+        <v>55.56</v>
       </c>
       <c r="D25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -1077,13 +1077,13 @@
         <v>9</v>
       </c>
       <c r="G25">
-        <v>63.64</v>
+        <v>81.82</v>
       </c>
       <c r="H25">
         <v>20.0</v>
       </c>
       <c r="I25">
-        <v>20.93</v>
+        <v>20.45</v>
       </c>
     </row>
     <row r="26">
@@ -1091,28 +1091,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C26">
-        <v>54.73</v>
+        <v>54.47</v>
       </c>
       <c r="D26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G26">
-        <v>63.64</v>
+        <v>54.55</v>
       </c>
       <c r="H26">
         <v>20.0</v>
       </c>
       <c r="I26">
-        <v>18.6</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="27">
@@ -1120,10 +1120,10 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C27">
-        <v>54.2</v>
+        <v>54.13</v>
       </c>
       <c r="D27">
         <v>6</v>
@@ -1141,7 +1141,7 @@
         <v>20.0</v>
       </c>
       <c r="I27">
-        <v>20.93</v>
+        <v>20.45</v>
       </c>
     </row>
     <row r="28">
@@ -1152,7 +1152,7 @@
         <v>37</v>
       </c>
       <c r="C28">
-        <v>53.51</v>
+        <v>53.79</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -1161,7 +1161,7 @@
         <v>1</v>
       </c>
       <c r="F28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G28">
         <v>54.55</v>
@@ -1170,7 +1170,7 @@
         <v>20.0</v>
       </c>
       <c r="I28">
-        <v>16.28</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="29">
@@ -1181,7 +1181,7 @@
         <v>49</v>
       </c>
       <c r="C29">
-        <v>53.16</v>
+        <v>53.45</v>
       </c>
       <c r="D29">
         <v>6</v>
@@ -1190,7 +1190,7 @@
         <v>1</v>
       </c>
       <c r="F29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G29">
         <v>54.55</v>
@@ -1199,7 +1199,7 @@
         <v>20.0</v>
       </c>
       <c r="I29">
-        <v>13.95</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="30">
@@ -1207,28 +1207,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="C30">
-        <v>52.5</v>
+        <v>52.77</v>
       </c>
       <c r="D30">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G30">
-        <v>81.82</v>
+        <v>54.55</v>
       </c>
       <c r="H30">
         <v>20.0</v>
       </c>
       <c r="I30">
-        <v>0.0</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="31">
@@ -1236,10 +1236,10 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="C31">
-        <v>52.46</v>
+        <v>52.43</v>
       </c>
       <c r="D31">
         <v>6</v>
@@ -1257,7 +1257,7 @@
         <v>20.0</v>
       </c>
       <c r="I31">
-        <v>9.3</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="32">
@@ -1265,28 +1265,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C32">
-        <v>52.11</v>
+        <v>52.25</v>
       </c>
       <c r="D32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G32">
-        <v>54.55</v>
+        <v>45.45</v>
       </c>
       <c r="H32">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I32">
-        <v>6.98</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="33">
@@ -1297,7 +1297,7 @@
         <v>33</v>
       </c>
       <c r="C33">
-        <v>51.23</v>
+        <v>51.57</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -1306,7 +1306,7 @@
         <v>2</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33">
         <v>45.45</v>
@@ -1315,7 +1315,7 @@
         <v>40.0</v>
       </c>
       <c r="I33">
-        <v>2.33</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="34">
@@ -1326,7 +1326,7 @@
         <v>2</v>
       </c>
       <c r="C34">
-        <v>50.88</v>
+        <v>51.23</v>
       </c>
       <c r="D34">
         <v>5</v>
@@ -1335,7 +1335,7 @@
         <v>2</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34">
         <v>45.45</v>
@@ -1344,7 +1344,7 @@
         <v>40.0</v>
       </c>
       <c r="I34">
-        <v>0.0</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="35">
@@ -1355,7 +1355,7 @@
         <v>30</v>
       </c>
       <c r="C35">
-        <v>50.88</v>
+        <v>51.23</v>
       </c>
       <c r="D35">
         <v>5</v>
@@ -1364,7 +1364,7 @@
         <v>2</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35">
         <v>45.45</v>
@@ -1373,7 +1373,7 @@
         <v>40.0</v>
       </c>
       <c r="I35">
-        <v>0.0</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="36">
@@ -1381,28 +1381,28 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C36">
-        <v>49.37</v>
+        <v>50.88</v>
       </c>
       <c r="D36">
         <v>5</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G36">
         <v>45.45</v>
       </c>
       <c r="H36">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I36">
-        <v>23.26</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="37">
@@ -1410,10 +1410,10 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C37">
-        <v>49.37</v>
+        <v>49.63</v>
       </c>
       <c r="D37">
         <v>5</v>
@@ -1422,7 +1422,7 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G37">
         <v>45.45</v>
@@ -1431,7 +1431,7 @@
         <v>20.0</v>
       </c>
       <c r="I37">
-        <v>23.26</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="38">
@@ -1439,28 +1439,28 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C38">
-        <v>48.33</v>
+        <v>47.02</v>
       </c>
       <c r="D38">
         <v>5</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G38">
         <v>45.45</v>
       </c>
       <c r="H38">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I38">
-        <v>16.28</v>
+        <v>40.91</v>
       </c>
     </row>
     <row r="39">
@@ -1468,28 +1468,28 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C39">
-        <v>46.81</v>
+        <v>45.53</v>
       </c>
       <c r="D39">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E39">
         <v>0</v>
       </c>
       <c r="F39">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="G39">
-        <v>45.45</v>
+        <v>27.27</v>
       </c>
       <c r="H39">
         <v>0.0</v>
       </c>
       <c r="I39">
-        <v>39.53</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="40">
@@ -1497,10 +1497,10 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="C40">
-        <v>45.59</v>
+        <v>44.12</v>
       </c>
       <c r="D40">
         <v>4</v>
@@ -1509,7 +1509,7 @@
         <v>1</v>
       </c>
       <c r="F40">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G40">
         <v>36.36</v>
@@ -1518,7 +1518,7 @@
         <v>20.0</v>
       </c>
       <c r="I40">
-        <v>32.56</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="41">
@@ -1526,28 +1526,28 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="C41">
-        <v>45.53</v>
+        <v>44.12</v>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="G41">
-        <v>27.27</v>
+        <v>36.36</v>
       </c>
       <c r="H41">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I41">
-        <v>100.0</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="42">
@@ -1555,10 +1555,10 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C42">
-        <v>43.85</v>
+        <v>43.44</v>
       </c>
       <c r="D42">
         <v>4</v>
@@ -1567,7 +1567,7 @@
         <v>1</v>
       </c>
       <c r="F42">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G42">
         <v>36.36</v>
@@ -1576,7 +1576,7 @@
         <v>20.0</v>
       </c>
       <c r="I42">
-        <v>20.93</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="43">
@@ -1584,10 +1584,10 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="C43">
-        <v>43.85</v>
+        <v>42.41</v>
       </c>
       <c r="D43">
         <v>4</v>
@@ -1596,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="F43">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G43">
         <v>36.36</v>
@@ -1605,7 +1605,7 @@
         <v>20.0</v>
       </c>
       <c r="I43">
-        <v>20.93</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="44">
@@ -1613,10 +1613,10 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C44">
-        <v>42.1</v>
+        <v>41.73</v>
       </c>
       <c r="D44">
         <v>4</v>
@@ -1625,7 +1625,7 @@
         <v>1</v>
       </c>
       <c r="F44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G44">
         <v>36.36</v>
@@ -1634,7 +1634,7 @@
         <v>20.0</v>
       </c>
       <c r="I44">
-        <v>9.3</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="45">
@@ -1642,28 +1642,28 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C45">
-        <v>41.41</v>
+        <v>40.82</v>
       </c>
       <c r="D45">
         <v>4</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G45">
         <v>36.36</v>
       </c>
       <c r="H45">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I45">
-        <v>4.65</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="46">
@@ -1674,7 +1674,7 @@
         <v>5</v>
       </c>
       <c r="C46">
-        <v>35.7</v>
+        <v>36.04</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -1683,7 +1683,7 @@
         <v>2</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46">
         <v>18.18</v>
@@ -1692,7 +1692,7 @@
         <v>40.0</v>
       </c>
       <c r="I46">
-        <v>2.33</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="47">
@@ -1703,7 +1703,7 @@
         <v>42</v>
       </c>
       <c r="C47">
-        <v>33.73</v>
+        <v>33.88</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -1712,7 +1712,7 @@
         <v>0</v>
       </c>
       <c r="F47">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G47">
         <v>18.18</v>
@@ -1721,7 +1721,7 @@
         <v>0.0</v>
       </c>
       <c r="I47">
-        <v>55.81</v>
+        <v>56.82</v>
       </c>
     </row>
     <row r="48">
@@ -1732,7 +1732,7 @@
         <v>31</v>
       </c>
       <c r="C48">
-        <v>31.4</v>
+        <v>31.72</v>
       </c>
       <c r="D48">
         <v>2</v>
@@ -1741,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G48">
         <v>18.18</v>
@@ -1750,7 +1750,7 @@
         <v>20.0</v>
       </c>
       <c r="I48">
-        <v>6.98</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="49">
@@ -1761,7 +1761,7 @@
         <v>41</v>
       </c>
       <c r="C49">
-        <v>30.59</v>
+        <v>30.81</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -1770,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="F49">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G49">
         <v>18.18</v>
@@ -1779,7 +1779,7 @@
         <v>0.0</v>
       </c>
       <c r="I49">
-        <v>34.88</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="50">
@@ -1790,7 +1790,7 @@
         <v>38</v>
       </c>
       <c r="C50">
-        <v>30.35</v>
+        <v>30.69</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -1799,7 +1799,7 @@
         <v>1</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50">
         <v>18.18</v>
@@ -1808,7 +1808,7 @@
         <v>20.0</v>
       </c>
       <c r="I50">
-        <v>0.0</v>
+        <v>2.27</v>
       </c>
     </row>
   </sheetData>
@@ -1867,762 +1867,762 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000092</v>
+        <v>115000093</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="I2">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000091</v>
+        <v>115000092</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
         <v>13</v>
       </c>
-      <c r="E3">
-        <v>24</v>
-      </c>
-      <c r="F3">
-        <v>25</v>
-      </c>
       <c r="G3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H3">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I3">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000090</v>
+        <v>115000091</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C4">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E4">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H4">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000089</v>
+        <v>115000090</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H5">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="I5">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000088</v>
+        <v>115000089</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F6">
         <v>21</v>
       </c>
       <c r="G6">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H6">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000087</v>
+        <v>115000088</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C7">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G7">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H7">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I7">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000086</v>
+        <v>115000087</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D8">
         <v>15</v>
       </c>
       <c r="E8">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F8">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G8">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H8">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I8">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000085</v>
+        <v>115000086</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C9">
         <v>3</v>
       </c>
       <c r="D9">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E9">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F9">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G9">
+        <v>47</v>
+      </c>
+      <c r="H9">
+        <v>49</v>
+      </c>
+      <c r="I9">
         <v>27</v>
-      </c>
-      <c r="H9">
-        <v>37</v>
-      </c>
-      <c r="I9">
-        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000084</v>
+        <v>115000085</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C10">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D10">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E10">
+        <v>17</v>
+      </c>
+      <c r="F10">
+        <v>18</v>
+      </c>
+      <c r="G10">
+        <v>27</v>
+      </c>
+      <c r="H10">
+        <v>37</v>
+      </c>
+      <c r="I10">
         <v>19</v>
-      </c>
-      <c r="F10">
-        <v>26</v>
-      </c>
-      <c r="G10">
-        <v>29</v>
-      </c>
-      <c r="H10">
-        <v>48</v>
-      </c>
-      <c r="I10">
-        <v>30</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000083</v>
+        <v>115000084</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E11">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F11">
         <v>26</v>
       </c>
       <c r="G11">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H11">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I11">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C12">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D12">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E12">
+        <v>23</v>
+      </c>
+      <c r="F12">
         <v>26</v>
       </c>
-      <c r="F12">
-        <v>32</v>
-      </c>
       <c r="G12">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H12">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I12">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C13">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D13">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E13">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F13">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G13">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H13">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I13">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D14">
         <v>14</v>
       </c>
       <c r="E14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G14">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H14">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I14">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E15">
         <v>25</v>
       </c>
       <c r="F15">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G15">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H15">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I15">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C16">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D16">
         <v>12</v>
       </c>
       <c r="E16">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F16">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G16">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H16">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="I16">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D17">
         <v>12</v>
       </c>
       <c r="E17">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F17">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G17">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H17">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I17">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E18">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F18">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G18">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H18">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I18">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C19">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D19">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E19">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F19">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G19">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H19">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I19">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C20">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D20">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E20">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F20">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G20">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H20">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I20">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C21">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D21">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E21">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F21">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G21">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H21">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I21">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E22">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F22">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G22">
         <v>35</v>
       </c>
       <c r="H22">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I22">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E23">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F23">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G23">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H23">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I23">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C24">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E24">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F24">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G24">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H24">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I24">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C25">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D25">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E25">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F25">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G25">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H25">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I25">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C26">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D26">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E26">
         <v>15</v>
@@ -2631,345 +2631,345 @@
         <v>18</v>
       </c>
       <c r="G26">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H26">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I26">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C27">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D27">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E27">
+        <v>15</v>
+      </c>
+      <c r="F27">
+        <v>18</v>
+      </c>
+      <c r="G27">
         <v>19</v>
       </c>
-      <c r="F27">
-        <v>23</v>
-      </c>
-      <c r="G27">
-        <v>39</v>
-      </c>
       <c r="H27">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I27">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C28">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D28">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E28">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F28">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G28">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H28">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I28">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C29">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D29">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E29">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F29">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G29">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H29">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I29">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C30">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D30">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E30">
+        <v>23</v>
+      </c>
+      <c r="F30">
+        <v>24</v>
+      </c>
+      <c r="G30">
         <v>29</v>
       </c>
-      <c r="F30">
-        <v>33</v>
-      </c>
-      <c r="G30">
-        <v>34</v>
-      </c>
       <c r="H30">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I30">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C31">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D31">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E31">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F31">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G31">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H31">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I31">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E32">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F32">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G32">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H32">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I32">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C33">
         <v>1</v>
       </c>
       <c r="D33">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E33">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F33">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G33">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H33">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I33">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C34">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D34">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E34">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F34">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G34">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H34">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I34">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C35">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D35">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E35">
         <v>25</v>
       </c>
       <c r="F35">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G35">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H35">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I35">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C36">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D36">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E36">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F36">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G36">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H36">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I36">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C37">
+        <v>8</v>
+      </c>
+      <c r="D37">
+        <v>9</v>
+      </c>
+      <c r="E37">
+        <v>16</v>
+      </c>
+      <c r="F37">
         <v>20</v>
-      </c>
-      <c r="D37">
-        <v>26</v>
-      </c>
-      <c r="E37">
-        <v>29</v>
-      </c>
-      <c r="F37">
-        <v>31</v>
       </c>
       <c r="G37">
         <v>37</v>
@@ -2978,441 +2978,441 @@
         <v>49</v>
       </c>
       <c r="I37">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C38">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D38">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E38">
         <v>29</v>
       </c>
       <c r="F38">
+        <v>31</v>
+      </c>
+      <c r="G38">
         <v>37</v>
       </c>
-      <c r="G38">
-        <v>47</v>
-      </c>
       <c r="H38">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I38">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C39">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D39">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E39">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F39">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G39">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="H39">
         <v>48</v>
       </c>
       <c r="I39">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C40">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D40">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E40">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F40">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G40">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H40">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I40">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C41">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D41">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E41">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F41">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G41">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H41">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I41">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C42">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D42">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E42">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F42">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G42">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H42">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I42">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C43">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D43">
+        <v>12</v>
+      </c>
+      <c r="E43">
         <v>18</v>
       </c>
-      <c r="E43">
-        <v>25</v>
-      </c>
       <c r="F43">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G43">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H43">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I43">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C44">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D44">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E44">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F44">
         <v>28</v>
       </c>
       <c r="G44">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H44">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I44">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D45">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E45">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F45">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G45">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H45">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I45">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C46">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D46">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E46">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F46">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G46">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H46">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I46">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C47">
+        <v>6</v>
+      </c>
+      <c r="D47">
+        <v>10</v>
+      </c>
+      <c r="E47">
+        <v>14</v>
+      </c>
+      <c r="F47">
+        <v>25</v>
+      </c>
+      <c r="G47">
+        <v>26</v>
+      </c>
+      <c r="H47">
+        <v>32</v>
+      </c>
+      <c r="I47">
         <v>7</v>
-      </c>
-      <c r="D47">
-        <v>14</v>
-      </c>
-      <c r="E47">
-        <v>16</v>
-      </c>
-      <c r="F47">
-        <v>37</v>
-      </c>
-      <c r="G47">
-        <v>39</v>
-      </c>
-      <c r="H47">
-        <v>47</v>
-      </c>
-      <c r="I47">
-        <v>34</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D48">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E48">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F48">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G48">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H48">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I48">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C49">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D49">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E49">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F49">
+        <v>19</v>
+      </c>
+      <c r="G49">
+        <v>20</v>
+      </c>
+      <c r="H49">
+        <v>40</v>
+      </c>
+      <c r="I49">
         <v>22</v>
-      </c>
-      <c r="G49">
-        <v>40</v>
-      </c>
-      <c r="H49">
-        <v>45</v>
-      </c>
-      <c r="I49">
-        <v>18</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C50">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D50">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E50">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F50">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G50">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H50">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I50">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C51">
         <v>4</v>
       </c>
       <c r="D51">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E51">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F51">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G51">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H51">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I51">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-10-02 第 115000093 期；威力彩 2026-10-01 第 115000079 期</t>
+          <t>大樂透 2026-10-02 第 115000093 期；威力彩 2026-10-05 第 115000080 期</t>
         </is>
       </c>
     </row>
@@ -112,7 +112,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -121,7 +121,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -143,7 +143,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8, 19, 24, 29, 35, 38</t>
+          <t>8, 17, 19, 24, 29, 35</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -161,7 +161,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.166 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.119 碼/期</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>0.952</v>
+        <v>0.929</v>
       </c>
       <c r="D2">
         <v>28.6</v>
@@ -3486,7 +3486,7 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>0.952</v>
+        <v>0.929</v>
       </c>
       <c r="D3">
         <v>28.6</v>
@@ -3508,10 +3508,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>0.929</v>
+        <v>0.905</v>
       </c>
       <c r="D4">
-        <v>26.2</v>
+        <v>23.8</v>
       </c>
       <c r="E4">
         <v>2.4</v>
@@ -3545,45 +3545,45 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>均衡分散</t>
+          <t>隨機基準</t>
         </is>
       </c>
       <c r="B6">
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.786</v>
+        <v>0.81</v>
       </c>
       <c r="D6">
-        <v>14.3</v>
+        <v>19.0</v>
       </c>
       <c r="E6">
-        <v>2.4</v>
+        <v>0.0</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>隨機基準</t>
+          <t>均衡分散</t>
         </is>
       </c>
       <c r="B7">
         <v>42</v>
       </c>
       <c r="C7">
-        <v>0.786</v>
+        <v>0.762</v>
       </c>
       <c r="D7">
-        <v>19.0</v>
+        <v>14.3</v>
       </c>
       <c r="E7">
-        <v>0.0</v>
+        <v>2.4</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -3645,28 +3645,28 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C2">
-        <v>77.68</v>
+        <v>74.83</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>71.43</v>
+        <v>100.0</v>
       </c>
       <c r="H2">
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>35.0</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="3">
@@ -3674,28 +3674,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>74.15</v>
+        <v>73.14</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G3">
-        <v>100.0</v>
+        <v>71.43</v>
       </c>
       <c r="H3">
-        <v>100.0</v>
+        <v>80.0</v>
       </c>
       <c r="I3">
-        <v>5.0</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="4">
@@ -3703,28 +3703,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C4">
-        <v>73.91</v>
+        <v>72.67</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>85.71</v>
+        <v>78.57</v>
       </c>
       <c r="H4">
-        <v>80.0</v>
+        <v>100.0</v>
       </c>
       <c r="I4">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="5">
@@ -3732,28 +3732,28 @@
         <v>4</v>
       </c>
       <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>72.19</v>
+      </c>
+      <c r="D5">
         <v>9</v>
       </c>
-      <c r="C5">
-        <v>69.93</v>
-      </c>
-      <c r="D5">
-        <v>10</v>
-      </c>
       <c r="E5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>71.43</v>
+        <v>64.29</v>
       </c>
       <c r="H5">
-        <v>60.0</v>
+        <v>100.0</v>
       </c>
       <c r="I5">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
@@ -3761,28 +3761,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>69.69</v>
+        <v>70.29</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>64.29</v>
+        <v>71.43</v>
       </c>
       <c r="H6">
         <v>60.0</v>
       </c>
       <c r="I6">
-        <v>50.0</v>
+        <v>52.38</v>
       </c>
     </row>
     <row r="7">
@@ -3793,7 +3793,7 @@
         <v>8</v>
       </c>
       <c r="C7">
-        <v>69.17</v>
+        <v>69.81</v>
       </c>
       <c r="D7">
         <v>11</v>
@@ -3802,7 +3802,7 @@
         <v>4</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7">
         <v>78.57</v>
@@ -3811,7 +3811,7 @@
         <v>80.0</v>
       </c>
       <c r="I7">
-        <v>10.0</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="8">
@@ -3819,28 +3819,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C8">
-        <v>68.18</v>
+        <v>69.8</v>
       </c>
       <c r="D8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>71.43</v>
+        <v>57.14</v>
       </c>
       <c r="H8">
-        <v>80.0</v>
+        <v>60.0</v>
       </c>
       <c r="I8">
-        <v>5.0</v>
+        <v>52.38</v>
       </c>
     </row>
     <row r="9">
@@ -3848,28 +3848,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C9">
-        <v>68.16</v>
+        <v>69.1</v>
       </c>
       <c r="D9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>85.71</v>
+        <v>78.57</v>
       </c>
       <c r="H9">
         <v>60.0</v>
       </c>
       <c r="I9">
-        <v>35.0</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="10">
@@ -3877,28 +3877,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="C10">
-        <v>67.19</v>
+        <v>68.63</v>
       </c>
       <c r="D10">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G10">
-        <v>64.29</v>
+        <v>85.71</v>
       </c>
       <c r="H10">
-        <v>80.0</v>
+        <v>60.0</v>
       </c>
       <c r="I10">
-        <v>0.0</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="11">
@@ -3906,25 +3906,25 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="C11">
-        <v>66.94</v>
+        <v>68.3</v>
       </c>
       <c r="D11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>57.14</v>
+        <v>50.0</v>
       </c>
       <c r="H11">
-        <v>80.0</v>
+        <v>100.0</v>
       </c>
       <c r="I11">
         <v>0.0</v>
@@ -3935,28 +3935,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C12">
-        <v>63.19</v>
+        <v>66.94</v>
       </c>
       <c r="D12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F12">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>64.29</v>
+        <v>57.14</v>
       </c>
       <c r="H12">
-        <v>40.0</v>
+        <v>80.0</v>
       </c>
       <c r="I12">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="13">
@@ -3967,7 +3967,7 @@
         <v>33</v>
       </c>
       <c r="C13">
-        <v>62.43</v>
+        <v>63.14</v>
       </c>
       <c r="D13">
         <v>10</v>
@@ -3976,7 +3976,7 @@
         <v>3</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13">
         <v>71.43</v>
@@ -3985,7 +3985,7 @@
         <v>60.0</v>
       </c>
       <c r="I13">
-        <v>0.0</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="14">
@@ -3993,28 +3993,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="C14">
-        <v>62.17</v>
+        <v>62.9</v>
       </c>
       <c r="D14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G14">
-        <v>78.57</v>
+        <v>64.29</v>
       </c>
       <c r="H14">
-        <v>40.0</v>
+        <v>60.0</v>
       </c>
       <c r="I14">
-        <v>30.0</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="15">
@@ -4022,28 +4022,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C15">
-        <v>62.05</v>
+        <v>62.67</v>
       </c>
       <c r="D15">
+        <v>11</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15">
         <v>7</v>
       </c>
-      <c r="E15">
-        <v>3</v>
-      </c>
-      <c r="F15">
-        <v>5</v>
-      </c>
       <c r="G15">
-        <v>50.0</v>
+        <v>78.57</v>
       </c>
       <c r="H15">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="I15">
-        <v>25.0</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="16">
@@ -4051,28 +4051,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C16">
-        <v>60.69</v>
+        <v>62.59</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16">
-        <v>57.14</v>
+        <v>50.0</v>
       </c>
       <c r="H16">
-        <v>40.0</v>
+        <v>60.0</v>
       </c>
       <c r="I16">
-        <v>25.0</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="17">
@@ -4080,28 +4080,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C17">
-        <v>60.16</v>
+        <v>62.43</v>
       </c>
       <c r="D17">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>85.71</v>
+        <v>71.43</v>
       </c>
       <c r="H17">
-        <v>40.0</v>
+        <v>60.0</v>
       </c>
       <c r="I17">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="18">
@@ -4109,28 +4109,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C18">
-        <v>60.01</v>
+        <v>61.23</v>
       </c>
       <c r="D18">
+        <v>8</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18">
         <v>6</v>
       </c>
-      <c r="E18">
-        <v>4</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
       <c r="G18">
-        <v>42.86</v>
+        <v>57.14</v>
       </c>
       <c r="H18">
-        <v>80.0</v>
+        <v>40.0</v>
       </c>
       <c r="I18">
-        <v>5.0</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="19">
@@ -4138,13 +4138,13 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19">
-        <v>59.94</v>
+        <v>60.53</v>
       </c>
       <c r="D19">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -4153,13 +4153,13 @@
         <v>4</v>
       </c>
       <c r="G19">
-        <v>57.14</v>
+        <v>78.57</v>
       </c>
       <c r="H19">
         <v>40.0</v>
       </c>
       <c r="I19">
-        <v>20.0</v>
+        <v>19.05</v>
       </c>
     </row>
     <row r="20">
@@ -4167,28 +4167,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C20">
-        <v>59.69</v>
+        <v>60.51</v>
       </c>
       <c r="D20">
         <v>8</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G20">
         <v>57.14</v>
       </c>
       <c r="H20">
-        <v>0.0</v>
+        <v>40.0</v>
       </c>
       <c r="I20">
-        <v>85.0</v>
+        <v>23.81</v>
       </c>
     </row>
     <row r="21">
@@ -4196,28 +4196,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="C21">
-        <v>59.26</v>
+        <v>59.8</v>
       </c>
       <c r="D21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G21">
-        <v>42.86</v>
+        <v>57.14</v>
       </c>
       <c r="H21">
-        <v>80.0</v>
+        <v>0.0</v>
       </c>
       <c r="I21">
-        <v>0.0</v>
+        <v>85.71</v>
       </c>
     </row>
     <row r="22">
@@ -4228,7 +4228,7 @@
         <v>31</v>
       </c>
       <c r="C22">
-        <v>58.93</v>
+        <v>59.57</v>
       </c>
       <c r="D22">
         <v>10</v>
@@ -4237,7 +4237,7 @@
         <v>2</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22">
         <v>71.43</v>
@@ -4246,7 +4246,7 @@
         <v>40.0</v>
       </c>
       <c r="I22">
-        <v>10.0</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="23">
@@ -4257,7 +4257,7 @@
         <v>25</v>
       </c>
       <c r="C23">
-        <v>58.44</v>
+        <v>59.09</v>
       </c>
       <c r="D23">
         <v>8</v>
@@ -4266,7 +4266,7 @@
         <v>2</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23">
         <v>57.14</v>
@@ -4275,7 +4275,7 @@
         <v>40.0</v>
       </c>
       <c r="I23">
-        <v>10.0</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="24">
@@ -4283,28 +4283,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C24">
-        <v>58.3</v>
+        <v>57.66</v>
       </c>
       <c r="D24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G24">
-        <v>50.0</v>
+        <v>57.14</v>
       </c>
       <c r="H24">
-        <v>60.0</v>
+        <v>20.0</v>
       </c>
       <c r="I24">
-        <v>0.0</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="25">
@@ -4312,28 +4312,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>57.19</v>
+        <v>55.69</v>
       </c>
       <c r="D25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F25">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G25">
-        <v>57.14</v>
+        <v>42.86</v>
       </c>
       <c r="H25">
-        <v>20.0</v>
+        <v>60.0</v>
       </c>
       <c r="I25">
-        <v>35.0</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="26">
@@ -4341,28 +4341,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C26">
-        <v>57.05</v>
+        <v>55.51</v>
       </c>
       <c r="D26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26">
         <v>5</v>
       </c>
       <c r="G26">
-        <v>50.0</v>
+        <v>57.14</v>
       </c>
       <c r="H26">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I26">
-        <v>25.0</v>
+        <v>23.81</v>
       </c>
     </row>
     <row r="27">
@@ -4370,28 +4370,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C27">
-        <v>56.8</v>
+        <v>54.26</v>
       </c>
       <c r="D27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
       <c r="F27">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G27">
-        <v>50.0</v>
+        <v>42.86</v>
       </c>
       <c r="H27">
         <v>0.0</v>
       </c>
       <c r="I27">
-        <v>90.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="28">
@@ -4399,28 +4399,28 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C28">
-        <v>55.76</v>
+        <v>51.94</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>42.86</v>
+        <v>57.14</v>
       </c>
       <c r="H28">
-        <v>60.0</v>
+        <v>20.0</v>
       </c>
       <c r="I28">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="29">
@@ -4428,28 +4428,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C29">
-        <v>54.94</v>
+        <v>51.4</v>
       </c>
       <c r="D29">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29">
-        <v>57.14</v>
+        <v>42.86</v>
       </c>
       <c r="H29">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I29">
-        <v>20.0</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="30">
@@ -4457,28 +4457,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C30">
-        <v>54.26</v>
+        <v>50.93</v>
       </c>
       <c r="D30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F30">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G30">
-        <v>42.86</v>
+        <v>35.71</v>
       </c>
       <c r="H30">
-        <v>0.0</v>
+        <v>60.0</v>
       </c>
       <c r="I30">
-        <v>100.0</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="31">
@@ -4486,28 +4486,28 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C31">
-        <v>50.76</v>
+        <v>49.73</v>
       </c>
       <c r="D31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31">
         <v>2</v>
       </c>
       <c r="G31">
-        <v>42.86</v>
+        <v>50.0</v>
       </c>
       <c r="H31">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I31">
-        <v>10.0</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="32">
@@ -4515,28 +4515,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C32">
-        <v>50.21</v>
+        <v>49.5</v>
       </c>
       <c r="D32">
         <v>5</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G32">
         <v>35.71</v>
       </c>
       <c r="H32">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="I32">
-        <v>0.0</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="33">
@@ -4544,28 +4544,28 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="C33">
-        <v>49.05</v>
+        <v>48.54</v>
       </c>
       <c r="D33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G33">
-        <v>50.0</v>
+        <v>42.86</v>
       </c>
       <c r="H33">
         <v>20.0</v>
       </c>
       <c r="I33">
-        <v>5.0</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="34">
@@ -4573,10 +4573,10 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C34">
-        <v>48.96</v>
+        <v>47.36</v>
       </c>
       <c r="D34">
         <v>5</v>
@@ -4585,7 +4585,7 @@
         <v>2</v>
       </c>
       <c r="F34">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G34">
         <v>35.71</v>
@@ -4594,7 +4594,7 @@
         <v>40.0</v>
       </c>
       <c r="I34">
-        <v>25.0</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="35">
@@ -4605,7 +4605,7 @@
         <v>27</v>
       </c>
       <c r="C35">
-        <v>46.71</v>
+        <v>47.36</v>
       </c>
       <c r="D35">
         <v>5</v>
@@ -4614,7 +4614,7 @@
         <v>2</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G35">
         <v>35.71</v>
@@ -4623,7 +4623,7 @@
         <v>40.0</v>
       </c>
       <c r="I35">
-        <v>10.0</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="36">
@@ -4631,28 +4631,28 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C36">
-        <v>43.96</v>
+        <v>43.31</v>
       </c>
       <c r="D36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E36">
         <v>1</v>
       </c>
       <c r="F36">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G36">
-        <v>35.71</v>
+        <v>28.57</v>
       </c>
       <c r="H36">
         <v>20.0</v>
       </c>
       <c r="I36">
-        <v>25.0</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="37">
@@ -4660,28 +4660,28 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C37">
-        <v>42.92</v>
+        <v>42.13</v>
       </c>
       <c r="D37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E37">
         <v>1</v>
       </c>
       <c r="F37">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G37">
-        <v>28.57</v>
+        <v>21.43</v>
       </c>
       <c r="H37">
         <v>20.0</v>
       </c>
       <c r="I37">
-        <v>45.0</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="38">
@@ -4689,28 +4689,28 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C38">
-        <v>41.88</v>
+        <v>40.46</v>
       </c>
       <c r="D38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
       <c r="F38">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G38">
-        <v>21.43</v>
+        <v>28.57</v>
       </c>
       <c r="H38">
         <v>20.0</v>
       </c>
       <c r="I38">
-        <v>65.0</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="39">
@@ -4721,7 +4721,7 @@
         <v>20</v>
       </c>
       <c r="C39">
-        <v>39.13</v>
+        <v>39.27</v>
       </c>
       <c r="D39">
         <v>3</v>
@@ -4730,7 +4730,7 @@
         <v>0</v>
       </c>
       <c r="F39">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G39">
         <v>21.43</v>
@@ -4739,7 +4739,7 @@
         <v>0.0</v>
       </c>
       <c r="I39">
-        <v>80.0</v>
+        <v>80.95</v>
       </c>
     </row>
   </sheetData>
@@ -4798,92 +4798,92 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2">
+        <v>21</v>
+      </c>
+      <c r="G2">
         <v>26</v>
-      </c>
-      <c r="G2">
-        <v>33</v>
       </c>
       <c r="H2">
         <v>37</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H3">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H4">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -4891,11 +4891,11 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C5">
@@ -4905,140 +4905,140 @@
         <v>8</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G5">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H5">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E6">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H6">
         <v>37</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D7">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F7">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>12</v>
+      </c>
+      <c r="E8">
+        <v>14</v>
+      </c>
+      <c r="F8">
+        <v>16</v>
+      </c>
+      <c r="G8">
+        <v>29</v>
+      </c>
+      <c r="H8">
+        <v>36</v>
+      </c>
+      <c r="I8">
         <v>8</v>
-      </c>
-      <c r="D8">
-        <v>17</v>
-      </c>
-      <c r="E8">
-        <v>18</v>
-      </c>
-      <c r="F8">
-        <v>29</v>
-      </c>
-      <c r="G8">
-        <v>33</v>
-      </c>
-      <c r="H8">
-        <v>38</v>
-      </c>
-      <c r="I8">
-        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E9">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F9">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G9">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H9">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -5046,108 +5046,108 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D10">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E10">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F10">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H10">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I10">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E11">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F11">
         <v>19</v>
       </c>
       <c r="G11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H11">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I11">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F12">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G12">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H12">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C13">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D13">
         <v>7</v>
@@ -5156,230 +5156,230 @@
         <v>9</v>
       </c>
       <c r="F13">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H13">
         <v>36</v>
       </c>
       <c r="I13">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E14">
         <v>9</v>
       </c>
       <c r="F14">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G14">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I14">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15">
+        <v>9</v>
+      </c>
+      <c r="F15">
         <v>11</v>
       </c>
-      <c r="E15">
-        <v>18</v>
-      </c>
-      <c r="F15">
-        <v>19</v>
-      </c>
       <c r="G15">
+        <v>29</v>
+      </c>
+      <c r="H15">
         <v>35</v>
       </c>
-      <c r="H15">
-        <v>38</v>
-      </c>
       <c r="I15">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F16">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G16">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H16">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="I16">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C17">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E17">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F17">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G17">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H17">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I17">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E18">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F18">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G18">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H18">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I18">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>7</v>
+      </c>
+      <c r="E19">
+        <v>8</v>
+      </c>
+      <c r="F19">
+        <v>20</v>
+      </c>
+      <c r="G19">
+        <v>26</v>
+      </c>
+      <c r="H19">
+        <v>33</v>
+      </c>
+      <c r="I19">
         <v>4</v>
-      </c>
-      <c r="D19">
-        <v>15</v>
-      </c>
-      <c r="E19">
-        <v>22</v>
-      </c>
-      <c r="F19">
-        <v>26</v>
-      </c>
-      <c r="G19">
-        <v>34</v>
-      </c>
-      <c r="H19">
-        <v>36</v>
-      </c>
-      <c r="I19">
-        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C20">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D20">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E20">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F20">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G20">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H20">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I20">
         <v>7</v>
@@ -5387,30 +5387,30 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C21">
+        <v>8</v>
+      </c>
+      <c r="D21">
+        <v>14</v>
+      </c>
+      <c r="E21">
+        <v>17</v>
+      </c>
+      <c r="F21">
         <v>19</v>
       </c>
-      <c r="D21">
-        <v>22</v>
-      </c>
-      <c r="E21">
-        <v>28</v>
-      </c>
-      <c r="F21">
-        <v>31</v>
-      </c>
       <c r="G21">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H21">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I21">
         <v>7</v>
@@ -5418,30 +5418,30 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C22">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D22">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E22">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F22">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G22">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H22">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I22">
         <v>7</v>
@@ -5449,24 +5449,24 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D23">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E23">
         <v>13</v>
       </c>
       <c r="F23">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G23">
         <v>29</v>
@@ -5475,97 +5475,97 @@
         <v>31</v>
       </c>
       <c r="I23">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C24">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D24">
+        <v>12</v>
+      </c>
+      <c r="E24">
+        <v>13</v>
+      </c>
+      <c r="F24">
         <v>23</v>
       </c>
-      <c r="E24">
-        <v>25</v>
-      </c>
-      <c r="F24">
+      <c r="G24">
         <v>29</v>
       </c>
-      <c r="G24">
-        <v>34</v>
-      </c>
       <c r="H24">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I24">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C25">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D25">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E25">
+        <v>25</v>
+      </c>
+      <c r="F25">
         <v>29</v>
       </c>
-      <c r="F25">
-        <v>32</v>
-      </c>
       <c r="G25">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H25">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I25">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C26">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D26">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E26">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F26">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G26">
         <v>35</v>
       </c>
       <c r="H26">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I26">
         <v>6</v>
@@ -5573,402 +5573,402 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D27">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E27">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F27">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G27">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H27">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D28">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E28">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F28">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G28">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H28">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I28">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C29">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E29">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F29">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G29">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H29">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I29">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C30">
+        <v>5</v>
+      </c>
+      <c r="D30">
         <v>6</v>
       </c>
-      <c r="D30">
-        <v>10</v>
-      </c>
       <c r="E30">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F30">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G30">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H30">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C31">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D31">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E31">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F31">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G31">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H31">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I31">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D32">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E32">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F32">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G32">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H32">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I32">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33">
+        <v>8</v>
+      </c>
+      <c r="E33">
+        <v>9</v>
+      </c>
+      <c r="F33">
+        <v>15</v>
+      </c>
+      <c r="G33">
+        <v>18</v>
+      </c>
+      <c r="H33">
+        <v>23</v>
+      </c>
+      <c r="I33">
         <v>4</v>
-      </c>
-      <c r="D33">
-        <v>17</v>
-      </c>
-      <c r="E33">
-        <v>19</v>
-      </c>
-      <c r="F33">
-        <v>25</v>
-      </c>
-      <c r="G33">
-        <v>28</v>
-      </c>
-      <c r="H33">
-        <v>29</v>
-      </c>
-      <c r="I33">
-        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D34">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E34">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F34">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G34">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H34">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I34">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D35">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E35">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F35">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G35">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H35">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I35">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C36">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D36">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E36">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F36">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G36">
         <v>28</v>
       </c>
       <c r="H36">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I36">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C37">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D37">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E37">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F37">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H37">
         <v>35</v>
       </c>
       <c r="I37">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E38">
+        <v>9</v>
+      </c>
+      <c r="F38">
+        <v>15</v>
+      </c>
+      <c r="G38">
         <v>24</v>
       </c>
-      <c r="F38">
-        <v>31</v>
-      </c>
-      <c r="G38">
-        <v>34</v>
-      </c>
       <c r="H38">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I38">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C39">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D39">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E39">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F39">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G39">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H39">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I39">
         <v>3</v>
@@ -5976,374 +5976,374 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C40">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D40">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E40">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F40">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G40">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H40">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I40">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C41">
         <v>6</v>
       </c>
       <c r="D41">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E41">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F41">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G41">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H41">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I41">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C42">
         <v>6</v>
       </c>
       <c r="D42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E42">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F42">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G42">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H42">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I42">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C43">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D43">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E43">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F43">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G43">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H43">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I43">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C44">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D44">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E44">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F44">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G44">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H44">
         <v>38</v>
       </c>
       <c r="I44">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C45">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D45">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E45">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F45">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G45">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H45">
         <v>38</v>
       </c>
       <c r="I45">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D46">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E46">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F46">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G46">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H46">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I46">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C47">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D47">
+        <v>4</v>
+      </c>
+      <c r="E47">
+        <v>13</v>
+      </c>
+      <c r="F47">
+        <v>19</v>
+      </c>
+      <c r="G47">
+        <v>27</v>
+      </c>
+      <c r="H47">
+        <v>30</v>
+      </c>
+      <c r="I47">
         <v>8</v>
-      </c>
-      <c r="E47">
-        <v>27</v>
-      </c>
-      <c r="F47">
-        <v>33</v>
-      </c>
-      <c r="G47">
-        <v>35</v>
-      </c>
-      <c r="H47">
-        <v>38</v>
-      </c>
-      <c r="I47">
-        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C48">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D48">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E48">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F48">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G48">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H48">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I48">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C49">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D49">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E49">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F49">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G49">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H49">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I49">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C50">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D50">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E50">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F50">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G50">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H50">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I50">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000030</v>
+        <v>115000031</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D51">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E51">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F51">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G51">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H51">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="I51">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-10-02 第 115000093 期；威力彩 2026-10-05 第 115000080 期</t>
+          <t>大樂透 2026-10-06 第 115000094 期；威力彩 2026-10-05 第 115000080 期</t>
         </is>
       </c>
     </row>
@@ -47,7 +47,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>115000093</v>
+        <v>115000094</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -56,7 +56,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -395,28 +395,28 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C2">
-        <v>73.8</v>
+        <v>73.38</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>90.91</v>
+        <v>100.0</v>
       </c>
       <c r="H2">
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>6.82</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="3">
@@ -424,28 +424,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C3">
-        <v>73.05</v>
+        <v>72.83</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3">
         <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>100.0</v>
+        <v>81.82</v>
       </c>
       <c r="H3">
         <v>100.0</v>
       </c>
       <c r="I3">
-        <v>0.0</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="4">
@@ -453,28 +453,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C4">
-        <v>72.5</v>
+        <v>69.11</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G4">
-        <v>81.82</v>
+        <v>90.91</v>
       </c>
       <c r="H4">
-        <v>100.0</v>
+        <v>80.0</v>
       </c>
       <c r="I4">
-        <v>0.0</v>
+        <v>8.89</v>
       </c>
     </row>
     <row r="5">
@@ -482,28 +482,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C5">
-        <v>65.1</v>
+        <v>63.83</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E5">
         <v>3</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>100.0</v>
+        <v>81.82</v>
       </c>
       <c r="H5">
         <v>60.0</v>
       </c>
       <c r="I5">
-        <v>13.64</v>
+        <v>8.89</v>
       </c>
     </row>
     <row r="6">
@@ -511,28 +511,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C6">
-        <v>63.52</v>
+        <v>63.55</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>81.82</v>
+        <v>72.73</v>
       </c>
       <c r="H6">
         <v>60.0</v>
       </c>
       <c r="I6">
-        <v>6.82</v>
+        <v>8.89</v>
       </c>
     </row>
     <row r="7">
@@ -540,28 +540,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C7">
-        <v>63.24</v>
+        <v>63.4</v>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>72.73</v>
+        <v>54.55</v>
       </c>
       <c r="H7">
         <v>60.0</v>
       </c>
       <c r="I7">
-        <v>6.82</v>
+        <v>15.56</v>
       </c>
     </row>
     <row r="8">
@@ -569,28 +569,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>63.18</v>
+        <v>63.06</v>
       </c>
       <c r="D8">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G8">
-        <v>81.82</v>
+        <v>54.55</v>
       </c>
       <c r="H8">
         <v>60.0</v>
       </c>
       <c r="I8">
-        <v>4.55</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="9">
@@ -598,28 +598,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>63.11</v>
+        <v>62.61</v>
       </c>
       <c r="D9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>54.55</v>
+        <v>63.64</v>
       </c>
       <c r="H9">
         <v>60.0</v>
       </c>
       <c r="I9">
-        <v>13.64</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="10">
@@ -627,28 +627,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>62.77</v>
+        <v>62.5</v>
       </c>
       <c r="D10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>54.55</v>
+        <v>81.82</v>
       </c>
       <c r="H10">
         <v>60.0</v>
       </c>
       <c r="I10">
-        <v>11.36</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="11">
@@ -656,28 +656,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C11">
-        <v>62.62</v>
+        <v>62.5</v>
       </c>
       <c r="D11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>63.64</v>
+        <v>81.82</v>
       </c>
       <c r="H11">
         <v>60.0</v>
       </c>
       <c r="I11">
-        <v>4.55</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="12">
@@ -685,10 +685,10 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="C12">
-        <v>62.28</v>
+        <v>62.27</v>
       </c>
       <c r="D12">
         <v>7</v>
@@ -706,7 +706,7 @@
         <v>60.0</v>
       </c>
       <c r="I12">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="13">
@@ -714,28 +714,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="C13">
-        <v>61.94</v>
+        <v>62.07</v>
       </c>
       <c r="D13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G13">
-        <v>63.64</v>
+        <v>54.55</v>
       </c>
       <c r="H13">
         <v>60.0</v>
       </c>
       <c r="I13">
-        <v>0.0</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="14">
@@ -746,7 +746,7 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>61.41</v>
+        <v>61.73</v>
       </c>
       <c r="D14">
         <v>6</v>
@@ -755,7 +755,7 @@
         <v>3</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14">
         <v>54.55</v>
@@ -764,7 +764,7 @@
         <v>60.0</v>
       </c>
       <c r="I14">
-        <v>2.27</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="15">
@@ -775,7 +775,7 @@
         <v>29</v>
       </c>
       <c r="C15">
-        <v>61.12</v>
+        <v>61.38</v>
       </c>
       <c r="D15">
         <v>11</v>
@@ -784,7 +784,7 @@
         <v>2</v>
       </c>
       <c r="F15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>100.0</v>
@@ -793,7 +793,7 @@
         <v>40.0</v>
       </c>
       <c r="I15">
-        <v>20.45</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="16">
@@ -801,28 +801,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C16">
-        <v>60.35</v>
+        <v>60.38</v>
       </c>
       <c r="D16">
+        <v>11</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16">
         <v>7</v>
       </c>
-      <c r="E16">
-        <v>2</v>
-      </c>
-      <c r="F16">
-        <v>10</v>
-      </c>
       <c r="G16">
-        <v>63.64</v>
+        <v>100.0</v>
       </c>
       <c r="H16">
         <v>40.0</v>
       </c>
       <c r="I16">
-        <v>22.73</v>
+        <v>15.56</v>
       </c>
     </row>
     <row r="17">
@@ -833,7 +833,7 @@
         <v>19</v>
       </c>
       <c r="C17">
-        <v>59.54</v>
+        <v>59.83</v>
       </c>
       <c r="D17">
         <v>9</v>
@@ -842,7 +842,7 @@
         <v>2</v>
       </c>
       <c r="F17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G17">
         <v>81.82</v>
@@ -851,7 +851,7 @@
         <v>40.0</v>
       </c>
       <c r="I17">
-        <v>13.64</v>
+        <v>15.56</v>
       </c>
     </row>
     <row r="18">
@@ -859,28 +859,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C18">
-        <v>58.99</v>
+        <v>59.73</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G18">
-        <v>63.64</v>
+        <v>54.55</v>
       </c>
       <c r="H18">
         <v>40.0</v>
       </c>
       <c r="I18">
-        <v>13.64</v>
+        <v>24.44</v>
       </c>
     </row>
     <row r="19">
@@ -888,28 +888,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C19">
-        <v>58.11</v>
+        <v>58.5</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G19">
-        <v>54.55</v>
+        <v>81.82</v>
       </c>
       <c r="H19">
         <v>40.0</v>
       </c>
       <c r="I19">
-        <v>13.64</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="20">
@@ -917,28 +917,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="C20">
-        <v>57.62</v>
+        <v>58.4</v>
       </c>
       <c r="D20">
+        <v>6</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20">
         <v>7</v>
       </c>
-      <c r="E20">
-        <v>2</v>
-      </c>
-      <c r="F20">
-        <v>2</v>
-      </c>
       <c r="G20">
-        <v>63.64</v>
+        <v>54.55</v>
       </c>
       <c r="H20">
         <v>40.0</v>
       </c>
       <c r="I20">
-        <v>4.55</v>
+        <v>15.56</v>
       </c>
     </row>
     <row r="21">
@@ -946,28 +946,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="C21">
-        <v>57.5</v>
+        <v>58.4</v>
       </c>
       <c r="D21">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E21">
         <v>2</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G21">
-        <v>81.82</v>
+        <v>54.55</v>
       </c>
       <c r="H21">
         <v>40.0</v>
       </c>
       <c r="I21">
-        <v>0.0</v>
+        <v>15.56</v>
       </c>
     </row>
     <row r="22">
@@ -975,28 +975,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C22">
-        <v>57.22</v>
+        <v>57.94</v>
       </c>
       <c r="D22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E22">
         <v>2</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G22">
-        <v>72.73</v>
+        <v>63.64</v>
       </c>
       <c r="H22">
         <v>40.0</v>
       </c>
       <c r="I22">
-        <v>0.0</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="23">
@@ -1004,28 +1004,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C23">
-        <v>56.03</v>
+        <v>56.94</v>
       </c>
       <c r="D23">
         <v>7</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G23">
         <v>63.64</v>
       </c>
       <c r="H23">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I23">
-        <v>27.27</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="24">
@@ -1033,28 +1033,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C24">
-        <v>55.84</v>
+        <v>56.94</v>
       </c>
       <c r="D24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>54.55</v>
+        <v>63.64</v>
       </c>
       <c r="H24">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I24">
-        <v>31.82</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="25">
@@ -1062,28 +1062,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C25">
-        <v>55.56</v>
+        <v>56.94</v>
       </c>
       <c r="D25">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>81.82</v>
+        <v>63.64</v>
       </c>
       <c r="H25">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I25">
-        <v>20.45</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -1091,28 +1091,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C26">
-        <v>54.47</v>
+        <v>56.06</v>
       </c>
       <c r="D26">
         <v>6</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G26">
         <v>54.55</v>
       </c>
       <c r="H26">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I26">
-        <v>22.73</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
@@ -1120,28 +1120,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C27">
-        <v>54.13</v>
+        <v>55.83</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G27">
-        <v>54.55</v>
+        <v>81.82</v>
       </c>
       <c r="H27">
         <v>20.0</v>
       </c>
       <c r="I27">
-        <v>20.45</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="28">
@@ -1149,10 +1149,10 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C28">
-        <v>53.79</v>
+        <v>55.4</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -1161,7 +1161,7 @@
         <v>1</v>
       </c>
       <c r="F28">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G28">
         <v>54.55</v>
@@ -1170,7 +1170,7 @@
         <v>20.0</v>
       </c>
       <c r="I28">
-        <v>18.18</v>
+        <v>28.89</v>
       </c>
     </row>
     <row r="29">
@@ -1178,10 +1178,10 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="C29">
-        <v>53.45</v>
+        <v>54.4</v>
       </c>
       <c r="D29">
         <v>6</v>
@@ -1190,7 +1190,7 @@
         <v>1</v>
       </c>
       <c r="F29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G29">
         <v>54.55</v>
@@ -1199,7 +1199,7 @@
         <v>20.0</v>
       </c>
       <c r="I29">
-        <v>15.91</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="30">
@@ -1207,10 +1207,10 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C30">
-        <v>52.77</v>
+        <v>54.06</v>
       </c>
       <c r="D30">
         <v>6</v>
@@ -1219,7 +1219,7 @@
         <v>1</v>
       </c>
       <c r="F30">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G30">
         <v>54.55</v>
@@ -1228,7 +1228,7 @@
         <v>20.0</v>
       </c>
       <c r="I30">
-        <v>11.36</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="31">
@@ -1236,10 +1236,10 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="C31">
-        <v>52.43</v>
+        <v>53.73</v>
       </c>
       <c r="D31">
         <v>6</v>
@@ -1248,7 +1248,7 @@
         <v>1</v>
       </c>
       <c r="F31">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G31">
         <v>54.55</v>
@@ -1257,7 +1257,7 @@
         <v>20.0</v>
       </c>
       <c r="I31">
-        <v>9.09</v>
+        <v>17.78</v>
       </c>
     </row>
     <row r="32">
@@ -1265,10 +1265,10 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C32">
-        <v>52.25</v>
+        <v>51.55</v>
       </c>
       <c r="D32">
         <v>5</v>
@@ -1277,7 +1277,7 @@
         <v>2</v>
       </c>
       <c r="F32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G32">
         <v>45.45</v>
@@ -1286,7 +1286,7 @@
         <v>40.0</v>
       </c>
       <c r="I32">
-        <v>9.09</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="33">
@@ -1294,10 +1294,10 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C33">
-        <v>51.57</v>
+        <v>51.55</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -1315,7 +1315,7 @@
         <v>40.0</v>
       </c>
       <c r="I33">
-        <v>4.55</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="34">
@@ -1323,10 +1323,10 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C34">
-        <v>51.23</v>
+        <v>51.22</v>
       </c>
       <c r="D34">
         <v>5</v>
@@ -1344,7 +1344,7 @@
         <v>40.0</v>
       </c>
       <c r="I34">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="35">
@@ -1352,28 +1352,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C35">
-        <v>51.23</v>
+        <v>51.06</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G35">
-        <v>45.45</v>
+        <v>54.55</v>
       </c>
       <c r="H35">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="I35">
-        <v>2.27</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="36">
@@ -1381,28 +1381,28 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="C36">
-        <v>50.88</v>
+        <v>47.37</v>
       </c>
       <c r="D36">
+        <v>4</v>
+      </c>
+      <c r="E36">
+        <v>2</v>
+      </c>
+      <c r="F36">
         <v>5</v>
       </c>
-      <c r="E36">
-        <v>2</v>
-      </c>
-      <c r="F36">
-        <v>0</v>
-      </c>
       <c r="G36">
-        <v>45.45</v>
+        <v>36.36</v>
       </c>
       <c r="H36">
         <v>40.0</v>
       </c>
       <c r="I36">
-        <v>0.0</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="37">
@@ -1410,28 +1410,28 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C37">
-        <v>49.63</v>
+        <v>47.22</v>
       </c>
       <c r="D37">
         <v>5</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G37">
         <v>45.45</v>
       </c>
       <c r="H37">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I37">
-        <v>25.0</v>
+        <v>42.22</v>
       </c>
     </row>
     <row r="38">
@@ -1439,28 +1439,28 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C38">
-        <v>47.02</v>
+        <v>46.89</v>
       </c>
       <c r="D38">
         <v>5</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="G38">
         <v>45.45</v>
       </c>
       <c r="H38">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I38">
-        <v>40.91</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="39">
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="F39">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G39">
         <v>27.27</v>
@@ -1500,7 +1500,7 @@
         <v>9</v>
       </c>
       <c r="C40">
-        <v>44.12</v>
+        <v>44.37</v>
       </c>
       <c r="D40">
         <v>4</v>
@@ -1509,7 +1509,7 @@
         <v>1</v>
       </c>
       <c r="F40">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G40">
         <v>36.36</v>
@@ -1518,7 +1518,7 @@
         <v>20.0</v>
       </c>
       <c r="I40">
-        <v>22.73</v>
+        <v>24.44</v>
       </c>
     </row>
     <row r="41">
@@ -1529,7 +1529,7 @@
         <v>44</v>
       </c>
       <c r="C41">
-        <v>44.12</v>
+        <v>44.37</v>
       </c>
       <c r="D41">
         <v>4</v>
@@ -1538,7 +1538,7 @@
         <v>1</v>
       </c>
       <c r="F41">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G41">
         <v>36.36</v>
@@ -1547,7 +1547,7 @@
         <v>20.0</v>
       </c>
       <c r="I41">
-        <v>22.73</v>
+        <v>24.44</v>
       </c>
     </row>
     <row r="42">
@@ -1558,7 +1558,7 @@
         <v>17</v>
       </c>
       <c r="C42">
-        <v>43.44</v>
+        <v>43.71</v>
       </c>
       <c r="D42">
         <v>4</v>
@@ -1567,7 +1567,7 @@
         <v>1</v>
       </c>
       <c r="F42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G42">
         <v>36.36</v>
@@ -1576,7 +1576,7 @@
         <v>20.0</v>
       </c>
       <c r="I42">
-        <v>18.18</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="43">
@@ -1587,7 +1587,7 @@
         <v>22</v>
       </c>
       <c r="C43">
-        <v>42.41</v>
+        <v>42.71</v>
       </c>
       <c r="D43">
         <v>4</v>
@@ -1596,7 +1596,7 @@
         <v>1</v>
       </c>
       <c r="F43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G43">
         <v>36.36</v>
@@ -1605,7 +1605,7 @@
         <v>20.0</v>
       </c>
       <c r="I43">
-        <v>11.36</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="44">
@@ -1616,7 +1616,7 @@
         <v>45</v>
       </c>
       <c r="C44">
-        <v>41.73</v>
+        <v>42.04</v>
       </c>
       <c r="D44">
         <v>4</v>
@@ -1625,7 +1625,7 @@
         <v>1</v>
       </c>
       <c r="F44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G44">
         <v>36.36</v>
@@ -1634,7 +1634,7 @@
         <v>20.0</v>
       </c>
       <c r="I44">
-        <v>6.82</v>
+        <v>8.89</v>
       </c>
     </row>
     <row r="45">
@@ -1645,7 +1645,7 @@
         <v>46</v>
       </c>
       <c r="C45">
-        <v>40.82</v>
+        <v>41.04</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -1654,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="F45">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G45">
         <v>36.36</v>
@@ -1663,7 +1663,7 @@
         <v>0.0</v>
       </c>
       <c r="I45">
-        <v>34.09</v>
+        <v>35.56</v>
       </c>
     </row>
     <row r="46">
@@ -1671,28 +1671,28 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="C46">
-        <v>36.04</v>
+        <v>34.02</v>
       </c>
       <c r="D46">
         <v>2</v>
       </c>
       <c r="E46">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F46">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="G46">
         <v>18.18</v>
       </c>
       <c r="H46">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="I46">
-        <v>4.55</v>
+        <v>57.78</v>
       </c>
     </row>
     <row r="47">
@@ -1700,28 +1700,28 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C47">
-        <v>33.88</v>
+        <v>32.02</v>
       </c>
       <c r="D47">
         <v>2</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G47">
         <v>18.18</v>
       </c>
       <c r="H47">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I47">
-        <v>56.82</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="48">
@@ -1729,10 +1729,10 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="C48">
-        <v>31.72</v>
+        <v>31.35</v>
       </c>
       <c r="D48">
         <v>2</v>
@@ -1741,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="F48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G48">
         <v>18.18</v>
@@ -1750,7 +1750,7 @@
         <v>20.0</v>
       </c>
       <c r="I48">
-        <v>9.09</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="49">
@@ -1758,28 +1758,28 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C49">
-        <v>30.81</v>
+        <v>31.02</v>
       </c>
       <c r="D49">
         <v>2</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G49">
         <v>18.18</v>
       </c>
       <c r="H49">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I49">
-        <v>36.36</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="50">
@@ -1787,28 +1787,28 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C50">
-        <v>30.69</v>
+        <v>31.02</v>
       </c>
       <c r="D50">
         <v>2</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G50">
         <v>18.18</v>
       </c>
       <c r="H50">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I50">
-        <v>2.27</v>
+        <v>37.78</v>
       </c>
     </row>
   </sheetData>
@@ -1867,793 +1867,793 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000093</v>
+        <v>115000094</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C2">
         <v>4</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E2">
         <v>20</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H2">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="I2">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000092</v>
+        <v>115000093</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H3">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="I3">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000091</v>
+        <v>115000092</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
         <v>13</v>
       </c>
-      <c r="E4">
-        <v>24</v>
-      </c>
-      <c r="F4">
-        <v>25</v>
-      </c>
       <c r="G4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H4">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I4">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000090</v>
+        <v>115000091</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C5">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E5">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H5">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000089</v>
+        <v>115000090</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F6">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H6">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000088</v>
+        <v>115000089</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F7">
         <v>21</v>
       </c>
       <c r="G7">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H7">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000087</v>
+        <v>115000088</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C8">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F8">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G8">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H8">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I8">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000086</v>
+        <v>115000087</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D9">
         <v>15</v>
       </c>
       <c r="E9">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F9">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G9">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H9">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I9">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000085</v>
+        <v>115000086</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C10">
         <v>3</v>
       </c>
       <c r="D10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E10">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F10">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G10">
+        <v>47</v>
+      </c>
+      <c r="H10">
+        <v>49</v>
+      </c>
+      <c r="I10">
         <v>27</v>
-      </c>
-      <c r="H10">
-        <v>37</v>
-      </c>
-      <c r="I10">
-        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000084</v>
+        <v>115000085</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C11">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D11">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E11">
+        <v>17</v>
+      </c>
+      <c r="F11">
+        <v>18</v>
+      </c>
+      <c r="G11">
+        <v>27</v>
+      </c>
+      <c r="H11">
+        <v>37</v>
+      </c>
+      <c r="I11">
         <v>19</v>
-      </c>
-      <c r="F11">
-        <v>26</v>
-      </c>
-      <c r="G11">
-        <v>29</v>
-      </c>
-      <c r="H11">
-        <v>48</v>
-      </c>
-      <c r="I11">
-        <v>30</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000083</v>
+        <v>115000084</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E12">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F12">
         <v>26</v>
       </c>
       <c r="G12">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H12">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I12">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C13">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D13">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E13">
+        <v>23</v>
+      </c>
+      <c r="F13">
         <v>26</v>
       </c>
-      <c r="F13">
-        <v>32</v>
-      </c>
       <c r="G13">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H13">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I13">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D14">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F14">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G14">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H14">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I14">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D15">
         <v>14</v>
       </c>
       <c r="E15">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F15">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G15">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H15">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E16">
         <v>25</v>
       </c>
       <c r="F16">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G16">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H16">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I16">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>12</v>
       </c>
       <c r="E17">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F17">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G17">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H17">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="I17">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D18">
         <v>12</v>
       </c>
       <c r="E18">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F18">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G18">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H18">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I18">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D19">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E19">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F19">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G19">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H19">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I19">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C20">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D20">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E20">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F20">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G20">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H20">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I20">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C21">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E21">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F21">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G21">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H21">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I21">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D22">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E22">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F22">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G22">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H22">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I22">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E23">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F23">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G23">
         <v>35</v>
       </c>
       <c r="H23">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I23">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E24">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F24">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G24">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H24">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I24">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C25">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E25">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F25">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G25">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H25">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I25">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C26">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D26">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E26">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F26">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G26">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H26">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I26">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C27">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D27">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E27">
         <v>15</v>
@@ -2662,345 +2662,345 @@
         <v>18</v>
       </c>
       <c r="G27">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H27">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I27">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C28">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D28">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E28">
+        <v>15</v>
+      </c>
+      <c r="F28">
+        <v>18</v>
+      </c>
+      <c r="G28">
         <v>19</v>
       </c>
-      <c r="F28">
-        <v>23</v>
-      </c>
-      <c r="G28">
-        <v>39</v>
-      </c>
       <c r="H28">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I28">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C29">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D29">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E29">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F29">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G29">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H29">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I29">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C30">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D30">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E30">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F30">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G30">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H30">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C31">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E31">
+        <v>23</v>
+      </c>
+      <c r="F31">
+        <v>24</v>
+      </c>
+      <c r="G31">
         <v>29</v>
       </c>
-      <c r="F31">
-        <v>33</v>
-      </c>
-      <c r="G31">
-        <v>34</v>
-      </c>
       <c r="H31">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I31">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C32">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D32">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E32">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F32">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G32">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H32">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I32">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E33">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F33">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G33">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H33">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I33">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C34">
         <v>1</v>
       </c>
       <c r="D34">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E34">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F34">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G34">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H34">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I34">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C35">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D35">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E35">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F35">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G35">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H35">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I35">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C36">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D36">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E36">
         <v>25</v>
       </c>
       <c r="F36">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G36">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H36">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I36">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C37">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D37">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E37">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F37">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G37">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H37">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I37">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C38">
+        <v>8</v>
+      </c>
+      <c r="D38">
+        <v>9</v>
+      </c>
+      <c r="E38">
+        <v>16</v>
+      </c>
+      <c r="F38">
         <v>20</v>
-      </c>
-      <c r="D38">
-        <v>26</v>
-      </c>
-      <c r="E38">
-        <v>29</v>
-      </c>
-      <c r="F38">
-        <v>31</v>
       </c>
       <c r="G38">
         <v>37</v>
@@ -3009,410 +3009,410 @@
         <v>49</v>
       </c>
       <c r="I38">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C39">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D39">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E39">
         <v>29</v>
       </c>
       <c r="F39">
+        <v>31</v>
+      </c>
+      <c r="G39">
         <v>37</v>
       </c>
-      <c r="G39">
-        <v>47</v>
-      </c>
       <c r="H39">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I39">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C40">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D40">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E40">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F40">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G40">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="H40">
         <v>48</v>
       </c>
       <c r="I40">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D41">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E41">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F41">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G41">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H41">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I41">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C42">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D42">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E42">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F42">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G42">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H42">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I42">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C43">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D43">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E43">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F43">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G43">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H43">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I43">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C44">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D44">
+        <v>12</v>
+      </c>
+      <c r="E44">
         <v>18</v>
       </c>
-      <c r="E44">
-        <v>25</v>
-      </c>
       <c r="F44">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G44">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H44">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I44">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D45">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E45">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F45">
         <v>28</v>
       </c>
       <c r="G45">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H45">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I45">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C46">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D46">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E46">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F46">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G46">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H46">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I46">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C47">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D47">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E47">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F47">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G47">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H47">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I47">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C48">
+        <v>6</v>
+      </c>
+      <c r="D48">
+        <v>10</v>
+      </c>
+      <c r="E48">
+        <v>14</v>
+      </c>
+      <c r="F48">
+        <v>25</v>
+      </c>
+      <c r="G48">
+        <v>26</v>
+      </c>
+      <c r="H48">
+        <v>32</v>
+      </c>
+      <c r="I48">
         <v>7</v>
-      </c>
-      <c r="D48">
-        <v>14</v>
-      </c>
-      <c r="E48">
-        <v>16</v>
-      </c>
-      <c r="F48">
-        <v>37</v>
-      </c>
-      <c r="G48">
-        <v>39</v>
-      </c>
-      <c r="H48">
-        <v>47</v>
-      </c>
-      <c r="I48">
-        <v>34</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D49">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E49">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F49">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G49">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H49">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I49">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C50">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D50">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E50">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F50">
+        <v>19</v>
+      </c>
+      <c r="G50">
+        <v>20</v>
+      </c>
+      <c r="H50">
+        <v>40</v>
+      </c>
+      <c r="I50">
         <v>22</v>
-      </c>
-      <c r="G50">
-        <v>40</v>
-      </c>
-      <c r="H50">
-        <v>45</v>
-      </c>
-      <c r="I50">
-        <v>18</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D51">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E51">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F51">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G51">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H51">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I51">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-10-06 第 115000094 期；威力彩 2026-10-05 第 115000080 期</t>
+          <t>大樂透 2026-10-06 第 115000094 期；威力彩 2026-10-08 第 115000081 期</t>
         </is>
       </c>
     </row>
@@ -112,7 +112,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -121,7 +121,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -143,7 +143,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8, 17, 19, 24, 29, 35</t>
+          <t>2, 7, 9, 17, 26, 29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -161,7 +161,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.119 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.072 碼/期</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3530,7 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>0.857</v>
+        <v>0.881</v>
       </c>
       <c r="D5">
         <v>16.7</v>
@@ -3552,16 +3552,16 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.81</v>
+        <v>0.857</v>
       </c>
       <c r="D6">
-        <v>19.0</v>
+        <v>21.4</v>
       </c>
       <c r="E6">
-        <v>0.0</v>
+        <v>2.4</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -3574,7 +3574,7 @@
         <v>42</v>
       </c>
       <c r="C7">
-        <v>0.762</v>
+        <v>0.786</v>
       </c>
       <c r="D7">
         <v>14.3</v>
@@ -3648,16 +3648,16 @@
         <v>29</v>
       </c>
       <c r="C2">
-        <v>74.83</v>
+        <v>71.5</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <v>100.0</v>
@@ -3666,7 +3666,7 @@
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>9.52</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="3">
@@ -3677,7 +3677,7 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>73.14</v>
+        <v>68.81</v>
       </c>
       <c r="D3">
         <v>10</v>
@@ -3686,16 +3686,16 @@
         <v>4</v>
       </c>
       <c r="F3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>71.43</v>
+        <v>66.67</v>
       </c>
       <c r="H3">
-        <v>80.0</v>
+        <v>66.67</v>
       </c>
       <c r="I3">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
     </row>
     <row r="4">
@@ -3706,7 +3706,7 @@
         <v>17</v>
       </c>
       <c r="C4">
-        <v>72.67</v>
+        <v>67.61</v>
       </c>
       <c r="D4">
         <v>11</v>
@@ -3715,16 +3715,16 @@
         <v>5</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>78.57</v>
+        <v>73.33</v>
       </c>
       <c r="H4">
-        <v>100.0</v>
+        <v>83.33</v>
       </c>
       <c r="I4">
-        <v>0.0</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="5">
@@ -3735,7 +3735,7 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>72.19</v>
+        <v>67.41</v>
       </c>
       <c r="D5">
         <v>9</v>
@@ -3744,16 +3744,16 @@
         <v>5</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>64.29</v>
+        <v>60.0</v>
       </c>
       <c r="H5">
-        <v>100.0</v>
+        <v>83.33</v>
       </c>
       <c r="I5">
-        <v>0.0</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="6">
@@ -3764,7 +3764,7 @@
         <v>9</v>
       </c>
       <c r="C6">
-        <v>70.29</v>
+        <v>66.68</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -3773,16 +3773,16 @@
         <v>3</v>
       </c>
       <c r="F6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>71.43</v>
+        <v>66.67</v>
       </c>
       <c r="H6">
-        <v>60.0</v>
+        <v>50.0</v>
       </c>
       <c r="I6">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
     </row>
     <row r="7">
@@ -3793,7 +3793,7 @@
         <v>8</v>
       </c>
       <c r="C7">
-        <v>69.81</v>
+        <v>65.49</v>
       </c>
       <c r="D7">
         <v>11</v>
@@ -3802,16 +3802,16 @@
         <v>4</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>78.57</v>
+        <v>73.33</v>
       </c>
       <c r="H7">
-        <v>80.0</v>
+        <v>66.67</v>
       </c>
       <c r="I7">
-        <v>14.29</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="8">
@@ -3819,28 +3819,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="C8">
-        <v>69.8</v>
+        <v>63.82</v>
       </c>
       <c r="D8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F8">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>57.14</v>
+        <v>46.67</v>
       </c>
       <c r="H8">
-        <v>60.0</v>
+        <v>83.33</v>
       </c>
       <c r="I8">
-        <v>52.38</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="9">
@@ -3848,28 +3848,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C9">
-        <v>69.1</v>
+        <v>63.15</v>
       </c>
       <c r="D9">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>78.57</v>
+        <v>53.33</v>
       </c>
       <c r="H9">
-        <v>60.0</v>
+        <v>66.67</v>
       </c>
       <c r="I9">
-        <v>42.86</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="10">
@@ -3877,28 +3877,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>68.63</v>
+        <v>62.57</v>
       </c>
       <c r="D10">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>85.71</v>
+        <v>60.0</v>
       </c>
       <c r="H10">
-        <v>60.0</v>
+        <v>66.67</v>
       </c>
       <c r="I10">
-        <v>38.1</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="11">
@@ -3906,28 +3906,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="C11">
-        <v>68.3</v>
+        <v>61.25</v>
       </c>
       <c r="D11">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>50.0</v>
+        <v>73.33</v>
       </c>
       <c r="H11">
-        <v>100.0</v>
+        <v>33.33</v>
       </c>
       <c r="I11">
-        <v>0.0</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="12">
@@ -3935,28 +3935,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C12">
-        <v>66.94</v>
+        <v>60.67</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G12">
-        <v>57.14</v>
+        <v>80.0</v>
       </c>
       <c r="H12">
-        <v>80.0</v>
+        <v>33.33</v>
       </c>
       <c r="I12">
-        <v>0.0</v>
+        <v>40.91</v>
       </c>
     </row>
     <row r="13">
@@ -3967,7 +3967,7 @@
         <v>33</v>
       </c>
       <c r="C13">
-        <v>63.14</v>
+        <v>59.86</v>
       </c>
       <c r="D13">
         <v>10</v>
@@ -3976,16 +3976,16 @@
         <v>3</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13">
-        <v>71.43</v>
+        <v>66.67</v>
       </c>
       <c r="H13">
-        <v>60.0</v>
+        <v>50.0</v>
       </c>
       <c r="I13">
-        <v>4.76</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="14">
@@ -3993,28 +3993,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="C14">
-        <v>62.9</v>
+        <v>59.57</v>
       </c>
       <c r="D14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E14">
         <v>3</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G14">
-        <v>64.29</v>
+        <v>46.67</v>
       </c>
       <c r="H14">
-        <v>60.0</v>
+        <v>50.0</v>
       </c>
       <c r="I14">
-        <v>4.76</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="15">
@@ -4022,28 +4022,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C15">
-        <v>62.67</v>
+        <v>59.18</v>
       </c>
       <c r="D15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G15">
-        <v>78.57</v>
+        <v>66.67</v>
       </c>
       <c r="H15">
-        <v>40.0</v>
+        <v>50.0</v>
       </c>
       <c r="I15">
-        <v>33.33</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="16">
@@ -4051,28 +4051,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C16">
-        <v>62.59</v>
+        <v>58.9</v>
       </c>
       <c r="D16">
+        <v>8</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16">
         <v>7</v>
       </c>
-      <c r="E16">
-        <v>3</v>
-      </c>
-      <c r="F16">
-        <v>6</v>
-      </c>
       <c r="G16">
-        <v>50.0</v>
+        <v>53.33</v>
       </c>
       <c r="H16">
-        <v>60.0</v>
+        <v>33.33</v>
       </c>
       <c r="I16">
-        <v>28.57</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="17">
@@ -4080,28 +4080,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C17">
-        <v>62.43</v>
+        <v>58.82</v>
       </c>
       <c r="D17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G17">
-        <v>71.43</v>
+        <v>46.67</v>
       </c>
       <c r="H17">
-        <v>60.0</v>
+        <v>33.33</v>
       </c>
       <c r="I17">
-        <v>0.0</v>
+        <v>54.55</v>
       </c>
     </row>
     <row r="18">
@@ -4109,28 +4109,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18">
-        <v>61.23</v>
+        <v>58.75</v>
       </c>
       <c r="D18">
         <v>8</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G18">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="H18">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="I18">
-        <v>28.57</v>
+        <v>86.36</v>
       </c>
     </row>
     <row r="19">
@@ -4138,28 +4138,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19">
-        <v>60.53</v>
+        <v>58.4</v>
       </c>
       <c r="D19">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>78.57</v>
+        <v>60.0</v>
       </c>
       <c r="H19">
-        <v>40.0</v>
+        <v>50.0</v>
       </c>
       <c r="I19">
-        <v>19.05</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="20">
@@ -4167,13 +4167,13 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C20">
-        <v>60.51</v>
+        <v>57.84</v>
       </c>
       <c r="D20">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -4182,13 +4182,13 @@
         <v>5</v>
       </c>
       <c r="G20">
-        <v>57.14</v>
+        <v>73.33</v>
       </c>
       <c r="H20">
-        <v>40.0</v>
+        <v>33.33</v>
       </c>
       <c r="I20">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="21">
@@ -4196,28 +4196,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C21">
-        <v>59.8</v>
+        <v>57.06</v>
       </c>
       <c r="D21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G21">
-        <v>57.14</v>
+        <v>66.67</v>
       </c>
       <c r="H21">
-        <v>0.0</v>
+        <v>33.33</v>
       </c>
       <c r="I21">
-        <v>85.71</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="22">
@@ -4225,28 +4225,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C22">
-        <v>59.57</v>
+        <v>56.86</v>
       </c>
       <c r="D22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E22">
         <v>2</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22">
-        <v>71.43</v>
+        <v>53.33</v>
       </c>
       <c r="H22">
-        <v>40.0</v>
+        <v>33.33</v>
       </c>
       <c r="I22">
-        <v>14.29</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="23">
@@ -4254,28 +4254,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="C23">
-        <v>59.09</v>
+        <v>54.43</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E23">
         <v>2</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>57.14</v>
+        <v>73.33</v>
       </c>
       <c r="H23">
-        <v>40.0</v>
+        <v>33.33</v>
       </c>
       <c r="I23">
-        <v>14.29</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="24">
@@ -4283,28 +4283,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C24">
-        <v>57.66</v>
+        <v>54.23</v>
       </c>
       <c r="D24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>57.14</v>
+        <v>60.0</v>
       </c>
       <c r="H24">
-        <v>20.0</v>
+        <v>33.33</v>
       </c>
       <c r="I24">
-        <v>38.1</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="25">
@@ -4312,28 +4312,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C25">
-        <v>55.69</v>
+        <v>53.4</v>
       </c>
       <c r="D25">
         <v>6</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="G25">
-        <v>42.86</v>
+        <v>40.0</v>
       </c>
       <c r="H25">
-        <v>60.0</v>
+        <v>0.0</v>
       </c>
       <c r="I25">
-        <v>9.52</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="26">
@@ -4341,28 +4341,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>55.51</v>
+        <v>52.95</v>
       </c>
       <c r="D26">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G26">
-        <v>57.14</v>
+        <v>40.0</v>
       </c>
       <c r="H26">
-        <v>20.0</v>
+        <v>50.0</v>
       </c>
       <c r="I26">
-        <v>23.81</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="27">
@@ -4370,28 +4370,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C27">
-        <v>54.26</v>
+        <v>52.61</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="G27">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="H27">
-        <v>0.0</v>
+        <v>16.67</v>
       </c>
       <c r="I27">
-        <v>100.0</v>
+        <v>40.91</v>
       </c>
     </row>
     <row r="28">
@@ -4399,25 +4399,25 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C28">
-        <v>51.94</v>
+        <v>50.9</v>
       </c>
       <c r="D28">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
       <c r="G28">
-        <v>57.14</v>
+        <v>40.0</v>
       </c>
       <c r="H28">
-        <v>20.0</v>
+        <v>50.0</v>
       </c>
       <c r="I28">
         <v>0.0</v>
@@ -4428,28 +4428,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C29">
-        <v>51.4</v>
+        <v>50.65</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G29">
-        <v>42.86</v>
+        <v>53.33</v>
       </c>
       <c r="H29">
-        <v>40.0</v>
+        <v>16.67</v>
       </c>
       <c r="I29">
-        <v>14.29</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="30">
@@ -4457,28 +4457,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C30">
-        <v>50.93</v>
+        <v>48.51</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
         <v>3</v>
       </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
       <c r="G30">
-        <v>35.71</v>
+        <v>46.67</v>
       </c>
       <c r="H30">
-        <v>60.0</v>
+        <v>16.67</v>
       </c>
       <c r="I30">
-        <v>4.76</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="31">
@@ -4486,28 +4486,28 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C31">
-        <v>49.73</v>
+        <v>47.6</v>
       </c>
       <c r="D31">
+        <v>5</v>
+      </c>
+      <c r="E31">
+        <v>2</v>
+      </c>
+      <c r="F31">
         <v>7</v>
       </c>
-      <c r="E31">
-        <v>1</v>
-      </c>
-      <c r="F31">
-        <v>2</v>
-      </c>
       <c r="G31">
-        <v>50.0</v>
+        <v>33.33</v>
       </c>
       <c r="H31">
-        <v>20.0</v>
+        <v>33.33</v>
       </c>
       <c r="I31">
-        <v>9.52</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="32">
@@ -4515,28 +4515,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C32">
-        <v>49.5</v>
+        <v>47.34</v>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G32">
-        <v>35.71</v>
+        <v>40.0</v>
       </c>
       <c r="H32">
-        <v>40.0</v>
+        <v>16.67</v>
       </c>
       <c r="I32">
-        <v>28.57</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="33">
@@ -4544,28 +4544,28 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C33">
-        <v>48.54</v>
+        <v>45.56</v>
       </c>
       <c r="D33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G33">
-        <v>42.86</v>
+        <v>33.33</v>
       </c>
       <c r="H33">
-        <v>20.0</v>
+        <v>33.33</v>
       </c>
       <c r="I33">
-        <v>28.57</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="34">
@@ -4573,10 +4573,10 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C34">
-        <v>47.36</v>
+        <v>45.56</v>
       </c>
       <c r="D34">
         <v>5</v>
@@ -4585,16 +4585,16 @@
         <v>2</v>
       </c>
       <c r="F34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G34">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="H34">
-        <v>40.0</v>
+        <v>33.33</v>
       </c>
       <c r="I34">
-        <v>14.29</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="35">
@@ -4602,10 +4602,10 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C35">
-        <v>47.36</v>
+        <v>44.19</v>
       </c>
       <c r="D35">
         <v>5</v>
@@ -4614,16 +4614,16 @@
         <v>2</v>
       </c>
       <c r="F35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G35">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="H35">
-        <v>40.0</v>
+        <v>33.33</v>
       </c>
       <c r="I35">
-        <v>14.29</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="36">
@@ -4634,7 +4634,7 @@
         <v>32</v>
       </c>
       <c r="C36">
-        <v>43.31</v>
+        <v>42.27</v>
       </c>
       <c r="D36">
         <v>4</v>
@@ -4643,16 +4643,16 @@
         <v>1</v>
       </c>
       <c r="F36">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G36">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="H36">
-        <v>20.0</v>
+        <v>16.67</v>
       </c>
       <c r="I36">
-        <v>47.62</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="37">
@@ -4660,28 +4660,28 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C37">
-        <v>42.13</v>
+        <v>38.97</v>
       </c>
       <c r="D37">
         <v>3</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G37">
-        <v>21.43</v>
+        <v>20.0</v>
       </c>
       <c r="H37">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I37">
-        <v>66.67</v>
+        <v>81.82</v>
       </c>
     </row>
     <row r="38">
@@ -4689,28 +4689,28 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C38">
-        <v>40.46</v>
+        <v>36.93</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G38">
-        <v>28.57</v>
+        <v>20.0</v>
       </c>
       <c r="H38">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I38">
-        <v>28.57</v>
+        <v>68.18</v>
       </c>
     </row>
     <row r="39">
@@ -4718,28 +4718,28 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C39">
-        <v>39.27</v>
+        <v>35.64</v>
       </c>
       <c r="D39">
         <v>3</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G39">
-        <v>21.43</v>
+        <v>20.0</v>
       </c>
       <c r="H39">
-        <v>0.0</v>
+        <v>16.67</v>
       </c>
       <c r="I39">
-        <v>80.95</v>
+        <v>31.82</v>
       </c>
     </row>
   </sheetData>
@@ -4798,123 +4798,123 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F3">
+        <v>21</v>
+      </c>
+      <c r="G3">
         <v>26</v>
-      </c>
-      <c r="G3">
-        <v>33</v>
       </c>
       <c r="H3">
         <v>37</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H4">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H5">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -4922,11 +4922,11 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C6">
@@ -4936,140 +4936,140 @@
         <v>8</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H6">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C7">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E7">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F7">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G7">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H7">
         <v>37</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D8">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E8">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H8">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C9">
+        <v>10</v>
+      </c>
+      <c r="D9">
+        <v>12</v>
+      </c>
+      <c r="E9">
+        <v>14</v>
+      </c>
+      <c r="F9">
+        <v>16</v>
+      </c>
+      <c r="G9">
+        <v>29</v>
+      </c>
+      <c r="H9">
+        <v>36</v>
+      </c>
+      <c r="I9">
         <v>8</v>
-      </c>
-      <c r="D9">
-        <v>17</v>
-      </c>
-      <c r="E9">
-        <v>18</v>
-      </c>
-      <c r="F9">
-        <v>29</v>
-      </c>
-      <c r="G9">
-        <v>33</v>
-      </c>
-      <c r="H9">
-        <v>38</v>
-      </c>
-      <c r="I9">
-        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F10">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G10">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H10">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I10">
         <v>2</v>
@@ -5077,108 +5077,108 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D11">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E11">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F11">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G11">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H11">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I11">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E12">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F12">
         <v>19</v>
       </c>
       <c r="G12">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H12">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I12">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F13">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G13">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H13">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D14">
         <v>7</v>
@@ -5187,230 +5187,230 @@
         <v>9</v>
       </c>
       <c r="F14">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H14">
         <v>36</v>
       </c>
       <c r="I14">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E15">
         <v>9</v>
       </c>
       <c r="F15">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G15">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H15">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>9</v>
+      </c>
+      <c r="F16">
         <v>11</v>
       </c>
-      <c r="E16">
-        <v>18</v>
-      </c>
-      <c r="F16">
-        <v>19</v>
-      </c>
       <c r="G16">
+        <v>29</v>
+      </c>
+      <c r="H16">
         <v>35</v>
       </c>
-      <c r="H16">
-        <v>38</v>
-      </c>
       <c r="I16">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F17">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G17">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H17">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="I17">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C18">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E18">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F18">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G18">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H18">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I18">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D19">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E19">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F19">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G19">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H19">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I19">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>7</v>
+      </c>
+      <c r="E20">
+        <v>8</v>
+      </c>
+      <c r="F20">
+        <v>20</v>
+      </c>
+      <c r="G20">
+        <v>26</v>
+      </c>
+      <c r="H20">
+        <v>33</v>
+      </c>
+      <c r="I20">
         <v>4</v>
-      </c>
-      <c r="D20">
-        <v>15</v>
-      </c>
-      <c r="E20">
-        <v>22</v>
-      </c>
-      <c r="F20">
-        <v>26</v>
-      </c>
-      <c r="G20">
-        <v>34</v>
-      </c>
-      <c r="H20">
-        <v>36</v>
-      </c>
-      <c r="I20">
-        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C21">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D21">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E21">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F21">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G21">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H21">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I21">
         <v>7</v>
@@ -5418,30 +5418,30 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C22">
+        <v>8</v>
+      </c>
+      <c r="D22">
+        <v>14</v>
+      </c>
+      <c r="E22">
+        <v>17</v>
+      </c>
+      <c r="F22">
         <v>19</v>
       </c>
-      <c r="D22">
-        <v>22</v>
-      </c>
-      <c r="E22">
-        <v>28</v>
-      </c>
-      <c r="F22">
-        <v>31</v>
-      </c>
       <c r="G22">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H22">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I22">
         <v>7</v>
@@ -5449,30 +5449,30 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C23">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D23">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E23">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F23">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G23">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H23">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I23">
         <v>7</v>
@@ -5480,24 +5480,24 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D24">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E24">
         <v>13</v>
       </c>
       <c r="F24">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G24">
         <v>29</v>
@@ -5506,97 +5506,97 @@
         <v>31</v>
       </c>
       <c r="I24">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C25">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D25">
+        <v>12</v>
+      </c>
+      <c r="E25">
+        <v>13</v>
+      </c>
+      <c r="F25">
         <v>23</v>
       </c>
-      <c r="E25">
-        <v>25</v>
-      </c>
-      <c r="F25">
+      <c r="G25">
         <v>29</v>
       </c>
-      <c r="G25">
-        <v>34</v>
-      </c>
       <c r="H25">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I25">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C26">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D26">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E26">
+        <v>25</v>
+      </c>
+      <c r="F26">
         <v>29</v>
       </c>
-      <c r="F26">
-        <v>32</v>
-      </c>
       <c r="G26">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H26">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I26">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C27">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D27">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E27">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F27">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G27">
         <v>35</v>
       </c>
       <c r="H27">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I27">
         <v>6</v>
@@ -5604,402 +5604,402 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C28">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D28">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E28">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F28">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G28">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H28">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D29">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E29">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F29">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G29">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H29">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I29">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C30">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D30">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E30">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F30">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G30">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H30">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I30">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C31">
+        <v>5</v>
+      </c>
+      <c r="D31">
         <v>6</v>
       </c>
-      <c r="D31">
-        <v>10</v>
-      </c>
       <c r="E31">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F31">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G31">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H31">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I31">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C32">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D32">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E32">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F32">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G32">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H32">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I32">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D33">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E33">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F33">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G33">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H33">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I33">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34">
+        <v>8</v>
+      </c>
+      <c r="E34">
+        <v>9</v>
+      </c>
+      <c r="F34">
+        <v>15</v>
+      </c>
+      <c r="G34">
+        <v>18</v>
+      </c>
+      <c r="H34">
+        <v>23</v>
+      </c>
+      <c r="I34">
         <v>4</v>
-      </c>
-      <c r="D34">
-        <v>17</v>
-      </c>
-      <c r="E34">
-        <v>19</v>
-      </c>
-      <c r="F34">
-        <v>25</v>
-      </c>
-      <c r="G34">
-        <v>28</v>
-      </c>
-      <c r="H34">
-        <v>29</v>
-      </c>
-      <c r="I34">
-        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C35">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D35">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E35">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F35">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G35">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H35">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I35">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D36">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E36">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F36">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G36">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H36">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I36">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C37">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D37">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E37">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F37">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G37">
         <v>28</v>
       </c>
       <c r="H37">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I37">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C38">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D38">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E38">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F38">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G38">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H38">
         <v>35</v>
       </c>
       <c r="I38">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E39">
+        <v>9</v>
+      </c>
+      <c r="F39">
+        <v>15</v>
+      </c>
+      <c r="G39">
         <v>24</v>
       </c>
-      <c r="F39">
-        <v>31</v>
-      </c>
-      <c r="G39">
-        <v>34</v>
-      </c>
       <c r="H39">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I39">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C40">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D40">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E40">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F40">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G40">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H40">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I40">
         <v>3</v>
@@ -6007,343 +6007,343 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C41">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D41">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E41">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F41">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G41">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H41">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I41">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C42">
         <v>6</v>
       </c>
       <c r="D42">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E42">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F42">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G42">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H42">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I42">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C43">
         <v>6</v>
       </c>
       <c r="D43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E43">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F43">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G43">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H43">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I43">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C44">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D44">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E44">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F44">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G44">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H44">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I44">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C45">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D45">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E45">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F45">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G45">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H45">
         <v>38</v>
       </c>
       <c r="I45">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C46">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D46">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E46">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F46">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G46">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H46">
         <v>38</v>
       </c>
       <c r="I46">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D47">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E47">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F47">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G47">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H47">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I47">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C48">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D48">
+        <v>4</v>
+      </c>
+      <c r="E48">
+        <v>13</v>
+      </c>
+      <c r="F48">
+        <v>19</v>
+      </c>
+      <c r="G48">
+        <v>27</v>
+      </c>
+      <c r="H48">
+        <v>30</v>
+      </c>
+      <c r="I48">
         <v>8</v>
-      </c>
-      <c r="E48">
-        <v>27</v>
-      </c>
-      <c r="F48">
-        <v>33</v>
-      </c>
-      <c r="G48">
-        <v>35</v>
-      </c>
-      <c r="H48">
-        <v>38</v>
-      </c>
-      <c r="I48">
-        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C49">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D49">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E49">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F49">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G49">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H49">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I49">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C50">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D50">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E50">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F50">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G50">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H50">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I50">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000031</v>
+        <v>115000032</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D51">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E51">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F51">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G51">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H51">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I51">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-10-06 第 115000094 期；威力彩 2026-10-08 第 115000081 期</t>
+          <t>大樂透 2026-10-09 第 115000095 期；威力彩 2026-10-08 第 115000081 期</t>
         </is>
       </c>
     </row>
@@ -47,7 +47,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>115000094</v>
+        <v>115000095</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -56,7 +56,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -78,7 +78,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4, 12, 14, 26, 29, 35</t>
+          <t>4, 12, 25, 26, 29, 35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -87,7 +87,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -96,7 +96,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.262 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.238 碼/期</t>
         </is>
       </c>
     </row>
@@ -302,16 +302,16 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.714</v>
+        <v>0.762</v>
       </c>
       <c r="D6">
-        <v>16.7</v>
+        <v>19.0</v>
       </c>
       <c r="E6">
-        <v>0.0</v>
+        <v>2.4</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -324,10 +324,10 @@
         <v>42</v>
       </c>
       <c r="C7">
-        <v>0.643</v>
+        <v>0.667</v>
       </c>
       <c r="D7">
-        <v>11.9</v>
+        <v>14.3</v>
       </c>
       <c r="E7">
         <v>0.0</v>
@@ -398,7 +398,7 @@
         <v>26</v>
       </c>
       <c r="C2">
-        <v>73.38</v>
+        <v>73.7</v>
       </c>
       <c r="D2">
         <v>11</v>
@@ -407,7 +407,7 @@
         <v>5</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>100.0</v>
@@ -416,7 +416,7 @@
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>2.22</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="3">
@@ -424,28 +424,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C3">
-        <v>72.83</v>
+        <v>69.4</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
         <v>5</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
       <c r="G3">
-        <v>81.82</v>
+        <v>90.91</v>
       </c>
       <c r="H3">
-        <v>100.0</v>
+        <v>80.0</v>
       </c>
       <c r="I3">
-        <v>2.22</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="4">
@@ -453,28 +453,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="C4">
-        <v>69.11</v>
+        <v>68.15</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4">
         <v>4</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G4">
-        <v>90.91</v>
+        <v>81.82</v>
       </c>
       <c r="H4">
         <v>80.0</v>
       </c>
       <c r="I4">
-        <v>8.89</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="5">
@@ -482,28 +482,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>63.83</v>
+        <v>66.94</v>
       </c>
       <c r="D5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>81.82</v>
+        <v>63.64</v>
       </c>
       <c r="H5">
-        <v>60.0</v>
+        <v>80.0</v>
       </c>
       <c r="I5">
-        <v>8.89</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
@@ -511,28 +511,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C6">
-        <v>63.55</v>
+        <v>64.13</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>72.73</v>
+        <v>81.82</v>
       </c>
       <c r="H6">
         <v>60.0</v>
       </c>
       <c r="I6">
-        <v>8.89</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="7">
@@ -540,28 +540,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C7">
-        <v>63.4</v>
+        <v>63.85</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G7">
-        <v>54.55</v>
+        <v>72.73</v>
       </c>
       <c r="H7">
         <v>60.0</v>
       </c>
       <c r="I7">
-        <v>15.56</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="8">
@@ -569,28 +569,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>63.06</v>
+        <v>62.82</v>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>54.55</v>
+        <v>81.82</v>
       </c>
       <c r="H8">
         <v>60.0</v>
       </c>
       <c r="I8">
-        <v>13.33</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="9">
@@ -598,28 +598,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C9">
-        <v>62.61</v>
+        <v>62.82</v>
       </c>
       <c r="D9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>63.64</v>
+        <v>81.82</v>
       </c>
       <c r="H9">
         <v>60.0</v>
       </c>
       <c r="I9">
-        <v>4.44</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="10">
@@ -627,28 +627,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="C10">
-        <v>62.5</v>
+        <v>62.59</v>
       </c>
       <c r="D10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10">
-        <v>81.82</v>
+        <v>63.64</v>
       </c>
       <c r="H10">
         <v>60.0</v>
       </c>
       <c r="I10">
-        <v>0.0</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="11">
@@ -656,28 +656,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C11">
-        <v>62.5</v>
+        <v>62.37</v>
       </c>
       <c r="D11">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G11">
-        <v>81.82</v>
+        <v>54.55</v>
       </c>
       <c r="H11">
         <v>60.0</v>
       </c>
       <c r="I11">
-        <v>0.0</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="12">
@@ -685,28 +685,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="C12">
-        <v>62.27</v>
+        <v>62.04</v>
       </c>
       <c r="D12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G12">
-        <v>63.64</v>
+        <v>54.55</v>
       </c>
       <c r="H12">
         <v>60.0</v>
       </c>
       <c r="I12">
-        <v>2.22</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="13">
@@ -714,28 +714,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C13">
-        <v>62.07</v>
+        <v>60.66</v>
       </c>
       <c r="D13">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G13">
-        <v>54.55</v>
+        <v>100.0</v>
       </c>
       <c r="H13">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="I13">
-        <v>6.67</v>
+        <v>17.39</v>
       </c>
     </row>
     <row r="14">
@@ -743,28 +743,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C14">
-        <v>61.73</v>
+        <v>60.1</v>
       </c>
       <c r="D14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G14">
-        <v>54.55</v>
+        <v>81.82</v>
       </c>
       <c r="H14">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="I14">
-        <v>4.44</v>
+        <v>17.39</v>
       </c>
     </row>
     <row r="15">
@@ -772,28 +772,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C15">
-        <v>61.38</v>
+        <v>59.98</v>
       </c>
       <c r="D15">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E15">
         <v>2</v>
       </c>
       <c r="F15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G15">
-        <v>100.0</v>
+        <v>54.55</v>
       </c>
       <c r="H15">
         <v>40.0</v>
       </c>
       <c r="I15">
-        <v>22.22</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="16">
@@ -801,28 +801,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C16">
-        <v>60.38</v>
+        <v>58.67</v>
       </c>
       <c r="D16">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E16">
         <v>2</v>
       </c>
       <c r="F16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G16">
-        <v>100.0</v>
+        <v>54.55</v>
       </c>
       <c r="H16">
         <v>40.0</v>
       </c>
       <c r="I16">
-        <v>15.56</v>
+        <v>17.39</v>
       </c>
     </row>
     <row r="17">
@@ -830,28 +830,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="C17">
-        <v>59.83</v>
+        <v>58.67</v>
       </c>
       <c r="D17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
       <c r="F17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G17">
-        <v>81.82</v>
+        <v>54.55</v>
       </c>
       <c r="H17">
         <v>40.0</v>
       </c>
       <c r="I17">
-        <v>15.56</v>
+        <v>17.39</v>
       </c>
     </row>
     <row r="18">
@@ -859,28 +859,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C18">
-        <v>59.73</v>
+        <v>58.25</v>
       </c>
       <c r="D18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G18">
-        <v>54.55</v>
+        <v>63.64</v>
       </c>
       <c r="H18">
         <v>40.0</v>
       </c>
       <c r="I18">
-        <v>24.44</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="19">
@@ -888,13 +888,13 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>58.5</v>
+        <v>57.92</v>
       </c>
       <c r="D19">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -903,13 +903,13 @@
         <v>3</v>
       </c>
       <c r="G19">
-        <v>81.82</v>
+        <v>63.64</v>
       </c>
       <c r="H19">
         <v>40.0</v>
       </c>
       <c r="I19">
-        <v>6.67</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="20">
@@ -917,28 +917,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="C20">
-        <v>58.4</v>
+        <v>57.77</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
       <c r="F20">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>54.55</v>
+        <v>90.91</v>
       </c>
       <c r="H20">
         <v>40.0</v>
       </c>
       <c r="I20">
-        <v>15.56</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="21">
@@ -946,28 +946,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="C21">
-        <v>58.4</v>
+        <v>57.27</v>
       </c>
       <c r="D21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E21">
         <v>2</v>
       </c>
       <c r="F21">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>54.55</v>
+        <v>63.64</v>
       </c>
       <c r="H21">
         <v>40.0</v>
       </c>
       <c r="I21">
-        <v>15.56</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="22">
@@ -975,10 +975,10 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C22">
-        <v>57.94</v>
+        <v>57.27</v>
       </c>
       <c r="D22">
         <v>7</v>
@@ -987,7 +987,7 @@
         <v>2</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22">
         <v>63.64</v>
@@ -996,7 +996,7 @@
         <v>40.0</v>
       </c>
       <c r="I22">
-        <v>6.67</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="23">
@@ -1004,10 +1004,10 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="C23">
-        <v>56.94</v>
+        <v>57.27</v>
       </c>
       <c r="D23">
         <v>7</v>
@@ -1016,7 +1016,7 @@
         <v>2</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23">
         <v>63.64</v>
@@ -1025,7 +1025,7 @@
         <v>40.0</v>
       </c>
       <c r="I23">
-        <v>0.0</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="24">
@@ -1033,28 +1033,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C24">
-        <v>56.94</v>
+        <v>56.64</v>
       </c>
       <c r="D24">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G24">
-        <v>63.64</v>
+        <v>100.0</v>
       </c>
       <c r="H24">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I24">
-        <v>0.0</v>
+        <v>23.91</v>
       </c>
     </row>
     <row r="25">
@@ -1062,28 +1062,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C25">
-        <v>56.94</v>
+        <v>56.39</v>
       </c>
       <c r="D25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E25">
         <v>2</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25">
-        <v>63.64</v>
+        <v>54.55</v>
       </c>
       <c r="H25">
         <v>40.0</v>
       </c>
       <c r="I25">
-        <v>0.0</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="26">
@@ -1091,28 +1091,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C26">
-        <v>56.06</v>
+        <v>56.08</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G26">
-        <v>54.55</v>
+        <v>81.82</v>
       </c>
       <c r="H26">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I26">
-        <v>0.0</v>
+        <v>23.91</v>
       </c>
     </row>
     <row r="27">
@@ -1120,28 +1120,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C27">
-        <v>55.83</v>
+        <v>55.63</v>
       </c>
       <c r="D27">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G27">
-        <v>81.82</v>
+        <v>54.55</v>
       </c>
       <c r="H27">
         <v>20.0</v>
       </c>
       <c r="I27">
-        <v>22.22</v>
+        <v>30.43</v>
       </c>
     </row>
     <row r="28">
@@ -1149,10 +1149,10 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="C28">
-        <v>55.4</v>
+        <v>54.33</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -1161,7 +1161,7 @@
         <v>1</v>
       </c>
       <c r="F28">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G28">
         <v>54.55</v>
@@ -1170,7 +1170,7 @@
         <v>20.0</v>
       </c>
       <c r="I28">
-        <v>28.89</v>
+        <v>21.74</v>
       </c>
     </row>
     <row r="29">
@@ -1178,10 +1178,10 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="C29">
-        <v>54.4</v>
+        <v>54.0</v>
       </c>
       <c r="D29">
         <v>6</v>
@@ -1190,7 +1190,7 @@
         <v>1</v>
       </c>
       <c r="F29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G29">
         <v>54.55</v>
@@ -1199,7 +1199,7 @@
         <v>20.0</v>
       </c>
       <c r="I29">
-        <v>22.22</v>
+        <v>19.57</v>
       </c>
     </row>
     <row r="30">
@@ -1207,10 +1207,10 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C30">
-        <v>54.06</v>
+        <v>53.67</v>
       </c>
       <c r="D30">
         <v>6</v>
@@ -1219,7 +1219,7 @@
         <v>1</v>
       </c>
       <c r="F30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G30">
         <v>54.55</v>
@@ -1228,7 +1228,7 @@
         <v>20.0</v>
       </c>
       <c r="I30">
-        <v>20.0</v>
+        <v>17.39</v>
       </c>
     </row>
     <row r="31">
@@ -1236,28 +1236,28 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="C31">
-        <v>53.73</v>
+        <v>51.94</v>
       </c>
       <c r="D31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="F31">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G31">
-        <v>54.55</v>
+        <v>63.64</v>
       </c>
       <c r="H31">
         <v>20.0</v>
       </c>
       <c r="I31">
-        <v>17.78</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="32">
@@ -1268,7 +1268,7 @@
         <v>2</v>
       </c>
       <c r="C32">
-        <v>51.55</v>
+        <v>51.86</v>
       </c>
       <c r="D32">
         <v>5</v>
@@ -1277,7 +1277,7 @@
         <v>2</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G32">
         <v>45.45</v>
@@ -1286,7 +1286,7 @@
         <v>40.0</v>
       </c>
       <c r="I32">
-        <v>4.44</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="33">
@@ -1297,7 +1297,7 @@
         <v>30</v>
       </c>
       <c r="C33">
-        <v>51.55</v>
+        <v>51.86</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -1306,7 +1306,7 @@
         <v>2</v>
       </c>
       <c r="F33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G33">
         <v>45.45</v>
@@ -1315,7 +1315,7 @@
         <v>40.0</v>
       </c>
       <c r="I33">
-        <v>4.44</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="34">
@@ -1323,10 +1323,10 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C34">
-        <v>51.22</v>
+        <v>50.88</v>
       </c>
       <c r="D34">
         <v>5</v>
@@ -1335,7 +1335,7 @@
         <v>2</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34">
         <v>45.45</v>
@@ -1344,7 +1344,7 @@
         <v>40.0</v>
       </c>
       <c r="I34">
-        <v>2.22</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="35">
@@ -1352,28 +1352,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="C35">
-        <v>51.06</v>
+        <v>49.47</v>
       </c>
       <c r="D35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G35">
-        <v>54.55</v>
+        <v>45.45</v>
       </c>
       <c r="H35">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I35">
-        <v>33.33</v>
+        <v>23.91</v>
       </c>
     </row>
     <row r="36">
@@ -1384,7 +1384,7 @@
         <v>21</v>
       </c>
       <c r="C36">
-        <v>47.37</v>
+        <v>47.66</v>
       </c>
       <c r="D36">
         <v>4</v>
@@ -1393,7 +1393,7 @@
         <v>2</v>
       </c>
       <c r="F36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G36">
         <v>36.36</v>
@@ -1402,7 +1402,7 @@
         <v>40.0</v>
       </c>
       <c r="I36">
-        <v>11.11</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="37">
@@ -1410,28 +1410,28 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C37">
-        <v>47.22</v>
+        <v>47.19</v>
       </c>
       <c r="D37">
         <v>5</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G37">
         <v>45.45</v>
       </c>
       <c r="H37">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I37">
-        <v>42.22</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="38">
@@ -1439,28 +1439,28 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C38">
-        <v>46.89</v>
+        <v>46.36</v>
       </c>
       <c r="D38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G38">
-        <v>45.45</v>
+        <v>36.36</v>
       </c>
       <c r="H38">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I38">
-        <v>6.67</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="39">
@@ -1468,28 +1468,28 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C39">
-        <v>45.53</v>
+        <v>45.88</v>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="F39">
         <v>0</v>
       </c>
-      <c r="F39">
-        <v>45</v>
-      </c>
       <c r="G39">
-        <v>27.27</v>
+        <v>45.45</v>
       </c>
       <c r="H39">
+        <v>20.0</v>
+      </c>
+      <c r="I39">
         <v>0.0</v>
-      </c>
-      <c r="I39">
-        <v>100.0</v>
       </c>
     </row>
     <row r="40">
@@ -1497,10 +1497,10 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="C40">
-        <v>44.37</v>
+        <v>44.62</v>
       </c>
       <c r="D40">
         <v>4</v>
@@ -1509,7 +1509,7 @@
         <v>1</v>
       </c>
       <c r="F40">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G40">
         <v>36.36</v>
@@ -1518,7 +1518,7 @@
         <v>20.0</v>
       </c>
       <c r="I40">
-        <v>24.44</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="41">
@@ -1526,10 +1526,10 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C41">
-        <v>44.37</v>
+        <v>43.97</v>
       </c>
       <c r="D41">
         <v>4</v>
@@ -1538,7 +1538,7 @@
         <v>1</v>
       </c>
       <c r="F41">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G41">
         <v>36.36</v>
@@ -1547,7 +1547,7 @@
         <v>20.0</v>
       </c>
       <c r="I41">
-        <v>24.44</v>
+        <v>21.74</v>
       </c>
     </row>
     <row r="42">
@@ -1555,28 +1555,28 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="C42">
-        <v>43.71</v>
+        <v>41.25</v>
       </c>
       <c r="D42">
         <v>4</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G42">
         <v>36.36</v>
       </c>
       <c r="H42">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I42">
-        <v>20.0</v>
+        <v>36.96</v>
       </c>
     </row>
     <row r="43">
@@ -1584,28 +1584,28 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C43">
-        <v>42.71</v>
+        <v>40.35</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="G43">
-        <v>36.36</v>
+        <v>18.18</v>
       </c>
       <c r="H43">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I43">
-        <v>13.33</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="44">
@@ -1613,28 +1613,28 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="C44">
-        <v>42.04</v>
+        <v>37.81</v>
       </c>
       <c r="D44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E44">
         <v>1</v>
       </c>
       <c r="F44">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G44">
-        <v>36.36</v>
+        <v>27.27</v>
       </c>
       <c r="H44">
         <v>20.0</v>
       </c>
       <c r="I44">
-        <v>8.89</v>
+        <v>15.22</v>
       </c>
     </row>
     <row r="45">
@@ -1642,28 +1642,28 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C45">
-        <v>41.04</v>
+        <v>37.16</v>
       </c>
       <c r="D45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G45">
-        <v>36.36</v>
+        <v>27.27</v>
       </c>
       <c r="H45">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I45">
-        <v>35.56</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="46">
@@ -1671,28 +1671,28 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C46">
-        <v>34.02</v>
+        <v>35.53</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46">
+        <v>1</v>
+      </c>
+      <c r="F46">
         <v>0</v>
       </c>
-      <c r="F46">
-        <v>26</v>
-      </c>
       <c r="G46">
-        <v>18.18</v>
+        <v>27.27</v>
       </c>
       <c r="H46">
+        <v>20.0</v>
+      </c>
+      <c r="I46">
         <v>0.0</v>
-      </c>
-      <c r="I46">
-        <v>57.78</v>
       </c>
     </row>
     <row r="47">
@@ -1700,28 +1700,28 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C47">
-        <v>32.02</v>
+        <v>34.16</v>
       </c>
       <c r="D47">
         <v>2</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="G47">
         <v>18.18</v>
       </c>
       <c r="H47">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I47">
-        <v>11.11</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="48">
@@ -1729,10 +1729,10 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C48">
-        <v>31.35</v>
+        <v>32.31</v>
       </c>
       <c r="D48">
         <v>2</v>
@@ -1741,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G48">
         <v>18.18</v>
@@ -1750,7 +1750,7 @@
         <v>20.0</v>
       </c>
       <c r="I48">
-        <v>6.67</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="49">
@@ -1758,10 +1758,10 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="C49">
-        <v>31.02</v>
+        <v>31.66</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -1770,7 +1770,7 @@
         <v>1</v>
       </c>
       <c r="F49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G49">
         <v>18.18</v>
@@ -1779,7 +1779,7 @@
         <v>20.0</v>
       </c>
       <c r="I49">
-        <v>4.44</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="50">
@@ -1787,28 +1787,28 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C50">
-        <v>31.02</v>
+        <v>31.33</v>
       </c>
       <c r="D50">
         <v>2</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G50">
         <v>18.18</v>
       </c>
       <c r="H50">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I50">
-        <v>37.78</v>
+        <v>6.52</v>
       </c>
     </row>
   </sheetData>
@@ -1867,824 +1867,824 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000094</v>
+        <v>115000095</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I2">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000093</v>
+        <v>115000094</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C3">
         <v>4</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E3">
         <v>20</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H3">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="I3">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000092</v>
+        <v>115000093</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H4">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="I4">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000091</v>
+        <v>115000092</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
         <v>13</v>
       </c>
-      <c r="E5">
-        <v>24</v>
-      </c>
-      <c r="F5">
-        <v>25</v>
-      </c>
       <c r="G5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H5">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I5">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000090</v>
+        <v>115000091</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H6">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000089</v>
+        <v>115000090</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H7">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="I7">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000088</v>
+        <v>115000089</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E8">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F8">
         <v>21</v>
       </c>
       <c r="G8">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H8">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I8">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000087</v>
+        <v>115000088</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C9">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F9">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G9">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H9">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I9">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000086</v>
+        <v>115000087</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D10">
         <v>15</v>
       </c>
       <c r="E10">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F10">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G10">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H10">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I10">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000085</v>
+        <v>115000086</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
       <c r="D11">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E11">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F11">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G11">
+        <v>47</v>
+      </c>
+      <c r="H11">
+        <v>49</v>
+      </c>
+      <c r="I11">
         <v>27</v>
-      </c>
-      <c r="H11">
-        <v>37</v>
-      </c>
-      <c r="I11">
-        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000084</v>
+        <v>115000085</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C12">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D12">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E12">
+        <v>17</v>
+      </c>
+      <c r="F12">
+        <v>18</v>
+      </c>
+      <c r="G12">
+        <v>27</v>
+      </c>
+      <c r="H12">
+        <v>37</v>
+      </c>
+      <c r="I12">
         <v>19</v>
-      </c>
-      <c r="F12">
-        <v>26</v>
-      </c>
-      <c r="G12">
-        <v>29</v>
-      </c>
-      <c r="H12">
-        <v>48</v>
-      </c>
-      <c r="I12">
-        <v>30</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000083</v>
+        <v>115000084</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E13">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F13">
         <v>26</v>
       </c>
       <c r="G13">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H13">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I13">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D14">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E14">
+        <v>23</v>
+      </c>
+      <c r="F14">
         <v>26</v>
       </c>
-      <c r="F14">
-        <v>32</v>
-      </c>
       <c r="G14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H14">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I14">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C15">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D15">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E15">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F15">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G15">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H15">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I15">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D16">
         <v>14</v>
       </c>
       <c r="E16">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F16">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G16">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H16">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I16">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E17">
         <v>25</v>
       </c>
       <c r="F17">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G17">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H17">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I17">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C18">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D18">
         <v>12</v>
       </c>
       <c r="E18">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F18">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G18">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H18">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="I18">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D19">
         <v>12</v>
       </c>
       <c r="E19">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F19">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G19">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H19">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I19">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E20">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F20">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G20">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H20">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I20">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C21">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D21">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E21">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F21">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G21">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H21">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I21">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C22">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D22">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E22">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F22">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G22">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H22">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I22">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C23">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D23">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E23">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F23">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G23">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H23">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I23">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E24">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F24">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G24">
         <v>35</v>
       </c>
       <c r="H24">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I24">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E25">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F25">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G25">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H25">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I25">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C26">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E26">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F26">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G26">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H26">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I26">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C27">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D27">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E27">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F27">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G27">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H27">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I27">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C28">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D28">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E28">
         <v>15</v>
@@ -2693,345 +2693,345 @@
         <v>18</v>
       </c>
       <c r="G28">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H28">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I28">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C29">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D29">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E29">
+        <v>15</v>
+      </c>
+      <c r="F29">
+        <v>18</v>
+      </c>
+      <c r="G29">
         <v>19</v>
       </c>
-      <c r="F29">
-        <v>23</v>
-      </c>
-      <c r="G29">
-        <v>39</v>
-      </c>
       <c r="H29">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I29">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C30">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D30">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E30">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F30">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G30">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H30">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I30">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C31">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D31">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E31">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G31">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H31">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I31">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C32">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D32">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E32">
+        <v>23</v>
+      </c>
+      <c r="F32">
+        <v>24</v>
+      </c>
+      <c r="G32">
         <v>29</v>
       </c>
-      <c r="F32">
-        <v>33</v>
-      </c>
-      <c r="G32">
-        <v>34</v>
-      </c>
       <c r="H32">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I32">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C33">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D33">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E33">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F33">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G33">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H33">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I33">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E34">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F34">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G34">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H34">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I34">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E35">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F35">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G35">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H35">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I35">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C36">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D36">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E36">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F36">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G36">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H36">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I36">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C37">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D37">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E37">
         <v>25</v>
       </c>
       <c r="F37">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G37">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H37">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I37">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C38">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D38">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E38">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F38">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G38">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H38">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I38">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C39">
+        <v>8</v>
+      </c>
+      <c r="D39">
+        <v>9</v>
+      </c>
+      <c r="E39">
+        <v>16</v>
+      </c>
+      <c r="F39">
         <v>20</v>
-      </c>
-      <c r="D39">
-        <v>26</v>
-      </c>
-      <c r="E39">
-        <v>29</v>
-      </c>
-      <c r="F39">
-        <v>31</v>
       </c>
       <c r="G39">
         <v>37</v>
@@ -3040,379 +3040,379 @@
         <v>49</v>
       </c>
       <c r="I39">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D40">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E40">
         <v>29</v>
       </c>
       <c r="F40">
+        <v>31</v>
+      </c>
+      <c r="G40">
         <v>37</v>
       </c>
-      <c r="G40">
-        <v>47</v>
-      </c>
       <c r="H40">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I40">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C41">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D41">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E41">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F41">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G41">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="H41">
         <v>48</v>
       </c>
       <c r="I41">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C42">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D42">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E42">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F42">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G42">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H42">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I42">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C43">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D43">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E43">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F43">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G43">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H43">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I43">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C44">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D44">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E44">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F44">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G44">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H44">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I44">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C45">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D45">
+        <v>12</v>
+      </c>
+      <c r="E45">
         <v>18</v>
       </c>
-      <c r="E45">
-        <v>25</v>
-      </c>
       <c r="F45">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G45">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H45">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I45">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C46">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D46">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E46">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F46">
         <v>28</v>
       </c>
       <c r="G46">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H46">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I46">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C47">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D47">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E47">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F47">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G47">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H47">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I47">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C48">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D48">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E48">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F48">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G48">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H48">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I48">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C49">
+        <v>6</v>
+      </c>
+      <c r="D49">
+        <v>10</v>
+      </c>
+      <c r="E49">
+        <v>14</v>
+      </c>
+      <c r="F49">
+        <v>25</v>
+      </c>
+      <c r="G49">
+        <v>26</v>
+      </c>
+      <c r="H49">
+        <v>32</v>
+      </c>
+      <c r="I49">
         <v>7</v>
-      </c>
-      <c r="D49">
-        <v>14</v>
-      </c>
-      <c r="E49">
-        <v>16</v>
-      </c>
-      <c r="F49">
-        <v>37</v>
-      </c>
-      <c r="G49">
-        <v>39</v>
-      </c>
-      <c r="H49">
-        <v>47</v>
-      </c>
-      <c r="I49">
-        <v>34</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D50">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E50">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F50">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G50">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H50">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I50">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C51">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D51">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E51">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F51">
+        <v>19</v>
+      </c>
+      <c r="G51">
+        <v>20</v>
+      </c>
+      <c r="H51">
+        <v>40</v>
+      </c>
+      <c r="I51">
         <v>22</v>
-      </c>
-      <c r="G51">
-        <v>40</v>
-      </c>
-      <c r="H51">
-        <v>45</v>
-      </c>
-      <c r="I51">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-10-09 第 115000095 期；威力彩 2026-10-08 第 115000081 期</t>
+          <t>大樂透 2026-10-09 第 115000095 期；威力彩 2026-10-12 第 115000082 期</t>
         </is>
       </c>
     </row>
@@ -112,7 +112,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -121,7 +121,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -143,7 +143,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2, 7, 9, 17, 26, 29</t>
+          <t>7, 9, 11, 13, 15, 19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -161,7 +161,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.072 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.096 碼/期</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3457,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>熱號觀察</t>
+          <t>冷號觀察</t>
         </is>
       </c>
       <c r="B2">
@@ -3467,7 +3467,7 @@
         <v>0.929</v>
       </c>
       <c r="D2">
-        <v>28.6</v>
+        <v>26.2</v>
       </c>
       <c r="E2">
         <v>2.4</v>
@@ -3479,17 +3479,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>冷熱混合</t>
+          <t>熱號觀察</t>
         </is>
       </c>
       <c r="B3">
         <v>42</v>
       </c>
       <c r="C3">
-        <v>0.929</v>
+        <v>0.881</v>
       </c>
       <c r="D3">
-        <v>28.6</v>
+        <v>26.2</v>
       </c>
       <c r="E3">
         <v>2.4</v>
@@ -3501,17 +3501,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>冷號觀察</t>
+          <t>冷熱混合</t>
         </is>
       </c>
       <c r="B4">
         <v>42</v>
       </c>
       <c r="C4">
-        <v>0.905</v>
+        <v>0.881</v>
       </c>
       <c r="D4">
-        <v>23.8</v>
+        <v>26.2</v>
       </c>
       <c r="E4">
         <v>2.4</v>
@@ -3530,7 +3530,7 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>0.881</v>
+        <v>0.857</v>
       </c>
       <c r="D5">
         <v>16.7</v>
@@ -3552,10 +3552,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>0.857</v>
+        <v>0.833</v>
       </c>
       <c r="D6">
-        <v>21.4</v>
+        <v>19.0</v>
       </c>
       <c r="E6">
         <v>2.4</v>
@@ -3645,28 +3645,28 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>71.5</v>
+        <v>72.42</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>100.0</v>
+        <v>60.0</v>
       </c>
       <c r="H2">
-        <v>100.0</v>
+        <v>80.0</v>
       </c>
       <c r="I2">
-        <v>0.0</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="3">
@@ -3674,28 +3674,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C3">
-        <v>68.81</v>
+        <v>72.4</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>66.67</v>
+        <v>73.33</v>
       </c>
       <c r="H3">
-        <v>66.67</v>
+        <v>100.0</v>
       </c>
       <c r="I3">
-        <v>40.91</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="4">
@@ -3703,13 +3703,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C4">
-        <v>67.61</v>
+        <v>72.15</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -3718,13 +3718,13 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>73.33</v>
+        <v>100.0</v>
       </c>
       <c r="H4">
-        <v>83.33</v>
+        <v>100.0</v>
       </c>
       <c r="I4">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="5">
@@ -3732,10 +3732,10 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C5">
-        <v>67.41</v>
+        <v>70.9</v>
       </c>
       <c r="D5">
         <v>9</v>
@@ -3744,16 +3744,16 @@
         <v>5</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5">
         <v>60.0</v>
       </c>
       <c r="H5">
-        <v>83.33</v>
+        <v>100.0</v>
       </c>
       <c r="I5">
-        <v>4.55</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
@@ -3761,28 +3761,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>66.68</v>
+        <v>69.36</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>66.67</v>
+        <v>73.33</v>
       </c>
       <c r="H6">
-        <v>50.0</v>
+        <v>80.0</v>
       </c>
       <c r="I6">
-        <v>54.55</v>
+        <v>21.74</v>
       </c>
     </row>
     <row r="7">
@@ -3790,28 +3790,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>65.49</v>
+        <v>67.2</v>
       </c>
       <c r="D7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E7">
         <v>4</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>73.33</v>
+        <v>60.0</v>
       </c>
       <c r="H7">
-        <v>66.67</v>
+        <v>80.0</v>
       </c>
       <c r="I7">
-        <v>18.18</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="8">
@@ -3819,28 +3819,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>63.82</v>
+        <v>66.55</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8">
-        <v>46.67</v>
+        <v>60.0</v>
       </c>
       <c r="H8">
-        <v>83.33</v>
+        <v>80.0</v>
       </c>
       <c r="I8">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="9">
@@ -3848,28 +3848,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C9">
-        <v>63.15</v>
+        <v>64.7</v>
       </c>
       <c r="D9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>53.33</v>
+        <v>40.0</v>
       </c>
       <c r="H9">
-        <v>66.67</v>
+        <v>100.0</v>
       </c>
       <c r="I9">
-        <v>4.55</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="10">
@@ -3877,28 +3877,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C10">
-        <v>62.57</v>
+        <v>64.48</v>
       </c>
       <c r="D10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G10">
-        <v>60.0</v>
+        <v>66.67</v>
       </c>
       <c r="H10">
-        <v>66.67</v>
+        <v>40.0</v>
       </c>
       <c r="I10">
-        <v>0.0</v>
+        <v>56.52</v>
       </c>
     </row>
     <row r="11">
@@ -3909,25 +3909,25 @@
         <v>19</v>
       </c>
       <c r="C11">
-        <v>61.25</v>
+        <v>63.18</v>
       </c>
       <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11">
         <v>11</v>
       </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
-      <c r="F11">
-        <v>10</v>
-      </c>
       <c r="G11">
-        <v>73.33</v>
+        <v>66.67</v>
       </c>
       <c r="H11">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I11">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
     </row>
     <row r="12">
@@ -3935,28 +3935,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C12">
-        <v>60.67</v>
+        <v>62.96</v>
       </c>
       <c r="D12">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G12">
-        <v>80.0</v>
+        <v>66.67</v>
       </c>
       <c r="H12">
-        <v>33.33</v>
+        <v>60.0</v>
       </c>
       <c r="I12">
-        <v>40.91</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="13">
@@ -3964,28 +3964,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C13">
-        <v>59.86</v>
+        <v>62.52</v>
       </c>
       <c r="D13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G13">
-        <v>66.67</v>
+        <v>46.67</v>
       </c>
       <c r="H13">
-        <v>50.0</v>
+        <v>60.0</v>
       </c>
       <c r="I13">
-        <v>9.09</v>
+        <v>34.78</v>
       </c>
     </row>
     <row r="14">
@@ -3993,28 +3993,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>59.57</v>
+        <v>62.31</v>
       </c>
       <c r="D14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E14">
         <v>3</v>
       </c>
       <c r="F14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G14">
-        <v>46.67</v>
+        <v>66.67</v>
       </c>
       <c r="H14">
-        <v>50.0</v>
+        <v>60.0</v>
       </c>
       <c r="I14">
-        <v>31.82</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="15">
@@ -4022,13 +4022,13 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C15">
-        <v>59.18</v>
+        <v>61.55</v>
       </c>
       <c r="D15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E15">
         <v>3</v>
@@ -4037,13 +4037,13 @@
         <v>1</v>
       </c>
       <c r="G15">
-        <v>66.67</v>
+        <v>60.0</v>
       </c>
       <c r="H15">
-        <v>50.0</v>
+        <v>60.0</v>
       </c>
       <c r="I15">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="16">
@@ -4054,7 +4054,7 @@
         <v>14</v>
       </c>
       <c r="C16">
-        <v>58.9</v>
+        <v>61.02</v>
       </c>
       <c r="D16">
         <v>8</v>
@@ -4063,16 +4063,16 @@
         <v>2</v>
       </c>
       <c r="F16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G16">
         <v>53.33</v>
       </c>
       <c r="H16">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I16">
-        <v>31.82</v>
+        <v>34.78</v>
       </c>
     </row>
     <row r="17">
@@ -4080,28 +4080,28 @@
         <v>16</v>
       </c>
       <c r="B17">
+        <v>24</v>
+      </c>
+      <c r="C17">
+        <v>60.01</v>
+      </c>
+      <c r="D17">
         <v>11</v>
       </c>
-      <c r="C17">
-        <v>58.82</v>
-      </c>
-      <c r="D17">
-        <v>7</v>
-      </c>
       <c r="E17">
         <v>2</v>
       </c>
       <c r="F17">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G17">
-        <v>46.67</v>
+        <v>73.33</v>
       </c>
       <c r="H17">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I17">
-        <v>54.55</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="18">
@@ -4109,28 +4109,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C18">
-        <v>58.75</v>
+        <v>59.26</v>
       </c>
       <c r="D18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G18">
-        <v>53.33</v>
+        <v>66.67</v>
       </c>
       <c r="H18">
-        <v>0.0</v>
+        <v>40.0</v>
       </c>
       <c r="I18">
-        <v>86.36</v>
+        <v>21.74</v>
       </c>
     </row>
     <row r="19">
@@ -4138,28 +4138,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C19">
-        <v>58.4</v>
+        <v>59.06</v>
       </c>
       <c r="D19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G19">
-        <v>60.0</v>
+        <v>53.33</v>
       </c>
       <c r="H19">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="I19">
-        <v>0.0</v>
+        <v>21.74</v>
       </c>
     </row>
     <row r="20">
@@ -4167,28 +4167,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C20">
-        <v>57.84</v>
+        <v>58.84</v>
       </c>
       <c r="D20">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G20">
-        <v>73.33</v>
+        <v>53.33</v>
       </c>
       <c r="H20">
-        <v>33.33</v>
+        <v>0.0</v>
       </c>
       <c r="I20">
-        <v>22.73</v>
+        <v>86.96</v>
       </c>
     </row>
     <row r="21">
@@ -4196,28 +4196,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C21">
-        <v>57.06</v>
+        <v>57.62</v>
       </c>
       <c r="D21">
+        <v>11</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
         <v>10</v>
       </c>
-      <c r="E21">
-        <v>2</v>
-      </c>
-      <c r="F21">
-        <v>4</v>
-      </c>
       <c r="G21">
-        <v>66.67</v>
+        <v>73.33</v>
       </c>
       <c r="H21">
-        <v>33.33</v>
+        <v>20.0</v>
       </c>
       <c r="I21">
-        <v>18.18</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="22">
@@ -4225,28 +4225,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="C22">
-        <v>56.86</v>
+        <v>56.75</v>
       </c>
       <c r="D22">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E22">
         <v>2</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G22">
-        <v>53.33</v>
+        <v>73.33</v>
       </c>
       <c r="H22">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I22">
-        <v>18.18</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="23">
@@ -4254,28 +4254,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C23">
-        <v>54.43</v>
+        <v>56.55</v>
       </c>
       <c r="D23">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E23">
         <v>2</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>73.33</v>
+        <v>60.0</v>
       </c>
       <c r="H23">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I23">
-        <v>0.0</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="24">
@@ -4283,13 +4283,13 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C24">
-        <v>54.23</v>
+        <v>55.8</v>
       </c>
       <c r="D24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E24">
         <v>2</v>
@@ -4298,10 +4298,10 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>60.0</v>
+        <v>53.33</v>
       </c>
       <c r="H24">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I24">
         <v>0.0</v>
@@ -4312,28 +4312,28 @@
         <v>24</v>
       </c>
       <c r="B25">
+        <v>11</v>
+      </c>
+      <c r="C25">
+        <v>55.78</v>
+      </c>
+      <c r="D25">
+        <v>7</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
         <v>13</v>
       </c>
-      <c r="C25">
-        <v>53.4</v>
-      </c>
-      <c r="D25">
-        <v>6</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>22</v>
-      </c>
       <c r="G25">
-        <v>40.0</v>
+        <v>46.67</v>
       </c>
       <c r="H25">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I25">
-        <v>100.0</v>
+        <v>56.52</v>
       </c>
     </row>
     <row r="26">
@@ -4341,10 +4341,10 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C26">
-        <v>52.95</v>
+        <v>54.05</v>
       </c>
       <c r="D26">
         <v>6</v>
@@ -4353,16 +4353,16 @@
         <v>3</v>
       </c>
       <c r="F26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G26">
         <v>40.0</v>
       </c>
       <c r="H26">
-        <v>50.0</v>
+        <v>60.0</v>
       </c>
       <c r="I26">
-        <v>13.64</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="27">
@@ -4370,28 +4370,28 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C27">
-        <v>52.61</v>
+        <v>53.4</v>
       </c>
       <c r="D27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F27">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>46.67</v>
+        <v>40.0</v>
       </c>
       <c r="H27">
-        <v>16.67</v>
+        <v>60.0</v>
       </c>
       <c r="I27">
-        <v>40.91</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="28">
@@ -4399,28 +4399,28 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C28">
-        <v>50.9</v>
+        <v>52.1</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G28">
-        <v>40.0</v>
+        <v>53.33</v>
       </c>
       <c r="H28">
-        <v>50.0</v>
+        <v>20.0</v>
       </c>
       <c r="I28">
-        <v>0.0</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="29">
@@ -4428,28 +4428,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>50.65</v>
+        <v>51.01</v>
       </c>
       <c r="D29">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G29">
-        <v>53.33</v>
+        <v>40.0</v>
       </c>
       <c r="H29">
-        <v>16.67</v>
+        <v>40.0</v>
       </c>
       <c r="I29">
-        <v>4.55</v>
+        <v>17.39</v>
       </c>
     </row>
     <row r="30">
@@ -4457,28 +4457,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C30">
-        <v>48.51</v>
+        <v>49.72</v>
       </c>
       <c r="D30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G30">
-        <v>46.67</v>
+        <v>33.33</v>
       </c>
       <c r="H30">
-        <v>16.67</v>
+        <v>40.0</v>
       </c>
       <c r="I30">
-        <v>13.64</v>
+        <v>34.78</v>
       </c>
     </row>
     <row r="31">
@@ -4486,28 +4486,28 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C31">
-        <v>47.6</v>
+        <v>49.5</v>
       </c>
       <c r="D31">
         <v>5</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="G31">
         <v>33.33</v>
       </c>
       <c r="H31">
-        <v>33.33</v>
+        <v>0.0</v>
       </c>
       <c r="I31">
-        <v>31.82</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="32">
@@ -4518,7 +4518,7 @@
         <v>10</v>
       </c>
       <c r="C32">
-        <v>47.34</v>
+        <v>48.62</v>
       </c>
       <c r="D32">
         <v>6</v>
@@ -4527,16 +4527,16 @@
         <v>1</v>
       </c>
       <c r="F32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G32">
         <v>40.0</v>
       </c>
       <c r="H32">
-        <v>16.67</v>
+        <v>20.0</v>
       </c>
       <c r="I32">
-        <v>31.82</v>
+        <v>34.78</v>
       </c>
     </row>
     <row r="33">
@@ -4544,10 +4544,10 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C33">
-        <v>45.56</v>
+        <v>47.76</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -4556,16 +4556,16 @@
         <v>2</v>
       </c>
       <c r="F33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G33">
         <v>33.33</v>
       </c>
       <c r="H33">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I33">
-        <v>18.18</v>
+        <v>21.74</v>
       </c>
     </row>
     <row r="34">
@@ -4573,10 +4573,10 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C34">
-        <v>45.56</v>
+        <v>46.45</v>
       </c>
       <c r="D34">
         <v>5</v>
@@ -4585,16 +4585,16 @@
         <v>2</v>
       </c>
       <c r="F34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G34">
         <v>33.33</v>
       </c>
       <c r="H34">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="I34">
-        <v>18.18</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="35">
@@ -4602,28 +4602,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C35">
-        <v>44.19</v>
+        <v>46.01</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G35">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="H35">
-        <v>33.33</v>
+        <v>20.0</v>
       </c>
       <c r="I35">
-        <v>9.09</v>
+        <v>17.39</v>
       </c>
     </row>
     <row r="36">
@@ -4634,25 +4634,25 @@
         <v>32</v>
       </c>
       <c r="C36">
-        <v>42.27</v>
+        <v>44.5</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G36">
-        <v>26.67</v>
+        <v>33.33</v>
       </c>
       <c r="H36">
-        <v>16.67</v>
+        <v>40.0</v>
       </c>
       <c r="I36">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="37">
@@ -4660,28 +4660,28 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C37">
-        <v>38.97</v>
+        <v>36.92</v>
       </c>
       <c r="D37">
         <v>3</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G37">
         <v>20.0</v>
       </c>
       <c r="H37">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I37">
-        <v>81.82</v>
+        <v>34.78</v>
       </c>
     </row>
     <row r="38">
@@ -4692,25 +4692,25 @@
         <v>5</v>
       </c>
       <c r="C38">
-        <v>36.93</v>
+        <v>35.6</v>
       </c>
       <c r="D38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38">
         <v>0</v>
       </c>
-      <c r="F38">
-        <v>15</v>
-      </c>
       <c r="G38">
+        <v>26.67</v>
+      </c>
+      <c r="H38">
         <v>20.0</v>
       </c>
-      <c r="H38">
+      <c r="I38">
         <v>0.0</v>
-      </c>
-      <c r="I38">
-        <v>68.18</v>
       </c>
     </row>
     <row r="39">
@@ -4718,28 +4718,28 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C39">
-        <v>35.64</v>
+        <v>35.6</v>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
       <c r="F39">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G39">
+        <v>26.67</v>
+      </c>
+      <c r="H39">
         <v>20.0</v>
       </c>
-      <c r="H39">
-        <v>16.67</v>
-      </c>
       <c r="I39">
-        <v>31.82</v>
+        <v>0.0</v>
       </c>
     </row>
   </sheetData>
@@ -4798,154 +4798,154 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H2">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4">
+        <v>21</v>
+      </c>
+      <c r="G4">
         <v>26</v>
-      </c>
-      <c r="G4">
-        <v>33</v>
       </c>
       <c r="H4">
         <v>37</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H5">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H6">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -4953,11 +4953,11 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C7">
@@ -4967,140 +4967,140 @@
         <v>8</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F7">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G7">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H7">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C8">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D8">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E8">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F8">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G8">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H8">
         <v>37</v>
       </c>
       <c r="I8">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C9">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D9">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E9">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F9">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G9">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H9">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <v>12</v>
+      </c>
+      <c r="E10">
+        <v>14</v>
+      </c>
+      <c r="F10">
+        <v>16</v>
+      </c>
+      <c r="G10">
+        <v>29</v>
+      </c>
+      <c r="H10">
+        <v>36</v>
+      </c>
+      <c r="I10">
         <v>8</v>
-      </c>
-      <c r="D10">
-        <v>17</v>
-      </c>
-      <c r="E10">
-        <v>18</v>
-      </c>
-      <c r="F10">
-        <v>29</v>
-      </c>
-      <c r="G10">
-        <v>33</v>
-      </c>
-      <c r="H10">
-        <v>38</v>
-      </c>
-      <c r="I10">
-        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E11">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G11">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H11">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I11">
         <v>2</v>
@@ -5108,108 +5108,108 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E12">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F12">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G12">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H12">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I12">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E13">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F13">
         <v>19</v>
       </c>
       <c r="G13">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H13">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I13">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F14">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G14">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D15">
         <v>7</v>
@@ -5218,230 +5218,230 @@
         <v>9</v>
       </c>
       <c r="F15">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G15">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H15">
         <v>36</v>
       </c>
       <c r="I15">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E16">
         <v>9</v>
       </c>
       <c r="F16">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G16">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H16">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I16">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <v>9</v>
+      </c>
+      <c r="F17">
         <v>11</v>
       </c>
-      <c r="E17">
-        <v>18</v>
-      </c>
-      <c r="F17">
-        <v>19</v>
-      </c>
       <c r="G17">
+        <v>29</v>
+      </c>
+      <c r="H17">
         <v>35</v>
       </c>
-      <c r="H17">
-        <v>38</v>
-      </c>
       <c r="I17">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F18">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G18">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H18">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="I18">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C19">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E19">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F19">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G19">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H19">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I19">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D20">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E20">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F20">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G20">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H20">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I20">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>7</v>
+      </c>
+      <c r="E21">
+        <v>8</v>
+      </c>
+      <c r="F21">
+        <v>20</v>
+      </c>
+      <c r="G21">
+        <v>26</v>
+      </c>
+      <c r="H21">
+        <v>33</v>
+      </c>
+      <c r="I21">
         <v>4</v>
-      </c>
-      <c r="D21">
-        <v>15</v>
-      </c>
-      <c r="E21">
-        <v>22</v>
-      </c>
-      <c r="F21">
-        <v>26</v>
-      </c>
-      <c r="G21">
-        <v>34</v>
-      </c>
-      <c r="H21">
-        <v>36</v>
-      </c>
-      <c r="I21">
-        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C22">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D22">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E22">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F22">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G22">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H22">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I22">
         <v>7</v>
@@ -5449,30 +5449,30 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C23">
+        <v>8</v>
+      </c>
+      <c r="D23">
+        <v>14</v>
+      </c>
+      <c r="E23">
+        <v>17</v>
+      </c>
+      <c r="F23">
         <v>19</v>
       </c>
-      <c r="D23">
-        <v>22</v>
-      </c>
-      <c r="E23">
-        <v>28</v>
-      </c>
-      <c r="F23">
-        <v>31</v>
-      </c>
       <c r="G23">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H23">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I23">
         <v>7</v>
@@ -5480,30 +5480,30 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C24">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D24">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E24">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F24">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G24">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H24">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I24">
         <v>7</v>
@@ -5511,24 +5511,24 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D25">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E25">
         <v>13</v>
       </c>
       <c r="F25">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G25">
         <v>29</v>
@@ -5537,97 +5537,97 @@
         <v>31</v>
       </c>
       <c r="I25">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C26">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D26">
+        <v>12</v>
+      </c>
+      <c r="E26">
+        <v>13</v>
+      </c>
+      <c r="F26">
         <v>23</v>
       </c>
-      <c r="E26">
-        <v>25</v>
-      </c>
-      <c r="F26">
+      <c r="G26">
         <v>29</v>
       </c>
-      <c r="G26">
-        <v>34</v>
-      </c>
       <c r="H26">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I26">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C27">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D27">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E27">
+        <v>25</v>
+      </c>
+      <c r="F27">
         <v>29</v>
       </c>
-      <c r="F27">
-        <v>32</v>
-      </c>
       <c r="G27">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H27">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I27">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C28">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D28">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E28">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F28">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G28">
         <v>35</v>
       </c>
       <c r="H28">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I28">
         <v>6</v>
@@ -5635,402 +5635,402 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C29">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D29">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E29">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F29">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G29">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H29">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I29">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E30">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F30">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G30">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H30">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I30">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C31">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D31">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E31">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F31">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G31">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H31">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I31">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C32">
+        <v>5</v>
+      </c>
+      <c r="D32">
         <v>6</v>
       </c>
-      <c r="D32">
-        <v>10</v>
-      </c>
       <c r="E32">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F32">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G32">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H32">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I32">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C33">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D33">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E33">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F33">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G33">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H33">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I33">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D34">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E34">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F34">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G34">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H34">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I34">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C35">
+        <v>2</v>
+      </c>
+      <c r="D35">
+        <v>8</v>
+      </c>
+      <c r="E35">
+        <v>9</v>
+      </c>
+      <c r="F35">
+        <v>15</v>
+      </c>
+      <c r="G35">
+        <v>18</v>
+      </c>
+      <c r="H35">
+        <v>23</v>
+      </c>
+      <c r="I35">
         <v>4</v>
-      </c>
-      <c r="D35">
-        <v>17</v>
-      </c>
-      <c r="E35">
-        <v>19</v>
-      </c>
-      <c r="F35">
-        <v>25</v>
-      </c>
-      <c r="G35">
-        <v>28</v>
-      </c>
-      <c r="H35">
-        <v>29</v>
-      </c>
-      <c r="I35">
-        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D36">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E36">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F36">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G36">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H36">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I36">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D37">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E37">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F37">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G37">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H37">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I37">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C38">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D38">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E38">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F38">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G38">
         <v>28</v>
       </c>
       <c r="H38">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I38">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C39">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D39">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E39">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F39">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G39">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H39">
         <v>35</v>
       </c>
       <c r="I39">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E40">
+        <v>9</v>
+      </c>
+      <c r="F40">
+        <v>15</v>
+      </c>
+      <c r="G40">
         <v>24</v>
       </c>
-      <c r="F40">
-        <v>31</v>
-      </c>
-      <c r="G40">
-        <v>34</v>
-      </c>
       <c r="H40">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I40">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C41">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D41">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E41">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F41">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G41">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H41">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I41">
         <v>3</v>
@@ -6038,312 +6038,312 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C42">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D42">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E42">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F42">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G42">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H42">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I42">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C43">
         <v>6</v>
       </c>
       <c r="D43">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E43">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F43">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G43">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H43">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I43">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C44">
         <v>6</v>
       </c>
       <c r="D44">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E44">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F44">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G44">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H44">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I44">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C45">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D45">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E45">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F45">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G45">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H45">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I45">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C46">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D46">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E46">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F46">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G46">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H46">
         <v>38</v>
       </c>
       <c r="I46">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C47">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D47">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E47">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F47">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G47">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H47">
         <v>38</v>
       </c>
       <c r="I47">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D48">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E48">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F48">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G48">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H48">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I48">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C49">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D49">
+        <v>4</v>
+      </c>
+      <c r="E49">
+        <v>13</v>
+      </c>
+      <c r="F49">
+        <v>19</v>
+      </c>
+      <c r="G49">
+        <v>27</v>
+      </c>
+      <c r="H49">
+        <v>30</v>
+      </c>
+      <c r="I49">
         <v>8</v>
-      </c>
-      <c r="E49">
-        <v>27</v>
-      </c>
-      <c r="F49">
-        <v>33</v>
-      </c>
-      <c r="G49">
-        <v>35</v>
-      </c>
-      <c r="H49">
-        <v>38</v>
-      </c>
-      <c r="I49">
-        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C50">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D50">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E50">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F50">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G50">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H50">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I50">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000032</v>
+        <v>115000033</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D51">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E51">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F51">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G51">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H51">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I51">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-10-09 第 115000095 期；威力彩 2026-10-12 第 115000082 期</t>
+          <t>大樂透 2026-10-13 第 115000096 期；威力彩 2026-10-12 第 115000082 期</t>
         </is>
       </c>
     </row>
@@ -47,7 +47,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>115000095</v>
+        <v>115000096</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -56,7 +56,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -96,7 +96,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.238 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.262 碼/期</t>
         </is>
       </c>
     </row>
@@ -258,10 +258,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>0.833</v>
+        <v>0.857</v>
       </c>
       <c r="D4">
-        <v>21.4</v>
+        <v>23.8</v>
       </c>
       <c r="E4">
         <v>2.4</v>
@@ -280,10 +280,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>0.81</v>
+        <v>0.833</v>
       </c>
       <c r="D5">
-        <v>21.4</v>
+        <v>23.8</v>
       </c>
       <c r="E5">
         <v>2.4</v>
@@ -324,7 +324,7 @@
         <v>42</v>
       </c>
       <c r="C7">
-        <v>0.667</v>
+        <v>0.643</v>
       </c>
       <c r="D7">
         <v>14.3</v>
@@ -395,10 +395,10 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C2">
-        <v>73.7</v>
+        <v>73.05</v>
       </c>
       <c r="D2">
         <v>11</v>
@@ -407,7 +407,7 @@
         <v>5</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <v>100.0</v>
@@ -416,7 +416,7 @@
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>4.35</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="3">
@@ -424,28 +424,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>69.4</v>
+        <v>72.22</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>90.91</v>
+        <v>72.73</v>
       </c>
       <c r="H3">
-        <v>80.0</v>
+        <v>100.0</v>
       </c>
       <c r="I3">
-        <v>10.87</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="4">
@@ -453,28 +453,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C4">
-        <v>68.15</v>
+        <v>69.01</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E4">
         <v>4</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4">
-        <v>81.82</v>
+        <v>100.0</v>
       </c>
       <c r="H4">
         <v>80.0</v>
       </c>
       <c r="I4">
-        <v>4.35</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="5">
@@ -482,28 +482,28 @@
         <v>4</v>
       </c>
       <c r="B5">
+        <v>18</v>
+      </c>
+      <c r="C5">
+        <v>64.41</v>
+      </c>
+      <c r="D5">
+        <v>9</v>
+      </c>
+      <c r="E5">
         <v>3</v>
       </c>
-      <c r="C5">
-        <v>66.94</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
       <c r="F5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>63.64</v>
+        <v>81.82</v>
       </c>
       <c r="H5">
-        <v>80.0</v>
+        <v>60.0</v>
       </c>
       <c r="I5">
-        <v>0.0</v>
+        <v>12.77</v>
       </c>
     </row>
     <row r="6">
@@ -511,28 +511,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C6">
         <v>64.13</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>81.82</v>
+        <v>72.73</v>
       </c>
       <c r="H6">
         <v>60.0</v>
       </c>
       <c r="I6">
-        <v>10.87</v>
+        <v>12.77</v>
       </c>
     </row>
     <row r="7">
@@ -540,28 +540,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7">
-        <v>63.85</v>
+        <v>63.45</v>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>72.73</v>
+        <v>81.82</v>
       </c>
       <c r="H7">
         <v>60.0</v>
       </c>
       <c r="I7">
-        <v>10.87</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="8">
@@ -572,7 +572,7 @@
         <v>4</v>
       </c>
       <c r="C8">
-        <v>62.82</v>
+        <v>63.13</v>
       </c>
       <c r="D8">
         <v>9</v>
@@ -581,7 +581,7 @@
         <v>3</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8">
         <v>81.82</v>
@@ -590,7 +590,7 @@
         <v>60.0</v>
       </c>
       <c r="I8">
-        <v>2.17</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="9">
@@ -601,25 +601,25 @@
         <v>20</v>
       </c>
       <c r="C9">
-        <v>62.82</v>
+        <v>62.86</v>
       </c>
       <c r="D9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>81.82</v>
+        <v>72.73</v>
       </c>
       <c r="H9">
         <v>60.0</v>
       </c>
       <c r="I9">
-        <v>2.17</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="10">
@@ -627,28 +627,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="C10">
-        <v>62.59</v>
+        <v>62.34</v>
       </c>
       <c r="D10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>63.64</v>
+        <v>54.55</v>
       </c>
       <c r="H10">
         <v>60.0</v>
       </c>
       <c r="I10">
-        <v>4.35</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="11">
@@ -656,28 +656,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C11">
-        <v>62.37</v>
+        <v>62.22</v>
       </c>
       <c r="D11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>54.55</v>
+        <v>72.73</v>
       </c>
       <c r="H11">
         <v>60.0</v>
       </c>
       <c r="I11">
-        <v>8.7</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="12">
@@ -685,28 +685,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="C12">
-        <v>62.04</v>
+        <v>62.22</v>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>54.55</v>
+        <v>72.73</v>
       </c>
       <c r="H12">
         <v>60.0</v>
       </c>
       <c r="I12">
-        <v>6.52</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="13">
@@ -714,28 +714,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C13">
-        <v>60.66</v>
+        <v>61.94</v>
       </c>
       <c r="D13">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>100.0</v>
+        <v>63.64</v>
       </c>
       <c r="H13">
-        <v>40.0</v>
+        <v>60.0</v>
       </c>
       <c r="I13">
-        <v>17.39</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="14">
@@ -743,28 +743,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C14">
-        <v>60.1</v>
+        <v>60.92</v>
       </c>
       <c r="D14">
+        <v>11</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
         <v>9</v>
       </c>
-      <c r="E14">
-        <v>2</v>
-      </c>
-      <c r="F14">
-        <v>8</v>
-      </c>
       <c r="G14">
-        <v>81.82</v>
+        <v>100.0</v>
       </c>
       <c r="H14">
         <v>40.0</v>
       </c>
       <c r="I14">
-        <v>17.39</v>
+        <v>19.15</v>
       </c>
     </row>
     <row r="15">
@@ -772,28 +772,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C15">
-        <v>59.98</v>
+        <v>60.09</v>
       </c>
       <c r="D15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E15">
         <v>2</v>
       </c>
       <c r="F15">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G15">
-        <v>54.55</v>
+        <v>72.73</v>
       </c>
       <c r="H15">
         <v>40.0</v>
       </c>
       <c r="I15">
-        <v>26.09</v>
+        <v>19.15</v>
       </c>
     </row>
     <row r="16">
@@ -804,7 +804,7 @@
         <v>27</v>
       </c>
       <c r="C16">
-        <v>58.67</v>
+        <v>58.94</v>
       </c>
       <c r="D16">
         <v>6</v>
@@ -813,7 +813,7 @@
         <v>2</v>
       </c>
       <c r="F16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G16">
         <v>54.55</v>
@@ -822,7 +822,7 @@
         <v>40.0</v>
       </c>
       <c r="I16">
-        <v>17.39</v>
+        <v>19.15</v>
       </c>
     </row>
     <row r="17">
@@ -830,28 +830,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C17">
-        <v>58.67</v>
+        <v>58.54</v>
       </c>
       <c r="D17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
       <c r="F17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G17">
-        <v>54.55</v>
+        <v>63.64</v>
       </c>
       <c r="H17">
         <v>40.0</v>
       </c>
       <c r="I17">
-        <v>17.39</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="18">
@@ -859,28 +859,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C18">
-        <v>58.25</v>
+        <v>58.09</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>63.64</v>
+        <v>90.91</v>
       </c>
       <c r="H18">
         <v>40.0</v>
       </c>
       <c r="I18">
-        <v>8.7</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="19">
@@ -888,28 +888,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C19">
-        <v>57.92</v>
+        <v>57.66</v>
       </c>
       <c r="D19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G19">
-        <v>63.64</v>
+        <v>54.55</v>
       </c>
       <c r="H19">
         <v>40.0</v>
       </c>
       <c r="I19">
-        <v>6.52</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="20">
@@ -917,28 +917,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C20">
-        <v>57.77</v>
+        <v>57.58</v>
       </c>
       <c r="D20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20">
-        <v>90.91</v>
+        <v>63.64</v>
       </c>
       <c r="H20">
         <v>40.0</v>
       </c>
       <c r="I20">
-        <v>0.0</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="21">
@@ -946,28 +946,28 @@
         <v>20</v>
       </c>
       <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>57.34</v>
+      </c>
+      <c r="D21">
         <v>6</v>
       </c>
-      <c r="C21">
-        <v>57.27</v>
-      </c>
-      <c r="D21">
-        <v>7</v>
-      </c>
       <c r="E21">
         <v>2</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G21">
-        <v>63.64</v>
+        <v>54.55</v>
       </c>
       <c r="H21">
         <v>40.0</v>
       </c>
       <c r="I21">
-        <v>2.17</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="22">
@@ -975,28 +975,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C22">
-        <v>57.27</v>
+        <v>56.88</v>
       </c>
       <c r="D22">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G22">
-        <v>63.64</v>
+        <v>100.0</v>
       </c>
       <c r="H22">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I22">
-        <v>2.17</v>
+        <v>25.53</v>
       </c>
     </row>
     <row r="23">
@@ -1004,28 +1004,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="C23">
-        <v>57.27</v>
+        <v>56.7</v>
       </c>
       <c r="D23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E23">
         <v>2</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>63.64</v>
+        <v>54.55</v>
       </c>
       <c r="H23">
         <v>40.0</v>
       </c>
       <c r="I23">
-        <v>2.17</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="24">
@@ -1033,28 +1033,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C24">
-        <v>56.64</v>
+        <v>56.7</v>
       </c>
       <c r="D24">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G24">
-        <v>100.0</v>
+        <v>54.55</v>
       </c>
       <c r="H24">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I24">
-        <v>23.91</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="25">
@@ -1062,28 +1062,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C25">
-        <v>56.39</v>
+        <v>56.33</v>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G25">
-        <v>54.55</v>
+        <v>81.82</v>
       </c>
       <c r="H25">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I25">
-        <v>2.17</v>
+        <v>25.53</v>
       </c>
     </row>
     <row r="26">
@@ -1091,28 +1091,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C26">
-        <v>56.08</v>
+        <v>55.21</v>
       </c>
       <c r="D26">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G26">
-        <v>81.82</v>
+        <v>54.55</v>
       </c>
       <c r="H26">
         <v>20.0</v>
       </c>
       <c r="I26">
-        <v>23.91</v>
+        <v>27.66</v>
       </c>
     </row>
     <row r="27">
@@ -1120,10 +1120,10 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="C27">
-        <v>55.63</v>
+        <v>54.58</v>
       </c>
       <c r="D27">
         <v>6</v>
@@ -1132,7 +1132,7 @@
         <v>1</v>
       </c>
       <c r="F27">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G27">
         <v>54.55</v>
@@ -1141,7 +1141,7 @@
         <v>20.0</v>
       </c>
       <c r="I27">
-        <v>30.43</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="28">
@@ -1149,10 +1149,10 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C28">
-        <v>54.33</v>
+        <v>54.26</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -1170,7 +1170,7 @@
         <v>20.0</v>
       </c>
       <c r="I28">
-        <v>21.74</v>
+        <v>21.28</v>
       </c>
     </row>
     <row r="29">
@@ -1178,10 +1178,10 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C29">
-        <v>54.0</v>
+        <v>53.94</v>
       </c>
       <c r="D29">
         <v>6</v>
@@ -1199,7 +1199,7 @@
         <v>20.0</v>
       </c>
       <c r="I29">
-        <v>19.57</v>
+        <v>19.15</v>
       </c>
     </row>
     <row r="30">
@@ -1207,28 +1207,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C30">
-        <v>53.67</v>
+        <v>52.26</v>
       </c>
       <c r="D30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G30">
-        <v>54.55</v>
+        <v>63.64</v>
       </c>
       <c r="H30">
         <v>20.0</v>
       </c>
       <c r="I30">
-        <v>17.39</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="31">
@@ -1236,28 +1236,28 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="C31">
-        <v>51.94</v>
+        <v>52.16</v>
       </c>
       <c r="D31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G31">
-        <v>63.64</v>
+        <v>45.45</v>
       </c>
       <c r="H31">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I31">
-        <v>0.0</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="32">
@@ -1265,10 +1265,10 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="C32">
-        <v>51.86</v>
+        <v>52.16</v>
       </c>
       <c r="D32">
         <v>5</v>
@@ -1277,7 +1277,7 @@
         <v>2</v>
       </c>
       <c r="F32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G32">
         <v>45.45</v>
@@ -1286,7 +1286,7 @@
         <v>40.0</v>
       </c>
       <c r="I32">
-        <v>6.52</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="33">
@@ -1294,10 +1294,10 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C33">
-        <v>51.86</v>
+        <v>51.2</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -1306,7 +1306,7 @@
         <v>2</v>
       </c>
       <c r="F33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G33">
         <v>45.45</v>
@@ -1315,7 +1315,7 @@
         <v>40.0</v>
       </c>
       <c r="I33">
-        <v>6.52</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="34">
@@ -1323,28 +1323,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C34">
-        <v>50.88</v>
+        <v>50.85</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G34">
-        <v>45.45</v>
+        <v>54.55</v>
       </c>
       <c r="H34">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="I34">
-        <v>0.0</v>
+        <v>31.91</v>
       </c>
     </row>
     <row r="35">
@@ -1355,7 +1355,7 @@
         <v>10</v>
       </c>
       <c r="C35">
-        <v>49.47</v>
+        <v>49.71</v>
       </c>
       <c r="D35">
         <v>5</v>
@@ -1364,7 +1364,7 @@
         <v>1</v>
       </c>
       <c r="F35">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G35">
         <v>45.45</v>
@@ -1373,7 +1373,7 @@
         <v>20.0</v>
       </c>
       <c r="I35">
-        <v>23.91</v>
+        <v>25.53</v>
       </c>
     </row>
     <row r="36">
@@ -1384,7 +1384,7 @@
         <v>21</v>
       </c>
       <c r="C36">
-        <v>47.66</v>
+        <v>47.94</v>
       </c>
       <c r="D36">
         <v>4</v>
@@ -1393,7 +1393,7 @@
         <v>2</v>
       </c>
       <c r="F36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G36">
         <v>36.36</v>
@@ -1402,7 +1402,7 @@
         <v>40.0</v>
       </c>
       <c r="I36">
-        <v>13.04</v>
+        <v>14.89</v>
       </c>
     </row>
     <row r="37">
@@ -1413,7 +1413,7 @@
         <v>33</v>
       </c>
       <c r="C37">
-        <v>47.19</v>
+        <v>47.48</v>
       </c>
       <c r="D37">
         <v>5</v>
@@ -1422,7 +1422,7 @@
         <v>1</v>
       </c>
       <c r="F37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G37">
         <v>45.45</v>
@@ -1431,7 +1431,7 @@
         <v>20.0</v>
       </c>
       <c r="I37">
-        <v>8.7</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="38">
@@ -1439,28 +1439,28 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="C38">
-        <v>46.36</v>
+        <v>46.2</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G38">
-        <v>36.36</v>
+        <v>45.45</v>
       </c>
       <c r="H38">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I38">
-        <v>4.35</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="39">
@@ -1468,28 +1468,28 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="C39">
-        <v>45.88</v>
+        <v>44.86</v>
       </c>
       <c r="D39">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G39">
-        <v>45.45</v>
+        <v>36.36</v>
       </c>
       <c r="H39">
         <v>20.0</v>
       </c>
       <c r="I39">
-        <v>0.0</v>
+        <v>27.66</v>
       </c>
     </row>
     <row r="40">
@@ -1497,28 +1497,28 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C40">
-        <v>44.62</v>
+        <v>41.49</v>
       </c>
       <c r="D40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G40">
-        <v>36.36</v>
+        <v>27.27</v>
       </c>
       <c r="H40">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I40">
-        <v>26.09</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="41">
@@ -1526,28 +1526,28 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="C41">
-        <v>43.97</v>
+        <v>41.45</v>
       </c>
       <c r="D41">
         <v>4</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G41">
         <v>36.36</v>
       </c>
       <c r="H41">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I41">
-        <v>21.74</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="42">
@@ -1555,28 +1555,28 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="C42">
-        <v>41.25</v>
+        <v>40.53</v>
       </c>
       <c r="D42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E42">
+        <v>2</v>
+      </c>
+      <c r="F42">
         <v>0</v>
       </c>
-      <c r="F42">
-        <v>17</v>
-      </c>
       <c r="G42">
-        <v>36.36</v>
+        <v>27.27</v>
       </c>
       <c r="H42">
+        <v>40.0</v>
+      </c>
+      <c r="I42">
         <v>0.0</v>
-      </c>
-      <c r="I42">
-        <v>36.96</v>
       </c>
     </row>
     <row r="43">
@@ -1596,7 +1596,7 @@
         <v>0</v>
       </c>
       <c r="F43">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G43">
         <v>18.18</v>
@@ -1613,10 +1613,10 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C44">
-        <v>37.81</v>
+        <v>39.04</v>
       </c>
       <c r="D44">
         <v>3</v>
@@ -1625,7 +1625,7 @@
         <v>1</v>
       </c>
       <c r="F44">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G44">
         <v>27.27</v>
@@ -1634,7 +1634,7 @@
         <v>20.0</v>
       </c>
       <c r="I44">
-        <v>15.22</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="45">
@@ -1642,10 +1642,10 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="C45">
-        <v>37.16</v>
+        <v>38.08</v>
       </c>
       <c r="D45">
         <v>3</v>
@@ -1654,7 +1654,7 @@
         <v>1</v>
       </c>
       <c r="F45">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G45">
         <v>27.27</v>
@@ -1663,7 +1663,7 @@
         <v>20.0</v>
       </c>
       <c r="I45">
-        <v>10.87</v>
+        <v>17.02</v>
       </c>
     </row>
     <row r="46">
@@ -1671,10 +1671,10 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C46">
-        <v>35.53</v>
+        <v>37.45</v>
       </c>
       <c r="D46">
         <v>3</v>
@@ -1683,7 +1683,7 @@
         <v>1</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G46">
         <v>27.27</v>
@@ -1692,7 +1692,7 @@
         <v>20.0</v>
       </c>
       <c r="I46">
-        <v>0.0</v>
+        <v>12.77</v>
       </c>
     </row>
     <row r="47">
@@ -1700,28 +1700,28 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C47">
-        <v>34.16</v>
+        <v>35.85</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G47">
-        <v>18.18</v>
+        <v>27.27</v>
       </c>
       <c r="H47">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="I47">
-        <v>58.7</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="48">
@@ -1729,28 +1729,28 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C48">
-        <v>32.31</v>
+        <v>34.29</v>
       </c>
       <c r="D48">
         <v>2</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="G48">
         <v>18.18</v>
       </c>
       <c r="H48">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I48">
-        <v>13.04</v>
+        <v>59.57</v>
       </c>
     </row>
     <row r="49">
@@ -1761,7 +1761,7 @@
         <v>5</v>
       </c>
       <c r="C49">
-        <v>31.66</v>
+        <v>31.95</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -1770,7 +1770,7 @@
         <v>1</v>
       </c>
       <c r="F49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G49">
         <v>18.18</v>
@@ -1779,7 +1779,7 @@
         <v>20.0</v>
       </c>
       <c r="I49">
-        <v>8.7</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="50">
@@ -1790,7 +1790,7 @@
         <v>38</v>
       </c>
       <c r="C50">
-        <v>31.33</v>
+        <v>31.63</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -1799,7 +1799,7 @@
         <v>1</v>
       </c>
       <c r="F50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G50">
         <v>18.18</v>
@@ -1808,7 +1808,7 @@
         <v>20.0</v>
       </c>
       <c r="I50">
-        <v>6.52</v>
+        <v>8.51</v>
       </c>
     </row>
   </sheetData>
@@ -1867,855 +1867,855 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000095</v>
+        <v>115000096</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="H2">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I2">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000094</v>
+        <v>115000095</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H3">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I3">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000093</v>
+        <v>115000094</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C4">
         <v>4</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>20</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H4">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="I4">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000092</v>
+        <v>115000093</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H5">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="I5">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000091</v>
+        <v>115000092</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
         <v>13</v>
       </c>
-      <c r="E6">
-        <v>24</v>
-      </c>
-      <c r="F6">
-        <v>25</v>
-      </c>
       <c r="G6">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H6">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I6">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000090</v>
+        <v>115000091</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D7">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G7">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H7">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000089</v>
+        <v>115000090</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E8">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F8">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G8">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H8">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="I8">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000088</v>
+        <v>115000089</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E9">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F9">
         <v>21</v>
       </c>
       <c r="G9">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H9">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I9">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000087</v>
+        <v>115000088</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C10">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E10">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G10">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H10">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I10">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000086</v>
+        <v>115000087</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D11">
         <v>15</v>
       </c>
       <c r="E11">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F11">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G11">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H11">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I11">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000085</v>
+        <v>115000086</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C12">
         <v>3</v>
       </c>
       <c r="D12">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E12">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F12">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G12">
+        <v>47</v>
+      </c>
+      <c r="H12">
+        <v>49</v>
+      </c>
+      <c r="I12">
         <v>27</v>
-      </c>
-      <c r="H12">
-        <v>37</v>
-      </c>
-      <c r="I12">
-        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000084</v>
+        <v>115000085</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C13">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D13">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E13">
+        <v>17</v>
+      </c>
+      <c r="F13">
+        <v>18</v>
+      </c>
+      <c r="G13">
+        <v>27</v>
+      </c>
+      <c r="H13">
+        <v>37</v>
+      </c>
+      <c r="I13">
         <v>19</v>
-      </c>
-      <c r="F13">
-        <v>26</v>
-      </c>
-      <c r="G13">
-        <v>29</v>
-      </c>
-      <c r="H13">
-        <v>48</v>
-      </c>
-      <c r="I13">
-        <v>30</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000083</v>
+        <v>115000084</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E14">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F14">
         <v>26</v>
       </c>
       <c r="G14">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H14">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I14">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C15">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D15">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E15">
+        <v>23</v>
+      </c>
+      <c r="F15">
         <v>26</v>
       </c>
-      <c r="F15">
-        <v>32</v>
-      </c>
       <c r="G15">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H15">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I15">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C16">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D16">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E16">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F16">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G16">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H16">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I16">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D17">
         <v>14</v>
       </c>
       <c r="E17">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F17">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G17">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H17">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I17">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E18">
         <v>25</v>
       </c>
       <c r="F18">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G18">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H18">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I18">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D19">
         <v>12</v>
       </c>
       <c r="E19">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F19">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G19">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H19">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="I19">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D20">
         <v>12</v>
       </c>
       <c r="E20">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F20">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G20">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H20">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I20">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E21">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F21">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G21">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H21">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I21">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C22">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D22">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E22">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F22">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G22">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H22">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I22">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C23">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D23">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E23">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F23">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G23">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H23">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I23">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D24">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E24">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F24">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G24">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H24">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I24">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E25">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F25">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G25">
         <v>35</v>
       </c>
       <c r="H25">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I25">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E26">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F26">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G26">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H26">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I26">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C27">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E27">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F27">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G27">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="H27">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I27">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C28">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E28">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F28">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G28">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H28">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I28">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C29">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D29">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E29">
         <v>15</v>
@@ -2724,345 +2724,345 @@
         <v>18</v>
       </c>
       <c r="G29">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H29">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I29">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C30">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D30">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E30">
+        <v>15</v>
+      </c>
+      <c r="F30">
+        <v>18</v>
+      </c>
+      <c r="G30">
         <v>19</v>
       </c>
-      <c r="F30">
-        <v>23</v>
-      </c>
-      <c r="G30">
-        <v>39</v>
-      </c>
       <c r="H30">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I30">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C31">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D31">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E31">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F31">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G31">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H31">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I31">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C32">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D32">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E32">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G32">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H32">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I32">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C33">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D33">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E33">
+        <v>23</v>
+      </c>
+      <c r="F33">
+        <v>24</v>
+      </c>
+      <c r="G33">
         <v>29</v>
       </c>
-      <c r="F33">
-        <v>33</v>
-      </c>
-      <c r="G33">
-        <v>34</v>
-      </c>
       <c r="H33">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I33">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C34">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D34">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E34">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F34">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G34">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H34">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I34">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E35">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F35">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G35">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H35">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I35">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C36">
         <v>1</v>
       </c>
       <c r="D36">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E36">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F36">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G36">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H36">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I36">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C37">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D37">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E37">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F37">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G37">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H37">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I37">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C38">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D38">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E38">
         <v>25</v>
       </c>
       <c r="F38">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G38">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H38">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I38">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C39">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D39">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E39">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F39">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G39">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H39">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I39">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="C40">
+        <v>8</v>
+      </c>
+      <c r="D40">
+        <v>9</v>
+      </c>
+      <c r="E40">
+        <v>16</v>
+      </c>
+      <c r="F40">
         <v>20</v>
-      </c>
-      <c r="D40">
-        <v>26</v>
-      </c>
-      <c r="E40">
-        <v>29</v>
-      </c>
-      <c r="F40">
-        <v>31</v>
       </c>
       <c r="G40">
         <v>37</v>
@@ -3071,348 +3071,348 @@
         <v>49</v>
       </c>
       <c r="I40">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="C41">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D41">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E41">
         <v>29</v>
       </c>
       <c r="F41">
+        <v>31</v>
+      </c>
+      <c r="G41">
         <v>37</v>
       </c>
-      <c r="G41">
-        <v>47</v>
-      </c>
       <c r="H41">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I41">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="C42">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D42">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E42">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F42">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G42">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="H42">
         <v>48</v>
       </c>
       <c r="I42">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C43">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D43">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E43">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F43">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G43">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H43">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I43">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C44">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D44">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E44">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F44">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G44">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H44">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I44">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C45">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D45">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E45">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F45">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G45">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H45">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I45">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C46">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D46">
+        <v>12</v>
+      </c>
+      <c r="E46">
         <v>18</v>
       </c>
-      <c r="E46">
-        <v>25</v>
-      </c>
       <c r="F46">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G46">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H46">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I46">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C47">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D47">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E47">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F47">
         <v>28</v>
       </c>
       <c r="G47">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H47">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I47">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C48">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D48">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E48">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F48">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G48">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H48">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I48">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C49">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D49">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E49">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F49">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G49">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H49">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I49">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C50">
+        <v>6</v>
+      </c>
+      <c r="D50">
+        <v>10</v>
+      </c>
+      <c r="E50">
+        <v>14</v>
+      </c>
+      <c r="F50">
+        <v>25</v>
+      </c>
+      <c r="G50">
+        <v>26</v>
+      </c>
+      <c r="H50">
+        <v>32</v>
+      </c>
+      <c r="I50">
         <v>7</v>
-      </c>
-      <c r="D50">
-        <v>14</v>
-      </c>
-      <c r="E50">
-        <v>16</v>
-      </c>
-      <c r="F50">
-        <v>37</v>
-      </c>
-      <c r="G50">
-        <v>39</v>
-      </c>
-      <c r="H50">
-        <v>47</v>
-      </c>
-      <c r="I50">
-        <v>34</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D51">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E51">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F51">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G51">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H51">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I51">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-10-13 第 115000096 期；威力彩 2026-10-12 第 115000082 期</t>
+          <t>大樂透 2026-10-13 第 115000096 期；威力彩 2026-10-15 第 115000083 期</t>
         </is>
       </c>
     </row>
@@ -112,7 +112,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -121,7 +121,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -143,7 +143,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7, 9, 11, 13, 15, 19</t>
+          <t>2, 7, 8, 17, 26, 29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -161,7 +161,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.096 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.072 碼/期</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>0.929</v>
+        <v>0.905</v>
       </c>
       <c r="D2">
         <v>26.2</v>
@@ -3479,17 +3479,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>熱號觀察</t>
+          <t>隨機基準</t>
         </is>
       </c>
       <c r="B3">
         <v>42</v>
       </c>
       <c r="C3">
-        <v>0.881</v>
+        <v>0.833</v>
       </c>
       <c r="D3">
-        <v>26.2</v>
+        <v>19.0</v>
       </c>
       <c r="E3">
         <v>2.4</v>
@@ -3501,17 +3501,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>冷熱混合</t>
+          <t>熱號觀察</t>
         </is>
       </c>
       <c r="B4">
         <v>42</v>
       </c>
       <c r="C4">
-        <v>0.881</v>
+        <v>0.833</v>
       </c>
       <c r="D4">
-        <v>26.2</v>
+        <v>23.8</v>
       </c>
       <c r="E4">
         <v>2.4</v>
@@ -3530,7 +3530,7 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>0.857</v>
+        <v>0.833</v>
       </c>
       <c r="D5">
         <v>16.7</v>
@@ -3545,7 +3545,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>隨機基準</t>
+          <t>冷熱混合</t>
         </is>
       </c>
       <c r="B6">
@@ -3555,7 +3555,7 @@
         <v>0.833</v>
       </c>
       <c r="D6">
-        <v>19.0</v>
+        <v>23.8</v>
       </c>
       <c r="E6">
         <v>2.4</v>
@@ -3574,7 +3574,7 @@
         <v>42</v>
       </c>
       <c r="C7">
-        <v>0.786</v>
+        <v>0.762</v>
       </c>
       <c r="D7">
         <v>14.3</v>
@@ -3645,28 +3645,28 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C2">
-        <v>72.42</v>
+        <v>72.97</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>60.0</v>
+        <v>73.33</v>
       </c>
       <c r="H2">
-        <v>80.0</v>
+        <v>100.0</v>
       </c>
       <c r="I2">
-        <v>43.48</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="3">
@@ -3674,13 +3674,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C3">
-        <v>72.4</v>
+        <v>72.75</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -3689,13 +3689,13 @@
         <v>2</v>
       </c>
       <c r="G3">
-        <v>73.33</v>
+        <v>100.0</v>
       </c>
       <c r="H3">
         <v>100.0</v>
       </c>
       <c r="I3">
-        <v>8.7</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="4">
@@ -3703,28 +3703,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>72.15</v>
+        <v>69.85</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G4">
-        <v>100.0</v>
+        <v>73.33</v>
       </c>
       <c r="H4">
-        <v>100.0</v>
+        <v>80.0</v>
       </c>
       <c r="I4">
-        <v>4.35</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="5">
@@ -3732,28 +3732,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>70.9</v>
+        <v>67.78</v>
       </c>
       <c r="D5">
         <v>9</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G5">
         <v>60.0</v>
       </c>
       <c r="H5">
-        <v>100.0</v>
+        <v>80.0</v>
       </c>
       <c r="I5">
-        <v>0.0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="6">
@@ -3761,28 +3761,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>69.36</v>
+        <v>67.77</v>
       </c>
       <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
         <v>11</v>
       </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
       <c r="G6">
-        <v>73.33</v>
+        <v>60.0</v>
       </c>
       <c r="H6">
-        <v>80.0</v>
+        <v>60.0</v>
       </c>
       <c r="I6">
-        <v>21.74</v>
+        <v>45.83</v>
       </c>
     </row>
     <row r="7">
@@ -3790,10 +3790,10 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>67.2</v>
+        <v>67.15</v>
       </c>
       <c r="D7">
         <v>9</v>
@@ -3811,7 +3811,7 @@
         <v>80.0</v>
       </c>
       <c r="I7">
-        <v>8.7</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="8">
@@ -3819,10 +3819,10 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C8">
-        <v>66.55</v>
+        <v>66.53</v>
       </c>
       <c r="D8">
         <v>9</v>
@@ -3840,7 +3840,7 @@
         <v>80.0</v>
       </c>
       <c r="I8">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="9">
@@ -3848,28 +3848,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C9">
-        <v>64.7</v>
+        <v>66.0</v>
       </c>
       <c r="D9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>40.0</v>
+        <v>66.67</v>
       </c>
       <c r="H9">
-        <v>100.0</v>
+        <v>80.0</v>
       </c>
       <c r="I9">
-        <v>8.7</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="10">
@@ -3877,28 +3877,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="C10">
-        <v>64.48</v>
+        <v>65.28</v>
       </c>
       <c r="D10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>66.67</v>
+        <v>40.0</v>
       </c>
       <c r="H10">
-        <v>40.0</v>
+        <v>100.0</v>
       </c>
       <c r="I10">
-        <v>56.52</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="11">
@@ -3909,7 +3909,7 @@
         <v>19</v>
       </c>
       <c r="C11">
-        <v>63.18</v>
+        <v>63.5</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -3918,7 +3918,7 @@
         <v>2</v>
       </c>
       <c r="F11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11">
         <v>66.67</v>
@@ -3927,7 +3927,7 @@
         <v>40.0</v>
       </c>
       <c r="I11">
-        <v>47.83</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="12">
@@ -3935,28 +3935,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="C12">
-        <v>62.96</v>
+        <v>61.1</v>
       </c>
       <c r="D12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>66.67</v>
+        <v>73.33</v>
       </c>
       <c r="H12">
         <v>60.0</v>
       </c>
       <c r="I12">
-        <v>13.04</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="13">
@@ -3964,28 +3964,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C13">
-        <v>62.52</v>
+        <v>60.9</v>
       </c>
       <c r="D13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>46.67</v>
+        <v>60.0</v>
       </c>
       <c r="H13">
         <v>60.0</v>
       </c>
       <c r="I13">
-        <v>34.78</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="14">
@@ -3993,28 +3993,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C14">
-        <v>62.31</v>
+        <v>60.47</v>
       </c>
       <c r="D14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G14">
-        <v>66.67</v>
+        <v>73.33</v>
       </c>
       <c r="H14">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="I14">
-        <v>8.7</v>
+        <v>29.17</v>
       </c>
     </row>
     <row r="15">
@@ -4022,28 +4022,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C15">
-        <v>61.55</v>
+        <v>59.75</v>
       </c>
       <c r="D15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G15">
-        <v>60.0</v>
+        <v>66.67</v>
       </c>
       <c r="H15">
-        <v>60.0</v>
+        <v>20.0</v>
       </c>
       <c r="I15">
-        <v>4.35</v>
+        <v>58.33</v>
       </c>
     </row>
     <row r="16">
@@ -4051,28 +4051,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C16">
-        <v>61.02</v>
+        <v>59.75</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E16">
         <v>2</v>
       </c>
       <c r="F16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G16">
-        <v>53.33</v>
+        <v>66.67</v>
       </c>
       <c r="H16">
         <v>40.0</v>
       </c>
       <c r="I16">
-        <v>34.78</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="17">
@@ -4080,28 +4080,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C17">
-        <v>60.01</v>
+        <v>57.97</v>
       </c>
       <c r="D17">
         <v>11</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G17">
         <v>73.33</v>
       </c>
       <c r="H17">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I17">
-        <v>26.09</v>
+        <v>45.83</v>
       </c>
     </row>
     <row r="18">
@@ -4109,28 +4109,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="C18">
-        <v>59.26</v>
+        <v>57.93</v>
       </c>
       <c r="D18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G18">
-        <v>66.67</v>
+        <v>46.67</v>
       </c>
       <c r="H18">
         <v>40.0</v>
       </c>
       <c r="I18">
-        <v>21.74</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="19">
@@ -4138,28 +4138,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C19">
-        <v>59.06</v>
+        <v>57.93</v>
       </c>
       <c r="D19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G19">
-        <v>53.33</v>
+        <v>46.67</v>
       </c>
       <c r="H19">
         <v>40.0</v>
       </c>
       <c r="I19">
-        <v>21.74</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="20">
@@ -4167,28 +4167,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C20">
-        <v>58.84</v>
+        <v>57.35</v>
       </c>
       <c r="D20">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G20">
-        <v>53.33</v>
+        <v>73.33</v>
       </c>
       <c r="H20">
-        <v>0.0</v>
+        <v>40.0</v>
       </c>
       <c r="I20">
-        <v>86.96</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="21">
@@ -4196,28 +4196,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C21">
-        <v>57.62</v>
+        <v>57.15</v>
       </c>
       <c r="D21">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G21">
-        <v>73.33</v>
+        <v>60.0</v>
       </c>
       <c r="H21">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I21">
-        <v>43.48</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="22">
@@ -4225,28 +4225,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C22">
-        <v>56.75</v>
+        <v>57.15</v>
       </c>
       <c r="D22">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E22">
         <v>2</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>73.33</v>
+        <v>60.0</v>
       </c>
       <c r="H22">
         <v>40.0</v>
       </c>
       <c r="I22">
-        <v>4.35</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="23">
@@ -4254,13 +4254,13 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C23">
-        <v>56.55</v>
+        <v>56.42</v>
       </c>
       <c r="D23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E23">
         <v>2</v>
@@ -4269,13 +4269,13 @@
         <v>1</v>
       </c>
       <c r="G23">
-        <v>60.0</v>
+        <v>53.33</v>
       </c>
       <c r="H23">
         <v>40.0</v>
       </c>
       <c r="I23">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="24">
@@ -4283,28 +4283,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C24">
-        <v>55.8</v>
+        <v>56.05</v>
       </c>
       <c r="D24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G24">
-        <v>53.33</v>
+        <v>46.67</v>
       </c>
       <c r="H24">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I24">
-        <v>0.0</v>
+        <v>58.33</v>
       </c>
     </row>
     <row r="25">
@@ -4312,28 +4312,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C25">
-        <v>55.78</v>
+        <v>55.43</v>
       </c>
       <c r="D25">
         <v>7</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G25">
         <v>46.67</v>
       </c>
       <c r="H25">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="I25">
-        <v>56.52</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="26">
@@ -4341,10 +4341,10 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="C26">
-        <v>54.05</v>
+        <v>54.03</v>
       </c>
       <c r="D26">
         <v>6</v>
@@ -4362,7 +4362,7 @@
         <v>60.0</v>
       </c>
       <c r="I26">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="27">
@@ -4370,7 +4370,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C27">
         <v>53.4</v>
@@ -4399,28 +4399,28 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C28">
-        <v>52.1</v>
+        <v>53.4</v>
       </c>
       <c r="D28">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>53.33</v>
+        <v>40.0</v>
       </c>
       <c r="H28">
-        <v>20.0</v>
+        <v>60.0</v>
       </c>
       <c r="I28">
-        <v>8.7</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="29">
@@ -4428,28 +4428,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C29">
-        <v>51.01</v>
+        <v>53.4</v>
       </c>
       <c r="D29">
         <v>6</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G29">
         <v>40.0</v>
       </c>
       <c r="H29">
-        <v>40.0</v>
+        <v>60.0</v>
       </c>
       <c r="I29">
-        <v>17.39</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="30">
@@ -4457,28 +4457,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C30">
-        <v>49.72</v>
+        <v>52.67</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G30">
-        <v>33.33</v>
+        <v>53.33</v>
       </c>
       <c r="H30">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I30">
-        <v>34.78</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="31">
@@ -4486,28 +4486,28 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C31">
-        <v>49.5</v>
+        <v>51.52</v>
       </c>
       <c r="D31">
+        <v>6</v>
+      </c>
+      <c r="E31">
+        <v>2</v>
+      </c>
+      <c r="F31">
         <v>5</v>
       </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-      <c r="F31">
-        <v>23</v>
-      </c>
       <c r="G31">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="H31">
-        <v>0.0</v>
+        <v>40.0</v>
       </c>
       <c r="I31">
-        <v>100.0</v>
+        <v>20.83</v>
       </c>
     </row>
     <row r="32">
@@ -4515,28 +4515,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C32">
-        <v>48.62</v>
+        <v>50.75</v>
       </c>
       <c r="D32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F32">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G32">
-        <v>40.0</v>
+        <v>33.33</v>
       </c>
       <c r="H32">
-        <v>20.0</v>
+        <v>60.0</v>
       </c>
       <c r="I32">
-        <v>34.78</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="33">
@@ -4544,28 +4544,28 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C33">
-        <v>47.76</v>
+        <v>49.5</v>
       </c>
       <c r="D33">
         <v>5</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="G33">
         <v>33.33</v>
       </c>
       <c r="H33">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="I33">
-        <v>21.74</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="34">
@@ -4573,28 +4573,28 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C34">
-        <v>46.45</v>
+        <v>46.52</v>
       </c>
       <c r="D34">
+        <v>6</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34">
         <v>5</v>
       </c>
-      <c r="E34">
-        <v>2</v>
-      </c>
-      <c r="F34">
-        <v>3</v>
-      </c>
       <c r="G34">
-        <v>33.33</v>
+        <v>40.0</v>
       </c>
       <c r="H34">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I34">
-        <v>13.04</v>
+        <v>20.83</v>
       </c>
     </row>
     <row r="35">
@@ -4602,28 +4602,28 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="C35">
-        <v>46.01</v>
+        <v>45.12</v>
       </c>
       <c r="D35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
       <c r="F35">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G35">
-        <v>40.0</v>
+        <v>33.33</v>
       </c>
       <c r="H35">
         <v>20.0</v>
       </c>
       <c r="I35">
-        <v>17.39</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="36">
@@ -4634,7 +4634,7 @@
         <v>32</v>
       </c>
       <c r="C36">
-        <v>44.5</v>
+        <v>45.12</v>
       </c>
       <c r="D36">
         <v>5</v>
@@ -4643,7 +4643,7 @@
         <v>2</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36">
         <v>33.33</v>
@@ -4652,7 +4652,7 @@
         <v>40.0</v>
       </c>
       <c r="I36">
-        <v>0.0</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="37">
@@ -4660,28 +4660,28 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C37">
-        <v>36.92</v>
+        <v>36.23</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37">
         <v>1</v>
       </c>
       <c r="F37">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G37">
-        <v>20.0</v>
+        <v>26.67</v>
       </c>
       <c r="H37">
         <v>20.0</v>
       </c>
       <c r="I37">
-        <v>34.78</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="38">
@@ -4689,10 +4689,10 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C38">
-        <v>35.6</v>
+        <v>36.23</v>
       </c>
       <c r="D38">
         <v>4</v>
@@ -4701,7 +4701,7 @@
         <v>1</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38">
         <v>26.67</v>
@@ -4710,7 +4710,7 @@
         <v>20.0</v>
       </c>
       <c r="I38">
-        <v>0.0</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="39">
@@ -4718,28 +4718,28 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C39">
-        <v>35.6</v>
+        <v>33.42</v>
       </c>
       <c r="D39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G39">
-        <v>26.67</v>
+        <v>13.33</v>
       </c>
       <c r="H39">
         <v>20.0</v>
       </c>
       <c r="I39">
-        <v>0.0</v>
+        <v>37.5</v>
       </c>
     </row>
   </sheetData>
@@ -4798,185 +4798,185 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>115000082</v>
+        <v>115000083</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>115000081</v>
+        <v>115000082</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H3">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>115000080</v>
+        <v>115000081</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>115000079</v>
+        <v>115000080</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F5">
+        <v>21</v>
+      </c>
+      <c r="G5">
         <v>26</v>
-      </c>
-      <c r="G5">
-        <v>33</v>
       </c>
       <c r="H5">
         <v>37</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>115000078</v>
+        <v>115000079</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F6">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G6">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H6">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>115000077</v>
+        <v>115000078</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H7">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -4984,11 +4984,11 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>115000076</v>
+        <v>115000077</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C8">
@@ -4998,140 +4998,140 @@
         <v>8</v>
       </c>
       <c r="E8">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G8">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H8">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I8">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>115000075</v>
+        <v>115000076</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C9">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D9">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E9">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F9">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G9">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H9">
         <v>37</v>
       </c>
       <c r="I9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>115000074</v>
+        <v>115000075</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C10">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D10">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E10">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F10">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G10">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H10">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>115000073</v>
+        <v>115000074</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C11">
+        <v>10</v>
+      </c>
+      <c r="D11">
+        <v>12</v>
+      </c>
+      <c r="E11">
+        <v>14</v>
+      </c>
+      <c r="F11">
+        <v>16</v>
+      </c>
+      <c r="G11">
+        <v>29</v>
+      </c>
+      <c r="H11">
+        <v>36</v>
+      </c>
+      <c r="I11">
         <v>8</v>
-      </c>
-      <c r="D11">
-        <v>17</v>
-      </c>
-      <c r="E11">
-        <v>18</v>
-      </c>
-      <c r="F11">
-        <v>29</v>
-      </c>
-      <c r="G11">
-        <v>33</v>
-      </c>
-      <c r="H11">
-        <v>38</v>
-      </c>
-      <c r="I11">
-        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>115000072</v>
+        <v>115000073</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E12">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F12">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G12">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H12">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I12">
         <v>2</v>
@@ -5139,108 +5139,108 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>115000071</v>
+        <v>115000072</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D13">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E13">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F13">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H13">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I13">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>115000070</v>
+        <v>115000071</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F14">
         <v>19</v>
       </c>
       <c r="G14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H14">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I14">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>115000069</v>
+        <v>115000070</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F15">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G15">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H15">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>115000068</v>
+        <v>115000069</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D16">
         <v>7</v>
@@ -5249,230 +5249,230 @@
         <v>9</v>
       </c>
       <c r="F16">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G16">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H16">
         <v>36</v>
       </c>
       <c r="I16">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>115000067</v>
+        <v>115000068</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E17">
         <v>9</v>
       </c>
       <c r="F17">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G17">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H17">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I17">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>115000066</v>
+        <v>115000067</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D18">
+        <v>2</v>
+      </c>
+      <c r="E18">
+        <v>9</v>
+      </c>
+      <c r="F18">
         <v>11</v>
       </c>
-      <c r="E18">
-        <v>18</v>
-      </c>
-      <c r="F18">
-        <v>19</v>
-      </c>
       <c r="G18">
+        <v>29</v>
+      </c>
+      <c r="H18">
         <v>35</v>
       </c>
-      <c r="H18">
-        <v>38</v>
-      </c>
       <c r="I18">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>115000065</v>
+        <v>115000066</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F19">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G19">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H19">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="I19">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>115000064</v>
+        <v>115000065</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C20">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E20">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F20">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G20">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H20">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I20">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>115000063</v>
+        <v>115000064</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D21">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E21">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F21">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G21">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H21">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I21">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>115000062</v>
+        <v>115000063</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <v>7</v>
+      </c>
+      <c r="E22">
+        <v>8</v>
+      </c>
+      <c r="F22">
+        <v>20</v>
+      </c>
+      <c r="G22">
+        <v>26</v>
+      </c>
+      <c r="H22">
+        <v>33</v>
+      </c>
+      <c r="I22">
         <v>4</v>
-      </c>
-      <c r="D22">
-        <v>15</v>
-      </c>
-      <c r="E22">
-        <v>22</v>
-      </c>
-      <c r="F22">
-        <v>26</v>
-      </c>
-      <c r="G22">
-        <v>34</v>
-      </c>
-      <c r="H22">
-        <v>36</v>
-      </c>
-      <c r="I22">
-        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>115000061</v>
+        <v>115000062</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C23">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D23">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E23">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F23">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G23">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H23">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="I23">
         <v>7</v>
@@ -5480,30 +5480,30 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>115000060</v>
+        <v>115000061</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="C24">
+        <v>8</v>
+      </c>
+      <c r="D24">
+        <v>14</v>
+      </c>
+      <c r="E24">
+        <v>17</v>
+      </c>
+      <c r="F24">
         <v>19</v>
       </c>
-      <c r="D24">
-        <v>22</v>
-      </c>
-      <c r="E24">
-        <v>28</v>
-      </c>
-      <c r="F24">
-        <v>31</v>
-      </c>
       <c r="G24">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H24">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I24">
         <v>7</v>
@@ -5511,30 +5511,30 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>115000059</v>
+        <v>115000060</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="C25">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D25">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E25">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F25">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G25">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H25">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I25">
         <v>7</v>
@@ -5542,24 +5542,24 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>115000058</v>
+        <v>115000059</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="C26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D26">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E26">
         <v>13</v>
       </c>
       <c r="F26">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G26">
         <v>29</v>
@@ -5568,97 +5568,97 @@
         <v>31</v>
       </c>
       <c r="I26">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>115000057</v>
+        <v>115000058</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C27">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D27">
+        <v>12</v>
+      </c>
+      <c r="E27">
+        <v>13</v>
+      </c>
+      <c r="F27">
         <v>23</v>
       </c>
-      <c r="E27">
-        <v>25</v>
-      </c>
-      <c r="F27">
+      <c r="G27">
         <v>29</v>
       </c>
-      <c r="G27">
-        <v>34</v>
-      </c>
       <c r="H27">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I27">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>115000056</v>
+        <v>115000057</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C28">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D28">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E28">
+        <v>25</v>
+      </c>
+      <c r="F28">
         <v>29</v>
       </c>
-      <c r="F28">
-        <v>32</v>
-      </c>
       <c r="G28">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H28">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I28">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>115000055</v>
+        <v>115000056</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C29">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D29">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E29">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F29">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G29">
         <v>35</v>
       </c>
       <c r="H29">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I29">
         <v>6</v>
@@ -5666,402 +5666,402 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>115000054</v>
+        <v>115000055</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C30">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D30">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E30">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F30">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G30">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H30">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>115000053</v>
+        <v>115000054</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D31">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E31">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F31">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G31">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H31">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I31">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>115000052</v>
+        <v>115000053</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C32">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D32">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E32">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F32">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G32">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H32">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I32">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>115000051</v>
+        <v>115000052</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C33">
+        <v>5</v>
+      </c>
+      <c r="D33">
         <v>6</v>
       </c>
-      <c r="D33">
-        <v>10</v>
-      </c>
       <c r="E33">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F33">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G33">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H33">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I33">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>115000050</v>
+        <v>115000051</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C34">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D34">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E34">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F34">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G34">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H34">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I34">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>115000049</v>
+        <v>115000050</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C35">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D35">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E35">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F35">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G35">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H35">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I35">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>115000048</v>
+        <v>115000049</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C36">
+        <v>2</v>
+      </c>
+      <c r="D36">
+        <v>8</v>
+      </c>
+      <c r="E36">
+        <v>9</v>
+      </c>
+      <c r="F36">
+        <v>15</v>
+      </c>
+      <c r="G36">
+        <v>18</v>
+      </c>
+      <c r="H36">
+        <v>23</v>
+      </c>
+      <c r="I36">
         <v>4</v>
-      </c>
-      <c r="D36">
-        <v>17</v>
-      </c>
-      <c r="E36">
-        <v>19</v>
-      </c>
-      <c r="F36">
-        <v>25</v>
-      </c>
-      <c r="G36">
-        <v>28</v>
-      </c>
-      <c r="H36">
-        <v>29</v>
-      </c>
-      <c r="I36">
-        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>115000047</v>
+        <v>115000048</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D37">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E37">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F37">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G37">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H37">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I37">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>115000046</v>
+        <v>115000047</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D38">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E38">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F38">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G38">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H38">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I38">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>115000045</v>
+        <v>115000046</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C39">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D39">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E39">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F39">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G39">
         <v>28</v>
       </c>
       <c r="H39">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I39">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>115000044</v>
+        <v>115000045</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D40">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E40">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F40">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G40">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H40">
         <v>35</v>
       </c>
       <c r="I40">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>115000043</v>
+        <v>115000044</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E41">
+        <v>9</v>
+      </c>
+      <c r="F41">
+        <v>15</v>
+      </c>
+      <c r="G41">
         <v>24</v>
       </c>
-      <c r="F41">
-        <v>31</v>
-      </c>
-      <c r="G41">
-        <v>34</v>
-      </c>
       <c r="H41">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I41">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>115000042</v>
+        <v>115000043</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="C42">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D42">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E42">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F42">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G42">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H42">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I42">
         <v>3</v>
@@ -6069,281 +6069,281 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>115000041</v>
+        <v>115000042</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C43">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D43">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E43">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F43">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G43">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H43">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I43">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>115000040</v>
+        <v>115000041</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C44">
         <v>6</v>
       </c>
       <c r="D44">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E44">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F44">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G44">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H44">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I44">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>115000039</v>
+        <v>115000040</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C45">
         <v>6</v>
       </c>
       <c r="D45">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E45">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F45">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G45">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H45">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I45">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>115000038</v>
+        <v>115000039</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C46">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D46">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E46">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F46">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G46">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H46">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I46">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>115000037</v>
+        <v>115000038</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C47">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D47">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E47">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F47">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G47">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H47">
         <v>38</v>
       </c>
       <c r="I47">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>115000036</v>
+        <v>115000037</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C48">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D48">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E48">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F48">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G48">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H48">
         <v>38</v>
       </c>
       <c r="I48">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>115000035</v>
+        <v>115000036</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D49">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E49">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F49">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G49">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H49">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I49">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>115000034</v>
+        <v>115000035</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C50">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D50">
+        <v>4</v>
+      </c>
+      <c r="E50">
+        <v>13</v>
+      </c>
+      <c r="F50">
+        <v>19</v>
+      </c>
+      <c r="G50">
+        <v>27</v>
+      </c>
+      <c r="H50">
+        <v>30</v>
+      </c>
+      <c r="I50">
         <v>8</v>
-      </c>
-      <c r="E50">
-        <v>27</v>
-      </c>
-      <c r="F50">
-        <v>33</v>
-      </c>
-      <c r="G50">
-        <v>35</v>
-      </c>
-      <c r="H50">
-        <v>38</v>
-      </c>
-      <c r="I50">
-        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>115000033</v>
+        <v>115000034</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C51">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D51">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E51">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F51">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G51">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H51">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I51">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/台灣彩券分析報告.xlsx
+++ b/台灣彩券分析報告.xlsx
@@ -31,7 +31,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>大樂透 2026-10-13 第 115000096 期；威力彩 2026-10-15 第 115000083 期</t>
+          <t>大樂透 2026-10-16 第 115000097 期；威力彩 2026-10-15 第 115000083 期</t>
         </is>
       </c>
     </row>
@@ -47,7 +47,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>115000096</v>
+        <v>115000097</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -56,7 +56,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -78,7 +78,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4, 12, 25, 26, 29, 35</t>
+          <t>3, 14, 15, 18, 26, 35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -87,7 +87,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -96,7 +96,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>回測最佳比隨機基準平均多 0.262 碼/期</t>
+          <t>回測最佳比隨機基準平均多 0.191 碼/期</t>
         </is>
       </c>
     </row>
@@ -207,17 +207,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>冷熱混合</t>
+          <t>近期趨勢</t>
         </is>
       </c>
       <c r="B2">
         <v>42</v>
       </c>
       <c r="C2">
-        <v>0.905</v>
+        <v>0.881</v>
       </c>
       <c r="D2">
-        <v>28.6</v>
+        <v>23.8</v>
       </c>
       <c r="E2">
         <v>2.4</v>
@@ -229,7 +229,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>熱號觀察</t>
+          <t>冷熱混合</t>
         </is>
       </c>
       <c r="B3">
@@ -239,7 +239,7 @@
         <v>0.881</v>
       </c>
       <c r="D3">
-        <v>26.2</v>
+        <v>28.6</v>
       </c>
       <c r="E3">
         <v>2.4</v>
@@ -251,7 +251,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>近期趨勢</t>
+          <t>均衡分散</t>
         </is>
       </c>
       <c r="B4">
@@ -273,17 +273,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>均衡分散</t>
+          <t>熱號觀察</t>
         </is>
       </c>
       <c r="B5">
         <v>42</v>
       </c>
       <c r="C5">
-        <v>0.833</v>
+        <v>0.857</v>
       </c>
       <c r="D5">
-        <v>23.8</v>
+        <v>26.2</v>
       </c>
       <c r="E5">
         <v>2.4</v>
@@ -324,10 +324,10 @@
         <v>42</v>
       </c>
       <c r="C7">
-        <v>0.643</v>
+        <v>0.69</v>
       </c>
       <c r="D7">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="E7">
         <v>0.0</v>
@@ -395,28 +395,28 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>73.05</v>
+        <v>72.53</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>100.0</v>
+        <v>72.73</v>
       </c>
       <c r="H2">
         <v>100.0</v>
       </c>
       <c r="I2">
-        <v>0.0</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="3">
@@ -424,28 +424,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C3">
-        <v>72.22</v>
+        <v>68.36</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>72.73</v>
+        <v>100.0</v>
       </c>
       <c r="H3">
-        <v>100.0</v>
+        <v>80.0</v>
       </c>
       <c r="I3">
-        <v>0.0</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="4">
@@ -453,28 +453,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C4">
-        <v>69.01</v>
+        <v>67.5</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E4">
         <v>4</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>100.0</v>
+        <v>81.82</v>
       </c>
       <c r="H4">
         <v>80.0</v>
       </c>
       <c r="I4">
-        <v>6.38</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="5">
@@ -485,7 +485,7 @@
         <v>18</v>
       </c>
       <c r="C5">
-        <v>64.41</v>
+        <v>64.68</v>
       </c>
       <c r="D5">
         <v>9</v>
@@ -494,7 +494,7 @@
         <v>3</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5">
         <v>81.82</v>
@@ -503,7 +503,7 @@
         <v>60.0</v>
       </c>
       <c r="I5">
-        <v>12.77</v>
+        <v>14.58</v>
       </c>
     </row>
     <row r="6">
@@ -511,28 +511,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C6">
-        <v>64.13</v>
+        <v>64.3</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>72.73</v>
+        <v>100.0</v>
       </c>
       <c r="H6">
         <v>60.0</v>
       </c>
       <c r="I6">
-        <v>12.77</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="7">
@@ -543,25 +543,25 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>63.45</v>
+        <v>63.47</v>
       </c>
       <c r="D7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>81.82</v>
+        <v>72.73</v>
       </c>
       <c r="H7">
         <v>60.0</v>
       </c>
       <c r="I7">
-        <v>6.38</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="8">
@@ -572,7 +572,7 @@
         <v>4</v>
       </c>
       <c r="C8">
-        <v>63.13</v>
+        <v>63.43</v>
       </c>
       <c r="D8">
         <v>9</v>
@@ -581,7 +581,7 @@
         <v>3</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8">
         <v>81.82</v>
@@ -590,7 +590,7 @@
         <v>60.0</v>
       </c>
       <c r="I8">
-        <v>4.26</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="9">
@@ -601,7 +601,7 @@
         <v>20</v>
       </c>
       <c r="C9">
-        <v>62.86</v>
+        <v>63.16</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -610,7 +610,7 @@
         <v>3</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9">
         <v>72.73</v>
@@ -619,7 +619,7 @@
         <v>60.0</v>
       </c>
       <c r="I9">
-        <v>4.26</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         <v>13</v>
       </c>
       <c r="C10">
-        <v>62.34</v>
+        <v>62.63</v>
       </c>
       <c r="D10">
         <v>6</v>
@@ -639,7 +639,7 @@
         <v>3</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10">
         <v>54.55</v>
@@ -648,7 +648,7 @@
         <v>60.0</v>
       </c>
       <c r="I10">
-        <v>8.51</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="11">
@@ -659,7 +659,7 @@
         <v>36</v>
       </c>
       <c r="C11">
-        <v>62.22</v>
+        <v>62.53</v>
       </c>
       <c r="D11">
         <v>8</v>
@@ -668,7 +668,7 @@
         <v>3</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11">
         <v>72.73</v>
@@ -677,7 +677,7 @@
         <v>60.0</v>
       </c>
       <c r="I11">
-        <v>0.0</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="12">
@@ -688,25 +688,25 @@
         <v>47</v>
       </c>
       <c r="C12">
-        <v>62.22</v>
+        <v>62.25</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>72.73</v>
+        <v>63.64</v>
       </c>
       <c r="H12">
         <v>60.0</v>
       </c>
       <c r="I12">
-        <v>0.0</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="13">
@@ -717,7 +717,7 @@
         <v>48</v>
       </c>
       <c r="C13">
-        <v>61.94</v>
+        <v>62.25</v>
       </c>
       <c r="D13">
         <v>7</v>
@@ -726,7 +726,7 @@
         <v>3</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13">
         <v>63.64</v>
@@ -735,7 +735,7 @@
         <v>60.0</v>
       </c>
       <c r="I13">
-        <v>0.0</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="14">
@@ -743,28 +743,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>60.92</v>
+        <v>61.94</v>
       </c>
       <c r="D14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>100.0</v>
+        <v>63.64</v>
       </c>
       <c r="H14">
-        <v>40.0</v>
+        <v>60.0</v>
       </c>
       <c r="I14">
-        <v>19.15</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="15">
@@ -775,7 +775,7 @@
         <v>19</v>
       </c>
       <c r="C15">
-        <v>60.09</v>
+        <v>60.34</v>
       </c>
       <c r="D15">
         <v>8</v>
@@ -784,7 +784,7 @@
         <v>2</v>
       </c>
       <c r="F15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>72.73</v>
@@ -793,7 +793,7 @@
         <v>40.0</v>
       </c>
       <c r="I15">
-        <v>19.15</v>
+        <v>20.83</v>
       </c>
     </row>
     <row r="16">
@@ -804,7 +804,7 @@
         <v>27</v>
       </c>
       <c r="C16">
-        <v>58.94</v>
+        <v>59.19</v>
       </c>
       <c r="D16">
         <v>6</v>
@@ -813,7 +813,7 @@
         <v>2</v>
       </c>
       <c r="F16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>54.55</v>
@@ -822,7 +822,7 @@
         <v>40.0</v>
       </c>
       <c r="I16">
-        <v>19.15</v>
+        <v>20.83</v>
       </c>
     </row>
     <row r="17">
@@ -833,7 +833,7 @@
         <v>28</v>
       </c>
       <c r="C17">
-        <v>58.54</v>
+        <v>58.82</v>
       </c>
       <c r="D17">
         <v>7</v>
@@ -842,7 +842,7 @@
         <v>2</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G17">
         <v>63.64</v>
@@ -851,7 +851,7 @@
         <v>40.0</v>
       </c>
       <c r="I17">
-        <v>10.64</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="18">
@@ -862,7 +862,7 @@
         <v>25</v>
       </c>
       <c r="C18">
-        <v>58.09</v>
+        <v>58.4</v>
       </c>
       <c r="D18">
         <v>10</v>
@@ -871,7 +871,7 @@
         <v>2</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18">
         <v>90.91</v>
@@ -880,7 +880,7 @@
         <v>40.0</v>
       </c>
       <c r="I18">
-        <v>2.13</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="19">
@@ -888,10 +888,10 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>57.66</v>
+        <v>57.63</v>
       </c>
       <c r="D19">
         <v>6</v>
@@ -909,7 +909,7 @@
         <v>40.0</v>
       </c>
       <c r="I19">
-        <v>10.64</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="20">
@@ -917,28 +917,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C20">
-        <v>57.58</v>
+        <v>57.11</v>
       </c>
       <c r="D20">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G20">
-        <v>63.64</v>
+        <v>100.0</v>
       </c>
       <c r="H20">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I20">
-        <v>4.26</v>
+        <v>27.08</v>
       </c>
     </row>
     <row r="21">
@@ -946,10 +946,10 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C21">
-        <v>57.34</v>
+        <v>57.0</v>
       </c>
       <c r="D21">
         <v>6</v>
@@ -958,7 +958,7 @@
         <v>2</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G21">
         <v>54.55</v>
@@ -967,7 +967,7 @@
         <v>40.0</v>
       </c>
       <c r="I21">
-        <v>8.51</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="22">
@@ -975,28 +975,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C22">
-        <v>56.88</v>
+        <v>56.94</v>
       </c>
       <c r="D22">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>100.0</v>
+        <v>63.64</v>
       </c>
       <c r="H22">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I22">
-        <v>25.53</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="23">
@@ -1004,28 +1004,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="C23">
-        <v>56.7</v>
+        <v>56.94</v>
       </c>
       <c r="D23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E23">
         <v>2</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>54.55</v>
+        <v>63.64</v>
       </c>
       <c r="H23">
         <v>40.0</v>
       </c>
       <c r="I23">
-        <v>4.26</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="24">
@@ -1033,28 +1033,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C24">
-        <v>56.7</v>
+        <v>56.28</v>
       </c>
       <c r="D24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G24">
-        <v>54.55</v>
+        <v>72.73</v>
       </c>
       <c r="H24">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="I24">
-        <v>4.26</v>
+        <v>27.08</v>
       </c>
     </row>
     <row r="25">
@@ -1062,28 +1062,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C25">
-        <v>56.33</v>
+        <v>56.17</v>
       </c>
       <c r="D25">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G25">
-        <v>81.82</v>
+        <v>100.0</v>
       </c>
       <c r="H25">
         <v>20.0</v>
       </c>
       <c r="I25">
-        <v>25.53</v>
+        <v>20.83</v>
       </c>
     </row>
     <row r="26">
@@ -1091,28 +1091,28 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C26">
-        <v>55.21</v>
+        <v>55.88</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>54.55</v>
+        <v>45.45</v>
       </c>
       <c r="H26">
-        <v>20.0</v>
+        <v>60.0</v>
       </c>
       <c r="I26">
-        <v>27.66</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
@@ -1120,10 +1120,10 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C27">
-        <v>54.58</v>
+        <v>55.44</v>
       </c>
       <c r="D27">
         <v>6</v>
@@ -1132,7 +1132,7 @@
         <v>1</v>
       </c>
       <c r="F27">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G27">
         <v>54.55</v>
@@ -1141,7 +1141,7 @@
         <v>20.0</v>
       </c>
       <c r="I27">
-        <v>23.4</v>
+        <v>29.17</v>
       </c>
     </row>
     <row r="28">
@@ -1149,10 +1149,10 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C28">
-        <v>54.26</v>
+        <v>52.94</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -1161,7 +1161,7 @@
         <v>1</v>
       </c>
       <c r="F28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G28">
         <v>54.55</v>
@@ -1170,7 +1170,7 @@
         <v>20.0</v>
       </c>
       <c r="I28">
-        <v>21.28</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="29">
@@ -1178,28 +1178,28 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C29">
-        <v>53.94</v>
+        <v>52.57</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="F29">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G29">
-        <v>54.55</v>
+        <v>63.64</v>
       </c>
       <c r="H29">
         <v>20.0</v>
       </c>
       <c r="I29">
-        <v>19.15</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="30">
@@ -1207,28 +1207,28 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="C30">
-        <v>52.26</v>
+        <v>52.45</v>
       </c>
       <c r="D30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G30">
-        <v>63.64</v>
+        <v>45.45</v>
       </c>
       <c r="H30">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="I30">
-        <v>2.13</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="31">
@@ -1236,10 +1236,10 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="C31">
-        <v>52.16</v>
+        <v>52.45</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -1248,7 +1248,7 @@
         <v>2</v>
       </c>
       <c r="F31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G31">
         <v>45.45</v>
@@ -1257,7 +1257,7 @@
         <v>40.0</v>
       </c>
       <c r="I31">
-        <v>8.51</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="32">
@@ -1265,28 +1265,28 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C32">
-        <v>52.16</v>
+        <v>52.0</v>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>4</v>
+        <v>3</v>
      